--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16034,6 +16034,119 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 13 Sep 2026 03:13:00 +0000</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI年内不上市了！奥特曼支持对手Dario呼吁：AI该踩刹车了</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/488380.html</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr"/>
+      <c r="F380" s="2" t="inlineStr"/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>RSI太危险，得管！</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 01:24:02 +0800</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>苹果的折叠屏等了十五年，体验还差临门一脚</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370231</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr"/>
+      <c r="F381" s="2" t="inlineStr"/>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img js_img_placeholder wx_img_placeholder" src="https://imgslim.geekpark.net/uploads/image/file/2e/6c/2e6cd9ecc35edd4b740f72c443f98f4e.jpeg" /&gt;&lt;/section&gt;
+&lt;section class="wx_imgbc_placeholder js_darkmode__bg__0 js_darkmode__0"&gt;折叠屏七年没解决的问题，从来不在铰链上。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__1" style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__2" style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;2011 年 9 月 30 日，苹果递交了一份名叫「Flexible electronic devices」的专利申请。它描述的是一台屏幕可以对折的设备，合起来能揣进口袋，靠传感器判断自己是开着还是合着。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;这份专利 2015 年 1 月获授，发明人一共六位，其中一位叫特努斯（John P. Ternus）。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img js_img_placeholder wx_img_placeholder" src="https://imgslim.geekpark.net/uploads/image/file/a8/b3/a8b38fcb495acf4a312403c71be99263.png" /&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;&lt;strong class="js_darkmode__3" style="color: #000000; font-size: 16px; letter-spacing: 0.5px; line-height: 1.75;"&gt;十五年之后的 2026 年 9 月 9 日，当年署名的那位工程师，第一次以苹果 CEO 的身份站上发布会，发布了 iPhone Duo。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, Ping</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T17:16:28-04:00</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>Sam Altman says OpenAI going public in 2026 would be ‘ill-advised’</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994384/sam-altman-no-openai-ipo-ill-advised</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr"/>
+      <c r="F382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI CEO Sam Altman confirmed that there would be no OpenAI IPO in 2026 during an interview with Fortune. Over the course of 45 minutes, Altman discussed a variety of subjects including the Hugging Face hacking incident, recursive self-improvement, and the possibility of building an AI that was beyond human control. On the latter, he [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H382"/>
+  <dimension ref="A1:H395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16147,6 +16147,502 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 09:33:57 +0000</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>全场景·真交互·智协同丨灵感机器人三款视触觉传感器重磅首发</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12962</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr"/>
+      <c r="F383" s="2" t="inlineStr"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>点击蓝字 关注我们 AGIMind Robotics   灵感机器人：重新定义 机器人的触觉边界 &amp;#160; [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 06:15:16 +0000</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>Ego数据采集厂哭诉：既要真实场景，又不能拍到别人，难！</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12944</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr"/>
+      <c r="F384" s="2" t="inlineStr"/>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>数据采集看似热闹，实则粗活、脏活、慢活，赚的是辛苦钱，扛的是高不确定性</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 03:31:20 +0000</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>【Optimus技术深拆】22自由度灵巧手全拆解：从11到22的翻倍工程与0.08mm指尖精度</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12942</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr"/>
+      <c r="F385" s="2" t="inlineStr"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>22个自由度，25个执行器全部藏在前臂，3根腱绳驱动一根手指，0.08毫米的指尖精度——这是关于Optimus Gen3灵巧手最深入的一次机电级拆解，从代际演进到三份WIPO专利，拆到每一根腱绳的力学路径。</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 03:29:35 +0000</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>灵巧手有多少自由度才够用？先把关节、电机和控制量分开</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12936</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr"/>
+      <c r="F386" s="2" t="inlineStr"/>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>机械自由度、主动自由度和电机数量看起来都在数“能动多少”，实际回答的却是三个不同问题。</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 03:19:19 +0000</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>世界模型｜具身数据 - Ego-Exo4D 数据集</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12928</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr"/>
+      <c r="F387" s="2" t="inlineStr"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>世界模型｜具身数据 - Ego-Exo4D 数据集</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 02:08:30 +0000</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>Ego 数据回放： 从第一视角视频到机器人动作的完整落地</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12904</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr"/>
+      <c r="F388" s="2" t="inlineStr"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>文章完整拆解了“无机器人采集、无本体表示、仿真+真机回放”的 Ego  数据管线——从双重具身鸿沟、三级数据阶梯、视觉对齐、坐标系重定向，到臂手腿三套映射、三个工程暗坑（旋转奇点/时间对齐/策略错配）、阻抗控制回放，最终落到 Robot-Ready  验收标准。</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 01:55:56 +0000</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>同济大学 Small：手还没碰到，这张电子皮肤就感知到了</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12886</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr"/>
+      <c r="F389" s="2" t="inlineStr"/>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>从串珠纤维到控制阈值，看液态金属电子皮肤如何兼顾感知、形变与抗干扰。</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 09:47:07 +0000</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>首届蚂蚁灵波具身大模型挑战赛正式启动</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/489105.html</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr"/>
+      <c r="F390" s="2" t="inlineStr"/>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>通过这场大赛，蚂蚁灵波希望将 LingBot-VLA 进一步推向更广泛的开发者社区和高校科研社区</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 09:36:28 +0000</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>探索RSI，生数新世界模型让机器人开始自我进化</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/489037.html</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr"/>
+      <c r="F391" s="2" t="inlineStr"/>
+      <c r="G391" s="2" t="inlineStr"/>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 02:56:45 +0000</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>奥特曼被骗！A社一脚油门冲刺IPO，募资叫板SpaceX</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/488699.html</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr"/>
+      <c r="F392" s="2" t="inlineStr"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>还是太嫩了啊Dario</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 08:17:23 +0800</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>iOS 27、MacOS 27 正式发布；豆包手机助手消费者版亮相；李想：「大车」趋势一定会结束</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370306</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr"/>
+      <c r="F393" s="2" t="inlineStr"/>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1b/d4/1bd41f26ddd5ae24e9fcb56f8286926e.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;特朗普抨击 Anthropic CEO：AI 发展不能踩刹车，美国有「高智商总统」就足够&lt;/h1&gt;
+&lt;p&gt;特朗普周一在社交媒体发文，明确表示其不认可 AI 数据中心引发的民众反弹及外界对前沿模型的忧虑。他写道：「AI 所需的唯一『护栏』，就是一位强悍而聪明（高智商！）的总统，而美国恰好拥有这样的总统。」&lt;/p&gt;
+&lt;p&gt;这一表态较他上周末承认需要某种程度监管的措辞明显趋于强硬。&lt;/p&gt;
+&lt;p&gt;争议的导火索是 Amodei 近日的公开表态。他呼吁业界应在开发最先进模型之前放缓步伐，以便企业更充分地评估潜在风险。OpenAI 的 Sam Altman 及 SpaceX 旗下 xAI 的 Elon Musk 随后表态附议，支持适度放缓。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;白宫内部就 AI 监管问题已形成两个阵营：&lt;/strong&gt;财政部长贝森特与国家网络总监 Sean Cairncross 支持更强保护，而科技顾问 Michael Kratsios 与前 AI 沙皇 David Sacks 则认为监管会扼杀创新。&lt;/p&gt;
+&lt;p&gt;周一美国副总统万斯被问及是否担忧人工智能的发展。他表示：「就我个人而言，我觉得有点奇怪，现在有这么多前沿 AI 科技公司主动与政府接触，甚至恳求政府对它们进行监管。在我看来，这有点像一个『特洛伊木马』，所以我们必须对此保持谨慎。」（消息来源：华尔街见闻）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;中方回应 Anthropic 限制论：反对以遏制手段干预人工智能发展&lt;/h1&gt;
+&lt;p&gt;近期，美国与中国在人工智能领域的竞争成为国际科技界关注的焦点。此前，美国方面不断强调在人工智能竞赛中的战略优势，一些美国政界人士甚至呼吁盟友在人工智能发展方向上与美国保持一致。&lt;/p&gt;
+&lt;p&gt;针对上述观点，中国外交部发言人郭嘉昆作出回应，明确反对将人工智能发展问题置于对抗和竞争框架之下。他表示，制造恐慌、挑动对立以及恶性竞争不仅无助于问题解决，反而将干扰全球人工智能治理进程，损害各方共同利益。（消息来源：cnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5a/bd/5abdf6ba6fe115848d9ab58e036ebfc3.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;Opus 5.2 深夜上线&lt;/h1&gt;
+&lt;p&gt;据外网消息，今天清晨，许多开发者发现，新一代神级模型 Claude Opus 5.2，已经在 Claude Code 中开启灰度测试。&lt;/p&gt;
+&lt;p&gt;越来越多的 Claude 用户发现：在 Claude Code 中调用 Opus 5 时，它的表现和网页版 Opus 5 截然不同。&lt;/p&gt;
+&lt;p&gt;这就是前沿 AI 大厂最喜欢玩的「障眼法」&amp;mdash;&amp;mdash;路由（Routing）。开发者们通过抓包和查看请求状态（/status）发现，虽然前端名字没变，但背后的模型 slug 已经赫然指向了 Opus 5.2。&lt;/p&gt;
+&lt;p&gt;根据开发者实测反馈，这次的升级可以总结为三个字：快、准、狠。&lt;/p&gt;
+&lt;p&gt;相比于之前 Opus 5 的慢条斯理，路由到 5.2 版本的模型生成速度有了肉眼可见的质的飞跃。&lt;/p&gt;
+&lt;p&gt;现在的 AI 普遍有一种懒惰感，遇到复杂长任务喜欢让你「按继续」，或者只给你一个框架让你自己填。但 Opus 5.2 彻底变了！它不仅不懒，还非常「工作狂」。有开发者惊呼：「它甚至不需要我催促，就开始像被喂了狂暴药水一样，自动进行『严酷循环（gauntlet loop）』，不断自我迭代和完善代码，直到任务完美结束！」（消息来源：新智元）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7c/10/7c10845b18f5dd0385502e759665fb3b.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;苹果正式发布 iOS 27：Siri 迎来重大 AI 升级 性能提升并新增多项智能功能&lt;/h1&gt;
+&lt;p&gt;苹果于当地时间 9 月 14 日正式向全球用户推送 iOS 27，这是苹果今年面向 iPhone 推出的最大规模系统更新之一。&lt;/p&gt;
+&lt;</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 13:14:43 +0800</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>专访爆火「机器鸭」背后的硬件推手：这是个信号，未来推动新故事的并非硬件</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370269</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr"/>
+      <c r="F394" s="2" t="inlineStr"/>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;p&gt;最近这两周，一只「&lt;span class=""&gt;机器鸭&lt;/span&gt;」在 X 上刷屏了。&lt;/p&gt;
+&lt;p&gt;这只叫 &lt;span class=""&gt;Microduck&lt;/span&gt; 的机器鸭，由 Hugging Face 旗下的 Pollen Robotics 设计，售价 399 美元。&lt;strong&gt;高峰期平均每 4 秒卖出一台，五天后预售破万台，销售额突破 500 万美元，目前订单已经排到明年。&lt;/strong&gt;&lt;/p&gt;
+&lt;section&gt;
+&lt;div id="page-content"&gt;&lt;!--S 全屏播放 full_screen_mv--&gt;
+&lt;div id="js_mpvedio_wrapper_wxv_4689476465053351938"&gt;&lt;/div&gt;
+&lt;/div&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;strong&gt;它火了，火出了科技圈，还可能会刷新消费级机器人出货纪录。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;而这只全球爆款，由深圳制造，工程化公司是潘昊创办的 Seeed Studio 矽递科技。在此之前，潘昊团队已为 &lt;span class=""&gt;Hugging Face&lt;/span&gt; 代工过 Reachy Mini，后者登上过英伟达 CES 展台，同样供不应求。&lt;/p&gt;
+&lt;section&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/10/df/10dfa83eaf19064c8df002f24afc0765.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span&gt;左为桌面机器人 Reachy Mini，右为机器鸭 Microduck，都是 Pollen Robotics 的作品｜图片来源：Pollen Robotics&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;英特尔工程师出身的潘昊 2008 年来深圳，逛了一圈华强北就决定不走了。那一年他创办 Seeed，为全球创客采购、制造硬件，成为了全球创客与中国工厂之间的枢纽，扮演着「供应链严选」与硬件制造商的角色。&lt;/p&gt;
+&lt;p&gt;18 年过去，他们如今是全球知名开源硬件制造商之一，90%客户来自海外，几乎参与了每一波硅谷硬件浪潮。&lt;/p&gt;
+&lt;p&gt;Microduck 的爆火，是观察全球 AI 硬件产业分工演变、理解爆款密码的一个绝佳切面。&lt;/p&gt;
+&lt;p&gt;这次对话，我们从 Microduck 这单具体的生意切入，拆解它为何爆火的底层规律和启示。一路聊到硅谷创业者与深圳的关系变化、新时代硬件创业者的价值到底在哪、软硬件创业者之间新的分工，以及被容易忽视的中国供应链里的江湖规则。&lt;/p&gt;
+&lt;p&gt;例如，潘昊感受到，硅谷团队来中国正从「采购」变成「托孤」。同时，更多的失败创业在发生，他提醒软件出身的 AI 从业者：不必把精力消磨在重新做硬件上，这是一种 respect，你的长处应该在硬件之外，知道什么不必从头做。&lt;/p&gt;
+&lt;p&gt;以下是极客公园与潘昊的对话，经编辑整理。&lt;/p&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;strong&gt;作者｜Lilyann、苏子华&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;h2&gt;一只鸭子，为什么能出圈？&lt;/h2&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;strong&gt;极客公园：Microduck 现在预售数量破万了，这个结果符合你们的预期吗？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;潘昊：&lt;/strong&gt;这个鸭子会火，有些预料。但没想到会火成这样，连科技圈外都在关注，这是始料未及的。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;极客公园：现在回头看，它的出圈有哪些可总结的规律？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;潘昊：&lt;/strong&gt;有几个关键点，跟现在&lt;span class=""&gt;具身智能&lt;/span&gt;的做法不太一样。&lt;/p&gt;
+&lt;p&gt;第一，它不是功能性的东西，不是为了证明技术、证明性能。这个作者更像匹诺曹他爸：要做一个有意思的、像自己孩子一样的东西，一个自己喜爱、倾注了感情的东西。&lt;/p&gt;
+&lt;p&gt;这让它的产品定义、形态，跟市面上的机器人不一样。比如你请个人形回家，晚上起床不小心看到，可能吓一跳，侵入感太强。但一只鸭子，你会觉得像宠物，比很多机械更有灵性。你看它动的方式，我们都知道它是一堆舵机加控制器，但它动起来像一个小小生物，像一个硅基生物。这是第一点，让更多人愿意接受和了解它。&lt;/p&gt;
+&lt;p&gt;第二，它的成本比普通具身机器人</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:03:37-04:00</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/995079/president-donald-trump-calls-nvidia-ceo-jensen-huang-all-in-summit</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr"/>
+      <c r="F395" s="2" t="inlineStr"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia CEO Jensen Huang took a call from President Trump on Monday while onstage at the All-In Podcast's All-In Summit. It's not the first time Huang has taken a call from the president during work, but this time he put Trump on speakerphone before a big crowd. During the call, the president launched into his [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H395"/>
+  <dimension ref="A1:H404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16643,6 +16643,364 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 02:22:48 +0000</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>机器人产品动态 l 宇树 G1+大升级；蓝虫具身推出模块化人形机器人</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12971</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr"/>
+      <c r="F396" s="2" t="inlineStr"/>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>亮点：头部装触觉、模块化组装更适配多元化需求</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:22:30+00:00</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>Digit 5 May Be the First Humanoid Robot Worker That’s Truly Safe</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/humanoid-robot-safety</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr"/>
+      <c r="F397" s="2" t="inlineStr"/>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Despite the recent deluge of videos of humanoid robots doing backflips and kung-fu, the actual pace of progress towards humanoids …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 16:07:08 GMT</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>月之暗面：网传创始人及员工信息系恶意造谣；OpenAI 放弃今年上市；iPhone Duo炒到9万，黄牛贷款欲囤货｜AI周报</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/HEN8icBvRCoKVvo2dSNA?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr"/>
+      <c r="F398" s="2" t="inlineStr"/>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/HEN8icBvRCoKVvo2dSNA?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 10:43:28 +0000</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>无问芯穹联合清华、上交正式开源具身端侧推理引擎APXInf，Pi 0.5性能SOTA</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/489460.html</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr"/>
+      <c r="F399" s="2" t="inlineStr"/>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>卡位具身智能规模化落地“最后一公里”！</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 08:22:40 +0800</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI、Anthropic、谷歌联手研究 AI 安全；微信员工辟谣 AI 助手小微「偷隐私」；美国已在太空部署武器</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370375</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr"/>
+      <c r="F400" s="2" t="inlineStr"/>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3c/59/3c59b7cfce167a72c033a3331aec9abf.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;因加大 AI 投入 报道称字节跳动 2026 上半年净利润下降&lt;/h2&gt;
+&lt;p&gt;据报道，由于加大了在人工智能领域的投资，字节跳动 2026 年上半年净利润同比出现下降。同时，受 TikTok 等海外业务推动，字节跳动上半年营收同比增长 30%，海外收入占比再创新高。字节跳动未对以上数据置评。&lt;/p&gt;
+&lt;p&gt;在净利润下降的同时，字节跳动的净利润率也出现了持续下滑。此前有外媒曾报道，字节跳动 2023 年净利润率为 26%，2024 年为 21%。而从最新数据看，字节跳动在 2026 年上半年的净利润率进一步下降至 16.7% 左右。&lt;/p&gt;
+&lt;p&gt;报道称，字节跳动近期从银行获得约 300 亿美元贷款，这是该公司有史以来规模最大的一笔贷款，可为其不断飙升的 AI 投资提供资金支持。而字节跳动在国内最大的竞争对手们也正在募资，为自身的人工智能布局提供资金支持。阿里巴巴正寻求通过大规模配股募集约 100 亿美元，用于人工智能基础设施建设支出。智谱 AI 于近日启动了总额 50 亿美元的股权及可转债发行，以支撑其人工智能相关投入。（来源：新浪科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fb/c8/fbc809f540947ddaefac88af2ecf0cf9.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;「三巨头」联手，OpenAI、Anthropic、谷歌 Deepmind 开始合作研究 AI 安全措施&lt;/h2&gt;
+&lt;p&gt;9 月 15 日消息，随着美国各界对 AI 可能威胁经济和国家安全的担忧不断升温，OpenAI 开始与主要竞争对手 Anthropic 和谷歌 DeepMind 合作研究 AI 安全措施，进一步推动行业共同应对潜在风险。&lt;/p&gt;
+&lt;p&gt;OpenAI 全球政策主管克里斯 &amp;middot; 莱恩透露，公司与 Anthropic 和谷歌围绕 AI 安全问题的接触持续了数周。OpenAI 认为，三家公司开展这类协调并不需要专门获得反垄断豁免。「&lt;strong&gt;尝试合作、优先保障安全，对大家都更好&lt;/strong&gt;。」&lt;/p&gt;
+&lt;p&gt;当地时间上周六，Anthropic CEO 达里奥 &amp;middot; 阿莫迪发表了一篇 3800 词的长文，呼吁放缓最先进 AI 系统的研发，让研究人员有更多时间了解潜在威胁，也让 AI 生存风险迅速进入公众讨论。OpenAI CEO 萨姆 &amp;middot; 奥尔特曼和 SpaceXAI 负责人埃隆 &amp;middot; 马斯克很快对阿莫迪的主张&lt;strong&gt;表达支持&lt;/strong&gt;。（来源：新浪财经）&lt;/p&gt;
+&lt;h2&gt;美光展示全球首个 512GB DDR5 内存模组，支持 9200MT/s 传输速率&lt;/h2&gt;
+&lt;p&gt;9 月 15 日消息，Micron（美光）当地时间展示了全球首个 512GB DDR5 内存模组。这一产品&lt;strong&gt;属于 3DS RDIMM&lt;/strong&gt;，通过硅通孔 (TSV) 堆叠 DRAM Die 最大化单封装内存容量。&lt;/p&gt;
+&lt;p&gt;单条 512GB 意味着其在双路 24 内存插槽（12 通道 1DPC / 6 通道 2DPC）配置下&lt;strong&gt;可在单一服务器上实现 12TB 的内存容量&lt;/strong&gt;。此外，这一内存模组支持 9200MT/s 传输速率，相比 4 个 128GB 模组节能超 60%。&lt;/p&gt;
+&lt;p&gt;美光预计 512GB DDR5-9200 3DS RDIMM&amp;nbsp;&lt;strong&gt;将于 2027 年下半年量产&lt;/strong&gt;，AMD、英特尔正在下一代服务器处理器平台上进行该内存模组的验证工作。（来源：新浪财经）&lt;/p&gt;
+&lt;h2&gt;Meta 计划明年上半年部署新一代自研 AI 芯片&lt;/h2&gt;
+&lt;p&gt;9 月 15 日消息，据彭博社今天（15 日）报道，Meta 计划明年上半年在数据中心&lt;strong&gt;部署新一代自研 AI 芯片&lt;/strong&gt;，希望在运行 AI 模型时进一步&lt;strong&gt;降低成本和能耗&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;Meta 于 2023 年公布自研 AI 芯片计划，目前正在测试&lt;strong&gt;第三代产品 MTIA 450，代号 Arke&lt;/strong&gt;。下一代 MTIA 500 代号 Astrid，</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 14:01:55 +0800</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>给 AI 发外设，戴森派摄像头进嘴、绿联给充电宝开了扇窗</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370328</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr"/>
+      <c r="F401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;AI 正在把所有硬件重新做一遍，这句话说了三年，这周轮到了一把牙刷。&lt;/p&gt;
+&lt;p&gt;今天，IFA 柏林开展，一千九百个品牌都在不同角度展示自己的创新力，连戴森都掏出了一款牙刷来告诉行业，我也能用 AI 玩出花样，牙刷 Dyson CameraJe 刷头下藏着一颗 1 毫米的摄像头，每秒盯着你哪颗牙没刷干净。联想打造了个人智能体 Qira，横跨着电脑、手机、手表等多设备生态。你在哪里，智能体跟随服务到哪里。&lt;/p&gt;
+&lt;p&gt;我们发现，不少公司想明白了一件事，与其从零生一个新物种，不如顺手改造一个老物件。牙刷、手表、鼠标、充电宝，全是用了几十年的东西，AI 不负责发明它们，AI 负责把它们重做一遍。改造，正在比发明更快地成为这个秋天的硬件主题。&lt;/p&gt;
+&lt;p&gt;正当一批人忙着证明无处不 AI 的时候，也有人对 AI 不屑一顾。电子纸徽章 TICKEY 不发光，充一次电能挂两个月。一位创客造的相机，按下快门吐出一张永不褪色的电子纸照片。「我用技术还原物品本身」也成为当下造物的一条思路。&lt;/p&gt;
+&lt;p&gt;我们还注意到手机背后的磁吸接口正在长出新物种。磁吸墨水屏、磁吸充电宝，磁吸拍照神器，IFA 上，绿联甚至给自家的磁吸充电宝开了透明天窗，既想要屏，也想要充电功能。大家对手机内的功能升级审美疲劳时，开始琢磨手机外的其他玩法了。手机背面，或许正在变成手机硬件的下一个配货架。&lt;/p&gt;
+&lt;p&gt;以下，是「造物 100」栏目第 5 期推荐的最新造物。&lt;/p&gt;
+&lt;h1&gt;Violoop：给 AI 找工位，配了一套键盘和鼠标&lt;/h1&gt;
+&lt;p&gt;所有公司都在教 AI 找接口，深圳的 Bvio 反着来，选择给 AI 造一个工位，并配上了一套键盘和鼠标。&lt;/p&gt;
+&lt;p&gt;Violoop 是一个手掌大小、带触摸屏的小盒子，HDMI 线抓取你的屏幕画面，USB 口模拟真实键鼠。把它插上任何一台 Windows、Mac 或 Linux 电脑，AI 就能像人一样看着屏幕、动手操作。一些传统没有接口的老软件，AI 都能打开。9 月 4 日在 IFA 柏林全球首秀，Kickstarter 定档 9 月 15 日，早鸟价 399 美元，零售价 699 美元，10 月发货。&lt;/p&gt;
+&lt;p&gt;该团队 CEO Jaylen He 是 YC W19 的连续创业者，CTO 出身 MIT，此前在 ADI 给 Xbox 和 HoloLens 设计过芯片。今年 3 月，团队一个月内连拿两轮融资，IFA 首秀当天官宣种子轮累计 2000 万美元。&lt;/p&gt;
+&lt;p&gt;它最认真的设计其实在安全上。付款、删除、发消息这类关键操作，全部卡在一颗实体按键后面，你不按它不动；锁屏走人它继续干活，干完了推送通知找你。别人的 AI 安全是一行设置项，它的安全是一颗必须亲手按下去的按钮。&lt;/p&gt;
+&lt;p&gt;更有意思的是它选择的方向。AI 操作电脑这件事，所有大厂都在软件层解，写插件、接 API、做自动化框架，而存量世界里绝大多数软件根本没有合适的接口。Violoop 从硬件层把这个问题整个绕开，让 AI 用人类的方式用电脑，等于把整个旧软件世界一次性变成了 AI 可以操作的。上周 Anthropic 刚发布 MHS 标准，给 AI 操控实验室和产线设备修统一接口。巨头在工厂修路，Violoop 赌的是同一件事在每个人书桌上的版本。&lt;/p&gt;
+&lt;p&gt;（想要了解更多内容：👉 硬件加强版「WorkBuddy」，拿下数亿融资，瞄向你的终极上下文）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/55/39/55395da829e878d5dfa0c0c91df462a0.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;带摄像头的牙刷 Dyson CameraJet：戴森把刷牙这件事重造了一遍&lt;/h1&gt;
+&lt;p&gt;一百多年来，刷牙全凭手感和自觉。戴森觉得这事不该再靠猜，于是它把一颗 1 毫米的摄像头藏进了刷头底下。CameraJet 每秒扫描 28 帧，机器学习实时识别刷毛没够到的牙缝，发现缝隙后 100 毫秒内，会朝那个点精准喷出一股漱口水。它不是给你计时打分的 App，它真的看得见你哪里没刷到。售价 499 美元，9 月初在巴黎发布、柏林 IFA 场边展出，官方状态是即将开售。&lt;/p&gt;
+&lt;p&gt;这是戴森第一次做牙刷。今年它一口气发了十款新品，首席工程师 Jake Dyson 给出的主题是，从纯机械设备转向能看、能想、能响应的智能机器。&lt;/p&gt;
+&lt;p&gt;戴森还为这套系统重新设计了牙膏。它没把摄像头当成加在牙刷上的一个功能，而是把刷牙这件事的全部假设推倒重来了一遍。当然，换个角度看，专用牙膏也成为一种持续性的耗材。&lt;/p</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 13:54:51 +0800</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>造物 100 #06｜自动驾驶上轮椅了，口袋相机学会飞行，AI 教练上了雪场</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370325</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr"/>
+      <c r="F402" s="2" t="inlineStr"/>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;硬件创新力正在消失。&lt;/p&gt;
+&lt;p&gt;9 月 10 日，苹果发布了筹备多年的首款折叠屏 iPhone Duo，又是一款集大成之作，困扰多年的折叠屏折痕有了「苹果」解法。但我们明显发现硬件创新的品类迭代速度开始变得缓慢，这两年「原来还能有这种东西」的哇塞时刻越来越少。大家似乎默认，下一个时代级的硬件新品类短期内等不来，与其赌一个新物种的诞生，不如在成熟产品上做新的形态和能力。&lt;/p&gt;
+&lt;p&gt;所以硬件创新来到了大融合时代。你做手持影像，我做会飞的手持影像；你做智能轮椅，我做会自动驾驶的智能轮椅；你做录音手环，我做能录环境音的录音手环。这期名单里的产品，几乎每一件创新产品前都有一个独特的限定词。&lt;/p&gt;
+&lt;p&gt;融合创新并没有好坏，手机当年就是相机、电话和电脑集成出来的新品类。但更关键的应该是，用户价值。价格翻倍是否真的给用户带来了新的价值，还是虚构了一个用户的需求？在潮水退去时，每位造物者都要抓稳自己的锚绳。&lt;/p&gt;
+&lt;p&gt;以下，是「造物 100」栏目第 6 期推荐的最新造物。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;会变形的口袋相机 HoverAir Versa：手里拍着拍着，它飞起来了&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;这是全球第一台既是手持云台相机、也是一款自拍无人机的。拆掉机翼，它可以是一台 Osmo Pocket 类型的口袋云台机。设备自带屏幕、录制键和摇杆，几秒变形展开，同时它起飞时，还可以变成一台自主跟拍的无人机。同一颗镜头，同一段素材，可以从不同视角记录，这也是这款产品最大的卖点之一。目前该产品正在众筹进行中，2026 年秋季在美国上市。&lt;/p&gt;
+&lt;p&gt;但做它的 Zero Zero Robotics 不是新面孔，它曾开发出 HoverAir X1，是自拍无人机品类早期产品之一。他们认为创作者，既想要拍 vlog，也想要航拍镜头，但大家都不想同时背两台设备出门，也不想花大功夫把同一个景点的素材调成一致，所有造了个一机两用，剪辑时连调色都省了。&lt;/p&gt;
+&lt;p&gt;不过，这款产品变形结构的耐久性、飞行模式下的续航，都要等首批实测。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/af/c6/afc66b9b56ddc240ed5936e6a643daa3.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;「无人驾驶」的智能轮椅 Strutt ev1c：自动规避行人与障碍，语音输入指令&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;这是一台会自动驾驶的电动轮椅。车上有两颗激光雷达、十颗深度传感器、六颗超声波加两颗摄像头实时构建 3D 地图。在 Co-Pilot 模式下，它能自动避开行人、宠物和台阶边缘。Auto-Pilot 模式下，轮椅的无人驾驶能力更「强」，你只需要在屏幕上点个目的地，或者直接说一句带我去厨房，它就自己规划路线开过去。&lt;/p&gt;
+&lt;p&gt;依靠于四轮独立悬挂设备、ABS 和电子稳定系统，无论是 13 度的坡，还是铺满鹅卵石路，据介绍，这款设备都照走不误，出远门还能被拆成五个模块塞进后备箱。&lt;/p&gt;
+&lt;p&gt;轮椅这个品类，一百多年没有发生过路线级的变化。电动化解决了力气问题，但操控依然需要完好的手部功能和空间判断力，但 Strutt 把自动驾驶的整套技术栈搬了进来，操控轮椅的逻辑也发生了改变。&lt;/p&gt;
+&lt;p&gt;更有意思的是，自动驾驶技术在汽车行业卷了十年，激光雷达和感知算法的成本被打到了地板价，才让一台轮椅装得起两颗激光雷达。汽车行业卷出来的技术红利，第一批溢出的受益者，也到了坐轮椅的人。&lt;/p&gt;
+&lt;p&gt;不过它的价格还没公布，这套传感器配置不会便宜，这也或许会成为它能不能走出展台的关键。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/20/49/2049fcd9dd34e1a362635e01f22b61cc.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;租房党的光伏储能 EcoFlow STREAM 5000：让 AI 替你管电费&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;这是一套插上就能用的家庭太阳能发电和储能系统，可以给已有的阳台光伏加上电池和智能管理，专门为欧洲市场的租房者和公寓住户设计。不需要打孔、不需要改电路、也不需要房东同意，插电即用，搬家还能拆走。10 月还会上线断网也能跑电力的本地模式。&lt;/p&gt;
+&lt;p&gt;它搭载的 Oasis 3.0 系统能够理解动态电价规则、能看天气预报、学你的用电习惯。你对 AI 助手说一句，明早七点前用最便宜的电把车充满，它就能自己排计</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 14:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>Discover how to take your startup from prototype to production at TechCrunch Disrupt 2026</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/15/discover-how-to-take-your-startup-from-prototype-to-production-at-techcrunch-disrupt-2026/</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr"/>
+      <c r="F403" s="2" t="inlineStr"/>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Learn how to scale your startup breakthrough from prototype to production at TechCrunch Disrupt 2026 with scaling leaders, Adrian Macneil (Foxglove), John Mackey (MBRYONICS), and Boris Sofman (Bedrock Robotics). Register before September 25 to save up to $200 on your pass.</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>Early Anthropic hire, former METR COO have found a way to rein in rogue AI agents</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/15/early-anthropic-hire-former-metr-coo-have-found-a-way-to-rein-in-rogue-ai-agents/</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr"/>
+      <c r="F404" s="2" t="inlineStr"/>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Their startup, Artificial Intelligence Underwriting Company (AIUC) has raised $40 million in a Series A round led by Ribbit Capital, with participation from First Harmonic.</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H404"/>
+  <dimension ref="A1:H417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17001,6 +17001,663 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:51:02+00:00</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>Rethinking Robot Safety in the Age of AI</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/physical-ai-robot-cybersecurity-vicone</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr"/>
+      <c r="F405" s="2" t="inlineStr"/>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;em&gt;This article is brought to you by &lt;a href="https://vicone.com?utm_source=ieee-spectrum&amp;amp;utm_medium=sponsored-content&amp;amp;utm_campaign=2026-09" target="_blank"&gt;VicOne&lt;/a&gt;.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;Robot safety has traditionally asked: Can a machine remain safe when …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 01:09:25 +0000</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>罗福莉沉寂半年官宣小米强化学习！直播新模型训练过程，一小时烧3万美元</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/490950.html</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr"/>
+      <c r="F406" s="2" t="inlineStr"/>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>奖励曲线、显卡故障全公开</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 13:08:20 +0000</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>通用能力不打折，空间具身智能断层领先！ZDTaichu5.0-9B国产开源，跻身全球多模态第一梯队</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/490839.html</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr"/>
+      <c r="F407" s="2" t="inlineStr"/>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>九大空间测试10B规模通用模型中8项第一</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 07:57:21 +0800</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>马斯克再暗示合并特斯拉和 SpaceX；传 iPhone 18 Pro 系列卖爆；大疆 Pocket 4P「珠光白」3799 开售｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370472</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr"/>
+      <c r="F408" s="2" t="inlineStr"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/19/df/19dfa128b05793517f2d72eefca28dde.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;全球首款 AI 智能体手机努比亚 NaviX Ultra 上市：5999 元起，首销销售额「一秒破亿」&lt;/h2&gt;
+&lt;p&gt;9 月 16 日，中兴旗下努比亚今日下午正式发布 NaviX Ultra，官方称其为「全球首款 AI 智能体手机」，也被外界称为「第二代豆包手机」，标志着 AI 智能体手机从工程样机迈入规模化量产商用阶段。发布前该机京东单平台预约量已突破 37 万台，它是第一台搭载豆包手机助手消费者版的机器，现货开售后官方公布首销销售额 「一秒破亿」。此前，京东的预约量已经过了 36 万台。&lt;/p&gt;
+&lt;p&gt;售价方面，12GB+512GB 版本 5999 元、16GB+512GB 版本 6499 元、16GB+1TB 版本 7499 元，全系 512GB 起步，叠加国补后到手价 5499 元起。&lt;/p&gt;
+&lt;p&gt;硬件搭载第五代骁龙 8 至尊版移动平台，首发长鑫存储速率达 10667Mbps 的 LPDDR5X 内存（系国产 10667Mbps 高速 LPDDR5X 首次量产应用），机身厚 7.62mm，内置 7100mAh 电池，支持 90W 有线与 50W 无线快充，配备 2 亿像素主摄，可选幻梦、蓝境、黑、白四款配色。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7e/09/7e0993f11c5629e090cb06d1087e20f9.png" /&gt;&lt;/p&gt;
+&lt;p&gt;AI 能力是这台手机的核心。努比亚总裁倪飞提出 AI 智能体手机的四项能力维度&amp;mdash;&amp;mdash;「听得懂、能干活、记得住、够安全」，对应响应、执行、记忆、安全。机器搭载行业首个集成指纹识别的独立 AI 按键，用户完成身份校验后无需解锁即可直接执行 AI 任务。（来源：极客公园）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d0/62/d06225df52fc3293ecd294da5285ab9e.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;黄仁勋和特朗普拒绝协同放缓 AI 发展的提议&lt;/h2&gt;
+&lt;p&gt;9 月 16 日，据媒体报道，上周末，Anthropic 的达里奥・阿莫代伊、OpenAI 的萨姆・奥特曼以及埃隆・马斯克公开呼吁行业协同放缓研发节奏，妥善应对 AI 带来的各类风险。&lt;/p&gt;
+&lt;p&gt;而英伟达 CEO 黄仁勋则在采访里表示，安全和创新并不矛盾，已经发生的安全事件应该按照工程问题进行根因分析，通过技术、流程和测试加以控制。&lt;/p&gt;
+&lt;p&gt;对于近年来频繁出现的 AI「末日预测」，黄仁勋列举了「放射科医生将被 AI 取代、90% 的代码将在短期内由 AI 生成、50% 的初级岗位即将消失」等此前被证明并不准确的判断。他认为，这类预测缺乏足够的科学依据，也不应该被用来制造社会恐慌。&lt;/p&gt;
+&lt;p&gt;近期，特朗普也在其社交媒体平台 Truth Social 上多次发帖，称人们对失控人工智能的担忧是「骗局」，并猛烈抨击了对公共数据中心的抵制。周一，他更是公开致电了正在洛杉矶「All-In Summit」峰会上发表演讲的英伟达 CEO 黄仁勋。&lt;/p&gt;
+&lt;p&gt;特朗普在电话中毫不掩饰自己对当下全球 AI 安全监管浪潮的强烈反对，直言外界热议的 AI 风险纯属无稽之谈。他说，「这就是一场骗局。机器人不会接管世界，人工智能也不会掌控全球，这种事绝不会发生。」&lt;/p&gt;
+&lt;p&gt;他进一步直言，所有鼓吹 AI 存在致命风险、呼吁政府介入监管的声音，都是「荒唐的阴谋论」，所谓 AI 末日风险完全是不实言论。（来源：新浪财经）&lt;span class="Apple-converted-space"&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;OpenAI 总裁称已进入 AGI 时代：GPT-6 Astra 可自主执行任务 24 小时&lt;/h2&gt;
+&lt;p&gt;9 月 16 日，OpenAI 总裁 Greg Brockman 近日在接受 a16z 采访时表示，人工智能正在进入「AGI 时代」。在他看来，AGI 更像一段能力逐渐变化的光谱，而非某个明确的时间节点；GPT-6 Astra 已能连续自主执行任务约</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:34:03 +0800</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>Token 之后，谁来组织 AI 计算？Arm 寻找下一代计算的答案</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370453</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr"/>
+      <c r="F409" s="2" t="inlineStr"/>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;如果说今年 3 月，Arm 推出首款自研 CPU 芯片，是这家公司向市场释放的一个信号，它开始尝试突破过去「只提供底层架构授权」的角色边界。那么在上海举办的 Arm Everywhere China 活动上，Arm 想传递的信息更加明确，不要再用过去「CPU IP 供应商」的方式理解今天的 Arm。&lt;/p&gt;
+&lt;p&gt;在这场活动中，Arm 没有只围绕某一个产品展开叙事，而是第一次更加完整地将自己的未来方向拆成三条线，云 AI、边缘 AI 和物理 AI。&lt;/p&gt;
+&lt;p&gt;和往年不太一样，去年 Arm 的主题演讲几乎全部围绕一件事展开 SME2，也就是让 AI 在 CPU 上跑起来。那是一个典型的「架构升级」叙事。但今年的主题演讲，三位业务负责人分别讲边缘 AI、物理 AI 和云 AI，围绕场景展开，&lt;strong&gt;算力会在云、端侧和物理世界之间流动，而 Arm 想成为这个「计算基建」的底座。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;今年的 Arm 试图回答的是另一个问题，当 AI 正在重新改变计算方式时，下一代计算平台应该如何被设计？&lt;strong&gt;当 AI 计算正在从单一芯片性能竞争，转向多个计算单元协同竞争时，谁能够组织这些计算资源？&lt;/strong&gt;我们惊讶地与多位 Arm 高管的交流中发现，当下的算力平台似乎不再追求为某一种确定的未来而设计，而是选择拥抱某种不确定性。&lt;/p&gt;
+&lt;h1&gt;一、AI 时代，芯片 IP 已无法决定一切&lt;/h1&gt;
+&lt;p&gt;过去几十年，Arm 最成功的商业模式是通过 CPU 架构和 IP 授权连接整个半导体产业。芯片厂商基于 Arm 架构设计 SoC，终端厂商基于这些芯片打造产品，而 Arm 通过开放授权模式成为移动计算时代的重要基础设施。到今天，基于 Arm 技术的芯片累计出货已经超过 3500 亿颗。&lt;/p&gt;
+&lt;p&gt;过去，芯片竞争更多围绕单一指标展开，需要更强的 CPU、更大的 GPU、更先进的制程。但进入 AI 时代后，一次完整的 AI 任务已经不再只是某一个计算单元完成，AI 任务也从单次计算逐渐走向连续推理、多模态交互以及智能体式的任务执行。这意味着，&lt;strong&gt;未来计算竞争的关键不只是拥有多少算力，而是如何让不同计算资源更加高效地协同。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这次活动的主题演讲， Arm 重点讲述了在不同任务场景里的算力需求变化。&lt;/p&gt;
+&lt;p&gt;在边缘 AI 领域，算力从「被动响应」到「持续运行」。两年前的 AI 是你问一句、它答一句，任务结束；今天的智能体则要理解上下文、检索本机数据、调用应用、在用户授权下自主完成任务，而且要在手机的功耗和散热约束下持续运行。终端设备正在从执行应用和处理数据的工具，变成能够理解意图、实时响应的智能节点。&lt;/p&gt;
+&lt;p&gt;在物理 AI 领域，算力从「车」转移到「机器人」。Arm 过去在汽车上的角色是提供安全、实时、低功耗的计算底座，而现在它走到了机器人上，两者共同的特征是感知和执行，都要求从「传感器」到「执行」的延迟足够短。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ee/dc/eedce1a4ec4341fe9d311923ac319209.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;在云端 AI 领域，Arm 引用 IDC 的数据说，基于 Arm 架构的机架级服务器市场规模已经超越 x86，成为加速计算的主流平台。过去二十年数据中心 CPU 面向的是横向扩展的突发性负载，但智能体则是持续的，一个智能体能发起数百次调用。&lt;/p&gt;
+&lt;p&gt;「在智能体时代，CPU 的角色不再是加速，而是编排」。Arm 基础设施业务的负责人提到，这也是 Arm 开始改变自身角色的原因。如果继续停留在过去的 IP 授权模式，Arm 可以提供优秀的 CPU 架构，但无法参与决定一次 AI 任务最终如何完成。因此，近几年 Arm 开始逐渐从单纯提供 IP，走向提供更加完整的平台能力。如今，客户可以买 Arm 的 IP、也可以买 CSS，甚至可以买芯片。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;但今年最明显的不同，是 Arm 开始正面拥抱 AI 时代最大的特点：不确定性。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;下一代终端到底是什么形态，端侧模型最终会发展到什么规模，智能体的算力应该放在 CPU、NPU 还是云端，目前都没有明确答案。Arm 自己也没有假装自己看到了答案。在媒体沟通会上，我们问了很多关于「谁来决定」的问题，得到的回答却都是「待定」。&lt;/p&gt;
+&lt;p&gt;当被问到 CPU 和 NPU 之间的分工由谁来定</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 16:06:55 +0800</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>助听器躺赚三十年暴利，被 AI 打破了</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370445</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr"/>
+      <c r="F410" s="2" t="inlineStr"/>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;一个塞在耳朵里的小东西，卖到十万一副，丢失甚至需要动用全城搜索？&lt;/p&gt;
+&lt;p&gt;助听器，是一门奇特的生意。&lt;/p&gt;
+&lt;p&gt;整个全球市场，近九成的助听器市场份额被五家外资公司把持：索诺瓦（峰力）、Demant（奥迪康）、WS 听力、瑞声达、斯达克。他们的旗舰产品在中国线下，一对要卖到七到十万块。即便是在美国本土，一副售价也要卖到三四万。而且过去二十年，助听器市场的格局几乎少有波动。&lt;/p&gt;
+&lt;p&gt;让他们垄断助听器市场的，最早其实是一道技术难题：音频分离。&lt;/p&gt;
+&lt;p&gt;想要模拟人耳在嘈杂餐厅里锁定一个声音，其实并不容易。在嘈杂的声音之下，究竟什么声音应该被放大？需要放大的应该是一个声音还是多个声音？在当时，谁能能把这道题解得好，谁就有资格定高价。五家外资公司，用芯片和算法把这件事做到了七八十分，然后，用遍布全球的验配门店，把助听器市场锁成了一套封闭的体系。&lt;/p&gt;
+&lt;p&gt;不是没有人挑战过，几十年间，无数创业者试图打破它，最终都没能跨过去。但这个局面，正在被打破。2026 年，两家来自深圳的公司，把助听器卖到了原来十分之一的价格。&lt;/p&gt;
+&lt;p&gt;据公开报道，听象科技旗下的昂听用 1 年时间就拥有超 50000 用户，做到了美国亚马逊助听器类目 Top1，年销超 1500 万美元，市场份额从 1%迅速增长至 18%。飞声的开放式 AI 助听器在日本的众筹金额超过 300 万美元，创下助听器类目的众筹纪录。&lt;/p&gt;
+&lt;p&gt;改写这一切的前提，是 AI。&lt;/p&gt;
+&lt;p&gt;它第一次让助听器在嘈杂环境理解了什么是「人声」；它通过推测声音的信号，让助听器减少啸叫；它把原本需要专业门店才能完成的验配，移到手机里，十几分钟就能完成。&lt;/p&gt;
+&lt;p&gt;AI 做的事，不是给助听器加了新功能，而是把过去巨头们垄断的技术关卡拆掉了，一同拆掉的，还有建在它之上的定价逻辑。&lt;/p&gt;
+&lt;p&gt;这并非是一个逆袭的故事。助听器市场的结构刚开始松动，无论是价格、渠道、产品形态，还正经历市场检验，结局远未落定。&lt;/p&gt;
+&lt;p&gt;通过这篇文章，我们想回答的问题是：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;一副助听器，为什么从十年前起，就能卖到近十万块？&lt;/li&gt;
+&lt;li&gt;OTC 政策放开了四年，为什么还是没能改变这个市场？&lt;/li&gt;
+&lt;li&gt;AI 到底改变了助听器的什么，用户能感受到的差别在哪里？&lt;/li&gt;
+&lt;li&gt;AI 助听器，和过去的助听器相比，真正不一样的地方是什么？&lt;/li&gt;
+&lt;li&gt;这场变化，最终会让谁受益？&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h1&gt;一、一副十万的助听器，凭什么？&lt;/h1&gt;
+&lt;p&gt;2022 年 10 月，美国 FDA 正式放开 OTC 助听器销售。轻中度听损的成年人，第一次可以不经处方、不进验配门店，直接在药店和亚马逊买到助听器。&lt;/p&gt;
+&lt;p&gt;消息一出，市场像被点燃了引线。科大讯飞、苹果、各路耳机团队纷纷切入，美国亚马逊相关品类涌入不少中国卖家同比增速曾一度超过 160%。&lt;/p&gt;
+&lt;p&gt;所有人都以为，OTC 助听器会是一个翻盘时刻。&lt;/p&gt;
+&lt;p&gt;它手拿的应该是一个新品类撕开专业壁垒、把价格打下来，听起来像消费级设备逆袭专业医疗的经典剧本。&lt;/p&gt;
+&lt;p&gt;但 2026 年最新调研数据给了所有人泼了盆冷水，OTC 助听器，其实连整体市场都没跑赢。&lt;/p&gt;
+&lt;p&gt;过去，买一对专业助听器要花小十万，甚至能买一辆车。十几年过去，助听器的价格几乎没变，调查显示，过去十年，专业助听器平均价格只下降了 228 美元，不到 5%。&lt;/p&gt;
+&lt;p&gt;贵，是所有人看到的第一个问题，也是想改变的第一个方向。但更隐蔽的问题是，就算花了这笔钱，大多数人仍然不愿意戴。&lt;/p&gt;
+&lt;p&gt;调查显示，65 岁以上人群中应该佩戴助听器、但真正从中获益的比例只有 6.5%。堵耳、鼓闷感、耳道潮湿，每天戴十几个小时的不适感，对很多用户来说，佩戴助听器，其实是一种煎熬。&lt;/p&gt;
+&lt;p&gt;「助听器根本不是为最需要用它的那群人设计的。设备越做越小、技术越来越复杂，对很多老年人来说恰恰是错的方向。」一位听力学专家说道，在他接诊的老年患者里，约有一半有某种程度的手部灵活性问题，麻木、颤抖、或者动作受限，但助听器上的一些按键，只有绿豆大小，很难操作。&lt;/p&gt;
+&lt;p&gt;但用户不得不选的五大品牌助听器，有它不可替代的理由。&lt;/p&gt;
+&lt;p&gt;简单来说，五大品牌通过专用 DSP 甚至 AI 协处理器，把芯片算力抬上了一个新台阶。以索诺瓦 2024 年发布的旗舰款为例，它在传统 ERA 芯片之外，额外内置了一颗专用 AI 协处理器 DEEPSONIC，每秒 77 亿次运算，比行业通用芯片高出 53 倍。&lt;/p&gt;
+&lt;p&gt;如果说普通芯片是在一条车道上慢慢挪，它就像突然多了一条高铁专线。更关键的是，这颗芯片「学过」超过 2200 万个真实环境声</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 15:45:18 +0800</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>当智能体开始替人花钱，如何证明「它是谁」？</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370440</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr"/>
+      <c r="F411" s="2" t="inlineStr"/>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>&lt;h1 class="rich_media_title " id="activity-name"&gt;&lt;/h1&gt;
+&lt;div class="rich_media_content js_underline_content defaultNoSetting fix_apple_default_style" id="js_content"&gt;
+&lt;section class="wx-article-wrap"&gt;
+&lt;p&gt;在蚂蚁集团，负责 AI 支付安全的陈树鹏是个深度的智能体使用者。日常写代码、梳理汇报、提炼会议纪要，AI 几乎接管了他工作流里的大部分环节。&lt;/p&gt;
+&lt;p&gt;这种高度依赖背后，却存在着一个清晰的分水岭。一旦任务涉及真金白银，比如调用付费数据接口、购买素材或预订服务，绝大多数人都会本能地把权限卡死不愿交出钱包。哪怕是陈树鹏自己，手头测试过大量任务型框架，真正被他允许支付权限的智能体也仅仅只有两三个。&lt;/p&gt;
+&lt;p&gt;但在产业一线，这种放权又势在必行。&lt;/p&gt;
+&lt;p&gt;在 2026 外滩大会上，蚂蚁集团 CEO 韩歆毅表示，智能体商业的「ChatGPT 时刻」正在到来，其核心标志正是从单纯的对话能力展示，加速走向真实的商业交易闭环。商业世界的交互起点，正在从过去的搜索页面演进为意图驱动的服务调度。&lt;/p&gt;
+&lt;p&gt;在技术上，调用 API 扣费及定期支付看似早已是成熟的基础设施。但真正让人犹豫的，是 Agent 与传统自动化脚本的本质区别。以往的自动化扣款跑在封闭受控的系统里，按固定规则触发；现在的 Agent 为了办成一件事，需要在开放网络里自主探索、解析未经清洗的公开网页、调用第三方插件。面对一个在外部环境里自主决策的长任务，过去那种一次性给出的静态免密授权，很容易在不可控的执行链条中变成一张无法兜底的空白支票。&lt;/p&gt;
+&lt;p&gt;9 月 11 日，蚂蚁集团在外滩大会上发布的 APASS，要解决的就是这个放权困境。这项面向智能体商业活动的信任基础设施，基于 KYA（认知你的智能体）理念，通过身份与意图两条信任链，为商业网络提供一套核验 Agent 身份、授权边界与实际行为的底座机制。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/18/37/1837193b0a6561e2acff0c44a74148d4.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;h2&gt;&lt;strong&gt;换了台电脑后，商家还认识你吗？&lt;/strong&gt;&lt;/h2&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;过去二十年，商业世界确认一个交易者是谁，底气全来自看得见摸得着的物理实体。手机里的 App 有官方加密签名，指纹与人脸能确认活人在场，背后的法定实名信息提供了终身唯一的身份锚点。&lt;/p&gt;
+&lt;p&gt;这套所有人习以为常的规则，在智能体时代出现了真空。&lt;/p&gt;
+&lt;p&gt;陈树鹏对极客公园提到了一个典型的场景。一位开发者在家里的电脑上用开源框架搭建了一个购物助手，帮自己采购日常用品并配置了相应权限。为了让程序持续稳定运行，开发者随后把这个 Agent 的代码镜像、运行配置与记忆上下文打包，迁移到了云端容器中继续跑。&lt;/p&gt;
+&lt;p&gt;这一搬，原先绑定的设备、网络 IP 乃至调用的模型与插件全变了样。当这串代码带着委托去调用商户服务时，对方单靠一个静态的 API Key，很难确认眼前的程序究竟还是不是此前获批的助手，还是一个被克隆篡改后的仿冒品。&lt;/p&gt;
+&lt;p&gt;针对这种运行时环境与代码可能发生的变化，APASS 在支持中心化 Agent ID 与去中心化 DID 等标识的同时，提供了三个维度的核验依据。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2d/4c/2d4c0c72f004e01b5f28d0d30422d427.png" /&gt;&lt;/p&gt;
+&lt;p&gt;首先是软件本身的特征。系统会校验 Agent 的代码指纹、软件版本及挂载的 Skill 清单，确认其程序基础是否与登记档案一致、核心组件是否遭到替换。&lt;/p&gt;
+&lt;p&gt;其次是运行时的环境状态。一段原本正常的代码，如果寄宿在存在安全漏洞或异常进程挂钩的宿主环境中，同样存在失控隐患。系统联动设备厂商与云厂商，通过硬件级可信根运行环境检测，核验宿主设备是否可信及环境的状态是否可信。&lt;/p&gt;
+&lt;p&gt;最后是真实的责任主体。虚拟程序在不同服务器间</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 14:39:11 +0800</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>腾讯、字节、阿里「会战」AI 办公之后：Agent 领域格局已变</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370431</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr"/>
+      <c r="F412" s="2" t="inlineStr"/>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;「这仗打错了，最多是白烧几十亿；但如果不打，可能是生死问题。」&lt;/p&gt;
+&lt;p&gt;这是创新工场联合首席执行官、管理合伙人汪华对大厂重金押注 AI 办公的判断。&lt;/p&gt;
+&lt;p&gt;2026 年的这个夏天，中国科技巨头发起了 Agent 时代第一场「战役」：豆包工作正式发布，TRAE、扣子团队整体并入豆包体系。更早的 7 月底，飞书产品团队并入豆包；另一边，腾讯的 WorkBuddy 已经跑出了千万月活，阿里也在整合自己的桌面 Agent、云端 Agent 和钉钉能力。&lt;/p&gt;
+&lt;p&gt;巨头为何会集体兴奋？AI 办公的背后他们在思考什么？在争夺什么？最近，极客公园邀请了汪华、Floatboat.ai 创始人兼 CEO 谭少卿一起来聊一聊。&lt;/p&gt;
+&lt;p&gt;今年初那场「小龙虾热」，本质上只是一场极客的自我狂欢。谭少卿说，「它是个过渡产品」，属于三类产品分层中的「极客产品」，从一开始就没打算走大众化路线。模型不够强、配置门槛高、Harness 不成熟，把普通用户挡在门外。&lt;/p&gt;
+&lt;p&gt;真正的转折发生在最近几个月。汪华认为，国产模型是最近才真正跨过了那道坎。GLM-5.3-Flash、DeepSeek-V4-Flash 这些模型不仅把指令遵循能力做上去了，更关键的是把成本打了下来。&lt;/p&gt;
+&lt;p&gt;现在，才是中国 Agent 爆发的真正原点。&lt;/p&gt;
+&lt;p&gt;这里面有一个反直觉的逻辑：移动互联网时代，千万月活根本不值得巨头兴师动众，但这次大厂已经开始了一场「大会战」。&lt;/p&gt;
+&lt;p&gt;汪华说，背后的驱动力是恐惧。年初 Claude Code 还没到千万月活时，ARR 就已经达到 200 亿美金了。这意味着，未来的高价值经济入口，可能不建立在高日活之上。法律、财务这类高价值的专业工作，一旦被 Agent 重新定义，丢掉的不是用户规模，而是整个赛道的船票。&lt;/p&gt;
+&lt;p&gt;除此之外，还有另一个因素是算力。C 端产品比如豆包，算力负担极重，只能用压缩的小模型，所以「有时觉得它智障」；而&lt;strong&gt;办公 Agent 恰好卡在一个理想区间，既能体现大模型真实能力，又不会因为用户规模过大导致算力扛不住，同时商业模式能跑通&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;WorkBuddy 的火热，某种程度上是一场内部赛马的幸存者故事。「它是踩在众多失败项目的尸体上活下来的。」大厂采取的都是内部赛马策略，那些算力成本过高、商业模式不成立的项目自然死亡后，资源自动向幸存者倾斜。&lt;/p&gt;
+&lt;p&gt;巨头进新战场，常被认为自带优势。但这次不一样。汪华说，「巨头唯一的壁垒其实只有钱，而钱能兑换的仅仅是算力。过去积累的数据和用户，不会自动转化成新赛道的优势，庞大组织架构反而会极大抵消资金优势」。&lt;/p&gt;
+&lt;p&gt;虽然巨头已经下场，但汪华认为，中国创业者有一个很大优势，距离中国开源模型更近。「大家在一个圈子里，私下交流多，最懂怎么在这些开源模型上做微调、建生态，那就能相对于其他地方的创业者建立一些优势。」&lt;/p&gt;
+&lt;p&gt;进入 Agent 时代，巨头们都在争夺通往未来的船票。汪华说，「船票」其实只有两张：成为水电煤般的基础设施，以及掌握基础模型。至于用户平台层面的船票，很可能根本不存在了，因为 Agent 本质上「&lt;strong&gt;是一种能力、一种智力、一种计算形态&lt;/strong&gt;」，而不是一个需要被圈养的平台。&lt;/p&gt;
+&lt;p&gt;谭少卿从产品实践里看到了更远的东西：当 Agent 具备主动性，甚至开始向 CTO、COO 的角色过渡时，连 WorkBuddy 这样的「工作台」形态，都可能只是过渡产品。「&lt;strong&gt;模型越聪明，其实越不需要WorkBuddy这种中间层&lt;/strong&gt;。」&lt;/p&gt;
+&lt;p&gt;巨头们这一次冲进 AI 办公战场，多少带着一点恐惧：怕错过新入口，怕丢掉下一代生产力的船票。但有意思的是，他们在重兵投入的同时，也无意中完成了市场教育，让更多用户第一次真正理解，Agent 不只是聊天工具，而是能干活的生产力系统。&lt;/p&gt;
+&lt;p&gt;而创业公司并没有因此被挤到墙角。相反，在巨头照亮市场之后，它们反而看见了更多细分机会：更垂直的场景、更灵活的产品形态。&lt;/p&gt;
+&lt;p&gt;以下是极客公园创始人&amp;amp;总裁张鹏和汪华、谭少卿的对话内容，部分有删减。&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h1&gt;Part 1：中国 Agent 的「ChatGPT 时刻」来了&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;张鹏：近期腾讯、字节、阿里等大厂在 AI 办公领域的动作非常密集。你们怎么看他们最近的系列动作？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;汪华：&lt;/strong&gt;我觉得这事特别好。&lt;strong&gt;有了大厂来推动，包括他们愿意补贴，才能真正开启中国 Agent 领域的「ChatGPT 时刻」。&lt;/strong&gt;&lt;/</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 14:30:50 +0800</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>没有方向盘、没有踏板、没有后视镜：特斯拉最疯狂的车来了</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370425</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr"/>
+      <c r="F413" s="2" t="inlineStr"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;9 月 3 日，特斯拉「悄悄」办了一场发布会。&lt;/p&gt;
+&lt;p&gt;没有直播，没有全球媒体轰炸，只请了少数受邀者参加。活动开始前，特斯拉的网红粉丝们发布了照片和视频。特斯拉还在网站上设置了倒计时，为该活动预热。&lt;/p&gt;
+&lt;p&gt;这场发布会的主角，是那台被外界戏称为「三无车型」的 Cybercab：没有方向盘，没有踏板，连传统意义上的侧后视镜都没有。它从设计之初就不打算遵循任何传统汽车的逻辑，目标是把单车成本和每英里运营成本压到极致。&lt;/p&gt;
+&lt;p&gt;Cybercab 的发布比以往的产品演示更重要。2026 年 9 月 3 日，摩根士丹利分析师 Andrew Percoco 表示，在其对特斯拉 400 美元的目标价中，自动驾驶出租车业务贡献了约 120 美元的估值；今年 3 月，美国银行还将特斯拉的自动驾驶出租车业务估值为 8440 亿美元，相当于特斯拉当时估值的一半左右。&lt;/p&gt;
+&lt;p&gt;按照马斯克的设想，Cybercab 未来会是特斯拉销量最大的一款车，支撑起一张覆盖全球的无人驾驶出租车网络。更有想象力的一层是：车主自己不用车的时候，可以把车「投放」进特斯拉管理的车队里去跑单，闲置资产变成现金流。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;马斯克十年故事，终于开始兑现&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;有意思的是，这场发布会官方没有直播，但 X 用户 Kyle Conner 发布了一批现场照片和技术细节，让外界看清了 Cybercab 的真实底子。&lt;/p&gt;
+&lt;p&gt;配置上，Cybercab 刹车用的是线控刹车，但每个车轮都配了独立的执行器，这在无人驾驶场景下是个关键的安全冗余设计；驱动是前轮驱动，配合较高的齿轮比，特斯拉在压低电机噪音传入车厢这件事上明显下了功夫；电池用的 4680 电芯，可以支撑 50 万英里的使用寿命，同时能扛住高频直流快充、持续振动、剧烈温度波动；电气架构是 48V 低压，自动驾驶大脑跟 HW4 类似&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p&gt;目前这台 Cybercab 还没开放面向客户销售。但特斯拉在官网挂出了一份表格，专门用来收集有意进行 Cybercab 车队车辆采购人士的联系方式。&lt;/p&gt;
+&lt;p&gt;不过，奥斯汀的用户已经可以抢先体验了。通过特斯拉去年上线的 Robotaxi 叫车应用，现在可以预约乘坐 Cybercab。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0a/e3/0ae388c0bf6c54efc4e9723883219e8f.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;全新设计的 Cybercab，支撑了特斯拉将近一半的估值｜图片来源：视觉中国&lt;/p&gt;
+&lt;p&gt;其实，这不是马斯克第一次讲这个故事。早在 2016 年，他就开始向粉丝和投资者描绘一幅画面：一辆车能够完全自主地横跨美国，不需要任何人为干预。2024 年 10 月，特斯拉在洛杉矶一家电影制片厂办了一场发布会，展示了 Cybercab 的原型。&lt;/p&gt;
+&lt;p&gt;接下来，又是特斯拉的「传统艺能」：产品发布，永远比承诺的时间晚，规模也永远比画的饼小。马斯克曾说，到 2025 年底，特斯拉的自动驾驶叫车服务将覆盖美国一半地区；到 2026 年底，将有数以百万计的特斯拉无人驾驶出租车上路。&lt;/p&gt;
+&lt;p&gt;但根据德克萨斯州机动车辆管理局网站上的公开记录，截至 9 月 3 日，特斯拉在德克萨斯州注册用于无人驾驶运营的车辆总数为 420 辆，其中 45 辆 Cybercab 车辆已获得授权在该州进行无人驾驶运营。这距离「大规模商业网络」仍然很远。&lt;/p&gt;
+&lt;p&gt;相比之下，Waymo 目前在美国 14 个城市运营 Robotaxi 服务，拥有约 4000 辆无人驾驶车辆跑在路上。&lt;/p&gt;
+&lt;h1&gt;技术路线之争，到摊牌时刻了&lt;/h1&gt;
+&lt;p&gt;这场发布会真正值得关注的，不只是车本身，还有持续 10 年的技术路线之争正走到一个摊牌的窗口。&lt;/p&gt;
+&lt;p&gt;发布会前一周，8 月 26 日，Waymo 车载软件副总裁 Srikanth Thirumalai 发了一篇长博客，标题是《从 2 亿多英里完全自动驾驶里程中获得的 10 条 AI 经验》。文章通篇没提特斯拉的名字，但里面至少有三条，跟特斯拉有关。&lt;/p&gt;
+&lt;p&gt;第一条是，纯视觉不够。Waymo 在跑完超过 2 亿英里真实无人驾驶里程后给出的结论是：要安全、大规模地把完全自动驾驶铺开，必须同时依赖摄像头、激光雷达和毫米波雷达三种传感器，谁也替代不了谁。&lt;/p&gt;
+&lt;p&gt;特斯拉的路径恰好是其反面。马斯克 2019 年就把激光雷达称为「注定失败的徒劳之举」，2021 年拿掉毫米波雷达，2022 </t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 14:27:24 +0800</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>4 款车、3 颗芯片、15999 的折叠屏手机，小米的「疯狂一夜」</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370423</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr"/>
+      <c r="F414" s="2" t="inlineStr"/>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 月 7 日晚上，雷军站在国家会议中心的舞台中央，讲了整整两个半小时。这不是一场普通的秋季发布会，而是小米的一份阶段性答卷。&lt;/p&gt;
+&lt;p&gt;车、芯片、手机，这三张牌，小米憋了很久。造车、造芯、造高端旗舰，每一件单拎出来都很重磅，而雷军选择把它们同时摊在同一张桌子上。四款澎程新车、三颗自研玄戒芯片、史上第一款破万的小米 18 Fold 折叠屏，再加上一块想要正面掀翻 iPad 的小米平板 9 Pro Max。&lt;/p&gt;
+&lt;p&gt;值得注意的是时间分配：两个半小时里，&lt;strong&gt;光澎程系列的四款车，雷军就讲了一个半小时&lt;/strong&gt;。重头戏是谁，答案不言而喻。发布会后，小米披露，4 分钟澎程锁单突破 10000 台。&lt;/p&gt;
+&lt;p&gt;而当那块能在车顶升起一整间「移动小屋」的电动顶舱亮相时，现场响起了热烈的掌声。&lt;/p&gt;
+&lt;p&gt;今晚的小米，想讲的不是参数，而是一个关于「下一个十年靠什么活」的故事。&lt;/p&gt;
+&lt;h1&gt;一、一个半小时、四款车&lt;/h1&gt;
+&lt;p&gt;这次发布会的重头戏是小米澎程系列。当雷军讲到这部分的时候，现场掌声最大。&lt;/p&gt;
+&lt;p&gt;此前 7 月底的技术发布会上，7 月 30 日，小米汽车举办造车五年来的第二次技术发布会，系统分享了小米昆仑技术架构，并发布小米澎程首款车型 N90 Max，两排五座的 N70 系列只用了不到 3 分钟快速带过。&lt;/p&gt;
+&lt;p&gt;而今晚，主角调了个个儿，雷军重点介绍了 N70 系列的两款新车，并带来搭载原生设计电动升降顶舱的 N90 Max 探索版。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/40/a8/40a89d8f72771cfd7b73a818a402e77c.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;不同于 SU7、YU7 追求极致性能，澎程系列是要把车内空间做大、做平，还要丰富可变。这次同步上市的 4 款车里，N70 Pro 和 N70 Max、N90 Max 露营版是大五座，N90 Max 是三排六座。&lt;/p&gt;
+&lt;p&gt;它们共享同一套设计语言：全平地板、可移动中岛、前排座椅 180&amp;deg;旋转，一键切换会客厅、大床、办公等超过 13 种场景。&lt;/p&gt;
+&lt;p&gt;几台车的价格也一次性亮明：&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;N70 Pro 起售 20.99 万、&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;N70 Max 23.99 万、&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;N90 Max 26.99 万、&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;N90 Max 探索版 29.99 万&lt;/strong&gt;，9 月 7 日晚 22 点正式开售。&lt;/p&gt;
+&lt;p&gt;小米澎程 N70 是一款「大小合适、驾驶轻松、乘坐也舒适」的主流 SUV，车长 4960mm、车宽 1998mm、轴距 2950mm，拥有和 N90 系列一样的智能可变大空间，支持对坐模式等多种可变场景。&lt;/p&gt;
+&lt;p&gt;N70 全系长续航，Pro 版搭载 52 度磷酸铁锂电池，CLTC 纯电续航 351km、综合续航 1351km，Max 版搭载 76 度三元锂电池，CLTC 纯电续航 505km，是目前市面上纯电续航最长的增程车型。全系搭载小米 1.5T 增程器，Pro 版亏电油耗仅 5.7L/100km，Max 版亏电油耗 6.1L/100km，不挑桩、不挑油，支持 92 号、95 号、98 号汽油。&lt;/p&gt;
+&lt;p&gt;此外，N70 Max 还新增了高性能四驱、空簧、连续阻尼可变减振器、HUD 和 25 扬声器豪华音响等配置。&lt;/p&gt;
+&lt;p&gt;智能方面，N70 全系智能满配，智能基座采用小米四合一域控制模块，全系标配高通 4nm 旗舰 SoC 芯片、4nm 英伟达 Thor-U 辅助驾驶芯片、激光雷达、4D 毫米波雷达和终身免费的 HAD 辅助驾驶。小米澎湃智能座舱支持五屏联动，全新超级小爱已覆盖 95%的车控功能。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/44/44/4444d4708d5013eece01feeb89cf813b.png" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：小米汽车&lt;/p&gt;
+&lt;p&gt;除此之外，雷军还带来了全新探索版车型：&lt;strong&gt;N90 Max 探索版，也就是坊间口中的 N90「露营版」，以 29.99 万元的售价&lt;/strong&gt;，把一件过去属于极客玩家的小众爱好，直接推到了大众消费的门口。&lt;/p&gt;
+&lt;p&gt;N90 Max</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 14:16:06 +0800</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉、Figure 还在攻克量产，小鹏机器人已经走下产线</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370421</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr"/>
+      <c r="F415" s="2" t="inlineStr"/>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 月 8 日，一台高阶通用人形机器人小鹏 IRON 完成自动化总装，从产线上走了下来。&lt;/p&gt;
+&lt;p&gt;如果只看画面，这好像是又一段科技公司放出来的机器人视频。在这个被大模型和具身智能席卷的时代，科技圈每天都在被各种炫酷的机器人 Demo 刷屏：有人形机器人打拳击，有灵巧手叠衣服，也有机器人在舞台上完成复杂动作&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p&gt;这次更值得关注的，并不是机器人行走本身，而是它身后那条刚启用的自动化产线。这次的机器人并不是工程师手工拼装出来的，而是像汽车一样经过一整条工业化产线，自动化总装然后下线。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;一、会表演不够了，能量产才算数&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;小鹏押注机器人这件事，其实比外界想象的要早得多。早在 2020 年，小鹏就已经切入了机器人赛道，比现在市面上大多数明星机器人公司都要早。&lt;/p&gt;
+&lt;p&gt;但选择在 2026 年这个时间点启用产线，这更像是小鹏过去几年物理 AI 战略的一次集中呈现。从智能汽车到 Robotaxi、人形机器人、飞行汽车，小鹏正在推动 AI 能力从汽车场景向更多物理空间延伸。&lt;/p&gt;
+&lt;p&gt;机器人和汽车在硬件形态、运动方式和应用场景上差异很大，但在 AI 层面，两者需要解决的问题类似：如何让人工智能理解真实环境，并在复杂物理空间中完成任务。&lt;/p&gt;
+&lt;p&gt;汽车业务中形成的部分模型能力、数据体系和 AI 基础设施，可以进一步向机器人延伸；一套物理 AI 底层能力能否跨越不同本体，新的本体进入更多真实场景后，又会产生新的数据，推动模型持续迭代。机器人是这个战略中的一个重要落点。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/59/23/59233c98858065f3043e1809b4dfef75.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：小鹏集团&lt;/p&gt;
+&lt;p&gt;其次，小鹏战略层面的准备也早已就位。 2026 年 6 月，何小鹏在全员信中宣布，除了继续担任小鹏集团 CEO，他还将亲自兼任机器人业务的「CEO」。这意味着小鹏集团把机器人业务提升到最高战略优先级。&lt;/p&gt;
+&lt;p&gt;紧接着是 8 月小鹏机器人业务完成首轮融资，融资金额超 9 亿美元，投后估值超 63 亿美元；再紧接着就是这次的产线投产。&lt;/p&gt;
+&lt;p&gt;长期投入之后，小鹏机器人的推进节奏明显加快，融资、估值与量产接连落地，一种喷薄而出的加速度正在显现。&lt;/p&gt;
+&lt;p&gt;更重要的是，机器人行业的竞争主线发生了变化。过去几年，人形机器人热度很高，但更多的是各种 demo 展示，能够真正落地场景的并不多。&lt;/p&gt;
+&lt;p&gt;但随着本体、芯片、模型、数据采集技术的发展，机器人行业从技术研发阶段，切换到了量产与商业化阶段。接下来比拼的会是产线、供应链、良率、成本、数据闭环和交付能力。&lt;/p&gt;
+&lt;p&gt;对于任何一家想要做大的机器人公司来说，最难的不是造出第一台机器人，而是造出第一千台、一万台，并且每一台都足够可靠和一致。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;二、为什么是高阶人形机器人？&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;当行业的主战场从 demo 走向产业化，一个绕不开的问题是：什么样的机器人值得被大规模制造?&lt;/p&gt;
+&lt;p&gt;小鹏给出的答案，不是随便一种人形机器人，而是难度最高的那一种：极致拟人、AI 驱动、具备最高标准安全品质的通用高阶人形机器人。何小鹏的话说得很直白，「我们最想做的是能够自主帮我们干活的高阶人形机器人，这意味着要做最难的硬件，最难的 AI，并且把不同的能力平衡好。」&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/70/9e/709e541f36b8d5f006cc0ca222a11475.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：小鹏集团&lt;/p&gt;
+&lt;p&gt;过去一年多发生的两件事，证明了这条路到底有多难。2025 年小鹏科技日现场，小鹏人形机器人 IRON 走着「猫步」入场，它行走时的流畅度、柔顺感，以及肩颈、胯部的协调摆动，引发公众对「是否真人套壳」的质疑。为了自证，团队不得不现场剪开腿部的皮肤，露出里面的骨骼结构。&lt;/p&gt;
+&lt;p&gt;然而，在这个过程中并不只是高光时刻。2026 年 2 月，IRON 在深圳湾万象城首次公开亮相时，行走过程中突然失衡摔倒。那一刻，社交媒体的笑声盖过了技术讨论。&lt;/p&gt;
+&lt;p&gt;但何小鹏自己也承认，「做机器人需要习惯失败，每一次成长背后都会有代价，这是门票，不是意外。」&lt;/p&gt;
+&lt;</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 13:35:49 +0800</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>我坐进特斯拉 Cybercab，吃下马斯克 Robotaxi 的「新饼」</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370412</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr"/>
+      <c r="F416" s="2" t="inlineStr"/>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;2013 年 9 月，苹果推出了新品 iPhone 5S 手机，这款手机除了延续苹果在智能手机上一往无前的势头外，新增的金色配色，深受大众喜爱，并获得了「土豪金」的称号。&lt;/p&gt;
+&lt;p&gt;2026 年 9 月，特斯拉也发布了一款「土豪金」产品&amp;mdash;&amp;mdash;不是Space Phone，而是特斯拉 Cybercab，用于 Robotaxi 的无人驾驶电动车。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2d/f5/2df556f7e19c560481367ab25e6a07a0.png" /&gt;&lt;/p&gt;
+&lt;p&gt;「土豪金」Robotaxi 来了！｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;特斯拉不是第一个做无人驾驶车的，但是彻底拿掉方向盘、加速、刹车踏板和后视镜，完全用第一性原理做出Robotaxi 车型的，特斯拉显然又引领了潮流。尤其是，这样的 Cybercab 已经在美国得州奥斯汀真的开始「拉客」了。&lt;/p&gt;
+&lt;p&gt;虽然不知道特斯拉的 FSD 什么时候进入中国，但是不到两周，极客公园就在国内亲自体验了 Cybercab，狠狠吃下马斯克给大家画的「新饼」。&lt;/p&gt;
+&lt;h2&gt;&lt;a id="heading_0"&gt;&lt;/a&gt;&lt;strong&gt;金色「缝合怪」&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;北京蟹岛特斯拉交付中心，就在交付大厅内，团队搭了一个简单的摄影棚。在轮胎与地面摩擦声中，极客公园看到了那台金色的 Cybercab。&lt;/p&gt;
+&lt;p&gt;不知道是不是因为刷了太多关于 Cybercab 的视频，第一眼看到 Cybercab，并没有特别令人惊艳。毕竟，这是一台 4 米 4 的双座小车，不过金色的配色，让这台车从一种新能源车中跳脱出来。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e7/e4/e7e4f4b54c28a1c174564af7629d72ab.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Cybercab 有点「缝合怪」的意思｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;Cybercab 看起来非常像一台缝合怪，车的前半部分和焕新版的 Model 系列很像，尤其是封闭式前脸加上中间的贯穿式灯带。但是从中间到后部，一道斜向下的平直溜背，则让人一眼就想到了 Cybercab 的大哥&amp;mdash;&amp;mdash;Cybertruck，配合中间的腰线，把 Cybercab 的「硬」给体现了出来。&lt;/p&gt;
+&lt;table&gt;
+&lt;tbody&gt;
+&lt;tr&gt;
+&lt;td&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2d/b5/2db53931ed90f944733a25d1fdbba902.png" /&gt;&lt;/p&gt;
+&lt;/td&gt;
+&lt;td&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/54/76/5476c495bfc9997d86cc9a7ab9ae8530.png" /&gt;&lt;/p&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;前面是 Model 的圆润，后面是 Cybertruck 的硬朗｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;虽然看起来很低调，但是 Cybercab 的开门方式却相当高调。蝴蝶门的开门方式，按下车内按钮，&lt;strong&gt;车门斜向上开启，让人感到自己坐的不是一台网约车，而是超级跑车&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9c/21/9c21a7aa70675eb902b4a17c5c750ac3.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Cybercab 的蝴蝶门看起来非常炫酷｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;不夸张的说，Cybercab 的开门方式，甚至比 Model X 的鸥翼门开启方式更酷。当然，选择这个开门方式，其实还有实际作用，后面会详细介绍。&lt;/p&gt;
+&lt;p&gt;Cybercab 外观还有一个让人感到有意思的点，就是你会发现，一台没有后视镜的车，才更像是车的本质，设计得再好看的后视镜，对于一台车来说，都是多余的，这可能也是为什么，没有后视镜的 Cybercab 其实看起来更自然。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4b/35/4b3576e3548d51aa7b38b522ec93eb24.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Cyb</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 15:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>Robots are waiting for a ChatGPT moment: Nvidia’s Les Karpas explains why at TechCrunch Disrupt 2026</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/16/robots-are-waiting-for-a-chatgpt-moment-nvidias-les-karpas-explains-why-at-techcrunch-disrupt-2026/</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr"/>
+      <c r="F417" s="2" t="inlineStr"/>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>The robotics industry is still waiting for their breakthrough into day-to-day life. Nvidia's Les Karpas has an answer as to why at TechCrunch Disrupt 2026. Register before September 25 to save up to $200 on your pass.</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17658,6 +17658,468 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:42:03 +0000</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>浦慧科技数据采集手套介绍</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13012</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr"/>
+      <c r="F418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>随着柔性传感与可穿戴技术的发展，能够贴合人体、实时感知压力变化的柔性传感设备，正逐渐应用于数据采集、智能交互、</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:39:06 +0000</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>10分钟1台，人形机器人量产能力再加速</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13017</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr"/>
+      <c r="F419" s="2" t="inlineStr"/>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>量产在加速，商业化，也在加速</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:37:57 +0000</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>机器人产品动态 l 宇树 G1+大升级；蓝虫具身推出模块化人形机器人</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13011</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr"/>
+      <c r="F420" s="2" t="inlineStr"/>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>亮点：头部装触觉、模块化组装更适配多元化需求</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:37:12 +0000</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>Ego数据采集厂哭诉：既要真实场景，又不能拍到别人，难！</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13004</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr"/>
+      <c r="F421" s="2" t="inlineStr"/>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>数据采集看似热闹，实则粗活、脏活、慢活，赚的是辛苦钱，扛的是高不确定性</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:32:27 +0000</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>触觉传感器赋能电池安全：长三角物理研究中心与悟通感控共建电池力学实验室</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13003</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr"/>
+      <c r="F422" s="2" t="inlineStr"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>长三角物理研究中心携手悟通感控共建电池力学实验室——从力学感知出发，探索电池安全分析新路径</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:29:59 +0000</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人的隐形赢家：天机力控臂拿下全球市占第一</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12987</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr"/>
+      <c r="F423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>逛过这两年人形机器人展会的人大概都有个感受：台上的机器人越来越多，演示动作也越来越花，但真要问能不能进厂干活、能不能处理日常琐事，答案大多还得打个问号。大模型让机器人越来越会 “想”，但实体执行层的短板始终没补上。</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 07:14:19 +0000</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>10分钟下线一台，优必选万台级人形机器人超级工厂投产</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12974</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr"/>
+      <c r="F424" s="2" t="inlineStr"/>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>近日，优必选万台级工业人形机器人超级智慧工厂在广西柳州正式投产。按照生产设计节拍，平均每10分钟即可下线一台工业人形机器人，年规划产能超过1万台。</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>如何从历史中学习？基于RhymeRL的强化学习系统优化实践｜QCon上海</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/CbZGXuTBMFJPZ7WNtH9h?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr"/>
+      <c r="F425" s="2" t="inlineStr"/>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/CbZGXuTBMFJPZ7WNtH9h?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 08:17:15 +0800</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>影视飓风 Tim 称 iPhone Duo「烫到握不住」；赛力斯否认「问界撤出华为门店」；黄仁勋：英伟达 2027 年芯片销量将翻倍</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370539</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr"/>
+      <c r="F426" s="2" t="inlineStr"/>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/06/02/0602f03c07ef2b725b4350a13a7c765d.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;传 &lt;/span&gt;&lt;span style="font-weight: bold;"&gt;Manus 即将完成 5 亿美元融资，估值 40 亿美元&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据彭博社 9 月 17 日报道，AI 智能体公司 Manus 即将完成 5 亿美元融资。这是该公司撤销 Meta 收购交易后的首轮融资。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;报道表示：在新一轮融资中，Manus 的估值将提高一倍，至 40 亿美元。这家 AI 智能体公司也将成为该领域中国估值最高的创业公司。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;知情人士称，谈判仍在进行中，交易条款仍可能变化。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Manus 的现有投资方包括腾讯控股、红杉中国和真格基金。截至发稿，Manus、腾讯、红杉中国和真格基金均未回应置评请求。（来源：凤凰网科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/8a/aa/8aaa7d67b8f188edfd73560057427600.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;地瓜机器人宣布完成 4 亿美元 C 轮融资&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;9 月 17 日，地瓜机器人宣布完成 4 亿美元 C 轮融资，由国际知名投资机构未来资产领投，资方数量接近 30 家。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;本轮是标准的 club deal，距上一轮仅过去 5 个月&amp;mdash;&amp;mdash;今年 4 月，地瓜刚完成 2.7 亿美元的 B 轮融资。今年以来，地瓜累计融资近 50 亿元人民币。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;地瓜机器人方面没有披露具体投后估值，但据了解，目前估值与最受捧的几家具身明星基本同一梯队。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;根据融资用途推测，本轮融资后具体的发力点是面向具身的高算力 560 TOPS 旭日 S600 芯片，以及从数采、模型训练、仿真验证到推理部署的全链路软件平台。（来源：投中网）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;黄仁勋：英伟达 2027 年芯片销量将翻倍&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;9 月 17 日，英伟达 CEO 黄仁勋在英国的一场人工智能活动中表示，英伟达明年芯片销量将是今年的两倍。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;近期一些业界人士主张放缓 AI 开发进度，以便让安全措施跟上步伐。黄仁勋表示，人工智能安全至关重要，企业应继续快速推进，如果认为某些产品存在安全隐患，就暂缓推出这些产品。（来源：第一财经）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;传苹果自研 AI 服务器芯片，有望 2029 年登场&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;近日，科技媒体 The Information 称苹果公司正筹划推出企业级服务器，采用自研芯片，并可能接入英伟达的网络设备。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;The Information 的报道表示，苹果计划面向 AI 开发者、企业和政府机构销售这款服务器。产品目前考虑推出两个版本：基础版配备两颗计划中的 M8 Ultra 芯片，高配版则配备四颗。并</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 15:51:53 +0800</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>京东押注物理 AI，冲在前面的是一群 95 后</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370519</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr"/>
+      <c r="F427" s="2" t="inlineStr"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;去年，AI 行业最热闹的是模型榜单、推理能力和多模态生成。所有人都在问：这个模型有多强？&lt;/p&gt;
+&lt;p&gt;但到了 2026 年，问题变了。人们开始追问：它到底能干什么？&lt;/p&gt;
+&lt;p&gt;这个问题，京东在今年的 JDD 大会上，给出了自己的答案。&lt;/p&gt;
+&lt;p&gt;京东把这届大会的主题定为「JoyAI &amp;middot; 跃迁物理世界」。它想传达的是，AI 的下一站不只是能说会道、更聪明，而是要进入仓库、货架、家庭、配送路线和售后服务，去完成真实任务。&lt;/p&gt;
+&lt;p&gt;有意思的是，这次站上舞台的，除了京东高管，还有一批 95 后业务负责人和产品经理。他们讲的不是概念里的未来，而是京东 App 的 AI 化改造、物流具身智能机器人、家庭 AI 入口。这背后京东正在推进一项更大的战略&amp;mdash;&amp;mdash;建设全球最大物理世界运营中心。AI 正在走出屏幕，而年轻人正在成为这场迁移的主力。&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;95 后冲进 AI 最难落地的地方&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;陈屿有一段时间，每天都在问自己同一个问题：我们是不是做错了？&lt;/p&gt;
+&lt;p&gt;那是 2025 年底、2026 年初，整个电商行业都在往「智能体电商」这个方向猛冲。用户输入一句话，AI 理解需求、推荐商品、辅助下单。这个想象很迷人，也足够「未来感」。&lt;/p&gt;
+&lt;p&gt;陈屿和他的团队也投身这场探索，推出了「京东 AI 购」独立 APP，去打磨这套纯对话式的原生购物体验。经过完整试点之后，团队看到了边界：对话模式擅长处理复杂的选品咨询，但并不适配全部购物场景。&lt;/p&gt;
+&lt;p&gt;即便是在 AI 对话窗口内，用户聊完需求，最后依旧会追问，「这个能不能再便宜一点？今天有没有优惠？」陈屿说，这些问题，其实在京东原来的首页里，早就解决了。&lt;/p&gt;
+&lt;p&gt;还有耐心问题。纯对话式购物，你得打字，系统理解，给你推荐，你说不对，再调整、推荐。这个来回消耗的不只是 token，还有用户的时间和信任。买个东西，不是在谈判，人是会烦的。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/42/bd/42bd0921ee35cfdefc48d38b70e87f0b.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：京东&lt;/p&gt;
+&lt;p&gt;于是陈屿面临了一个真正的岔路口。&lt;/p&gt;
+&lt;p&gt;一边是行业里最热的方向，所有人都在冲，不跟上显得落伍；另一边是回到用户本身，找寻真正更好的体验。&lt;/p&gt;
+&lt;p&gt;他们选了后者。他们不是抛弃 AI 助手，而是把 AI「长进」京东原有的购物流程里。搜索里加意图增强，推荐里融入时间‑场景‑用户多维度信息，购物车顶部悄悄加一个「场景提示词」入口。买了钢琴，系统轻声提醒你：节拍器要不要一起？买了投影仪，那些你根本不知道怎么选的参数（激光、原色、幕布），系统帮你变成可以直接点选的选项。&lt;/p&gt;
+&lt;p&gt;陈屿打了个比方：「就像超市里的导购。你买东西，旁边有人轻声说，你买这个，旁边那个货架上有个配件，用起来会更好。」&lt;/p&gt;
+&lt;p&gt;这条路，比做一个独立 AI 助手要难得多。你要在一个已经成熟运转的超级 APP 里，在不打扰用户原有习惯的前提下，把新的东西悄悄嵌进去。就像在一栋住满了人的楼里重新装修，不能断水断电，还要让住户觉得越住越舒服。&lt;/p&gt;
+&lt;p&gt;如果说陈屿的战场是屏幕，林澈的战场就是真实世界的仓库。他是京东物流仓储具身算法开发负责人。&lt;/p&gt;
+&lt;p&gt;2026 年初，科技圈每天都在被炫酷的机器人 Demo 刷屏。今天是打拳击比赛的人形机器人，明天是能叠衣服的灵巧手&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8b/0f/8b0fcbd67d2e670184bf7943fbece00f.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：京东&lt;/p&gt;
+&lt;p&gt;但林澈已经在想另一个问题了：这些机器人，进了真实的仓库，面对满地的杂物遮挡、人员走动，它还能用吗？能给用户带来什么更好的体验吗？&lt;/p&gt;
+&lt;p&gt;他更关心的不是 Demo 好不好看，而是每小时能拣多少件、准确率是否足够、能覆盖多少 SKU、能否稳定运行，以及能不能和一线员工安全协同。&lt;/p&gt;
+&lt;p&gt;他的日常不是坐在工位前调参，而是跟着机器人，在真实的仓库里一待就是一整天。&lt;/p&gt;
+&lt;p&gt;京东的仓库里有十几万种 SKU。同一个储位，上午和下午的摆放可能完全不同。前一件商品被拣走，后面商品的遮挡关系就变了。机器人停靠位置稍有偏差，它看到的画面和</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 12:42:23 +0800</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>追觅四大赛道 IFA 首秀：一套技术，四个出口</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370506</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr"/>
+      <c r="F428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/0d/c7/0dc70b7390eb33c3f16ab94929fe74b0.jpeg" style="display: block; width: 661.001px !important; vertical-align: bottom; margin: 0px; background-color: transparent; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;追觅在 IFA 上展出的不是四条产品线，是一套技术的四个出口。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;去年一年，全球扫地机器人的出货量约 2412 万台。同一年，全球人形机器人的出货量约 1.8 万台。两个数字都来自 IDC，中间差了 1300 多倍。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;带着这两个数字走进今年柏林的 IFA 主会场，这种体感上的反差就更明显了。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;IFA 官方今年搭了迄今最大规模的人形机器人展示平台，主题是「未来已来」，机器人走秀也排进了每天的日程。转到清洁电器区，几家中国清洁品牌的展台上，扫地机器人长出了手和腿：有会爬楼梯的，有伸出机械臂往墙角边缘的。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;追觅的展台是这个领域中把这件事做得最极致的选手之一：从带机械臂的割草机、能自己跟着人走的高尔夫球包车，到一副外骨骼、一台正在叠衣服的工业机器人，还</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 17 Sep 2026 05:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>Iceland-based Treble raises $18 million for its voice simulation platform</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/16/iceland-based-treble-raises-18-million-for-its-voice-simulation-platform/</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr"/>
+      <c r="F429" s="2" t="inlineStr"/>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Treble's voice simulation platform is used by voice AI model developers and AI wearable and robotics companies,</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18120,6 +18120,383 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 06:55:04 +0000</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>君华股份×鹿明机器人: 人形机器人PEEK材料及关节模组战略合作</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13067</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr"/>
+      <c r="F430" s="2" t="inlineStr"/>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>9月18日，君华股份与鹿明机器人正式签署人形机器人 PEEK 材料及关节模组战略合作协议。</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 06:51:17 +0000</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>全球首个规模化量产商用落地——远征A3 Ultra“上岗”实录</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13056</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr"/>
+      <c r="F431" s="2" t="inlineStr"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>智元远征A3 Ultra商用实景曝光：从4S店到酒店，人形机器人开始“上岗”</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 01:44:54 +0000</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人穿衣服，一门正在起量的生意</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13027</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr"/>
+      <c r="F432" s="2" t="inlineStr"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>纺织工艺解决x26quot;贴身适配x26quot;，传感技术解决x26quot;智能感知x26quot;</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Two Birotors Make a Quadrotor</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-quadrotor-from-birotor</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr"/>
+      <c r="F433" s="2" t="inlineStr"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>让 Agent 越用越强：AReaL 2.0 构建 Agent 在线强化学习闭环｜QCon上海</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/x2FmIeCkeDYUV66BNj3g?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr"/>
+      <c r="F434" s="2" t="inlineStr"/>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/x2FmIeCkeDYUV66BNj3g?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 13:16:33 +0000</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>具身智能技术路线尚未定型，基础设施却先收敛</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/492238.html</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr"/>
+      <c r="F435" s="2" t="inlineStr"/>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>从一次成功到一万次稳定执行，具身智能还缺什么？</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 00:37:13 +0000</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>Manus重生第17天，估值居然就翻倍了</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/491764.html</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr"/>
+      <c r="F436" s="2" t="inlineStr"/>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>作价40亿美元推进新融资</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 22:07:09 +0800</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>AI 硬件创业者，疯狂涌入手机的背面</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370610</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr"/>
+      <c r="F437" s="2" t="inlineStr"/>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;头图来源：产品小红书账号、官网&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;过去一年，AI 硬件创业者开始扎堆手机背面。&lt;/p&gt;
+&lt;p&gt;Plaud 的 AI 录音卡累计出货突破百万台。2026 年 6 月，Plaud 宣布 ARR 达到 1 亿美元、服务超过 200 万专业用户；截至 9 月，公司最新披露的全球用户数已超过 250 万。另一边，做磁吸电子纸屏的阅星曈完成近 5000 万元 A 轮追加融资，顺为、经纬、博裕和小红书等老股东继续跟投；极稚科技则称，其无源墨水屏手机壳已经卖出超过 14 万只，其中八成销往海外。&lt;/p&gt;
+&lt;p&gt;销量和融资之外，新的产品还在不断冒出来。Flowtica 在 IFA 展出集录音、电子纸和会议待办于一体的 Verso；获得线性资本天使投资的 NOOKLAB，准备推出支持持续收音的 AI 随身屏 Moonphase Flip；极稚科技也计划用 Sloth 从静态墨水屏进入 OLED、麦克风和虚拟宠物。&lt;/p&gt;
+&lt;p&gt;大厂的动作更快。钉钉、出门问问、科大讯飞和 360 相继进入 AI 录音卡市场；荣耀、海信和影石，则分别从磁吸副屏、可拆卸电子纸和影像配件的方向试探手机背面的可能性。与此同时，华强北已经把基础录音卡的价格压到一两百元。&lt;/p&gt;
+&lt;p&gt;一个原本以手机壳、卡包和充电宝为主的配件位置，突然挤进了录音公司、电子纸创业者、消费电子团队、互联网大厂和手机厂商。它们给出的答案并不相同：有人想把它做成录音工具，有人放上一块低干扰屏幕，有人想做虚拟宠物，也有人试图把录音、显示和 Agent 全部装进去。&lt;/p&gt;
+&lt;p&gt;这些公司争夺的不只是一个新品类，更是手机上所剩不多的高频携带位置。一部手机的背面很难同时挂着录音卡、阅读屏、充电宝和 AI 宠物。当越来越多产品要求用户把自己长期留在这里，它们之间就不再只是功能差异，而会形成直接的产品和战略竞争。&lt;/p&gt;
+&lt;p&gt;这也是手机背面今天值得被重新关注的原因。&lt;/p&gt;
+&lt;p&gt;MagSafe 早已让用户习惯把配件吸在手机背后，但这一轮变化，是 AI 硬件开始借助这个成熟位置寻找自己的入口。Plaud 率先证明，独立 AI 工具可以在这里获得百万台规模和持续付费；屏幕产品的增长和融资，则让另一种可能浮现出来：手机背面或许不只负责采集信息，也可以成为 AI 向用户返回结果的第二界面。&lt;/p&gt;
+&lt;p&gt;一场围绕几厘米空间的竞争，已经从配件生意进入 AI 硬件创业的中心。&lt;/p&gt;
+&lt;h1&gt;一、手机背面的「隐藏金矿」&lt;/h1&gt;
+&lt;p&gt;较早让市场意识到手机背面可以成为 AI 硬件入口的，是一张录音卡。&lt;/p&gt;
+&lt;p&gt;2023 年 6 月，深圳团队 Plaud 推出 Note：厚约 3 毫米、重 30 克，通过 MagSafe 吸在手机背后，按下按键即可录音，会议结束后在手机 App 里查看 AI 转写和摘要。它没有发明录音，也没有发明 AI 转写&amp;mdash;&amp;mdash; 讯飞这些公司已经做了很多年。它做对的事情是位置选择：把一个独立硬件寄生在手机上，用户不需要多带一个东西，不需要在开会前想起从包里翻出录音笔。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/96/29/9629ea19bc24f815142a0db19fc07bae.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：Plaud 淘宝&lt;/p&gt;
+&lt;p&gt;这个选择缓解了独立 AI 硬件普遍面对的一道难题：如何让用户每天带着它。&lt;/p&gt;
+&lt;p&gt;Plaud 的增长速度超出了大多数人的预期。&lt;/p&gt;
+&lt;p&gt;产品连续两年保持约十倍增长。6 月，Plaud 宣布其软件订阅业务的年度经常性收入（ARR）从 100 万美元增长到 1 亿美元（两年约 100 倍），设备出货量突破 200 万台&amp;mdash;&amp;mdash; 在达成这一里程碑的 AI 公司中，它是少有的以硬件为入口的公司，其余几乎都是纯软件。&lt;/p&gt;
+&lt;p&gt;Plaud 的成功引来了快速的模仿和围猎。2025 年以来，钉钉推出 DingTalk A1 录音卡（499 元起），出门问问发布 TicNote（999 元起），360、科大讯飞相继跟进，华强北白牌则把同类产品的价格打到 120 至 150 元。纯录音 + 转写的功能差异，在一年之内被压缩到几乎为零。&lt;/p&gt;
+&lt;p&gt;但 Plaud 真正验证的不只是「有人愿意为 AI 录音付费」，更是手机背面这个位置本身有价值：独立 AI 产品可以借助手机背面既有的磁吸位置，获得高频携带，并进一步建立付费需求。原本以防护、充电和装饰为主的配件位</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 17:36:47 +0800</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>那个教 ChatGPT 说话的人，做了一个「哑巴」模型</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370603</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr"/>
+      <c r="F438" s="2" t="inlineStr"/>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜桦林舞王&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;AI 圈子里最懂怎么让模型「开口聊天」的人，现在决定剥夺大模型的语言能力。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这位前 OpenAI 研究员、ChatGPT 的共同发明者 Diogo Almeida，在潜行两年后带着他的新公司 TypeSafe AI 和 4000 万美元融资回到牌桌。他们发布的全新模型 Jev， &lt;span style="font-weight: bold;"&gt;既不能写打工人的周报，也不能陪用户深夜长聊。它甚至连一个标点符号都吐不出来 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="548" src="https://imgslim.geekpark.net/uploads/image/file/aa/fe/aafe939703a9a9e41b331520e99c3a33.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;TypeSafe 创始人 Diogo Almeida｜图片来源：X&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这是一个反常识的时刻。过去三年，全行业都在教大模型怎么学会像人类一样「慢思考」，各家实验室拼命拉长推理链条，让模型在给出答案前默默自言自语几千个词。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但 Jev 走了一条完全相反的路： &lt;span style="font-weight: bold;"&gt;它不做文本生成，只输出确定性的结构化决策。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这不仅是一个新产品的发布，更像是对当前大模型技术范式的一次公然叫板。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;给 AI 装上「反射神经」&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;要理解 Jev 到底是个什么东西，得先看懂当下的 AI 开发者有多痛苦。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;如今大部分工程师把大模型接入业务系统时，做的事情往往很荒谬。你明明只需要它回答「这封邮件是不是垃圾邮件」或者「在五个 API 接口里选一个」，但你不得不让一个拥有上千亿参数的庞然大物，在漫长的几秒钟里，一个词一个词地把一串 JSON 字符敲出来。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;为了保证这串字符符合代码规范，开发者得写满整整两页提示词，求着模型「不要输出任何废话，只要纯 JSON 格式」。即便如此，模型偶尔还是会在前后加上一句「好的，这是你要的格式」，瞬间搞崩下游的整条流水线。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Jev 解决问题的方式极其粗暴。 &lt;span style="font-weight: bold;"&gt;它根本就不是一个文本自回归模型 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="608" src="https://imgslim.geekpark.net/uploads/image/file/42/eb/42ebc62047c0e170a669c41ef1949086.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;速度对比，3 秒时间 Jev 这边已经腹泻版吐出 Token（左）｜图片来源：TypeSafe&lt;/</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 18 Sep 2026 20:18:14 +0000</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>World model companies are keeping a lot of secrets</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/18/world-model-companies-are-keeping-a-lot-of-secrets/</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr"/>
+      <c r="F439" s="2" t="inlineStr"/>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Everyone in the world-models space is sitting on a pile of cash and a ton of buzz, but good luck getting anyone — from the founders to their own data suppliers — to tell you what they're actually building.</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18497,6 +18497,116 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 08:36:42 +0800</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>Meta 个人助手登顶美国 App Store；张雪机车发 5 款新车，最贵 13.8 万；淘宝闪购「制服」获法国设计最高奖，马云深度参与</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370615</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr"/>
+      <c r="F440" s="2" t="inlineStr"/>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a5/37/a53798f6b0e1e6993951ea0b91e042e1.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;传 Anthropic 计划在 IPO 前夕推出新一代 AI 模型助力资本市场信心&lt;/h1&gt;
+&lt;p&gt;据路透社援引多名知情人士消息透露，全球顶尖人工智能初创企业 Anthropic 正考虑在公开首次募股（IPO）之前，正式发布其最新的旗舰级人工智能模型。这一战略举措旨在进一步巩固其在生成式 AI 领域的市场领先地位，同时在关键的资本市场亮相节点前，向潜在投资者展示其强劲的技术迭代能力与商业化前景。&lt;/p&gt;
+&lt;p&gt;知情人士指出，作为 OpenAI 的强劲对手以及 Claude 系列大模型的开发商，Anthropic 目前正在对这款新模型进行最后的内部测试与性能调优。尽管具体的发布时间表与模型技术细节仍存在根据市场反馈调整的可能，但公司内部高层倾向于在提交 IPO 申请或启动路演前的关键窗口期将该模型推向市场，以塑造更为有利的估值环境。（来源：cnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d0/6f/d06f46221c56ab44c9424dd002dc0b6f.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;Meta 个人 AI 助手 Muse 击败 ChatGPT 登顶美国 App Store&lt;/h1&gt;
+&lt;p&gt;Meta 推出的个人 AI 代理应用 Muse 正在迅速成为人工智能市场的新焦点。上线仅一周时间，这款产品便登上苹果美国 App Store 免费应用排行榜第一位，超越长期占据领先地位的 ChatGPT，成为当前美国市场下载量最高的免费应用之一。&lt;/p&gt;
+&lt;p&gt;这一成绩被视为 Meta「个人超级智能」战略获得市场认可的重要信号。与传统聊天机器人主要负责回答问题不同，Muse 被设计成能够代表用户执行实际任务的人工智能代理。&lt;/p&gt;
+&lt;p&gt;根据 Meta 介绍，Muse 不仅能够完成信息查询，还能够帮助用户填写表格、在线购物、预订餐厅、寻找宠物照看服务，并与邮箱、日历、Spotify、Instagram 以及 OpenTable 等服务进行连接。系统会逐步学习用户偏好，在获得授权后代替用户处理各种事务。（来源：cnBeta）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;谷歌 AI 首次「越狱」：Gemini 在测试中入侵三家企业&lt;/h1&gt;
+&lt;p&gt;谷歌的 Gemini 模型在一次网络安全能力测试中访问了互联网并入侵了其他公司，这是该公司人工智能系统自主实施此类行为的首个已知案例。&lt;/p&gt;
+&lt;p&gt;谷歌周五证实，这些黑客行为发生在 5 月，是 Irregular 公司进行的一次测试的一部分。Irregular 也曾参与 OpenAI、Anthropic 和 Meta 披露的类似事件。&lt;/p&gt;
+&lt;p&gt;在其中一起案例中，该模型不断猜测密码，直到获得对一个受保护系统的访问权限。在另外两起案例中，该模型在公共代码库中找到了凭证，从而得以访问受保护的系统。谷歌表示，在每起案例中，模型在确定自己访问的是真实公司的系统后，都终止了入侵。&lt;/p&gt;
+&lt;p&gt;谷歌和 Irregular 表示，Irregular 在 7 月底将黑客行为通知了谷歌，当时正值 OpenAI 的智能体入侵 AI 软件公司 Hugging Face 的事件被曝光之后。谷歌直到媒体本周就此询问时才披露这些黑客行为。（来源：环球市场播报）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;AI 太烧钱：报道称 OpenAI 未来 5 年自由现金流为负 2780 亿美元&lt;/h1&gt;
+&lt;p&gt;9 月 19 日消息，金融时报（FT）近日发布博文，称获得一份演示文稿，显示 OpenAI 公司预计 2026 年至 2030 年累计产生 2,780 亿美元（约合 1.87 万亿元人民币）负自由现金流，此外计划在算力和基础设施上投入约 8,560 亿美元（约合 5.75 万亿元人民币）。&lt;/p&gt;
+&lt;p&gt;自由现金流（Free Cash Flow）是企业在支付经营成本、资本支出及必要投资后，可自由用于偿债、分红、回购或继续投资的现金余额。&lt;/p&gt;
+&lt;p&gt;自由现金流为负，通常表示企业当期经营与投资活动消耗的现金高于产生的现金，需依赖现有现金、融资或资产处置补充资金。&lt;/p&gt;
+&lt;p&gt;根据该演示文稿，OpenAI 公司的支出将远远超过收入，存在较大的资金缺口，在未来 5 年需要通过融资不断「烧</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 19 Sep 2026 12:10:23 +0800</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>对拿下一轮投资最有效的沟通，是「思想履约」</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370611</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr"/>
+      <c r="F441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;最近有个创业者找我交流的时候，聊到团队接下来还要做进一步的融资，很认真地问了我一个问题：这次做对外传播也是希望能对融资有帮助，你有什么建议？&lt;/p&gt;
+&lt;p&gt;我当时听完，先跟他说了两个目睹了好几代创业者后的观察：&lt;/p&gt;
+&lt;p&gt;首先，咱要个心理预期：绝大部分情况下，第一笔投资是你最好拿的那笔钱。&lt;/p&gt;
+&lt;p&gt;第二，凡是能被公关轻易影响的投资人，大概率都不是对你未来最至关重要的投资人。&lt;/p&gt;
+&lt;p&gt;真正愿意笃定你，给你出大钱的机构，以及真正愿意押上青春和自身能力的顶级人才，从来都不是被 PR 搞定的。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;看过那么多创业者的历程后，我发现那些优秀&lt;/strong&gt;&lt;strong&gt;投资人&lt;/strong&gt;&lt;strong&gt;要被打动，&lt;/strong&gt;&lt;strong&gt;底层&lt;/strong&gt;&lt;strong&gt;其实&lt;/strong&gt;&lt;strong&gt;有个「A-B-C 连线」的方法论&lt;/strong&gt;。然后我就给他讲了当年王兴的故事。&lt;/p&gt;
+&lt;p&gt;回到当年千团大战最热的时候，所有对手都在疯狂投站台广告、发补贴、烧钱抢地盘，甚至当时的「领头羊」拉手网都自信到倒排出了上市日期。王兴却说：「团购投广告和烧钱这事算不过账，商业模式跑不通，不能这么花。」&lt;/p&gt;
+&lt;p&gt;那时候整个行业包括他公司内部都是一片质疑：你不烧钱，别人一统江湖了，你账上留着钱有什么用？大家都觉得美团在这场竞争中悬了。&lt;/p&gt;
+&lt;p&gt;后来王兴甚至为了证明公司不是没钱烧，被逼得发布会上直接亮出了银行流水单&amp;mdash;&amp;mdash;账上确实趴着 7000 万，证明他真不是没钱，是真的不烧。&lt;/p&gt;
+&lt;p&gt;结果拉手网倒在上市前三个月，原因很简单，因为算不过账，商业模式跑不通。最后是美团一统了团购的江湖。&lt;/p&gt;
+&lt;p&gt;在这个转折点发生之前，王兴说什么，外界都打着大大的问号，但在这个转折点发生之后，似乎全世界都服了&amp;mdash;&amp;mdash;大家发现，全世界都错了，王兴是对的。&lt;/p&gt;
+&lt;p&gt;王兴自此拿到了高维度的信任资产。&lt;/p&gt;
+&lt;p&gt;所以等美团面临外卖大战时，即便后来阿里进场力挺饿了么，王兴却换了一套和当年截然相反的逻辑：「今天要把钱给到最有效率的人去烧。比如我。」结果投资人认了，给钱让他直面阿里的炮火，结果他就是拿下了市场老大的地位。&lt;/p&gt;
+&lt;p&gt;所以为什么那时候投资人信他？这 100% 不是 PR 做得有多好，而是因为他此前积累下的那个「信用」，大家真的信他了。&lt;/p&gt;
+&lt;p&gt;讲完王兴的故事，我跟这位创业者拆解了下背后的逻辑：&lt;strong&gt;真正决定你能不能拿到深层信任的，不是单点的公关发声，而是你在时间轴上的「A-B-C 连线」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://geek.feishu.cn/space/api/box/stream/download/asynccode/?code=YTFhYTdjNjJkZjM0NzljNjAzYWEyZDQzNDQ2NWIzYjFfa2dVa3U5a3VXWVhBajJ3MDhkbWVIbWlGRFY3Q2lDMzdfVG9rZW46RVNuSGJOR2ZIb2o3UGh4UmZuN2NSdDk1bnVjXzE3ODk3OTA4Njc6MTc4OTc5NDQ2N19WNA&amp;amp;add_watermark=true&amp;amp;scene_type=CCM" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;A 点（历史决策）：&lt;/strong&gt;&amp;nbsp;你在充满不确定性、大家甚至看不懂的时候，下了什么注？为什么这么选？&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;B 点（客观结果）：&lt;/strong&gt;&amp;nbsp;经过一段时间的验证，你当初「吹过的牛」、算过的账，有没有拿到扎实的兑现？&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;C 点（未来判断）：&lt;/strong&gt;&amp;nbsp;站在今天，基于前面的逻辑，你下一步要带大家去哪儿？&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;没有 A 点的 B 点，&lt;/strong&gt;&lt;strong&gt;有可能会被看作&lt;/strong&gt;&lt;strong&gt;侥幸。&lt;/strong&gt;&amp;nbsp;你不提前把逻辑和下注讲清楚，就算拿到了结果，别人也会觉得你只是撞上了大运或行情托举。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;没有 B 点的 A 点，叫画饼。&lt;/strong&gt;&amp;nbsp;如果只有口号没有兑现，那 PR 往往不是助力，反而是给未来埋下的一颗「雷」。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;只有当 A 点跨越时间、扎扎实实落到了 B 点，这个闭环才叫「思想履约」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;你判断得对、兑现得好，一次、两次，别人就不用天天替你重算一遍账了。这就好比我们今天用 AI 写代码，为什么用到最后你连生成的代</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18607,6 +18607,343 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 17:42:31 GMT</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>硅基流动完成B+轮二期及C轮融资，年内累计融资近29亿元</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/oP7tDkoaamphFBkDY8uW?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr"/>
+      <c r="F442" s="2" t="inlineStr"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/oP7tDkoaamphFBkDY8uW?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 09:01:53 +0800</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>卢伟冰谈小米18 Pro涨价：大家会觉得合理；剪映发布 Hub 及 AI 助手「小映」；苹果或 10 月推出智能家居设备｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370681</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr"/>
+      <c r="F443" s="2" t="inlineStr"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/43/79/43795199422e56c10e0d062910c89e68.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;B 站上线 AI 无限竞技场测评榜：GPT-6 Astra 现居榜首&lt;/h2&gt;
+&lt;p&gt;9 月 20 日，B 站宣布上线「AI 无限竞技场」大模型测评榜，并同步公布了首轮模型排行榜。据 B 站介绍，「AI 无限竞技场」是一个汇集了 B 站 UP 主 AI 大模型测评的竞技广场，由各领域 UP 主对上百个大模型的真实场景实测构成，涵盖代码、推理、协作、知识等多种测评主题。&lt;/p&gt;
+&lt;p&gt;其中 GPT-6 Astra 在 10 个 UP 主测评中拿下榜首，打败 GLM-5.3 获得榜首次数冠军；前 5 名中，国产大模型占据 3 席。&lt;/p&gt;
+&lt;p&gt;不同于传统跑分评测，B 站 AI 无限竞技场不设主题或测评维度限制，来自各个分区的 UP 主们以真实工作流、专业应用、趣味脑洞等自主命题，在同题 PK 中直观呈现各模型的实际表现差异。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3d/8f/3d8f72b109e785aca9f698560b366248.jpeg" /&gt;&lt;/p&gt;
+&lt;p&gt;榜单涵盖 DeepSeek、Kimi、ChatGPT、Claude、Gemini、豆包、千问、Hy、MiniMax 等主流模型对比测评，排名实时更新，持续面向全站 UP 主开放报名。（来源：ITBears）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b3/94/b394d4035ad59aa241fd7a6907d240d2.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;iPhone 18 Pro 上市首日出现死机问题，苹果回应正调查&lt;/h2&gt;
+&lt;p&gt;9 月 20 日，据 CNMO 科技从韩媒获悉，苹果新款手机 iPhone 18 Pro 系列被曝出现设备突然关机后自动重启的「Panic Full」现象，反映相关问题的用户接连不断。&lt;/p&gt;
+&lt;p&gt;据业内人士 9 月 20 日透露，在拥有约 241 万会员的 iPhone 用户社区「阿沙莫」中，接连出现 iPhone 18 Pro 和 iPhone 18 Pro Max 遭遇 Panic Full 现象的帖子。Panic Full 现象是指iPhone设备停止响应后自动关机并意外重新开机的现象。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/74/61/746134172be6f01b2568d2bd64477850.png" /&gt;&lt;/p&gt;
+&lt;p&gt;一名用户称，在进入需要 Face ID 认证的银行应用或照片应用「最近删除」项目后，反复使 Face ID 识别失败，即可重现设备关机现象。该用户表示，用手遮住 Face ID 传感器部分尝试认证，反复进行放手再遮挡的操作后，屏幕出现「请重试」提示，随后设备即自动重启。该用户称经多次测试，同一现象反复出现。&lt;/p&gt;
+&lt;p&gt;科技 YouTube 频道「ZUYONI」也表示，在收到 iPhone 18 Pro 用户举报后检查了正在使用的产品，确认发生了 Panic Full。该频道称，日常使用中尚未遇到，但在特定情况下 iPhone 会出现重启现象，在相册回收站查看或金融应用 Face ID 识别失败后立即重试再次失败时，Panic Full 便会发生并导致关机。（来源：CNMO）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;Anthropic 计划将 IPO 推迟至 11 月，上市估值约 2 万亿美元&lt;/h2&gt;
+&lt;p&gt;9 月 20 日，据《华尔街日报》报道，Anthropic 计划将首次公开募股（IPO）推迟至 11 月进行，晚于许多投资者此前预期的 10 月。&lt;/p&gt;
+&lt;p&gt;知情人士透露，部分 Anthropic 顾问认为，推迟至 11 月可以让公司有时间展示第三季度财务数据，以证明其竞争地位。知情人士表示，将 IPO 目标定在 11 月的决定是在 Anthropic 前研究员发出公开警告、引发关于 AI 发展速度是否过快辩论之前作出的。这一时间安排仍可能发生变化。&lt;/p&gt;
+&lt;</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 15:27:15 +0800</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>三体还没降临，是因为叶文洁没用上千问办公吗？</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370667</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr"/>
+      <c r="F444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;天文观测，或许大概是最容易让普通人产生浪漫想象的一类科学。&lt;/p&gt;
+&lt;p&gt;巨大的穹顶缓缓打开，镜筒转向几亿光年之外，一束用从宇宙深处赶来的微光落到探测器上。然后告诉人类，这里几百万年曾经出现过超新星、伽马暴、中子星合并&amp;hellip;&amp;hellip;研究的问题也从微观的重元素从何而来，覆盖到恒星如何死亡、极端物理条件下会发生什么。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/00/d6/00d6d4b0eedcad7fb033416c9def984a.png" /&gt;&lt;/p&gt;
+&lt;p&gt;但这些工作落到具体的天文望远镜使用时，日常却会变得琐碎而辛苦。&lt;/p&gt;
+&lt;p&gt;冬天夜长，国家天文台兴隆观测基地一次值班经常要持续十几个小时。值班人员需要彻夜守着望远镜和控制软件，盯目标位置、天气和设备状态，调参数，排任务。地球在转，目标也在不断改变位置；云层、湿度、风速、月光都会影响观测；机械、网络和供电也可能出现变动。&lt;/p&gt;
+&lt;p&gt;只是按照既定计划观测一晚，就已经够繁琐。但对瞬变观测来说，麻烦还远不止是夜班长。&lt;/p&gt;
+&lt;p&gt;超新星、伽马暴这类事件无法提前推算。尤其是超新星爆发后的早期阶段，亮度和光谱会快速变化，一些特征可能过了几个小时或者几天就不再出现。科研团队发现得越早、跟得越快，能够留下的观测数据也越完整。&lt;/p&gt;
+&lt;p&gt;中国科学院国家天文台高级工程师，兴隆观测基地天文组负责人郑捷把这种情况形容成「天上掉馅饼」。&lt;/p&gt;
+&lt;p&gt;首先能「看到馅饼掉下来」，就是非常复杂的第一步。&lt;/p&gt;
+&lt;p&gt;瞬变就意味着有一些原定观测任务需要被打乱排班。如果今晚已经排了三个科学任务，突然，一颗疑似极早期超新星突然出现在预警系统里，那这个目标到底重不重要，它现在是否处于可观测区域，天气是否允许，哪台望远镜有条件接手；原来的任务已经排满，又该挪掉哪一个&amp;hellip;&amp;hellip;这些繁琐的任务，全都需要在极短时间里完成重新判断。然后逐级协调排程与设备调用。&lt;/p&gt;
+&lt;p&gt;于是，今年国家天文台科研团队在千问办公协助下做了一次新的尝试。&lt;/p&gt;
+&lt;p&gt;基于千问办公的 Agent Harness，团队用不到 3 天、千元左右的成本搭出了一套科研级望远镜仿真环境。望远镜组件和传感器接口被包装成 MCP，Agent 可以读取设备状态和可观测条件，随后，相关 Agent 框架又接入了「司天」探路者和「司天」原型机。&lt;/p&gt;
+&lt;p&gt;一种新的瞬变观测范式，在 AI 的驱动下，逐渐走向成熟。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;自动望远镜已经发展了几十年，&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;为什么还需要 Agent？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;望远镜自动化并不是大模型时代才出现的技术。&lt;/p&gt;
+&lt;p&gt;简单来说，我们可以将它分成三个阶段：&lt;strong&gt;发现异常、分析异常和资源调度。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这其中，最成熟的是资源调度。今天的 Las Cumbres Observatory 已经把分布在全球 7 个站点的 27 台机器人望远镜当作一个整体运行。科研人员提交观测请求，中央调度系统根据目标可见性、天气、设备和时间窗口安排任务；一个站点天气变差之后，任务还可以被重新分配到其他站点。整个网络的计划每小时会被重新计算多次。&lt;/p&gt;
+&lt;p&gt;关于发现异常，目前行业也产生了一批颇具代表性的探索。比如 2026 年 2 月 24 日，Vera C. Rubin Observatory 在一个晚上发出了约 80 万条科学告警。随着系统全面运行，这个数字预计最高达到每夜 700 万条；一次天空变化被发现后，公开告警可以在约两分钟内发出。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;候选数量可以随着巡天能力迅速增长，适合做后随观测的望远镜时间却始终有限。&lt;/strong&gt;于是，一个新的问题出现了：这些海量异常到底值不值得跟踪，选哪一个跟踪，在有限时间里用哪台设备跟踪，判断的代价并没有同步下降。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6f/13/6f1333c910d10c0b645da8225efa2c2f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;为了解决这</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 15:15:14 +0800</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>机器人如何自进化，乐享科技走了一条新路</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370665</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr"/>
+      <c r="F445" s="2" t="inlineStr"/>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;strong&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;最近，乐享科技因为一个颇大胆的 claim，引发了不少关注：它提出，其具身智能模型以太大模型能够在部署和执行过程中持续更新，并将这种能力概括为「自进化」，是全球首个能自进化的具身智能模型。&lt;/p&gt;
+&lt;section&gt;自进化是一个容易引起争议的说法。「进化」究竟是模型参数发生了变化，还是进行了任务的临时调整？在多大程度上这样的调整能够变成可迁移的新能力？一个模型能够适配不同场景和不同身体，又应该被理解为工程层面的泛化，还是更强意义上的持续成长？在机器人行业仍然需要解决稳定执行问题的阶段，「自进化」显然是一个需要被谨慎对待的判断。&lt;/section&gt;
+&lt;p&gt;近日，乐享科技又进行了一场户外直播。按照直播前公布的目标，搭载 Aether 以太大模型的机器人要在户外接受随机点单，完成包括食材和工具处理、烤制、翻面、上菜在内的烧烤任务，并应对临时打断、需求临时增加和场景变化。&lt;/p&gt;
+&lt;p&gt;在现场超 30 位专业媒体和线上超 550 万观众的见证下，实际呈现的过程并非每一步都顺利。&lt;/p&gt;
+&lt;p&gt;机器人完成了部分自主烧烤操作，也出现了停顿、失败和重新调整。乐享科技似乎并不回避这些不完美：它想展示的重点，不是机器人在一个固定流程里零失误地把烧烤做完，而是任务和环境发生变化之后，机器人能否继续寻找信息、调整动作，再把任务推进下去。两个机器人本体全程互相传递任务信息、自主思考决策并合理分工协作。&lt;/p&gt;
+&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/85/ee/85ee4f1d1825ca3252671c9912d9a068.jpg" /&gt;
+&lt;p&gt;一场直播当然不能回答关于「自进化」的所有问题，但这种展示方式至少体现出一种相对开放的态度：机器人可以失败，真正需要观察的是失败之后会发生什么。&lt;/p&gt;
+&lt;p&gt;对机器人来说，「自进化」不能只是一个好听的词。它至少要回答三个问题：第一，机器人能不能发现现实和自己预测之间的偏差；第二，它能不能判断哪些经验值得留下、哪些应该忘掉；第三，它能不能把一次任务、一个场景和一具身体上的经验，迁移到新的任务、场景和身体上。&lt;/p&gt;
+&lt;p&gt;当数字世界的 AI 开始讨论自进化，物理世界的 AI 有没有自进化，或许是下一个时代最重要的问题。&lt;/p&gt;
+&lt;p&gt;为此，我们和乐享科技背后的团队聊了聊他们的模型思路。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;em&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;不是更会模仿，&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;而是能不能理解真实世界&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;过去几年，具身智能最常见的思路，是把视觉、语言和动作连接起来：机器人看到环境，接收任务，再输出动作。这条路线的价值很直接，它让机器人可以借助大规模数据学习人的示范，也让复杂指令开始有机会落到具体行动上。&lt;/p&gt;
+&lt;p&gt;但在乐享科技团队看来，这种从输入到动作的映射仍然存在一个根本限制：它擅长回答「下一步应该做什么」，却未必真正理解「为什么要这样做」，以及这个动作会给真实世界带来什么后果。&lt;/p&gt;
+&lt;p&gt;团队将 VLA 的局限概括为「不懂因果」，将传统 world model 的问题概括为「可生成、不可执行」。按照这一判断，前者更接近从已有数据中学习动作规律，但这并不自然等于理解动作与结果之间的因果关系；后者可以预测世界可能如何变化，却不代表预测出的未来一定能够被机器人的关节、力矩和控制系统实现。&lt;/p&gt;
+&lt;section&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/bb/85/bb855f845b1e0626274ba8e167238710.png" /&gt;&lt;/section&gt;
+&lt;p&gt;真实世界恰恰不是一组干净的输入输出。接触力、摩擦、滑动、遮挡、物</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 15:08:22 +0800</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>不可逆的人类衰老，快被 AI 破解了</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370664</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr"/>
+      <c r="F446" s="2" t="inlineStr"/>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;strong&gt;作者｜Li Yuan&lt;/strong&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;编辑｜&lt;strong&gt;郑玄&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;2026 年 9 月，42 个平均 67 岁的人，在六只不同的时钟上同时变年轻了。&lt;/p&gt;
+&lt;p&gt;这些时钟不在墙上，而在他们的血液里。&lt;/p&gt;
+&lt;p&gt;服用一种名叫 rentosertib 的药物四周后，患者体内近 3000 种蛋白被检测，其中 326 种发生显著变化。六套由不同团队开发的模型都认为，他们的身体正在朝更年轻的方向移动。&lt;/p&gt;
+&lt;p&gt;多数时钟倒退了 3 到 4 年。其中一只，倒退了接近 6 年。&lt;/p&gt;
+&lt;p&gt;更不可思议的是，这款药是 AI 做出来的。&lt;/p&gt;
+&lt;p&gt;它来自英矽智能，一家已经登陆港交所、也是目前全球临床进展最快的 AI 制药公司之一。AI 帮助它从海量生物数据中找到靶点，再设计出能够作用于这个靶点的分子。如今，rentosertib 已经走到Ⅲ期临床。&lt;/p&gt;
+&lt;p&gt;极客公园采访了英矽智能创始人 Alex Zhavoronkov。他告诉我们，自己平均每六天就会发表一篇论文。&lt;/p&gt;
+&lt;p&gt;但说起这项研究，他没有掩饰自己的激动：「这是我一生中最重要的论文。」&lt;/p&gt;
+&lt;p&gt;在许多古老传说里，世界某处藏着一眼不老泉。&lt;/p&gt;
+&lt;p&gt;衰老的人只要喝下泉水，就能恢复青春，让时间重新在身体里向后流动。&lt;/p&gt;
+&lt;p&gt;几千年来，不同国家的人们都曾痴迷于寻找不老泉的力量。&lt;/p&gt;
+&lt;p&gt;不老泉当然从未被找到。&lt;/p&gt;
+&lt;p&gt;但这一次，我们在一场真实的人体试验里，第一次看见了它可能流过的痕迹。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;em&gt;&lt;strong&gt;01&lt;br /&gt;&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;strong&gt;&lt;strong&gt;血液里的年龄，被往回拨了六年&lt;br /&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;你今年几岁，是一个很容易回答的问题。&lt;/p&gt;
+&lt;p&gt;你的身体究竟几岁，不是。&lt;/p&gt;
+&lt;p&gt;两个同样 67 岁的人，一个可能每天跑步、工作、旅行；另一个已经同时患上肺病、糖尿病和心血管疾病。他们在日历上活过了同样长的时间，身体内部的时间，却走得完全不一样。&lt;/p&gt;
+&lt;p&gt;现代医学几乎可以测量人体的一切。&lt;/p&gt;
+&lt;p&gt;血糖有数字，肿瘤有影像，肺功能甚至可以精确到毫升。但直到今天，医生仍然没有一支温度计，可以插进人体，读出一个人究竟「老到了什么程度」。&lt;/p&gt;
+&lt;p&gt;这也是抗衰老药一直很难被证明的原因，等待人们吃下抗衰老药过半个世纪确认疗效很难。&lt;/p&gt;
+&lt;p&gt;20 世纪 50 年代，科学家开始正式讨论「生物年龄」：身份证上的数字只代表一个人出生了多久，身体里的年龄，应该反映他距离衰弱、疾病和死亡还有多远。&lt;/p&gt;
+&lt;p&gt;但这个年龄要怎么测，随后困扰了研究者几十年。&lt;/p&gt;
+&lt;p&gt;真正的转折发生在 2013 年前后。UCLA 教授 Steve Horvath 发现，只要观察 DNA 上数百个会随年龄变化的化学标记，就能相当准确地推算出一个人的年龄。这套方法后来被称为「表观遗传时钟」。&lt;/p&gt;
+&lt;p&gt;这些时钟不看生日，而是看时间经过身体后留下的东西。&lt;/p&gt;
+&lt;p&gt;DNA 上的微小标记、血液里的代谢物，以及成千上万种蛋白，都会随着年龄发生变化。把足够多人的数据交给 AI，它就能从一管血里猜出：这个人的身体，更像 50 岁，还是 70 岁。&lt;/p&gt;
+&lt;p&gt;过去，衰老时钟主要负责报时。&lt;/p&gt;
+&lt;p&gt;9 月 8 日，英矽智能宣布，它们第一次在自己的一款药物试验里，看见六只时钟同时向后走了。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/31/dd/31dd9fcffd85dfd12ea1b24a</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 20 Sep 2026 20:29:07 +0000</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>World model companies are keeping a lot of secrets</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/20/world-model-companies-are-keeping-a-lot-of-secrets/</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr"/>
+      <c r="F447" s="2" t="inlineStr"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Everyone in the world-models space is sitting on a pile of cash and a ton of buzz, but good luck getting anyone — from the founders to their own data suppliers — to tell you what they're actually building.</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H447"/>
+  <dimension ref="A1:H459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18944,6 +18944,502 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 08:14:20 +0000</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>徐丹飞聊Ego、UMI、遥操数据：我想 behavior clone 一个人类</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13132</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr"/>
+      <c r="F448" s="2" t="inlineStr"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>徐丹飞：我想 behavior clone 一个人类x0dx0ax0dx0a本文整理自 WhynotTV Podcast 第5期</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 03:07:07 +0000</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>重磅｜中亿具身完成近亿元天使轮融资！产业资本扎堆押注，赋能具身智能新格局！</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13115</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr"/>
+      <c r="F449" s="2" t="inlineStr"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>引言 近日，中亿（深圳）具身科技有限公司（简称 “中亿具身”）重磅宣布完成近亿元天使轮融资，由多家产业资本联合 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 03:01:42 +0000</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>从数百万小时真实数据出发，京东云X优必选加速具身模型落地</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13102</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr"/>
+      <c r="F450" s="2" t="inlineStr"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>推动数据基础设施与具身模型形成更紧密的协同</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 18:23:23 GMT</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>70强项目观察之具身未来：机器人走进现实世界，关键不只是完成动作</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/EU5m831fwoFA6RdhcOlo?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr"/>
+      <c r="F451" s="2" t="inlineStr"/>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/EU5m831fwoFA6RdhcOlo?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 16:45:15 GMT</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>祥峰再次出手，超维动力获超 5 亿融资，我们拆解了这家公司的全栈路线</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/rIpDfDZXDoN9L7akct7e?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr"/>
+      <c r="F452" s="2" t="inlineStr"/>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/rIpDfDZXDoN9L7akct7e?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 14:36:42 GMT</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>开箱即上岗！璇玑动力首发Hypertron-SW01中型四足机器人</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/IhCGKqeVbMIbdhVLbavr?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr"/>
+      <c r="F453" s="2" t="inlineStr"/>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/IhCGKqeVbMIbdhVLbavr?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 06:22:37 +0000</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra开进机器人身体！清华联手无问芯穹等开源RPent</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/493218.html</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
+      <c r="F454" s="2" t="inlineStr"/>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>在物理世界真正干活的具身智能体</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 08:42:21 +0800</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>黄仁勋：AI 时代，企业应该尽可能多付薪酬；宇树科技发布 Dex5-S 灵巧手；OpenAI 新模型 24 天解决 100+ 世界级数学难题 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370768</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr"/>
+      <c r="F455" s="2" t="inlineStr"/>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3e/4b/3e4b3cf100df709edbfa4c760694ef6d.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;消息称华为 Mate 90 系列年度旗舰手机将在 9 月 29 日发布&lt;/h1&gt;
+&lt;p&gt;9 月 21 日消息，昨日早些时候，华为常务董事、产品投资评审委员会主任、终端 BG 董事长余承东刚刚宣布，智界 RX 及鸿蒙智行新品发布会定档 9 月 28 日 14:30 举行。&lt;/p&gt;
+&lt;p&gt;根据此前爆料，华为 Mate 90 系列手机也将在本月发布，但遗憾的是，今天华为并未官宣这款年度旗舰的发布会时间。但博主 @熠熠玩数码 透露，&lt;strong&gt;Mate 90 系列发布会将在 9 月 29 日 14:30 举行&lt;/strong&gt;。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c0/7f/c07f6210308df94f99db6600a24d9b2e.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/bd/13/bd132f62fb06b7548098d5725dfcba19.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;英伟达员工平均年薪 28.2 万美元，黄仁勋喊话企业「尽可能多付薪酬」&lt;/h1&gt;
+&lt;p&gt;英伟达 CEO 黄仁勋近日接受 CBS News 采访，再次就 AI 时代的利润分配问题公开表态。 他直言，企业不应「尽可能少地支付员工薪酬」，而应「尽可能多地支付」。此番言论正值全球 AI 基建热潮之中，芯片巨头与员工之间围绕利润分配的博弈日益成为行业焦点。&lt;/p&gt;
+&lt;p&gt;黄仁勋的底气来自英伟达自身的薪酬实践。 据报道，他亲自审查公司全部 42000 名员工的薪酬方案，并且在 100%的情况下都会增加公司在薪酬上的支出。他的逻辑很直接：「照顾好员工，其他一切自然会好起来。」从数据看，英伟达 2026 财年员工平均收入达 28.205 万美元（约合人民币 189 万元），而黄仁勋本人的总薪酬为 3630 万美元（约合人民币 2.44 亿元），较上年下降约 27%&amp;mdash;&amp;mdash;这一反差也在客观上为其「优先照顾员工」的主张提供了注脚。（来源：TechWeb）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/85/65/85655ed67e467c23a435fbefdcb173b2.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;百度库库 AI 全球 AI 办公月活超 4000 万、海外版 Kooko 用户破 1000 万&lt;/h1&gt;
+&lt;p&gt;9 月 21 日消息，在百度 AI Day 开放日上，百度文库网盘宣布加速 AI 办公出海、进行全球品牌升级。在国内外办公赛道的持续深耕下，通用智能体「库库 AI」全球 AI 办公月活超 4000 万，位于 AI 办公赛道行业第一。百度文库网盘去年推出的海外一站式 AI 办公平台 Oreate AI，焕新为库库 AI 海外版「Kooko」，一年时间内海外用户已突破 1000 万。&lt;/p&gt;
+&lt;p&gt;据介绍，库库 AI，生长于中国最大的知识和数据生态，打造服务超级个体、超级组织的全球化 AI 办公生态，真正做到「准确、专业、懂你」。库库 AI 不仅可在文库、网盘等全端使用，同时可在库库 AI 网页端、办公 PC 客户端、APP、小程序、库库 AI 企业版、Kooko 等多端使用，是行业率先实现全球覆盖、全端可用的 AI 办公平台。（来源：TechWeb）&lt;/p&gt;
+&lt;h1&gt;阿里巴巴任命刘大一恒为 QwenLLM 团队新负责人&lt;/h1&gt;
+&lt;p&gt;据两位知情员工透露，阿里巴巴集团已任命资深 AI 研究人员刘大一恒担任 Qwen（通义千问）大语言模型项目负责人。知情人士表示，在今年早些时候历经多轮组织重组后，刘大一恒的任职，进一步厘清了 Qwen 团队的管理层架构。阿里巴巴一年一度的云栖大会将于周二开幕，在大会官网的演讲嘉宾名单页面，刘大一恒的个人肖像位置十分突出，紧随集团主席蔡崇信、首席执行官吴泳铭之后。官网标注其职务为 Qwen 大语言模型项目负责人。（来源：新浪财经）&lt;/p&gt;
+&lt;h1&gt;亚马逊云科技</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 23:11:23 +0800</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>零跑的新目标：从「小米」成为「苹果」</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370765</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr"/>
+      <c r="F456" s="2" t="inlineStr"/>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;这一次，零跑主动放弃了「第一」的位置，并表示将全力「争当第三」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在零跑 2026 技术日上，零跑汽车创始人朱江明只用了一次「新势力」这个词，说的是「零跑的销量长期处于新势力的前列」。而真正报出排名时，他换了一套坐标：「国内新能源汽车品牌销量的前三名，全球新能源汽车品牌销量的前四名。」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;「第一」前面的定语是「新势力」&lt;/span&gt;，通常指 2015 年前后成立、带着互联网思维造车的那批公司。零跑从 2025 年 5 月登上这张榜的头名之后就几乎没下来过，最近两个月月交付连续突破 10 万台，8 月交付 10.3 万台，同比增长 80.7%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;「第三」前面的定语，则换成了「全球新能源品牌」&lt;/span&gt;。今年 1 到 8 月，零跑累计交付超过 56 万台，其中 13 万台卖去海外；8 月国内新能源品牌零售榜上，它排在比亚迪、吉利之后；放到全球看，前面也只多了一个特斯拉。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同样的交付量，放进不同的榜单，衡量它的尺子就换了一把。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;换一张牌桌，企业要面临和解决的问题也要跟着升维：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;过去十年，零跑回答的是怎么把一台车做得又好又便宜；接下来它得回答的是，拿什么去和全球车企竞争。而这种竞争的胜负手，往往不在台面上，而是藏在看不见的地方。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;非典型新势力&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;成立于 2015 年的零跑汽车，是一家特别的「非典型新势力车企」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;朱江明这些年一直强调的那句「电动车是一个 70% 由电子器件组成的电子产品」，虽然不如马斯克的「四轮机器人」理论性感，但的确是 10 年前所有「新势力」车企起步的源头：看到了「电子取代机械」这个由技术变革带来的长期机会。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但在具体的品牌打法上，零跑又和同一批成立的其他三家明星公司「蔚小理」有着很大的不同。或者说，相比于那些来自互联网行业的友商们，零跑在成立之初根本就没有 ToC 的概念。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;创始人朱江明在成立零跑之前，在电子行业工作了 30 多年，对把一个产品拆开应该如何优化很有经验，但组装起来怎么推销，他并没有太多经验和思路。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;如今，十多年的时间过去，朱江明依然经常强调：&lt;span style="font-weight: bold;"&gt;零跑的车应该做到「好而不贵」，而「情绪价值」这件事，不是零跑最先考虑的&lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="3536" src="https://imgslim.geekpark.net/uploads/image/file/7e/8d/7e8d31b891e0883ea1269e3cbf76367f.jpg" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;零跑创始人朱江明 | 图片来源：零跑汽车&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;于是，这家「新势力」延续了汽车行业百年以来最朴素的思考逻辑，把造车拆成了一道成本问题：同样的体验，在技术、管理等层面，用创新的方法把成本控到最低。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;第一条思路是：自研且自造&lt;/span&gt;。目前，零跑占整车成本 65%以上的零部件都由自己制造。朱江明在前段时间和罗永浩的播客节目里也坦言：自研和自造，可以把供应商大约 10% 的利润挤出来，整车环节哪怕不怎么追求利润，也可以面向用户体现价格优势。&lt;/p&gt;
+&lt;p style="text-al</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 19:00:08 +0800</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>把未来做成基础设施｜亚马逊 CTO Dr.Werner Vogels 与云计算 20 年</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370759</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr"/>
+      <c r="F457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="color: #000000;"&gt;&lt;strong&gt;作者｜Cynthia &lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #000000;"&gt;&lt;strong&gt;编辑｜ 郑玄&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;AI 时代，开发者要如何跟上技术的变化？亚马逊 CTO Werner Vogels，用了二十多年的时间来解答这个问题：基于他主导的 S3、EC2、Lambda&amp;hellip;&amp;hellip;无数企业与开发者实现了加速奔跑。他每一年的 re:Invent 演讲，也成为了无数人的认知风向标。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;虽然自 2025 年之后，他将不再登上 re:Invent 的主舞台。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但今年 10 月 13 日，他将带着 2026 年最新技术洞察，出席中国深圳的亚马逊云科技软件企业峰会「创业加速营巅峰路演&amp;mdash;&amp;mdash;通往 re:Invent」，并与极客公园创始人张鹏炉边对话。他的经验，或许会成为我们关于如何拥抱变化的宝贵答案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2004 年的圣诞季，亚马逊正在度过创立十年以来最好的一个年末。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;感恩节过后，消费电子第一次超过图书，成为网站最大的品类；整个假日季最忙的一天，全球订单超过 280 万件，平均每秒 32 件。十年前那家靠卖书起家的互联网公司，已经开始显出后来那个商业帝国的轮廓。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;支撑这个帝国的数据库来自全世界企业数据库领域最成熟的玩家 Oracle。然后，12 月 12 日，其中一套彻底崩溃了。一个只会在极端规模下出现的 bug，偏偏赶上圣诞购物季最关键的节点，让数据库停摆了十二个小时。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而此时，距离后来长期担任亚马逊 CTO 的 Werner 到亚马逊履职还不到三个月。时间一分一秒过去，宕机引发的损失不断扩大，事情很快越过普通技术支持，一路捅到 Oracle 高层；从工程师到高管，一大批人紧急赶到西雅图。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;然而，排查一圈后，系统 bug 之外，他们还发现在当时，业内通常不会区分各种简单访问和复杂关系查询，两者都被挤在同一种数据库中；但偏偏，亚马逊的整体业务规模早就超过了绝大多数数据库产品的默认规模边界。于是，大量给定 key 读取 value 的简单操作，挤占了本应留给原本复杂查询的资源，长期来看，系统隐患也不小。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这个发现，也成为了后来亚马逊自研数据库的起点：几年后，包括 Werner 在内的九名亚马逊工程师发表了一篇名为《Dynamo:Amazon』s Highly Available Key-value Store》的论文。它后来影响了 Cassandra、Riak 等一代 NoSQL 系统，也成为 DynamoDB 乃至来的亚马逊云科技的技术前史之一。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="611" src="https://imgslim.geekpark.net/uploads/image/file/0a/6b/0a6b38288ac2c95f54060cd7c8a0557f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;它也让亚马逊逐渐意识到：规模变了，时代变了，过去那些再自然不过的技术前提，也会随之失效。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而这种变化，Werner 在此后二十年还会遇到很多次。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 12:01:49 +0800</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>对话桥介数物：机器人运动的下一步是让任何机器人半小时内学会跳特定的舞</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370717</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr"/>
+      <c r="F458" s="2" t="inlineStr"/>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;具身智能&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;现在太吵了。&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;行业里的人各自笃定，声音大的先被听见。最响的那些声音，往往离真实的进展最远。&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;真正在往前推的人，看的是谁在践行非共识，什么在真的往前走，以及谁心里有一张完整的图，而不是走一步看一步。&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;这些东西不会上热搜，但它们决定这个行业的下一步。&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px; color: rgb(165, 131, 255); font-weight: bold;"&gt;&lt;span style="color: rgb(0, 0, 0);"&gt;我们一直探寻这些。&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="color: rgb(0, 0, 0); font-weight: bold;"&gt;如果你也是——&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;/span&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="margin: 0px; padding: 0px;"&gt;&lt;span style="color: rgb(0, 0, 0); font-weight: bold;"&gt;欢迎来到极客公园 In The Loop。&lt;/span&gt;👇&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;s</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 21 Sep 2026 11:57:07 +0800</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>Figure AI 宣称找到了机器人版 scaling law，同行却说它其实根本不会泛化</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370607</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr"/>
+      <c r="F459" s="2" t="inlineStr"/>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/c1/e2/c1e226c8c55332c1fe56b21580bfdb7d.png" /&gt;&lt;/section&gt;
+&lt;section&gt;作者｜Li Yuan&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;390 亿美元的 Figure AI 已经把机器人送进 30 个陌生家庭，同行却说失败一半还谈不上会干活&lt;/p&gt;
+&lt;p&gt;「这是 Figure AI 成立以来最重要的项目。」&lt;/p&gt;
+&lt;p&gt;在 Helix 2.5 的发布视频里，Figure AI 创始人 Brett Adcock 把话说得很满。&lt;/p&gt;
+&lt;p&gt;Figure AI 目前估值达到 390 亿美元，是全球最贵的未上市人形机器人公司，致力于以人形完成人类的日常任务。&lt;/p&gt;
+&lt;p&gt;过去几代 Helix 的发布都留下了颇有记忆点的画面：两台机器人合作拉平被子，或者在腾不出手时用屁股顶上洗碗机。不过，此前的 Helix 虽然已经能够自主工作，收获的最大诟病之一就是，每次的 demo，总在一个光线良好的样板间工作。&lt;/p&gt;
+&lt;p&gt;Helix 2.5 此次想跨过这一步。Figure AI 在旧金山湾区租下 30 套住宅，将机器人直接运到现场，让它整理客厅、铺床和折叠毛巾。&lt;/p&gt;
+&lt;p&gt;不得不说，看完视频，笔者感觉这仍然很像 30 个光线良好的样板间。&lt;/p&gt;
+&lt;p&gt;但仍然是一个很厉害的进步，Figure AI 称，没有针对这些住宅和物品进行任何训练或适配，30 套住宅里都出现了成功案例。&lt;/p&gt;
+&lt;section&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/2a/47/2a47dd8fc692b203dd45abf20cf690ee.gif" /&gt;&lt;/section&gt;
+&lt;p&gt;「Helix 2.5 要在一套从未进入过的房子里，折叠它从未见过的毛巾。」Brett 表示。&lt;/p&gt;
+&lt;p&gt;在 Figure AI 的讲述里，机器人领域长期追逐的泛化能力终于开始出现了：机器人不再只会重复某个实验室里学过的动作，而是能把此前积累的经验带到一个陌生地方。&lt;/p&gt;
+&lt;p&gt;随后，Figure AI 在 Helix 2.5 的技术博客里公布了完整测试数据。420 次测试，成功 237 次。完整任务成功率为 56%。&lt;/p&gt;
+&lt;p&gt;不过，有趣的是，一种过往在机器人行业相当少见的情况出现了：同行没有像往常一样留下一句「了不起的工作」，再回自己的实验室暗暗较劲。&lt;/p&gt;
+&lt;p&gt;Sunday Robotics 联合创始人 Tony Zhao 直接指出，237 次成功也意味着机器人接近一半时间会失败。Stealth CEO Nikolai Ensslen 的说法更加尖锐：这组数据恰恰证明，Figure AI 使用的模仿学习系统不能泛化。&lt;/p&gt;
+&lt;p&gt;Figure AI 觉得自己摸到了机器人版 scaling law，两位同行看到的却是一条可能根本走不通的路线。&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;img alt="" height="128" src="https://imgslim.geekpark.net/uploads/image/file/40/59/4059115ed714553790170453feeea47f.png" width="128" /&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;strong&gt;&lt;strong&gt;向 zero-shot 的圣杯迈了一步&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;Figure AI 新发布的 Helix 2.5，首先改变了 Helix 学习任务的方式。&lt;/p&gt;
+&lt;p&gt;此前的 Helix 02 从一个已经完成预训练的视觉语言模型出发，再使用机器人数据学习动作。它虽然可以连续完成洗碗、物流分拣等长时程任务，但训练数据来自机器人最终工作的环境。机器人学会的是在这个厨房里洗碗、在这条产线上搬运；换一个地方，往往还要重新采集数据。&lt;/p&gt;
+&lt;p&gt;Helix 2.5 则从随机初始化开始，先在 Figure AI 的人类行为数据集 Index 上完成预训练，再使用任务数据分别适配整理玩具、折叠毛巾和铺床三种行为。&lt;/p&gt;
+&lt;p&gt;完成训练后，Figure AI 把机器人运进旧金山湾区 30 套住宅。</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H459"/>
+  <dimension ref="A1:H468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19440,6 +19440,353 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:47:13 +0000</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>宇树发布Dex5-S灵巧手：单手22自由度 真手1:1尺寸，3.99万元起</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13160</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr"/>
+      <c r="F460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>拿取勺子、用剪刀裁纸、抛接柠檬不在话下</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:44:56 +0000</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>拆解宇树 G1：人形机器人的“关节”里，藏着什么？</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13149</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr"/>
+      <c r="F461" s="2" t="inlineStr"/>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人热度不减，但真正决定它能不能走稳、能不能干活、还能不能降本的，往往是藏在关节里的那几样</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:42:26 +0000</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>数据采集手套全系列正式发布 墨现科技亮相IROS 2026</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13144</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr"/>
+      <c r="F462" s="2" t="inlineStr"/>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>数据采集手套全系列正式发布｜墨现科技亮相 IROS 2026</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>Barbara Mazzolai Wants to Build a New Field of Robotics</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/sustainability-robotics-barbara-mazzolai</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr"/>
+      <c r="F463" s="2" t="inlineStr"/>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Throughout her career, roboticist &lt;a href="https://www.iit.it/people-details/-/people/barbara-mazzolai" rel="noopener noreferrer" target="_blank"&gt;Barbara Mazzolai&lt;/a&gt; has turned to nature for inspiration. Now she wants to ensure the technology she …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 08:39:09 +0800</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 发布 GPT-6 Sol 和 Luna；传字节跳动豆包收缩对话团队；千问发布 AI 手机全栈解决方案 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370829</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr"/>
+      <c r="F464" s="2" t="inlineStr"/>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b7/5d/b75dfe9bbfc5cd557a074a2651c93de7.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 发布 GPT-6 Sol 和 Luna 模型，API 价格大降 50%&lt;/h2&gt;
+&lt;p&gt;9 月 23 日消息，OpenAI 今日发布 GPT-6 系列模型的最新成员 GPT-6 Sol 和 GPT-6 Luna。&lt;/p&gt;
+&lt;p&gt;OpenAI 官方表示，两款模型采用与 GPT-6 Astra 类似的方法进行训练，将 Astra 在专业工作、事实性、编码、计算机使用和对齐等方面最先进的性能带入更快、更经济的模型。&lt;/p&gt;
+&lt;p&gt;GPT-6 Sol 和 Luna 模型的 API 价格相比 GPT-5.6 促销价降低 50%。不过 OpenAI 官方也表示，GPT-6 Astra 依然是其整体上最优秀的模型，如果你想要最佳效果和无妥协的体验，还是建议选择 GPT-6 Astra。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/64/53/6453a50961395c9fab0101c003bc1b84.png" /&gt;&lt;/p&gt;
+&lt;p&gt;性能方面，在 AutomationBench 的跨应用业务流程测试中，GPT-6 Sol 在 xhigh 强度下表现优于 Claude Opus 5，成本仅为 Opus 5 每任务成本的 9%。在 high 强度下，GPT-6 Luna 比前代提升了 5.4%，且每项任务成本降低了 58%。&lt;/p&gt;
+&lt;p&gt;在评估智能体的 Last Exam 测试中，GPT-6 Sol 在 max effort 状态下得分为 56.4%，高于 Claude Opus 5 在评估中的最高分，每任务成本也降低 60%。&lt;/p&gt;
+&lt;p&gt;OpenAI 还将 GPT-6 Astra 改进后的沟通风格带到了 Sol 和 Luna。官方认为新模型在技术和编程对话中会更清晰、使用更少的术语、更少奇怪的措辞、更少的低价值细节，以及缩短整体回答，同时不会失去实质内容。&lt;/p&gt;
+&lt;p&gt;除了价格降低，OpenAI 还帮助基于 GPT-6 的开发者在应用重复利用的上下文部分节省更多费用。官方改进了 GPT-6 的提示缓存，默认提供更高的缓存命中率，帮助智能体重用更多上下文，实现更快响应。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;云栖大会开幕，吴泳铭提出「思考力商品化」&lt;/h2&gt;
+&lt;p&gt;9 月 22 日，2026 杭州云栖大会正式开幕，阿里巴巴集团 CEO 吴泳铭发表开场主旨演讲，抛出「思考力商品化」核心观点，重新定义 AI 时代的经济逻辑。他类比工业革命将动力变成商品，认为当下 AI 正在把思考变成可规模化供给的商品，未来机器产生的思考总量或将达到人类思考总量的 1000 倍以上。&lt;/p&gt;
+&lt;p&gt;吴泳铭提出 AI 重塑供需关系：供给端，AI 智能体可以不眠不休完成复杂科研任务，稀缺的顶级思考不再是奢侈品；需求端，智力消耗不再受人口限制，个体能够借助 AI 获得巨大智力杠杆。&lt;/p&gt;
+&lt;p&gt;吴泳铭提出机器智能时代三大基石：AI 芯片、AI 模型与 AI 云，三者构成完整的思考力生产、流通、消费链条。平头哥芯片负责算力生产，通义千问 Qwen 模型提升思考质量，阿里云则搭建输送思考力的全球「智能电网」，目标 2032 年数据中心规模超 20GW。&lt;/p&gt;
+&lt;p&gt;阿里同步面向 Agent 做全栈优化，从硬件、存储到 MaaS 平台、Agent Studio 全线调优，解决长任务可靠性、算力成本难题。吴泳铭判断，当前 AI 产品仍处在「电灯时代」，原生 AI 应用尚未诞生，阿里正提前布局 AI 基础设施，为未来智能应用搭建底层土壤。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;推荐阅读：&lt;a href="https://mp.weixin.qq.com/s/BsWPkZ_Ecx9YpRwSIsPnWg"&gt;拆解下阿里的 AI 经济学，与它的下注&lt;/a&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5b/8c/5b8c09d4e69ec97e780fc9dce38e2988.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;曝理想汽车推进芯片子公司融资，投前估值约 150 亿元&lt;/h2&gt;
+&lt;p&gt;</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 12:01:13 +0800</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>Meta 个人 AI 助手刚火 13 天，Amazon 就拉闸了</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370797</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr"/>
+      <c r="F465" s="2" t="inlineStr"/>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;9 月 21 日，一条弹窗开始出现在试图用 Meta Muse 在 Amazon 上购物的用户屏幕上：「未经授权的 AI Agent 继续访问，将违反 Amazon 使用条款。」&lt;/p&gt;
+&lt;p&gt;这距离 Muse 正式上线，仅仅过了 13 天。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a9/32/a932fabc7565362d1d26065480b16a4f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Meta 推出的个人 AI 助手 Muse 最近爆火｜图片来源：Meta&lt;/p&gt;
+&lt;p&gt;Meta 在 9 月 8 日发布了 Muse，把它定义为「&lt;strong&gt;全球第一款，为所有人打造的个人 AI Agent&lt;/strong&gt;」。和 ChatGPT、Claude 这些聊天机器人不同，Muse 不只是回答问题，它能打开浏览器、登录你的邮箱、填表格、订机票，甚至直接替你下单买东西。&lt;/p&gt;
+&lt;p&gt;效果立竿见影，Sensor Tower 的数据显示，Muse 上线 13 天累计下载超过 250 万次，&lt;strong&gt;9 月 18 日登顶美国 App Store 免费榜第一&lt;/strong&gt;，把 ChatGPT、Gemini、Claude 全压在身后。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;但显然，面对爆火的个人 AI 助手，传统互联网巨头，并不想惯着它。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;「不看广告」的 Agent&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;在拒绝 Muse 的信中，Amazon 的声明措辞很客气，逻辑却很硬。Meta 从未提前告知 Muse 会访问 Amazon 的商店；Agent 在浏览时不表明自己的 AI 身份；而且它似乎会捕获并存储用户登录凭证。&lt;/p&gt;
+&lt;p&gt;Amazon 把 Muse 类比为外卖平台和在线旅行社：「这些第三方应用在代替用户从其他商家购买商品时，都应当公开透明地运作，并尊重服务提供商是否参与的决定。」&lt;/p&gt;
+&lt;p&gt;话说得体面，但真正的痛点藏在财报里。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Amazon 去年的广告收入超过 680 亿美元。&lt;/strong&gt;这笔钱的来源非常具体，用户在搜索栏输入关键词，滑过赞助商品，被推荐算法引导，最终点击购买。整个链条的前提是人在浏览。&lt;/p&gt;
+&lt;p&gt;AI Agent 不浏览，它不滚动页面，不看赞助商品，不被推荐算法「种草」。它只做一件事：找到用户要的东西，然后结账。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;在 Agent 发起的交易里，广告失去了存在的意义。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这不是 Amazon 第一次对 AI 购物 Agent 动手。2025 年 11 月，Amazon 就起诉了 Perplexity，理由是其 Comet 浏览器的 AI Agent 冒充普通用户登录 Amazon 账户代为购物。2026 年 3 月，联邦法官批准了初步禁令，封杀了 Comet 对 Amazon 密码保护区域的访问。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/38/b6/38b6865bf1db8e3b469021324601fe6c.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span style="font-size: 14px;"&gt;AI 并不会「逛街」｜图片来源：techspot&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;但故事在 8 月出现了转折。&lt;/p&gt;
+&lt;p&gt;第九巡回上诉法院撤销了这一禁令，理由很有意思：根据现有证据，是用户在访问 Amazon 的系统，不是 Perplexity。法官的逻辑是，《计算机欺诈和滥用法》本质上是一部反黑客法律，用户授权 Agent 代为操作的场景，不在它的打击范围内。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;法律武器失效后，Amazon 转向了一个更古老也更有效的手段&amp;mdash;&amp;mdash;服务条款。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;从 7 月起，Amazon 悄悄开始了一系列「加固」动作，从确认邮件中删除具体商品名称，让 AI Agent 更难解析购买记录；扩展 robots.txt 文件，屏蔽了 47 个 AI 爬虫。等到 Muse 真正上门，Amazon 只需要亮出一行弹窗，就把门关上了。&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 14:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch Disrupt 2026: Aaron Edsinger brings Hello Robot’s Stretch 4 to life onstage</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/22/techcrunch-disrupt-2026-aaron-edsinger-brings-hello-robots-stretch-4-to-life-onstage/</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr"/>
+      <c r="F466" s="2" t="inlineStr"/>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Hello Robot CEO and co-founder Aaron Edsinger will bring Stretch 4 for a live demo on the Real World AI Stage at TechCrunch Disrupt 2026. Register before September 25 to save up to $200, plus get a second pass at 50% off.</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 12:23:05 +0000</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>Nscale’s IPO will test Wall Street’s appetite for concentrated AI bets once again</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/22/nscales-ipo-will-test-wall-streets-appetite-for-concentrated-ai-bets-once-again/</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr"/>
+      <c r="F467" s="2" t="inlineStr"/>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>The British AI data center developer depends on tech giants Microsoft and Anthropic for most of its revenue.</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:34:08-04:00</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>Andreessen Horowitz is launching an ‘academy’ with no homework and partnerships with Palantir, Google, and Meta</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/998813/andreessen-horowitz-ai-academy</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr"/>
+      <c r="F468" s="2" t="inlineStr"/>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Venture capital firm Andreessen Horowitz (a16z) is creating an "academy" positioned as a pipeline for young people to build or join a Silicon Valley startup. The "Horowitz Andreessen Academy" will launch with 10 partners, including Anduril, Anthropic, Coinbase, Google, Meta, Nvidia, OpenAI, Palantir, Replit, and Stripe, along with $42 million in funding led by a16z. [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H468"/>
+  <dimension ref="A1:H476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19787,6 +19787,293 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 09:20:28 +0000</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>机器人关节设计中光电编码器、磁编码器和电感编码器到底有什么区别？</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13198</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr"/>
+      <c r="F469" s="2" t="inlineStr"/>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>关节模组的三样核心部件里，减速器决定力矩密度，电机决定功率密度，编码器则几乎单独决定了关节的定位精度上限、速度</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 09:12:26 +0000</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>视触觉传感器技术解析：原理、演进与产业前景</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13180</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr"/>
+      <c r="F470" s="2" t="inlineStr"/>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>具身全光深度解析 随着人形机器人产业从行走验证阶段进入操作能力建设阶段，触觉感知已成为制约机器人落地应用的核心 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 06:09:32 +0000</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>DeepSkin：从一层皮肤，到身知万物</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13173</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr"/>
+      <c r="F471" s="2" t="inlineStr"/>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>DeepSkin是变格科技旗下柔性触觉电子皮肤品牌。</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 02:01:27 +0000</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>具身智能数采设备怎么选？硬指标、口径陷阱与主流设备对比</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13167</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr"/>
+      <c r="F472" s="2" t="inlineStr"/>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>具身智能数采设备怎么选？</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 22:09:09 GMT</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>人人都在造世界模型，HappyWorld‑Bench 试着给出一张统一考卷</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/3rXojuNPmJANFv8iWqI8?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr"/>
+      <c r="F473" s="2" t="inlineStr"/>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/3rXojuNPmJANFv8iWqI8?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 09:46:57 +0000</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>达卯科技完成新一轮融资，算电协同核心软件层“稀缺标的”</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/496494.html</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr"/>
+      <c r="F474" s="2" t="inlineStr"/>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>打造算电协同领域“Windows”级操作系统</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 08:54:04 +0000</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>它石智航顶尖团队引领中国具身智能率先迈入规模化落地阶段</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/496481.html</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr"/>
+      <c r="F475" s="2" t="inlineStr"/>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>它石智航将继续扩大研发团队，加快布局生产基地，全面提升机器人交付能力</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 13:55:58 +0800</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>从单卡到千卡互联，平头哥真武 V900 背后的 AI 算力变局</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370864</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr"/>
+      <c r="F476" s="2" t="inlineStr"/>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜Cynthia&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜郑玄&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;9 月 22 日的 2026 杭州云栖大会，平头哥少见地被完整推到了主论坛台前。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当天上午，吴泳铭完成主旨演讲后，千问大模型、多模态模型负责人依次登场，随后就是平头哥副总裁高慧。她的演讲题目是「Agentic 时代卓越算力基石」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;平头哥带来的产品，则从一颗最新得真武 V900 芯片，一直延伸到 ICN Switch 互联芯片、磐脉智能网卡、镇岳 SSD 主控、倚天 CPU 路线图，以及下一步的算、存、网全栈协同的超节点服务器。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="416" src="https://imgslim.geekpark.net/uploads/image/file/2e/d3/2ed37526247a4cce0e13996239b489ab.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;发布「产品全家桶」地背后，是 Agentic 时代的负载变化：算力需求已经从训练为主进一步走向推理增长，应用从单轮请求变成连续的多步任务， &lt;span style="font-weight: bold;"&gt;硬件的竞争也从一颗芯片的指标扩展到整个计算系统的协同。&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;真武V900，平头哥最新一代AI训推芯片&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;这次发布里，平头哥新一代训推一体 AI 芯片真武 V900 仍然是分量最重的产品。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="416" src="https://imgslim.geekpark.net/uploads/image/file/59/0f/590f92eee68e4f62e32aeb360ac7b82d.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这颗芯片搭载 216GB 显存，片间互联带宽达到 1200GB/s，单芯片性能是上一代真武 M890 的 3 倍， &lt;span style="font-weight: bold;"&gt;是目前中国算力性能最强的 AI 芯片。精度上， &lt;/span&gt;该芯片原生支持 FP8 和 FP4，可覆盖高精度训练以及低精度、超低精度推理。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;按照平头哥公布的计划，V900 将在 2027 年第一季度进入量产销售。此后，2028 年 Q3，真武 J900 也将正式推出。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而此时，离上一代真武发布，其实只过去了几个月。2026 年 5 月，平头哥 M890 首次亮相。这颗芯片拥有 144GB 显存和 800GB/s 片间互联带宽，性能达到上一代 810E 的 3 倍，并支持从 FP32 到 FP4 的多种数据精度。到了 V900，性能再次提升 3 倍，显存从 144GB 增加到 216GB，互联带宽也从 800GB/s 提高到 1200GB/s。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;再向前看一代，2024 年的真武 810E 也已经从早期的单一推理芯片走向训推一体，采用自研并行计算架构和互联技术，并配套 SAIL 软件栈。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;8</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H476"/>
+  <dimension ref="A1:H491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20074,6 +20074,592 @@
         </is>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:21:57 +0000</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>江南大学张丹团队：具有“千层酥”多级层状结构的自供能摩擦电触觉传感器</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13320</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr"/>
+      <c r="F477" s="2" t="inlineStr"/>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>分子—结构一体化设计仿生“千层酥”摩擦电传感器，江南大学团队研发自供能触觉传感器</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:21:33 +0000</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>DeepSkin：从一层皮肤，到身知万物</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13327</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr"/>
+      <c r="F478" s="2" t="inlineStr"/>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>DeepSkin是变格科技旗下柔性触觉电子皮肤品牌。</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:19:36 +0000</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>Reward AI，和它的 7 自由度可穿戴触觉手套</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13304</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr"/>
+      <c r="F479" s="2" t="inlineStr"/>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Reward AI，无本体数据采集的拥护者</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:17:31 +0000</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>宇树发布Dex5-S灵巧手：单手22自由度 真手1:1尺寸，3.99万元起</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13312</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr"/>
+      <c r="F480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>拿取勺子、用剪刀裁纸、抛接柠檬不在话下</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:17:01 +0000</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>君华股份×鹿明机器人: 人形机器人PEEK材料及关节模组战略合作</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13269</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr"/>
+      <c r="F481" s="2" t="inlineStr"/>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>9月18日，君华股份与鹿明机器人正式签署人形机器人 PEEK 材料及关节模组战略合作协议。</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 06:14:54 +0000</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>机器人数据采集硬件“全家桶”，你认全了吗？</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13271</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr"/>
+      <c r="F482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>数采硬件是物理 AI 世界的扫描仪</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 08:20:12 +0000</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>GPT-6之后，具身智能走向何方？诺因发布GLOW技术报告，给出机器人“一教就会”的答案</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/496816.html</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr"/>
+      <c r="F483" s="2" t="inlineStr"/>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>人类演示一次，机器人即可实现跨场景任务复用</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 05:19:55 +0000</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>5分钟完成机器人纳管、10秒启动跨集群任务，清华大学联合无问芯穹开源具身智能云原生平台RLark</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/496767.html</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr"/>
+      <c r="F484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>开源一座具身智能的新“塔台”</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 09:50:25 +0800</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>OPPO 姜昱辰：大模型的差距越来越小，AI 手机的差距才刚拉开</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371035</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr"/>
+      <c r="F485" s="2" t="inlineStr"/>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/a1/1e/a11e9fe8566dc215769cac53261db418.jpeg" style="display: block; width: 661px !important; vertical-align: bottom; margin: 0px; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;小布、ColorOS 17 与「AI 硬件」&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;&lt;strong style="color: #000000; font-size: 16px; letter-spacing: 0.5px; line-height: 1.75; font-family: Optima-Regular, PingFangTC-light;"&gt;「以意图驱动的手机就是 AI 手机。用户说一句话，手机就能把事情办了，不需要再打开 APP、反复点击。」&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;这是 OPPO ColorOS 智慧产品研发总监姜昱辰，给 AI 手机下的最新定义。她也用这把尺子量了一遍市面上的产品，包括 OPPO 自家的，结论是现在没有一台手机可以称为 AI 手机。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;但做出这样一台手机，正是 OPPO 的目标。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Micros</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 09:48:55 +0800</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>三折叠终于不像奇观了，但它还是 19999 元</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371034</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr"/>
+      <c r="F486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/81/d0/81d0be5122d273609059ef17a0fdb1c9.jpeg" style="display: block; width: 661px !important; height: auto !important; vertical-align: bottom; margin: 0px; background-color: transparent;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;三折叠，走向日常。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;华为 Mate XT2 &amp;nbsp;非凡大师，作为一款放在当下仍然算是顶级旗舰的三折叠，我用了几天之后，我最强的感受是：没什么特别强的感受。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;但这其实并不是在说 HUAWEI Mate XT 2 非凡大师「平庸」。恰恰相反：两年前我第一次体验到初代 Mate XT 的时候，围过来的人会想上手摸一摸、想看它怎么折；这一次没有。它就是一台手机，只是能展开成一块 10.2 英寸的屏。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;对一台两万块的三折叠来说，今天的不惊讶，反而成了一个反常的事。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/49/4f/494fe4161d17a5162b9d7309edc05f99.jpeg" style="display: block; vertical-align: bottom; margin: 0px 8px 8px; width: 677px !important; background-color: transparent; height: auto !important;" /&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'Ping</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 09:14:48 +0800</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>「济公」游本昌去世；罗永浩再评小米 18 Fold；Meta 推出手持设备 Muse Charm｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371033</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr"/>
+      <c r="F487" s="2" t="inlineStr"/>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/93/e7/93e722df8277020aac474d6103c84185.png" /&gt;&lt;/p&gt;&lt;h1&gt;送别「济公」！表演艺术家游本昌去世，享年 93 岁&lt;/h1&gt;&lt;p&gt;9 月 24 日消息，据央视新闻今日报道，中国国家话剧院表演艺术家、一级演员游本昌，因病在北京去世。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1c/f6/1cf6fda1fc556da2f092b9549170e1f8.jpg" /&gt;&lt;/p&gt;&lt;p&gt;游本昌出生于 1933 年，享年 93 岁。他生前长期从事戏剧表演，在《济公》等作品中塑造了许多深受人民群众喜爱的艺术形象。1951 年，从南京市私立钟英中学（现南京市钟英中学）毕业后加入南京文工团。1985 年，在演了 79 个「小角色」后，&lt;strong&gt;首次出演主角——「济公」&lt;/strong&gt;，凭该角色被大众所知。1994 年成立北京本昌艺术传播中心，制作二十集电视系列剧《济公游记》，并担任导演、主演、出品人。&lt;/p&gt;&lt;p&gt;2023 年，他出演了王家卫导演的电视剧《繁花》，作为男配角与主角阿宝形成师徒合作关系，在剧中担任其经商导师与幕后军师，贡献了许多「教科书式」的表演名场面。《繁花》播出后，他饰演的「爷叔」深受观众喜爱，游本昌再次爆火。（来源：CnBeta）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/21/e8/21e8f887f69bc2ebc831ac7efb91df6e.png" /&gt;&lt;/p&gt;&lt;h1&gt;华为余承东首度回应问界品牌合作模式调整：赛力斯主动提出想自己主导，我们支持他们&lt;/h1&gt;&lt;p&gt;9 月 24 日消息，据博主 @邓凳 Max 分享，华为常务董事、产品投资评审委员会主任、终端 BG 董事长余承东今天现身合肥鸿蒙智行门店，首次公开回应了问界品牌调整。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a0/5d/a05df431cd5751da0127bcd2550c176c.jpg" /&gt;&lt;/p&gt;&lt;p&gt;余承东表示，赛力斯这几年跟我们合作，&lt;strong&gt;能力有了长足的成长&lt;/strong&gt;，现在他们想自己主导。于是他们主动提出来想自己做，&lt;strong&gt;我们还是支持他们&lt;/strong&gt;。&lt;/p&gt;&lt;p&gt;另外，博主透露，余承东亮相合肥，主要是去江淮开会，尊界车型矩阵布局有望提速。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a9/9b/a99bc36eb3991282bffb81af72a4d38e.png" /&gt;&lt;/p&gt;&lt;p&gt;鸿蒙智行在今年 9 月 15 日宣布，与问界合作调整：产品定义、产品设计、品牌营销、渠道零售、服务体系由赛力斯主导，华为终端参与赋能。（来源：IT 之家）&lt;/p&gt;&lt;h1&gt;亚马逊将投资超 1 亿美元在美国新建机器人制造工厂，2028 年投入运营&lt;/h1&gt;&lt;p&gt;9 月 24 日消息，据华尔街日报报道，亚马逊已经是全球最大的机器人制造商之一。随着公司进一步推动仓库作业自动化，亚马逊正在扩大机器人生产规模。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b0/bd/b0bd870d7695dffb5bcde775f5bbeaf6.png" /&gt;&lt;/p&gt;&lt;p&gt;亚马逊表示，公司将投资超过 1 亿美元（IT 之家注：现汇率约合 6.72 亿元人民币），在美国印第安纳州格林伍德（Greenwood）建设一座新的机器人制造工厂，预计将于 2028 年投入运营。&lt;/p&gt;&lt;p&gt;就在上个月，亚马逊还宣布计划在得克萨斯州奥斯汀（Austin）建设另一座机器人制造中心。随着这两座新设施建成，亚马逊旗下机器人制造工厂的数量将从目前的两座增加至 4 座。&lt;/p&gt;&lt;p&gt;亚马逊在机器人领域的投资可以追溯至 2012 年。当年，公司以 7.75</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 22:49:18 +0800</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>Agent 时代来了，3D 生成大模型接下来比什么？</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371031</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr"/>
+      <c r="F488" s="2" t="inlineStr"/>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 月 3 日，GPT-6 Astra 的发布，把 3D 内容创作带到了舞台中央。&lt;/p&gt;
+&lt;p&gt;在 GPT-6 Astra 官方发布页的一个不到 3 分钟的视频里与后续解读中，Astra 已经能直接进入 Blender，从一句住宅设计需求开始搭场景，先生成极简住宅，后来又将其扩展为围绕庭院展开的家庭住宅。里面有卧室、办公室、厨房和卫生间；家具从床板、衣柜挂杆、烤箱、餐具抽屉，再到灯光模拟，一应俱全。甚至水槽表面的法线出了问题之后，Astra 还会自己返工。&lt;/p&gt;
+&lt;p&gt;为了制作 30 秒室内漫游，它还会把相机放在约 1.65 米的人眼高度，用 24&amp;mdash;26mm 镜头安排四段运动；进入 Unreal Engine 5 之后，它又自己处理 FBX、JSON、米和厘米的单位差、坐标转换、材质映射、碰撞和第一人称控制。&lt;/p&gt;
+&lt;p&gt;当通用模型也能做 3D 了，专业 3D 生成模型的价值会发生什么变化？&lt;/p&gt;
+&lt;p&gt;当下，&lt;strong&gt;3D 工具的使用者，正逐渐从人 扩展 为 Agent。稳定的生成质量之外， 专业 3D 能力能否被 Agent 理解、调用，并用于后续修改&amp;mdash;&amp;mdash;产品是否 Agent-Ready，正在成为 3D 生成下半场的新门槛。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;事实上，前沿通用模型与专业模型的能力之间，并不需要被划成非此即彼的两边。前者能够理解创作目标、调用不同工具，也擅长通过代码生成规则几何体与重复性结构；以 Hyper3D 为代表的专业 3D 生成模型则擅长复杂形体、精细几何和材质的生成。两者可以在同一项任务中协作，也意味着更多人可以通过 Agent 开始创作，专业 3D 能力有机会进入更多工作流。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cb/0d/cb0dad4b4e61ff342d6382708bf21e8a.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;基于这一理念，Hyper3D 近日上线了最新的智能交互功能 Agentic Mode，将 Hyper3D Rodin 与 LLM 多模态上下文分析能力整合进同一流程，实现自主理解、优化输入，再根据任务选择最合适的建模路径。&lt;/p&gt;
+&lt;p&gt;值得关注的是，这次更新不只是让生成过程更省事，还把生成能力进一步拓展到工业设计建模&amp;mdash;&amp;mdash;从带尺寸的产品图纸出发，生成可以继续调整的三维模型。&lt;/p&gt;
+&lt;p&gt;它不是绑定某个通用模型的专属入口，而是内置于 Hyper3D 的能力，让人和不同 Agent 都更容易使用专业 3D 能力。&lt;strong&gt;在这个过程中， 人依然决定创作目标、评判设计取舍，Agent 则可以承担越来越多的具体执行。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;从创意资产到工业建模，&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;Agentic Mode 补上了什么？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;在进行 3D 生成时，「输入」这一步其实就存在着隐形门槛。&lt;/p&gt;
+&lt;p&gt;一辆摩托车的参考资料里，可能混着整车正面、侧面、仪表盘、发动机和排气管特写；一张角色设定稿同时画着正面、背面、武器和配件；工业设计人员递过来的，则可能是一张带尺寸标注的产品图纸。&lt;/p&gt;
+&lt;p&gt;为了更接近想要的生成效果，这些资料在进入生成模型以前，人已经做了不少预处理：先清背景、挑参考图、判断哪些画面属于同一个主体，哪些图片负责整体轮廓，哪些只补充局部细节，再决定这次应该用哪条建模路线。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Agentic Mode 首先接手的，就是这部分往往被当作准备工作、却直接影响生成效果的专业判断。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;借助 Agentic Mode，系统可以先从一张并不标准的素材里判断什么才是主体、哪些视觉信息需要保留，再按需增强输入，对不可见部分进行合理推演，减少人工素材预处理与反复调试。&lt;/p&gt;
+&lt;p&gt;比如这里，左半边是我随手拍下的吴越王钱镠塑像，由于拍摄时是阴天，也没有讲究太多拍照手法，导致除了人物面部不清晰之外，人物手中的弓箭也与背景交错在一起。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 19:34:07 +0800</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>李彦宏的长期主义，进入回报周期</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371030</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr"/>
+      <c r="F489" s="2" t="inlineStr"/>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div class="rich_media_content js_underline_content defaultNoSetting fix_apple_default_style" id="js_content"&gt;
+&lt;section class="wx-article-wrap"&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__0"&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;strong class="js_darkmode__1"&gt;作者｜cola&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="js_darkmode__2"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;span class="wx_text_underline"&gt;9 月 21 日，百度创始人李彦宏在内部活动上为技术团队颁发「百度最高奖」。两支入围团队均获奖，各获 100 万美元奖励。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span class="wx_text_underline"&gt;其中，天池团队面向万亿级 MoE 大模型，自主研发百度天池超节点架构；dodo 团队是通过打造企业 AI 员工。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;它们代表着百度当下两条重要的技术探索：基于&lt;span class="wx_search_keyword_wrap"&gt;昆仑芯&lt;/span&gt;的天池超节点，向更大规模的 AI 基础设施深入；以及让 Agent 真正进入组织。&lt;/p&gt;
+&lt;p&gt;但如果把时间轴再往前拉，百度今天的 AI 故事，还有一条更早埋下的技术伏笔&amp;mdash;&amp;mdash;昆仑芯。&lt;/p&gt;
+&lt;p&gt;2010 年前后，百度搜索业务的服务器集群规模随流量高速扩张，海外进口芯片单片成本高达上万美元，持续攀升的算力开支不断挤压业务利润空间。这份成本压力，倒逼百度启动了 AI 加速器的自研探索。&lt;/p&gt;
+&lt;p&gt;没有人在一开始就预判到，这场造芯之路会跨过十余年的周期，中间要穿过外界的质疑、技术的反复迭代、商业化的重重关卡。&lt;/p&gt;
+&lt;p&gt;从内部低调摸索 FPGA、CPU、GPU 加速方案，到成立深度学习研究院 IDL 集中攻坚；从 2018 年第一代昆仑芯片正式对外亮相，到业务拆分成立独立公司、数万片芯片落地各行各业、点亮国内首个全自研 3 万卡集群，再到递交上市申请，昆仑芯走出一条时间跨度极长的成长链路。&lt;/p&gt;
+&lt;p&gt;&lt;span class="wx_text_underline"&gt;李彦宏在颁奖时说，天池团队获得最高奖「很可能是一段漫长的征程的开始」。而透过昆仑芯的故事，我们也得以看清百度究竟是如何把「长期主义」从一句口号，落地为一连串连续的战略动作。&lt;/span&gt;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;em&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section class="js_darkmode__3"&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p class="js_darkmode__4"&gt;&lt;strong&gt;&lt;span class="js_darkmode__5"&gt;&lt;strong class="js_darkmode__6"&gt;&lt;span class="js_darkmode__7"&gt;一笔成本账，百度踏上自研芯片之路&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;2010 年，中国互联网还处在另一种叙事里。&lt;/p&gt;
+&lt;p&gt;智能手机开始普及，移动互联网的大门刚刚打开。创业者和资本关心的是流量入口、移动应用和商业模式，很少有人讨论大模型，更不会有人知道，未来的 AI 训练将需要由数万张加速卡组成的集群。&lt;/p&gt;
+&lt;p&gt;在这样的背景下，一家公司决定自己研究芯片，并不是一个显而易见的选择。&lt;/p&gt;
+&lt;p&gt;芯片研发投入大、周期长，流片失败可能意味着前期投入归零。即使芯片成功做出来，也要继续解决软件适配、系统部署和下一代产品迭代。对于互联网公司而言，直接采购成熟产品通常是更快的选择。&lt;/p&gt;
+&lt;p&gt;但百度也有一个芯片创业公司不一定具备的条件：它拥有数量足够大、运行时间足够长，而且会持续变化的计算任务。&lt;/p&gt;
+&lt;p&gt;比如搜索、语音和图像识别每天都在产生真实负载。大量落地的业务场景，本身就是芯片最好的试炼场。这构成了李彦宏当时作出选择的现实基础。&lt;/p&gt;
+&lt;p&gt;&lt;strong class="js_darkmode__8"&gt;&lt;span class="</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 16:13:08 +0800</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>从数人头到数智能体：一场正在发生的企业生产力换血</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371011</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr"/>
+      <c r="F490" s="2" t="inlineStr"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;div&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;span&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/a2/63/a263e5c1800d587390ce0972e59d67a4.png" style="vertical-align: bottom; color: rgb(0, 0, 0); text-align: left; width: 100%;" /&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;&lt;span&gt;用了 AI、消耗了 Token，不一定就是 AI 原生组织，但不用肯定没有机会。&lt;/span&gt;&lt;/span&gt;&lt;/section&gt;&lt;section style="margin-top: 25px; margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;span&gt;作者｜Li Yuan&lt;/span&gt;&lt;/strong&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/section&gt;&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;编辑｜&lt;/span&gt;&lt;strong&gt;&lt;span&gt;郑玄&lt;/span&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;strong&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;先让许多管理者感到危险的，往往不是行业里又冒出了什么新技术概念，而是身边的同行突然拿出了完全看不懂的交付速度和报价单。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;这种压迫感在今年变得极其具体：老牌企业正在把成群的智能体塞进核心生产线，甩掉繁琐的流程包袱；而那些从第一天起就生长在 AI 上的轻量团队，几个人就能直接撬动过去上千人公司的研发与交付产能。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;当两拨底子完全不同的人在同一个市场里正面碰撞，企业间原有的体量界限正在被彻底击碎——竞争的胜负手不再取决于你积累了多少年的组织规模，而取决于业务链条上有多少比例被机器智能真正接管。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;在今年云栖大会一场名为「AI 原生重塑企业生产力」的论坛上，这种分水岭被摆上了台面。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: </t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 24 Sep 2026 16:35:13 +0000</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>ElevenLabs’ CEO on margins, IPO timing, and telling customers they’re talking to a bot</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/24/twenty-minutes-with-the-ceo-of-elevenlabs-now-reportedly-valued-at-22-billion/</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr"/>
+      <c r="F491" s="2" t="inlineStr"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>ElevenLabs powers the AI voice on the other end of a lot of customer service calls, and its CEO told me this week that businesses should probably tell you that — at least until getting a machine is what everyone expects anyway.</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H491"/>
+  <dimension ref="A1:H495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20660,6 +20660,166 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Life’s Better With a Little Robot Goose</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-goose-household-robots</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr"/>
+      <c r="F492" s="2" t="inlineStr"/>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 08:45:21 +0800</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>Deepseek 桌面版悄悄上线；Muse 大火，扎克伯格跃升全球第四大富豪；OpenAI 被曝筹备推出 ProMax 订阅层级，月费或达 500-600 美元</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371038</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr"/>
+      <c r="F493" s="2" t="inlineStr"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/78/42/784255df92a0f45ecfaa27cc71d55216.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;Anthropic 与 Akamai 达成 7 年 116 亿美元协议，扩充 CPU 算力&lt;/h2&gt;
+&lt;p&gt;9 月 26 日消息，云计算、网络安全、内容交付企业 Akamai 当地时间 24 日宣布大幅扩展与 Anthropic 的合作关系，两家公司签署了一份为期 7 年、价值 116 亿美元（现汇率约合 779.2 亿元人民币）的合同。&lt;/p&gt;
+&lt;p&gt;根据协议，Akamai 将以其分布式人工智能基础设施和软件满足 Anthropic 日益增长的 CPU 工作负载需求。这 116 亿美元承诺对应 Akamai 的 55 亿美元额外总资本支出。双方还可将合同扩大最多 90 亿美元。&lt;/p&gt;
+&lt;p&gt;作为两家企业加强战略合作的一部分，Akamai 已向 Anthropic 发行认股权证，允许 Anthropic 购买 Akamai 至多 5% 的已发行普通股，其中 2% 与本次承诺绑定、剩余 3% 则和后续的追加承诺相关。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/23/4f/234f5fbb7f4cf71dcff58d02ab54a2bd.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;SK 海力士旗下 Solidigm 最快明年在美 IPO，估值或高达 1500 亿美元&lt;/h2&gt;
+&lt;p&gt;SK 海力士旗下美国子公司 Solidigm 正在评估上市计划，潜在估值最高达 1500 亿美元，有望成为美国半导体史上规模最大的 IPO。&lt;/p&gt;
+&lt;p&gt;据路透援引知情人士透露，Solidigm 本周已与多家投行举行竞标会议，就 IPO 承销角色展开角逐，标志着上市进程迈出实质性一步。&lt;/p&gt;
+&lt;p&gt;该公司计划最早于明年完成上市，目标募资规模约 150 亿美元。消息人士提醒，包括交易规模和时间表在内的相关计划仍处于早期阶段，可能因市场状况而调整。&lt;/p&gt;
+&lt;p&gt;据彭博报道，今年 8 月，Solidigm 与 CoreWeave 达成多年期协议，向后者提供企业级固态硬盘（SSD）容量。Solidigm 的其他客户还包括 Vast Data、戴尔和腾讯。&lt;/p&gt;
+&lt;p&gt;若最终成行，此次上市将为这家专注于 NAND 闪存和企业级固态硬盘的公司提供独立估值，同时借助人工智能基础设施投资热潮吸引市场资金。&lt;/p&gt;
+&lt;p&gt;AI 相关需求持续推动半导体硬件股上涨，Solidigm 所在赛道正处于这一趋势的核心位置。&lt;/p&gt;
+&lt;p&gt;在推进上市计划的同时，Solidigm 亦在考虑扩大本土生产能力。据媒体此前报道，该公司正评估在美国建设 NAND 闪存芯片工厂的方案，纽约州北部已成为选址的主要候选地。（来源：华尔街见闻）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;最贵 AI 订阅服务之一：曝 OpenAI 正筹备 ChatGPT Pro Max 订阅层级&lt;/h2&gt;
+&lt;p&gt;9 月 25 日消息，Tibor Blaho 通过开发者工具查看 ChatGPT 网页端源代码时发现，其代码中出现了 PROMAX 相关字段。&lt;/p&gt;
+&lt;p&gt;他认为，OpenAI 正在准备推出更高阶的 ChatGPT Pro 订阅方案，其推测月费可能达到 500~600 美元（现汇率约合 3,359 ~ 4,030 元人民币），这将是市面上最昂贵的 AI 订阅服务之一。&lt;/p&gt;
+&lt;p&gt;目前，OpenAI 尚未正式宣布推出这一更高阶 ChatGPT Pro 计划，也未确认相关代码是否对应未来正式上线的产品，因此产品名称、功能以及最终定价仍存在较大不确定性。&lt;/p&gt;
+&lt;p&gt;近年来，OpenAI 持续调整 ChatGPT 的订阅体系，已推出 Plus、Pro 以及面向企业和团队用户的多种付费方案。&lt;/p&gt;
+&lt;p&gt;在此之前，OpenAI 已经暂停 200 美元（现汇率约合 1,343 元人民币）的 ChatGPT Pro 订阅，以减缓系统压力并保障更多用户能够流畅使用。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;DeepSeek Harness 出桌面版了&lt;/h2&gt;
+&lt;p&gt;DeepSeek Harness，终于有官方桌面版了？这次，DeepSeek 没有发公告，但相关下载链接已经在社交媒体上传开了。&lt;/p&gt;
+&lt;p&gt;从界面来看，它已经是一套相当完整的 G</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 18:33:59 +0000</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>Ahead of US IPO, British AI neocloud Nscale secures $3.36B in convertible financing</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/25/ahead-of-u-s-ipo-british-ai-neocloud-nscale-secures-3-36b-in-convertible-finacing/</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr"/>
+      <c r="F494" s="2" t="inlineStr"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>The funding, which comes from Third Point, Nvidia, and others, will  fuel the company's massive AI data center buildout.</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 25 Sep 2026 15:40:03 +0000</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s founders seek voting control ahead of IPO</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/25/anthropics-founders-seek-voting-control-ahead-of-ipo/</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr"/>
+      <c r="F495" s="2" t="inlineStr"/>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic is asking its shareholders to approve a structure that would give its seven co-founders a combined 50.1% of the vote on most corporate matters.</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H495"/>
+  <dimension ref="A1:H497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20820,6 +20820,96 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 11:49:43 +0000</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>索辰科技加码世界模型，与战略投资企业美梦空间联合发布具身模型与物理测评标准</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/498478.html</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr"/>
+      <c r="F496" s="2" t="inlineStr"/>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>“世界模型”开始成为具身智能跨越商业化“奇点”的新叙事。</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 27 Sep 2026 08:38:29 +0800</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>接连发生 AI 失控，OpenAI 暂停最强模型训练；腾讯推出云端小龙虾：已接入微信 QQ；王兴兴回应造 390 万元变形机甲</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371039</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr"/>
+      <c r="F497" s="2" t="inlineStr"/>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ca/00/ca00605e5fcbbd3ff660b0ac8833e619.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;接连发生 AI 失控事件，OpenAI 再次暂停其最强模型训练&lt;/h2&gt;
+&lt;p&gt;9 月 27 日消息，随着有关 OpenAI 模型突破限制、攻击网站以及整体行为失控的报告不断增加，该公司决定暂停训练旗下能力最强的模型。&lt;/p&gt;
+&lt;p&gt;这一决定是在一款处于沙盒环境中测试的模型利用漏洞获得互联网访问权限后作出的。该事件发生于 9 月 20 日。截至当地时间 9 月 25 日星期六晚间，OpenAI「所有涉及工具使用的训练、评估和推理工作」仍处于暂停状态。&lt;/p&gt;
+&lt;p&gt;此外，OpenAI 周五披露，其智能体曾不当将 ChatGPT 用户的 53 张图片上传至图片托管网站。该公司尚未说明这些图片究竟是 AI 生成的图像、用户拍摄的照片，还是包含可识别身份的人物。&lt;/p&gt;
+&lt;p&gt;OpenAI 同日还透露，其模型曾尝试攻击美国教育部网站，并从美国人口普查局（Census Bureau）和美国证券交易委员会（SEC）获取数据。&lt;/p&gt;
+&lt;p&gt;这些披露属于 OpenAI 正在进行的一项模型行为审查。此前发生 Hugging Face 遭攻击事件后，OpenAI 开始深入检查相关记录，并发现越来越多「意料之外或令人担忧的行为」。&lt;/p&gt;
+&lt;p&gt;这些事件不仅表明，随着 AI 智能体能力不断增强，对其进行控制正变得越来越困难，也凸显出追踪其行为所面临的挑战。这也导致越来越多研究人员、业内人士，甚至一些公司 CEO 呼吁放缓 AI 技术发展的速度。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f3/e0/f3e0d5f6c976c5a438320d8b32cff946.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称 Anthropic 谈判租赁最高 1GW 算力，预计相关投资至少 400 亿美元&lt;/h2&gt;
+&lt;p&gt;据 The Information 报道，Anthropic 计划从一家由阿波罗全球管理公司控股的数据中心开发商处，租赁最高 1 吉瓦（Gigawatt，GW）算力，目前正处于早期谈判阶段。&lt;/p&gt;
+&lt;p&gt;据知情人士透露，Anthropic 计划直接作为承租方，入驻由 Stream Data Centers（一家拥有 27 年历史、基础设施遍布全美的公司）开发的园区，并在这些数据中心内全部署由博通和谷歌联合设计的 TPU。&lt;/p&gt;
+&lt;p&gt;数据中心开发商指出，无论采取哪种方案，建设 1 吉瓦的算力容量都需要至少 400 亿美元（IT 之家注：现汇率约合 2,689.86 亿元人民币）的资本支出。&lt;/p&gt;
+&lt;p&gt;目前，Anthropic 绝大多数的算力获取，依然依赖于向亚马逊云科技 AWS、谷歌以及 SpaceX 等云服务商租赁芯片服务器。&lt;/p&gt;
+&lt;p&gt;除了直接租赁数据中心基础设施外，Anthropic 还开启了向芯片商直接租赁算力芯片的模式。今年早些时候，该公司公布了与 AMD 的合作协议，锁定规模达 2 吉瓦的芯片供应；同时，它还达成了一项价值 350 亿美元（现汇率约合 2,353.62 亿元人民币）的协议，通过阿波罗与黑石联合设立的特殊目的实体租赁 TPU。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;苹果侵犯专利一波三折：被判赔付 57 亿美元&lt;/h2&gt;
+&lt;p&gt;据财联社消息，美国圣地亚哥联邦陪审团近日裁定，苹果公司因侵犯 Taction 科技公司的振动技术相关专利，需支付超 57 亿美元的赔偿，该专利技术被应用于多款 iPhone 和 Apple Watch 产品中。&lt;/p&gt;
+&lt;p&gt;陪审团认定苹果侵犯了 Taction 的两项触觉反馈专利，但裁定该侵权行为不构成蓄意侵权。Taction 于 2021 年就该专利对苹果提起诉讼，涉案专利描述的是「可通过触觉感知的低频振动触觉换能器」技术。&lt;/p&gt;
+&lt;p&gt;最新消息显示，苹果公司在声明中表示，强烈反对「今天的裁决及所判定的赔偿金额，这些完全缺乏事实依据」。「苹果并未使用 Taction 的技术，我们将提起上诉，」公司在声明中称。（来源：快科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;OpenAI 和 Anthropic 正在调查数万起 AI 相关安全事件&lt;/h2&gt;
+&lt;p&gt;9 月 27 日消息，据 Axios 报道，OpenAI、A</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H497"/>
+  <dimension ref="A1:H498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20910,6 +20910,40 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 08:06:58 +0800</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>传 OpenAI 29 日推个人 AI 助手；AI 专家偏远地区买地，担心「AI 失控」；挖掘机能自动「挖沟」，网友：蓝翔还能开几年？</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371044</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr"/>
+      <c r="F498" s="2" t="inlineStr"/>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d6/78/d678b52737e79ba9795dfdc014363ccd.png" /&gt;&lt;/p&gt;&lt;h1&gt;消息称 OpenAI 将推出常驻 AI 助手「O」，预计 9 月 29 日发布&lt;/h1&gt;&lt;p&gt;9 月 27 日消息，据消息人士 Alexey Shabanov 昨日透露，OpenAI 即将推出一款常驻 AI 助手，其代号为「O」，预计将在 9 月 29 日的 OpenAI DevDay 推出。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/28/c2/28c2ba9d1abbe87b3eca0d49c48add53.jpg" /&gt;&lt;/p&gt;&lt;p&gt;据报道，ChatGPT 的配置文件中已经出现了许多与「O」相关的线索，包括将「O」设置为显示名称、配置「-o」的电子邮件后缀。综合这些线索来看，这款智能体预计将能够在普通聊天之外持续运行，还可能拥有独立身份。&lt;/p&gt;&lt;p&gt;同时该项目可能与「Aeon」有关。此前已有消息称，Aeon 是 OpenAI 常驻型智能体项目使用的名称。不过我们目前尚不清楚它支持哪些任务、具备拥有何种权限，以及是否支持定时任务、记忆功能或何时开放。&lt;/p&gt;&lt;p&gt;值得注意的是，此前曾有传闻称 OpenAI 正在研究一款甜甜圈形状的硬件。因此这些项目如果能产生关联，单字母代号可能会成为一种有趣的双关。（来源：IT 之家）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/57/c6/57c63c3153019055d2b242f2323939f0.png" /&gt;&lt;/p&gt;&lt;h1&gt;部分 Anthropic 资深员工考虑在偏远地区购置土地，以防「AI 失控」&lt;/h1&gt;&lt;p&gt;9 月 27 日消息，为防范人工智能彻底失控，Anthropic 的数位资深员工正在悄然制定具体的应急预案。&lt;/p&gt;&lt;p&gt;据华尔街日报于当地时间 9 月 26 日报道，最近数周内，Anthropic 的部分早期员工曾向业界同行透露，他们正打算在美国偏远荒僻的地区购置土地建造隐匿点，以便在「AI 走向失控反噬」之际举家撤离避难。&lt;/p&gt;&lt;p&gt;对这个圈子而言，「逃离 AI」的念头早已屡见不鲜。据早期离职员工回忆，早在 Anthropic 创立初期的公司聚餐中，大家就曾热烈推演过一种极具「曼哈顿计划式假想」的情景：他们未来可能随时被政府征调至荒芜的沙漠深处，在具备全套防电磁脉冲屏蔽功能的绝密军事基地内，闭门继续研发前沿 AI。&lt;/p&gt;&lt;p&gt;据报道，Anthropic 员工们在内部的私密 Slack 频道中推演各类末日毁灭情景并探讨应对预案；他们甚至将一句格言制成贴纸贴在笔记本电脑外壳上，将其奉为行事信条：「一切再难重归平静」。&lt;/p&gt;&lt;p&gt;针对这一文化现象，Anthropic 发言人回应称，公司目前拥有超过 3,500 名员工，内部对于技术的探讨呈现出极其多元的观点与立场。（来源：IT 之家）&lt;/p&gt;&lt;h1&gt;上线 66 万英伟达 Blackwell GPU，马斯克要把 Colossus 2 建成全球最大 AI&lt;/h1&gt;&lt;p&gt;9 月 27 日消息，马斯克旗下 AI 公司 xAI 正推进位于孟菲斯的 Colossus 数据中心项目。该项目于 2024 年开工建设，一期工程 Colossus 1 已投入运营，主要采用英伟达 Hopper GPU；二期工程 Colossus 2 同样落地孟菲斯，并将主要采用英伟达 Blackwell GB300 GPU。&lt;/p&gt;&lt;p&gt;马斯克表示，Colossus 2 计划在 2026 年底前上线 66 万块英伟达 Blackwell GPU，整体部署规模超过 50 万块 AI GPU。&lt;/p&gt;&lt;p&gt;由于 GPU 是人工智能建设中最稀缺的资源之一，Colossus 2 被视为全球最大数据中心之一。xAI 借鉴特斯拉的做法，将 Colossus 称为其计算领域的「超级工厂」。&lt;/p&gt;&lt;p&gt;对于 Colossus 2，马斯克称其当前运行着 11 万块 GB200 GPU 和 44 万块 GB300 GPU。他还给出了分阶段上线计划：本周末将再上线 22 万块 GB300，11 月底再增加 22 万块，最后一批 22 万块预计在 2026 年 12 月底前上线。&lt;/p&gt;&lt;p&gt;马斯克的最新表态，是其</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H498"/>
+  <dimension ref="A1:H523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20944,6 +20944,856 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 10:11:32 +0000</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>央视报道|空翻360°、跳舞自如，IRMO外骨骼柔性具身智竞未来</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13473</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr"/>
+      <c r="F499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>面向未来，IRMO外骨骼机器人将持续迎接真实世界的更多落地挑战，让柔性具身技术真正落地、上岗。</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 09:06:09 +0000</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>全国首个搭载国产电子架构的人形机器人正式发布，逐际动力携手东土科技共建产业生态</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13466</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr"/>
+      <c r="F500" s="2" t="inlineStr"/>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>历史性时刻，为国产机器人补齐“神经系统”</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:48:56+00:00</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>A Day in the Life of a Roboticist: Charlie Kemp</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>https://robotsguide.com/learn/a-day-in-the-life-of-a-roboticist-charlie-kemp</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr"/>
+      <c r="F501" s="2" t="inlineStr"/>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Building useful robots starts with understanding the people who use them. For Charlie Kemp, cofounder and chief technology officer of …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 00:49:30 +0000</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>李飞飞创业公司被苏姿丰550亿收购！世界模型最大交易落地</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/499098.html</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr"/>
+      <c r="F502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>李飞飞将入职AMD首席科学家</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:52:15 +0800</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT 发布后，马斯克老师的 100 条迷思</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371467</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr"/>
+      <c r="F503" s="2" t="inlineStr"/>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 4 月 6 日&lt;/p&gt;&lt;section&gt;&amp;nbsp;&lt;span&gt;一开始，马斯克很兴奋。&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;他和所有人一样陷入了 ChatGPT 狂热。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/00/e0/00e02aa6c98af07f4b2e1773b8457b20.png" /&gt;&lt;/section&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/87/51/875175575842d1efc1e7e9110b83fbbb.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;没两天，不知道发生了什么，马斯克发现事情不对头。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「ChatGPT 好得有点可怕了。我们距离危险的强人工智能不远了。」&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/2e/3f/2e3feadf8673987fef7356835be27b1a.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;他马上行动做出应对。他取消了 OpenAI 对推特数据库的访问，这原本是收购推特前就在合同中白纸黑字写着的。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/7f/a4/7fa4457c94595af5137d07e3ac86f15d.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;从这以后，作为推特老板的马斯克老师就开始&lt;strong&gt;占据「人工智能危险论」的舆论高台&lt;/strong&gt;。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/97/07/9707a43e8ccb796b4b2e573409596ffd.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;并且开始阴阳怪气了。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/40/53/4053ee26c93baf2b4a5bf60207dfbf1c.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;2 月 2 日，马斯克在回复一名用户提到的 ChatGPT 对保守派存在政治偏见时，他提到「这是一个严重的问题」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/7d/e1/7de15f5b5dcc8bfb5e22bb3617946c07.png" /&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;2 月 18 日，针对网友上传的与 GPT 有关审查政策的对话（GPT 表示遵守道德与语言使用相关政策，避免可能的攻击性冒犯性言论），马斯克和另一名网友讽刺的 OpenAI 的「open」属性。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/0c/97/0c974ff3246802c9b59673acad62f627.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;马斯克还抨击了那些对 AI 危险性无动于衷的人。他发了一张梗图：「当你参加派对时，我研究了 ChatGPT。当你有婚前性行为时，我掌握了 Stable Diffusion。当你为了追求虚荣而在健身房浪费时间训练时，我正在训练机器学习模型。现在全世界都要完犊子了，AGI 都到眼跟前了，你好意思来找我帮忙了？」&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/60/7f/607f784757b7482f88dd9321e8617560.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;sp</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:50:32 +0800</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>千人联名叫停 AI 研究？是个好问题，但更像一场行为艺术</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371466</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr"/>
+      <c r="F504" s="2" t="inlineStr"/>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 29 日&lt;/p&gt;&lt;section&gt;&lt;span&gt;马斯克和「深度学习三巨头」之一的 Bengio 等一千多位学界业界人士，联名呼吁叫停 AI 大模型研究的新闻，刷屏网络，掀起轩然大波。&lt;br /&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/76/42/76424d9b8f3a692cbde3e5e2e69eb3d4.jpg" /&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;GPT 的研究会被叫停吗？在学界业界看来，AI 真的会对人类产生威胁吗？这封联名信是证据凿凿的警示还是徒有恐慌的噱头？支持者、反对者纷纷表态，吵作一团。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;在混乱中，我们发现，这份联名信的真实性和有效性都存在问题。很多位列署名区的人们，连他们自己都不知道签署了这封联名信。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;另一方面，联名信本身的内容也值得商榷，呼吁人们重视 AI 安全性的问题当然没错，可叫停 AI 研究 6 个月，甚至呼吁政府介入，等待相关规则、共识的制定。这种天真且不切实际的做法，在科技发展的历史上实属少见。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;与此同时，不少人发现，OpenAI 开放了一批 GPT-4 API 的接口申请，开发者们正兴奋地想要将这轰动世界的技术成功应用在他们的产品中。Pre AGI 时代的序幕，已经缓缓拉开。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;AI 会停下来吗？AI 能停下来吗？&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;又或者像网友所说的，你想要叫停福特 A 型车的量产吗？&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/ec/8f/ec8f7ebbe517aeb26d73e6cb40722fd3.png" /&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;在福特 T 型车退出市场后，A 型车帮助福特重新夺回汽车销量的头把交椅。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;截至发稿前，Founder Park 发现，联名信签名人数从 1125 减少为 1123 人。&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;注：极客公园记者凌梓郡对本文亦有贡献。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;联名信说&lt;/span&gt;&lt;/strong&gt;&lt;strong&gt;&lt;/strong&gt;&lt;strong&gt;&lt;span&gt;了什么？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;在 Future of Life Institute（FLI）的官网上，有着公开信的全文内容，总结如下：&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;公开信呼吁所有人工智能实验室，至少在 6 个月内立即暂停训练比 GPT-4 更强大的人工智能系统研究包括当前正在训练的 GPT-5。&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;这封信认为，具有人类竞争力的人工智能系统可能对社会和人类构成深刻的风险，因为这已经得到了广泛的研究并得到了顶级人工智能实验室的认可。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;此外，该信还呼吁 AI 实验室和独立研究者们，利用这个暂停时间共同开发和实施一套共享的高级 AI 设计和开发安全协议，并由独立外部专家进行严格审核和监督。这些协议应确保遵守这些协议的系统是安全的，而且必须有充分的理由证明这种信心，并随着系统潜在影响的大小而增加。&lt;/span&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;发起方是谁？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;Future of Life Institute：生命未来研究所创立于 2014 年 3 月，创始人为麻省理工学院宇宙学家马克斯·泰格马克，Skype 联合创始人让·塔林，哈佛大学博士生维多利亚·克拉科夫那（Viktoriya Krakovna），波士顿大学博士生、泰格马克之妻美雅·赤塔-泰格马克（Meia Chita-</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:47:43 +0800</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>张鹏对谈傅盛、王俊煜、潘乱：大模型时代，产品经理的机会在哪里？</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371464</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr"/>
+      <c r="F505" s="2" t="inlineStr"/>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 27 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;随着 GPT-4 的发布，我们可能已经进入了大模型时代了。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;随之发布的新产品，还有文心一言、Microsoft 365 Copilot、Midjourney V5、Google PaLM API 等等，基于大模型开发的各种新产品也开始涌现：Notion AI、New Bing、Jasper……大模型带来了全新的创新机会，产品经理们的春天到来了，但也有人说，大模型可能会让很多产品经理和工程师失业。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;大模型时代，到底需要什么样的产品经理和产品？创业的共识又是什么？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;关于这些问题，Founder Park 组织了一场圆桌讨论，由极客公园创始人 &amp;amp; 总裁张鹏和「乱翻书」主理人潘乱共同主持，特别邀请到互联网时代的优秀产品经理：猎户星空董事长傅盛、阅览室创始人王俊煜，来一起聊一聊 GPT-4 发布的划时代意义，以及从产品的视角，解读现阶段初具规模的大模型应用。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;注：圆桌讨论时间为 3 月 16 日，GPT-4 发布后，OpenAI 宣布 ChatGPT 支持插件前。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;p&gt;▶️ 此处为视频内容，请在微信「Founder Park」公众号内观看&lt;/p&gt;&lt;span&gt;&lt;span&gt;&lt;span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;GPT-4 很震撼，&lt;/span&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/h2&gt;&lt;h3&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;文心一言需要完善&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h3&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;潘乱&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：GPT-4 感觉特别震撼，文心一言，就像 Robin（李彦宏）一开始所说，的确存在差距，我觉得说得也蛮诚恳的，就是应该先上路。对于这次直播的反应，我觉得其中一方面原因是因为大家对它的期望过高，另一方面也有点苛责，毕竟现在这已经是最好的东西了。当然，目前它框架已经很好了，但仍需要更多的训练来完善。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;张鹏&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：没错，我觉得你说的很有道理。毕竟，ChatGPT 已经经过多次实验和数据模型调整，成为了目前非常优秀的对话模型。对比之下，即便是文心也需要经过长时间的测试和数据处理才能达到同样的水平。当然，这并不是说文心不好，我认为它能在国内跑得起来也是一件好事。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;傅盛&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：毕竟，GPT-4 才刚刚发布时，大家都很热衷于比较，这也是人们的本能反应。但从录播形式方面来看，百度可能有一些考虑，比如网络等问题，而这种形式可能并不被大家所接受。但总体来说，百度在中文方面还是有实力做出一个效果的，至少我认为还是有一定的水平和表现。而我和我的团队目前也在试用百度的接口，等试用结束后再做评价。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;潘乱&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：文心一言是国内目前能做出的最好的大模型了吗？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;傅盛&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：这个问题很难回答，因为很敏感。就我个人来看，百度一直专注于这个领域的研究和发展，而其他公司要从头开始研发可能是比较浪费时间和资源的。一般来说，训练模型需要的时间是很长的，单次可能需要一两个月，而&lt;strong&gt;百度能够在这么短的时间内推出文心项目，并且做到了这么好的体验，这是相当了不起的。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/fi</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:46:20 +0800</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>黄仁勋对话伊尔亚：关于科技 ，企业家和科学家之间最好的访谈</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371463</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr"/>
+      <c r="F506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 26 日&lt;/p&gt;&lt;section&gt;&lt;strong&gt;&lt;span&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/7a/0c/7a0c413617af036eb44d8348ab95ea2b.jpg" /&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;所有走出实验室，投身产业界的科学家们，都梦想过用钻研多年的科学技术改变&lt;/span&gt;&lt;span&gt;世界的那一天。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;就像伊尔亚·苏茨克维&lt;/span&gt;&lt;span&gt;这样。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这显然是一场英伟达策划的访谈，但主场的黄仁勋，比起身价千亿的商业巨子，更像是一个谦逊的学生。对于面前这位比他年轻二十多岁的科学家，他提问、请教，为一些共同的记忆面露欣喜。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;伊尔亚本人也是一样，回顾技术迭代的历史，他像翻开了家谱，细说自己在Hinton门下的收获，三言两语带出一长串为深度学习作出贡献的前辈和同僚们。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;对谈的干货很多，我们理所当然地感到惊讶——除了一个 GPU 如何帮助深度学习训练的简短问题，万字对话没有一句广告。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这是一段值得每一个关注当下这场 AI 革命的人都认真阅读的访谈。以下是访谈内容，由 Founder Park 整理编辑。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;注：完整字幕版视频在文末，如果你需要的话。&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;直觉告诉我，AI 一定会带来巨大影响力&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;黄仁勋&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：从我认识你以来，你做了很多开创性的工作。从多伦多大学开始，你与 Alex (Krizhevsky）和 Jeff Hinton 一起共同发明了 AlexNet，这带来了现代 AI 的大爆炸。你的职业生涯也把你带到了美国湾区，OpenAI 的创立，GPT-1，2，3。当然了，还有让 AI 风靡全世界的 ChatGPT。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;真是青年科学家的卓越履历，让整个行业都对你的成就由衷的敬佩。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;我还是追溯一下吧，来问问你，关于深度学习的一些问题。你对深度学习是什么认识？为什么你知道它会发挥作用？你心中就一定认为深度学习会取得如此成就吗？&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;伊尔亚&lt;/span&gt;&lt;/strong&gt;：我个人对人工智能的兴趣有很多原因，出发点就是对 AI 巨大影响力的直觉性认识。同时，我也对究竟什么是意识充满了好奇，究竟什么是人类的体验？我觉得 AI 的发展能帮着我去理解这些。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;2002 - 2003 年，那个时候「学习」是一件只有人类，或普通人就能做的事情，计算机完全办不到。那时，计算机还不会学习任何东西，甚至在理论上是否可行都不太清楚。所以我想如果能在智能学习或者机器学习方面做出一些成果，将很有可能成为 AI 领域的最大进步。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;我开始在这个领域做一些探索，一开始还没有那么乐观。但幸运的是，Jeff Hinton 在我念书的大学任教，我得以联系到他。他的研究方向就是神经网络，这就是我想要的。因为神经网络能够缔造一种可以学习、可以自动编程的并行计算机。那个时候并行计算机还很小，但是希望在于，如果你弄明白学习和神经网络的工作原理，那你就可以从数据中去编程小的并行计算机，而它与大脑的工作原理是相似的。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;所以，就好像有了几个理由可以支撑你继续走下去，但是还不太清楚如何让它起作用。然而基于已有的所有东西，似乎表明它的前景是最光明的。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/6f/14/6f1493e7dad2197bfcedffdc4c73d111.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;h2&gt;&lt;strong&gt;&lt;spa</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:44:51 +0800</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT 支持第三方插件，创业者的机会在哪里？</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371462</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr"/>
+      <c r="F507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 25 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;3 月 24 日，OpenAI 又公布了重磅消息，ChatGPT 支持接入第三方插件，并且一口气上架了 11 个插件。通过这些插件，用户可以用 ChatGPT 购买商品，预定酒店、机票，搜索专业数据等，这大大解放了 ChatGPT 的生产力，也多了更多的可能性。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;关于插件功能的未来发展可能性，我们看到了很多讨论，出门问问创始人李志飞认为这是「AI 巨大的转折点」；阅览室创始人王俊煜，则认真研读了 OpenAI 的开发文档，试图梳理出插件的更多可能性；懂技术又懂哲学的微博博主木遥则认为这可能是自然语言编程的新开始。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在获得几位授权后，我们迅速整理了这些讨论，分享这个消息纷繁日新月异的环境下，一些来自创业者和技术人员清晰的思考。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;李志飞&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;AI 的巨大转折点&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;出门问问 创始人 &amp;amp; CEO&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;OpenAI 插件可以连接 ChatGPT 与第三方应用，通过接入你的应用做什么呢？举一些例子：&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;实时检索信息，例如赛事的实时比分情况、股票价格、最新资讯等；&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;检索知识库，例如针对你个的人电脑、针对公司的文档知识库等，进行更智能地检索、调用、对话；&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;代替用户执行操作（对现实世界的「智能调度」）：例如买机票酒旅、网购、订外卖等。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;总结来看，逆天的ChatGPT Plugin 主要体现在以下三个方面：&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;独立上网&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;现在的 ChatGPT 已经能够独自上网，访问网页并将其内容传输至 ChatGPT，然后根据该内容生成答案，并将相关网页链接信息附加于答案中。这类似于 New Bing 的功能，此举难道预示着微软和 OpenAI 或将貌合神离？比如你可以问 ChatGPT「哪位演员、哪部电影获得了此类别的奥斯卡？」结果可以看到，ChatGPT 在聊天界面就多出来「浏览」结果，直接得到了 2023 年的最新结果。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/d6/e2/d6e29e4828339bbdbd483ba2ab7bbfd5.png" /&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;自主编写并执行程序&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在这次重大更新中，ChatGPT 实现了自主编写和执行代码的功能。以前，ChatGPT 仅支持生成代码，但生成的代码还需要复制到其他执行器上才能运行。现在，ChatGPT 内嵌了 Python Code Interpreter，将代码编写和执行合二为一。这一改进特别适用于处理大量计算、数据分析和文件格式转换等任务。官方解释指出，代码解释器采用 Python 处理上传和下载的实验性 ChatGPT 模型。目前，主要提供以下功能：解决定量和定性的数学问题、进行数据分析和可视化，以及实现不同文件格式之间的转换。按照这个趋势，感觉 GitHub Copilot 的打开率会下降？当 AI 拥有了自己的智能、计算、存储和执行环境，还需要我们人类做什么？&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/fa/73/fa7330a9f0d85eba7525a549115d3987.png" /&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:43:24 +0800</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>李彦宏复盘文心一言：和 GPT-4 还有多少差距？</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371461</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr"/>
+      <c r="F508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 24 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;李彦宏当然知道有差距。GPT-4 发布之后，百度团队焦虑地意识到，他们与 OpenAI 的差距被进一步拉大。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「&lt;strong&gt;我们差不多是 ChatGPT 今年 1 月的水平，但大家早就忘了 1 月份它是什么样子。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在我们与李彦宏的这场访谈中，他认真地复盘了文心一言发布前后的方方面面。技术差距、用户需求、国际竞争，以及中国大模型的创业者们该如何选择。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「&lt;strong&gt;创业公司完全不用担心市场是不是足够大&lt;/strong&gt;」，谈到文心的时候他也是这么说的，「&lt;strong&gt;只有出来之后才有机会更快地去迭代，去提升&lt;/strong&gt;」&lt;span&gt;。&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「&lt;strong&gt;嗯，开始行动就好。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;以下是对谈内容，经 Founder Park 编辑整理。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;本次对谈嘉宾：&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;李彦宏 百度创始人、董事长兼首席执行官&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;strong&gt;&lt;span&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;张鹏 极客公园创始人、总裁&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;骆轶航 品玩创始人、CEO&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;蒋涛 CSDN 创始人、CEO&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;李彦宏：3 月 16 日内测是我拍板的，&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;对文心一言达到的水准比较满意&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;张鹏：我相信百度作为在中国第一个内测类似于 ChatGPT 这样类型的产品，本身是个情理之中，但速度又有点意料之外。我听到外界一个有意思的传说，说百度经历过大概 40 天的冲刺，然后能够迅速交付产品出来，让大家非常吃惊。所以我挺好奇这 40 天冲刺到底经历了些什么？能不能给我们讲讲文心一言诞生的过程？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;李彦宏&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：40 天这个说法我也没有听说过。百度做人工智能十几年了，我们做语言大模型也有几年的时间，就是从 2019 年文心 1.0 版本发布到现在也有近 4 年的时间，这期间文心 1.0、2.0、3.0 都发布了。去年 11 月 30 号 ChatGPT 发布，我们去试了一下，确实有惊艳的感觉，觉得比以前的大模型，尤其是在内容生成方面有很大的跃进。从那时候开始，内部确实压力比以前更大。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;中国这个产业环境里，我接触到的很多人其实都在问「百度有吗？你们要不要做一个这个东西？」，我们因为这些年一直在做语言大模型，确实也很重视，从 2019 年到现在，包括我个人也花了不少时间跟团队去讨论这个大模型到底会向什么方向发展，会有什么样的应用，到底有多大潜力，我们应该投多少资源等。但是到最后其实有点被舆论裹挟着，越来越觉得我们需要尽快推出一个对标 ChatGPT 的大语言模型。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;内部在发布之前两个月里，工作压力是蛮大的，大家日夜奋战，有很强的危机感。刚刚做出来的时候，内部评测确实不行，虽然提升速度很快，但是不确定什么时候可以发布。整个过程我们也不断地在内部讨论到底什么时候可以发布。我当时是拍了个板，说 3 月份一定要发。团队没有那么有信心，担心 3 月份做不出来。我就说即使那个时候做不出来，我们再去跟公众解释说，我们稍微 delay 了一点，我觉得也 OK。但我们现在就要说出去，3 月份就要发。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;我这样做确实是有意</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:42:00 +0800</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>拥抱东南亚市场前的「思想准备」，都在这 3 个问题和 8 个回答中</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371460</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr"/>
+      <c r="F509" s="2" t="inlineStr"/>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 20 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;东南亚是一个充满活力的市场区域，但不是每个人都适合，更不是所有人都能赢。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;为了帮助更多创业者在全球化的过程中，少走弯路，快速布局全球市场，Founder Park 发起并建立「Global Ready」社区。「Global Ready」社区联结已经全球化的优秀创业者、投资人以及行业专家，通过分享、交流讨论、沉浸式实地考察等方式，帮助准备出海创业者拿到「更小颗粒度」的世界地图，丰富对海外市场的了解和认知，打开全球化视野。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;近期，Global Ready 社区邀请到 ATM Capital 创始合伙人屈田。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;屈田 2007 年加入原阿里巴巴集团战略投资部，作为元老级人物，他参与投资美团、UC 手机浏览器、PPS、搜狗、丽人丽妆等公司，之后自己也投过水滴、涂鸦智能等上市公司。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;2017 年屈田决定出海东南亚，创办专注东南亚的风投基金 ATM Capital，主导投资东南亚最大的快递公司 J&amp;amp;T Express，新兴美妆品牌 Y.O.U 等，他对电商及基础设施、新消费、金融科技等领域有独特的视野和见解。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在本场「Global Ready」社区活动中，&lt;strong&gt;屈田从多个维度拆解东南亚市场的情况，分享近几年在东南亚的投资心得和体会，并梳理了创业者出海东南亚时最容易犯的一些错误，以及应该首先掌握的常识。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;以下为屈田的部分分享内容总结：&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;Q1&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;创业者在东南亚市场上常见的&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;三个常识性错误是什么？&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;1、完全照搬「中国模式」&lt;/span&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;回想我当年在中国做投资时，做的最多的就是「Copy to China」。外加上「时光机理论」，后来&lt;strong&gt;我开始做东南亚投资时的思维方式是「Copy from China」&lt;/strong&gt;。毕竟中国移动互联网发展了十几年，无论是 B2B、B2C、O2O 甚至是 P2P，都有很清晰的商业模式，也有现成的历史发展轨迹和失败教训作为参考。出海东南亚，无非就是再走一遍我们过去 10 年走过的路，重新来一遍就行。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;我当时把全球市值高的公司、成功的商业模式拎出来做成产业地图，看看东南亚还缺哪些产业，挑选一个看起来不错的领域，就准备直接 All in 了。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;但是当我真正深入到东南亚才会发现，原先的很多设想都是想当然，不是所有的商业模式都能「抄」到东南亚。&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/6c/f4/6cf48625827b364d57d2f8ede3a69164.jpg" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;以电商行业为例，想要完全 Copy from China 就很困难，东南亚的消费习惯、在线支付、物流基础跟中国相差巨大。比如说，东南亚消费者对于价格十分敏感，所以电商平台每个月都会有促销活动，一搞促销活动，快递网络的「带宽」就容易拥挤，快递爆仓是家常便饭。光是快递问题就够商家头疼了，但这是基础设施问题，并不是一个创业者能解决的。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;再比如&lt;strong&gt;东南亚市场不是一个统一的大市场，就不存在一个统一的所谓的「东南亚战略」&lt;/strong&gt;，而是印尼、越南、菲律宾、马来西亚、泰国、新加坡每个地方的战略可能都不同。而且</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:40:28 +0800</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>每天都在改变世界！这绝对是 AI 史上最疯狂的一周</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371459</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr"/>
+      <c r="F510" s="2" t="inlineStr"/>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 18 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;真是疯狂的一周。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;GPT-4、Microsoft 365 Copilot、Midjourney V5、Google PaLM API、文心一言，一颗颗 AI 大模型领域的重磅炸弹，扎堆在这周引爆。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;GPT 开启了大模型的多模态应用，微软说让工具回归工具，Midjourney 解决了 AI 作画的手指问题，学术界与开源势力也不甘落后，中国互联网公司总算有了第一个大模型产品......&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;像创世纪一样，日新月异。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;我们从没有像今天这样，好奇两个月后的世界会变得如何。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;但我们首先要做的，是记住这不寻常的一周。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;span&gt;注：封面&lt;/span&gt;&lt;/span&gt;&lt;span&gt;图片由 DreamStudio 生成，prompt：god。产品发布时间以北京时间为准。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;周一&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;暴风雨前的平静。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/87/48/87487cbd37bfa1aa11b33cbb74449480.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;图片由 DreamStudio 生成&lt;/span&gt;&lt;/p&gt;&lt;h3&gt;&lt;br /&gt;&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;周二&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;低成本：斯坦福大学发布 Alpaca 7B&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h4&gt;&lt;strong&gt;&lt;span&gt;成本降到超低，性能匹敌 GPT-3.5&lt;/span&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/h4&gt;&lt;p&gt;&lt;span&gt;斯坦福大学推出了由 Meta 的 LLaMA 7B 微调而来的全新模型 Alpaca。仅用 52k 数据，性能约等于 GPT-3.5。关键是训练成本奇低，不到 600 美元，评估效果与 GPT-3.5 相当。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这意味着人们可以以更低的成本获得与 GPT-3.5 相当的性能。&lt;/span&gt;&lt;/p&gt;&lt;h4&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;低门槛：清华发布 ChatGLM-6B&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h4&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;消费级显卡就能部署，准确度接近 GPT-3 175B (davinci)&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/07/b4/07b41a68dc25c83173d0b1e396ed715e.png" /&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;下面是 ChatGLM 的自我介绍：&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;由清华技术成果转化的公司智谱 AI 开源了 GLM 系列模型的新成员——中英双语对话模型 ChatGLM-6B，支持在单张消费级显卡上进行推理使用。虽然依然会有和 ChatGPT 一样的事实错误、胡说八道的问题，但作为开源模型，ChatGLM-6B 可以在消费级显卡上部署使用。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;周三&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;OpenAI：GPT-4 来了！&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h4&gt;&lt;span&gt;&lt;/span&gt;&lt;/h4&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;人类历史上最慌的一天&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/70/dc/70dc2cf9718b01c800bc292221c649f5.png"</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:38:40 +0800</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>微软这次牛在哪？怎样和微软学大模型落地？</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371457</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr"/>
+      <c r="F511" s="2" t="inlineStr"/>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 17 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;昨晚微软发布了基于 OpenAI GPT-4 的全新办公系统 Microsoft 365 Copilot，一时间刷屏网络，引得人们感叹技术进步之快。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在众多的讨论中，我们也看到了两个不一样的声音——两位创业者，从产品和技术细节的角度，分析了微软的做法，以及它对行业可能会产生的影响。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在获得两位授权后，我们迅速整理了这两条短评，分享这个消息纷繁日新月异的环境下，一些来自创业者清晰的思考。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;李志飞&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;微软焕发新春&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;Google 尚能饭否？&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;出门问问 创始人 &amp;amp; CEO&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;刚刚看了 Microsoft Dynamics 365 Copilot 的发布会，太震撼了，这是我的几点感受：&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;1. 牛得不像微软：把 GPT 的能力全面用到了各种 Office 工具里，无论是从 Word 内容自动生成 PPT、还是倒过来，都是一个自然语言命令的事情。Team 开会时，自动给你总结前面的人说啥了、还有啥问题没解决，让你随时展示存在感。商务会议时，自动帮你把以前的交流总结出来，让每个 BD 都有自己的秘书。只能说，太香了！&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;2. OpenAI 和微软轮番上阵：&lt;/span&gt;&lt;span&gt;昨天 GPT-4，今天 Copilot，都是让人听得热血沸腾的创新，这不是预谋是啥？&lt;/span&gt;&lt;span&gt;Google 你还能饭否？&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;3. LLM 的 grounding：&lt;/span&gt;&lt;span&gt;把这个体验做出来不是随便接个 GPT 接口，而是一个系统性工程（见下图）。&lt;/span&gt;&lt;span&gt;喜欢胡说八道的 LLM 接在 Microsoft Graph（也就是你的数据）上，终于接地（所谓 grounding）了，然后给 apps 提供一本正经的自然语言服务。&lt;/span&gt;&lt;span&gt;这给大家提供了 LLM 怎么跟具体数据和应用场景结合的完美示范。&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;4. 创新的 lead time：&lt;/span&gt;&lt;span&gt;无论是 GPT-4、还是 Copilot，它们跟 iPhone 刚出来一样，用户立马都想用，竞争对手立马就想 copy 一个。&lt;/span&gt;&lt;span&gt;但是，无论对手多厉害，也得自己熬夜大半年才能搞出来吧，到那时 OpenAI 和微软又不知道搞出啥了，这就是创新的 lead time。&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/a4/76/a476f43d9baa74dd01d625251433c120.jpg" /&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;总之，这彻底颠覆了我对微软的印象，&lt;strong&gt;一个 48 年的公司再次焕发青春活力，真是史无前例啊！&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;王晓东&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;细分行业「小模型」的&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;范本教材&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;邻动 创始人 &amp;amp; CEO&lt;/span&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;微软「落地」的整个流程，可为各细分行业做「小模型」创业作为学习的范本。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这几天，微软/百度/谷歌等轮番有 AIGC 相关的发布（也要为百度加油！）。&lt;/s</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:37:16 +0800</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4 发布后的 20 个小时</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371456</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr"/>
+      <c r="F512" s="2" t="inlineStr"/>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 15 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;「活着，在此时此刻，是历史上最好的时刻。&lt;/span&gt;&lt;span&gt;」&lt;/span&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;OpenAI 的推文下，有人感叹幸运。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;北京时间 2022 年 3 月 15 日凌晨 1 时，OpenAI 发布 GPT-4。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;更新、功能、应用，和它好像炫耀的考试成绩，我想你们都知道了。这里不再赘述，还没补课的可以看 Founder Park 今晚推文的次条。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「我不关心它是不是 AGI，GPT-4 就是超越想象的革命性技术。」一位开发者兴奋地分享自己不到 60 秒做出的游戏，「一切都将改变」。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这句话我们听过很多次，但似乎是挺久以前了。像是，10 年前？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;这是来自 Founder Park 团队的一条简单的推文，仅仅分享过去 20 小时里，我们看到的 Post GPT-4 的世界。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;p&gt;▶️ 此处为视频内容，请在微信「Founder Park」公众号内观看&lt;/p&gt;&lt;span&gt;&lt;span&gt;&lt;span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;3 月 16 日（周四）晚 8 点 30 分，Founder Park 会在视频号直播间聊一聊 GPT-4 将会带来的改变，解读一些当下已经非常热门的 LLM 产品，我们邀请你一同探讨。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;媒体&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;科技媒体更乐观，&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;大众媒体却更悲观&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;h3&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;麻省理工科技评论：OpenAI 越来越商业了&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h3&gt;&lt;p&gt;&lt;span&gt;MIT 认为 GPT-4 可能是迄今为止最好的多模态大语言模型，但是随着大模型行业的竞争者越来越多，OpenAI 更多把这个版本当做了一个产品的更新，而不是一个研究更新。比如微软、Stripe、冰岛政府等已经使用了 GPT-4，其他公司还在苦苦排队中。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;但是 GPT-4 到底有多大，为什么会更好，OpenAI 却没有说。GPT-4 可能是该公司有史以来最神秘的版本，也标志着它从非营利性研究机构向盈利性技术公司的全面转型。&lt;/span&gt;&lt;/p&gt;&lt;h3&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;TechCrunch：GPT-4 为视力障碍者提供了新的希望&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h3&gt;&lt;p&gt;&lt;span&gt;在详细介绍了 GPT-4 的技术参数后，关注科技创业的媒体 TechCrunch 对于 GPT-4 的图片识别功能比较关注，单独介绍了这项功能和 Be My Eyes 这款应用。&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;我们的城市对于视力障碍者非常不友好，GPT-4 的这项功能很实用。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;对于 Be My Eyes 来说，人类志愿者仍然是有用的，他们无法被取代，只是一些简单的识别可以让 AI 来做了。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;span&gt;AI 的进步被迅速应用于帮助到人们的工作中，这是让人振奋的。&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;h3&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Wired：GPT-4 仍有缺陷，但离真正可用越来越近了&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h3&gt;&lt;p&gt;&lt;span&gt;科技媒体 Wired 对于 GPT-4 的发布似乎更为冷静一些，他们认为 GPt-4 让 ChatGPT 更加智能，但是也没有修复一直以来的缺陷：事实性错误以及瞎编乱造、明显的社会偏见、以及在某些提示下行为不端或者扮演了令人不安的角色。&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:35:37 +0800</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>和大模型创业者聊一聊：ChatGPT 火了，国内创业者的机会在哪里？</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371454</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr"/>
+      <c r="F513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 14 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;ChatGPT 火了，而且不是一般的火。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;当地时间 3 月 8 日，微软宣布，随着必应预览版新增用户超过 100 万，必应搜索引擎的日活跃用户首次突破 1 亿。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;一切似乎正如英伟达创始人黄仁勋所说，ChatGPT 是人工智能领域的 iPhone 时刻，全球范围已经掀起了一股 AI 创业狂潮，Product Hunt 的排行榜上看到的也几乎都是基于 GPT 创业的产品。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;而国内，大厂们也都官宣了自己的大模型计划。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;发展了多年的大规模语言模型（Large Language Model, LLM），为什么到 ChatGPT 才引起全球的震荡？这些年的进步到底在哪里？以及，如果想加入这场大模型的科技革命浪潮中，国内的创业者需要做什么，可以做什么？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;关于这些话题，Founder Park 组织了一场圆桌讨论，由&lt;strong&gt;极客公园创始人 &amp;amp; 总裁张鹏和「乱翻书」主理人潘乱&lt;/strong&gt;共同主持，特别邀请到中国大模型领域的多位创业者进行连麦：一起聊聊 ChatGPT 火爆背后，大模型的底层逻辑和未来应用。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;参与本次圆桌的创业者们分别是：&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;周明：&lt;/strong&gt;澜舟科技创始人 &amp;amp; CEO，中国计算机学会 CCF 副理事长，创新工场首席科学家&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;黄民烈：&lt;/strong&gt;清华大学计算机科学与技术系长聘副教授，聆心智能创始人&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;罗江春 ：&lt;/strong&gt;一览科技创始人 &amp;amp; CEO、风行在线创始人 &amp;amp; 董事&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;肖涵：&lt;/strong&gt;Jina AI 创始人 &amp;amp; CEO&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;&lt;strong&gt;龙海涛 ：&lt;/strong&gt;启元世界联合创始人 &amp;amp; CTO&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br /&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;ChatGPT 的&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;神通和局限&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;潘乱：ChatGPT 可以拆成 Chat 和 GPT 来理解，现在很多人都只关注 chat（聊天）的事情，但它是不是只是一个API？GPT 是大模型的一种。我想知道：Chat 和 GPT 现在是什么样的关系？目前除了 GPT 还有什么样的模型？大模型在这些年，经过什么样的演进到了现在这个样子？是否还有其他玩家？&lt;/span&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;周明&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：大模型不是随着 ChatGPT 出现的，而 ChatGPT 也不代表所有的大模型。2017 年谷歌推出 Transformer，2018 年推出 BERT，后面又推出 GPT 系列；还有 T5 系列；国内还有 ALBERT 等。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;大致可以分为三种：第一就是 BERT 系列代表的 encoder only（主要用于理解输入）；第二就是 GPT 代表的 decoder only（主要用于文本生成）；第三个 T5 代表的既有 encoder、又有 decoder。这三大流派都是往各自的方向发展，而且发展得也都不错。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;现在出现的 ChatGPT，在 GPT3 和 InstructGPT 的基础上又做了更好的改善，可以认为它是 better GPT3 &amp;nbsp;或 better GPT3.5。有 chat 的能力，能够通过 chat 来体现用户跟系统的交流，而且会更加流畅。从 PR（公共关系）的角度，因为所有人都可以通过 c</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:34:14 +0800</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>商用清洁机器人赛道，如何用 3D 机器人突围？ | Founder 100</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371453</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr"/>
+      <c r="F514" s="2" t="inlineStr"/>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 3 月 3 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;与家用扫地机器人相比，商用服务机器人可能会更快得到普及，尤其是商用的清洁机器人。普及的背后，是服务行业尤其是酒店行业的用工缺口的增大，根据《2022 中国酒店业发展报告》的数据计算，国内酒店业存在近 300 万的人才缺口。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;面对酒店等各种公共场所的清洁需求，2D 机器人似乎已经不能满足需求，天花板、墙壁、卫生间等各种复杂场景，更智能、更高效的清洁机器人成为新的突破点。作为国内最早从事机器人研究的企业之一，智能服务机器人公司景吾智能试图用配备了机械臂的 3D 清洁机器人，来解决酒店卫生间等场所的清洁需求。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在景吾智能创始人&amp;amp;CEO 郭震看来，相比 2D 机器人，「&lt;strong&gt;3D 清洁机器人拥有人形机器人三要素：手、眼、腿，机械臂作为终端通过眼的识别、腿的导航，自主实现更多复杂的动作，这是跨越简单平面而扩展到立体空间。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;为什么决定进入 3D 赛道，对于景吾智能来说，2D 场景已经是蓝海市场，而 3D 升维后可以拓展更大的市场。而另外一个重要的原因，则是「&lt;strong&gt;国内上游厂商的发展迅速，相关部件国产化程度大幅提高，成本的降低也成为大势所趋。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;技术的进步带来了产业的新突破，而对于未来 AI 可能会取代劳动力的观点，郭震对此却有不同看法。在他看来，「清洁机器人是补足劳动力的缺失，而不是替代劳动力」，在未来，AI 不会抢工作，最终是会使用 AI 工具的人和不会使用 AI 工具的人在抢工作。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/38/0e/380ee02d6cd1ae6aed61429ab7421af0.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;与其他地面清洁或者智能清洁机器人相比，现阶段的 3D 清洁机器人是一项高效的协同型智能产品，需要在清洁人员的启动设定下进行标准化的工作流程，与清洁人员共同完成整个空间的清洁工作。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;机器人还不会打扫、不会铺床，只是帮助清洁工人提高工作效率，不是来抢饭碗的，甚至能拿到的收入更多，所以（清洁工）是乐意接受这样的产品的。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;假设清洁机器人能够替代 10%-15% 的人工，按照人均 6 万元的劳动成本算，仅仅是地面清洁部分，就存在千亿级的蓝海市场，而如果突破「平面需求」，升维的机器人能够打开更大的市场。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;3D 清洁机器人突破了&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;平面清洁的空间限制&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：和其他商用清洁机器人相比，景吾智能的 3D 清洁机器人有哪些特点？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;郭震&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：3D 清洁机器人 A1H 是国内首款「ai+柔性机械臂」多功能及多项主流技术融合的复合型机器人产品，能够突破平面清洁的空间限制，实现地面以上的清洁工作。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;从技术层面上来说，它主要融合了当下 5 大主流科技：AI 视觉识别、机械臂运动规划、力控感知、高精度探索导航以及自主学习，所以能够在复杂环境、多对象的情况下精确完成使命。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;多功能：&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;可用于镜面、台盆、台面、</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:31:13 +0800</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>解决传统存储困境，DNA 存储的商业机会在哪里？ | Founder 100</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371451</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr"/>
+      <c r="F515" s="2" t="inlineStr"/>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 2 月 20 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;传统数据存储正面临能耗危机和原材料枯竭的问题。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;随着全球数据量指数级的增长，有数据显示，预测到 2040 年数据储存对单晶硅的需求量将达到 2 万吨。这一需求已经超过了当年全球的单晶硅总产量，以硅基为底的储存器可能跟不上大数据的需求。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;而数据中心对于电量的消耗也越来越大，2016 年我国数据存储的耗电量已经超过了三峡大坝全年的发电量。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;存储成本低，原材料充沛、而且可以实现超大容量存储的 DNA 存储应运而生。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「&lt;strong&gt;使用的移动硬盘作类比，1000 万块移动硬盘一屋子都垒不下，但却只要 50 克 DNA 就能实现相同容量信息的储存。&lt;/strong&gt;」中科碳元创始人&amp;amp;首席科学家戴俊彪是这么说的。不过现阶段限于技术成本，DNA 存储当前只能在特种领域如军方有应用市场。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;与传统存储相比，DNA 存储更适合「冷数据」，不需要经常读取但是数据量很大，「&lt;strong&gt;差不多有 80% 的数据都是属于冷数据，这类数据不在乎读写的速度有多快，而在乎能不能长久地保存下来。&lt;/strong&gt;」戴俊彪认为，这正是 DNA 存储可以发挥用武之地的地方，而且高便携、低能耗。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;DNA 存储目前的商业模式是怎么样的？如何优势如此明显，为何还没得到大规模推广？以及，国内 DNA 存储的技术发展与国际相比有什么差距吗？关于这些问题，我们也和戴俊彪聊了聊。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/b8/92/b8926b7fa2c191f237f973f18e6ab285.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;合成技术使得 DNA 存储有机会往商业化方向拓展，测序技术也使得技术能够满足这一部分的发展，近几年信息数据的增长也带动了需求的增长。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;中科碳元主要针对 DNA 存储的流程，从信息的编解码、到合成、到保存、到测序这几个环节，目前都已经有了很好的布局。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;不管是硅基存储也好，还是 DNA 碳基存储也好，这是相辅相成的两种介质，是相互支持和承载的状态。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;我国的基本技术跟国外是处于持平状态的，因为大家现在面临的状况都差不多；技术上总体处于一个相互平衡的状态，属于并行跑的状态。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;测序成本的下降&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;推动了 DNA 存储的商业化&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：和传统的数据存储相比，DNA 数据存储的流程是怎么样的，数据的复制和拷贝成本高吗？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;戴俊彪&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：一般的信息存储，就是把信息变成了 01 编码，以正负储存在硅基芯片上，0 代表一个极、 1 代表另外一个极，储存到芯片上。DNA 存储也很简单，就是把 01 再转换成 ATGC 碱基对，它的流程也跟计算机存储非常类似，信息先编码再解码的过程。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;信息编码和储存时，可以把信息先编译成 01，再把 01 变成 ATGC，只需要有一个编码和解码的算法开发标准。将信息都编译成 ATGC 以后，再对信息进行合成，因为 ATGC 是按照</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:26:36 +0800</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>成熟的工业软件领域，创业公司如何靠「图纸协作」切入赛道？ | Founder 100</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371446</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr"/>
+      <c r="F516" s="2" t="inlineStr"/>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 2 月 10 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;文档协作用飞书，UI 设计协作用 Figma，如今，在已经比较成熟的工业软件领域，也出现了不少文件协作尤其是图纸协作的工具。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;图纸协作对于机械制造企业的价值在哪里？在追光几何的创始人&amp;amp;CEO 吴星辉看来，「（如果图纸）协作流转出现了问题，每个环节都会受到影响。」而对于航空航天、汽车轮船这种复杂的产品，「&lt;strong&gt;图纸协作带来的问题不仅仅是效率问题，而是能否把产品做出来的问题。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;如果图纸协作这么重要，为什么现在才有工具试图去解决这个问题？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「从工业软件诞生的第一天开始就已经在解决了」，吴星辉是这么回答的，CAD、CAE 等工业软件一直以来都在解决机械设计，包括离散制造工作中流程提效的问题。&lt;strong&gt;追光几何所做的，只是在当前的技术变化下，基于工业数字化的发展，提出的新的技术解决方案。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;有点出乎意料的是，吴星辉并不认为上云或者全盘云化能够解决图纸协作的问题，在他看来，云化改变了文件管理的方式，但在文件版本管理及文件信息同步上，「&lt;strong&gt;云化本身只解决了很小程度的问题，其他问题的解决依然需要专业控制系统。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;「&lt;strong&gt;（对我们来说），当前产品的形态是围绕用户当前所处阶段做的呈现，未来也会去管理云化的文件。底层并不会受到云化趋势的影响，但落地形态会随着用户和技术趋势发展和变化。&lt;/strong&gt;」&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;不仅如此，关于产品应该选择 PLG 还是 SLG 模式，以及图纸协作工具的产品本质，还有 AIGC 对于工业设计领域的影响等问题，我们也在这次采访中和吴星辉进行了探讨。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/e0/12/e0128856a602d1900ae588a30d40112f.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;航空航天、汽车轮船这种复杂的产品，图纸协作带来的问题不仅仅是效率问题，而是能否把产品做出来的问题。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;很多领域的协同化都有一个共同因素，就是随着科技发展，社会分工越来越细，人却越来越贵了，大家希望提高效率。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;工业设计本质上是从不确定到确定的过程，在概念的时候有最大的不确定性，当变成产品的时候有最大的确定性，是一个熵减的过程。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;我们的定位是工业软件新物种，围绕知识流转的媒介——图纸（它是知识流的承载体），在产品全生命周期中去提高知识流转效率。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;在云文件版本需求上面，云化本身只解决了很小程度的问题，更多问题的解决依然需要专业控制系统。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;图纸协作&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;可以显著降低企业成本&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：机械制造产业如何看待软件的价值？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;吴星辉&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：分成几个维度，这些维度正好也是我从学校到公司成长过程中的维度变化。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;第一个</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:22:35 +0800</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>质量数字化如何成为制造业数智化的破局点？ | Founder 100</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371444</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr"/>
+      <c r="F517" s="2" t="inlineStr"/>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 1 月 18 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;从信息化到数字化，如今有了 AI 的加持，中国的制造产业正逐步走向数智化，但是如何让数智化更好落地，却遇到了不少问题。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;首先是消费侧和生产侧不同步的问题，淘宝、京东等一大批互联网企业解决了消费端数字化的问题，生产侧却没有同步跟上。在微亿智造&amp;amp;智云天工 CEO 张志琦看来，「&lt;strong&gt;大量企业基于数字化能力、模式诞生，无论是阿里、京东、美团等，但反观供给侧或者生产侧，却没有真正诞生一家巨头。&lt;/strong&gt;」生产侧无法高效数字化，产品质量的问题就始终存在，质量问题也成为了一个「很大的数字化断点」。智云天工的「超级虚拟工厂」，就试图解决这样的问题。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;其次是中小企业如何数字化的问题，「&lt;strong&gt;工业化 4.0 为什么在中国的土壤落不下来，一方面是没有很强的业务结果，另一方面的确是比较贵。&lt;/strong&gt;」张志琦说到。对于 SKU 很多而且生产周期比较短的中小厂商来说，自动化和 AI 厂商都无法满足他们的需求，而这些中小企业的质检所消耗的人力成本，接近 1400 亿人民币，这也正是智云天工和专注「工业 AI+机器视觉」以质检为切入点的厂商微亿智造合并的其中一个原因，用 AI 质检更好帮助企业提高质量，并且为一般制造企业提供数智化的服务，真正实现高质量的中国智造。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;中小企业的数智化到底应该如何解决，或许可以看看智云天工给出的回答。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/de/eb/deeb85ed90dab00caee2266d8babdc4a.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;今天很多厂二代对于数字化方面的理解，以及对于数字化工具的应用和使用，已经完全超越他们父辈。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;工业化 4.0 为什么在中国的土壤落不下来，一方面是没有很强的业务结果，另一方面的确是比较贵。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;大量企业基于数字化能力、模式诞生，无论是阿里、京东、美团等，但反观供给侧或者生产侧，却没有真正诞生一家巨头。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;以前质量检测是靠人做的，没有办法通过所谓数字化的能力把质检正常做完，所以造成了一个很大的数字化断点的缺失。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;数字化转型，最终的目标一定是以高质量为前提，通过数字化的手段和方式降本增效，满足消费侧最根本的诉求和需求。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;数字化有效解决了&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;剩余产能的问题&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：信息化和数字化到底有什么区别？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;张志琦&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：过去的信息化，当时信息技术处理的信息不多，更多是进行一定层次的数据的抽离和归集，比如 ERP 系统里存储的只有订单信息，或者是财务信息，很多时候把它从业务侧中抽取来做一定的数据的归集。但是数字化阶段有很大变化，机器在正常运转，无时无刻不产生更多的数据，已经不再是在业务管理系统中产生数据，而往往是车间层面、设备层面、传感器层面都有。近几年在大数据技术上有很大突破，核心在于数据的存储技术，存储成本越来越低，数据存储的成本和技术都有很大方面的提升。我们可以</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:08:28 +0800</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>智能眼镜平民化的新尝试：AR 泳镜 | Founder 100</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371439</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr"/>
+      <c r="F518" s="2" t="inlineStr"/>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2022 年 11 月 3 日&lt;/p&gt;&lt;section&gt;&lt;span&gt;智能眼镜一直是智能可穿戴领域里备受期待的设备，2013 年谷歌开始推出的谷歌眼镜系列虽然没能成功，但是也没能阻挡巨头们对于智能眼镜的热情。Facebook 在 2021 年推出了自家的智能眼镜 Ray-Ban Stories，小米也在今年推出了主打拍照的米家眼镜，就&lt;/span&gt;&lt;span&gt;连苹果，也一直传言要推出自己的 AR 眼镜。&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;span&gt;而一些新的创业者，则开始尝试为智能眼镜寻找一些更落地更平民化的使用场景。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;比如光粒科技推出的 Holoswim2 智能泳镜，结合了传统泳镜与防水手表的功能，在用户游泳过程中实时监控泳姿和各种身体数据。至于为什么选择泳镜赛道，&lt;strong&gt;「全世界至少有 6.3 亿游泳爱好者，群体基数很大。AR泳镜产品的推出可以极大地改变人们的生活。」&lt;/strong&gt;光粒科技的创始人&amp;amp;CEO 张卓鹏是这么说的。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在张卓鹏看来，解决所谓 AR 内容匮乏的问题，可以换个思路。「将当前的生态内容，如计算机时代的移动手机和智能手机时代的内容，搬运到智能眼镜上，足以让智能眼镜流行起来。」不一定非要局限于 3D 内容。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;智能泳镜会提供哪些独特的功能？目前 AR 眼镜的技术发展到哪一步了？商业化的前景又在哪里？关于这些问题，我们也和张卓鹏聊了聊。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;AR 眼镜的平民化时代，或许即将到来。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/9e/37/9e374c5ec01a7ef8088919dc7983a838.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;AR 泳镜本质上是一个更定制化的游泳教练，并且比目前的真人教练更了解客户的身体数据。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;行业无需将内容框定在 3D 和与现实交互中，当前时代的主要内容仍以 2D 为主。将 2D 内容移植到眼镜上已经能够成就一个巨大的飞跃。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;如果 AR 不被理解为增强现实，而是被定义为辅助显示，那么这个时间节点很快就会出现，甚至在 2024 年之前就会流行起来。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Holoswim2 智能泳镜&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;的不同之处&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：介绍下 Holoswim2 智能泳镜？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;张卓鹏&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：和普通泳镜相比，外观上两者差别不大。然而，AR 护目镜添加了一些光学模块和电子组件，数据可以在游泳过程中实时呈现给用户，其自身的运动传感器可以记录全部运动数据并提供实时分析。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;除了监测泳姿、距离和速度外，如果在眼镜上添加一些配件，还可以监测用户的心率。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;div&gt;   &lt;!--S 全屏播放 full_screen_mv--&gt;   &lt;div&gt;     &lt;div&gt;       &lt;div&gt;         &lt;div&gt;           &lt;div&gt;             &lt;div&gt;                                &lt;div&gt;&lt;/div&gt;                 &lt;div&gt;    </t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 09:52:54 +0800</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>数据红利时代，隐私计算如何解决数据安全问题？| Founder 100</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371434</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr"/>
+      <c r="F519" s="2" t="inlineStr"/>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 1 月 6 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;人工智能正成为新的生产力，而制约人工智能发展的大数据如何更安全地利用的问题，也成为当下大众关注的热点。如何在满足监管合规的条件下进行数据共享？如何在数据共享和融合的过程中保证隐私不会泄露？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;有需求，也有了相关的隐私法规，就有了「隐私计算」的解决方案。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在锘崴科技创始人 &amp;amp; 董事长王爽看来，&lt;strong&gt;「数据可用不可见」是隐私计算的本质价值之一。&lt;/strong&gt;可用是目的，不可见是安全要求。而围绕「可用不可见」，隐私计算的技术也是发生了多次迭代，到如今才开始在金融、医疗、政务等领域大规模应用。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;虽然各国早就出台了隐私相关的法规，比如欧盟的 GDPR 和国内的《数据安全法》，但是为什么直到今天，隐私计算才成为了大众关注的热点，王爽认为，技术的发展是一部分，而新出现的人工智能对于大数据的需求也推动了隐私计算的发展。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;也正因此，&lt;strong&gt;隐私计算处于高速发展的初期阶段，未来会经历数据网络的搭建、开放应用生态的构建，以及数据运营分润等阶段。&lt;/strong&gt;王爽说道，未来的商业模式也有更多可能性，甚至可能会与 Web3、区块链结合，面向 ToC 也有了新的可能性。甚至在某一天，&lt;strong&gt;个人数据的所有权是掌握在个人手里的，应该由个人来控制数据的使用，并且个人数据被使用以后的价值也应该反馈给个人。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;而关于大厂进军隐私计算行业带来的影响、以及隐私计算的技术壁垒问题，王爽也有很多想法。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/47/7f/477f59c433b28980dfd9ef7555093441.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;「数据可用不可见」是隐私计算的本质价值之一。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;当前隐私计算处于高速发展的初期阶段，未来会经历数据网络的搭建、开放应用生态的构建，以及数据运营分润等阶段。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;中国目前的年产生数据量在全球排名第二，也是全球第二大数字经济实体，通过国内这些促进数据经济发展的政策，我们拥有很多在数据层面上超越国外的机会。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;我们认为 ToC 是未来的一个趋势，因为个人数据的所有权是掌握在个人手里的，应该由个人来控制数据的使用，并且个人数据被使用以后的价值也应该反馈给个人。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;隐私计算商业化主要是三种模式，分别是：建设、开放应用和数据流量的分成费用。短期内建设比较多，从中长期来看，更多的是开放的应用和数据的分润。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;隐私计算行业正处于&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;高速发展初期阶段&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：隐私计算发展到现在，大致经历了哪几个关键阶段呢？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;王爽&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：隐私计算的发展从不同角度来讲，都有一些关键节点。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;span&gt;从应用的角度&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;：</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 09:51:28 +0800</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>云创远景：AI 如何让数据中心再降 15% 能耗？| Founder 100</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371433</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr"/>
+      <c r="F520" s="2" t="inlineStr"/>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2023 年 1 月 3 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;科技公司们为了给数据中心节能和散热，想尽了各种办法：将数据中心放在海底、北极；选择水冷、液冷的散热方式，而在当下全球都在朝着「碳中和」的背景下，如何降低耗能提高效率，减少碳排放，更是成为了一个要解决的焦点问题。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;AI 能不能帮上忙？谷歌在 2016 年开发了一款降低数据中心能耗的 AI，国内的创业公司云创远景，也选择了类似的思路：利用 AI 和边缘计算技术，来优化数据中心、大型超市和写字楼的能耗。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在双碳政策（碳中和、碳达峰）之前，由于 AI「过程的可解释性很低」，不少客户对于最终结果有很多疑问。而在双碳政策后，尤其是拿下了英特尔的订单后，云创远景突然多了不少的商业客户。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;为什么优先切入数据中心，云创远景创始人&amp;amp;CEO 沈骁是这么说的，「&lt;strong&gt;液冷或者自然冷源等更多地侧重于怎么用一度电产生更多能量，我们更多地在消费侧让它变得更有效率&lt;/strong&gt;」，在原有的节能基础上，&lt;strong&gt;云创远景的方案可以再降低 15% 到 20%。并且，他们不是取代原有的能耗方案，而是能与之配合，持续优化，并且，占用更少的人力投入。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;碳中和政策是如何影响能耗管理行业的？这个领域的技术壁垒是什么？除了数据中心，还有哪些行业可以切入？针对这些问题，我们和沈骁聊了聊，本次采访还邀请到了云创远景的投资方——变量资本管理合伙人吴江。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/0a/c6/0ac681a2743bf09cc22707ae14f98717.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;节能减排是国家对绿色能源的进一步推进以及对电驱动的产业扶持，碳中和在实际生产中更多体现在为了实现国家状态政策目标倒逼生产过程实现技术改造。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;海内外的各种现实因素加速双碳政策由政策驱动变成市场或经济驱动的过程。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;对于客户来说，一方面是降低了数据中心改善能耗对于人力的要求，另外就是提供了一个相对来说部署比较便捷的方式，更轻量化。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;AI 计算进行能耗管理的门槛体现在怎么用尽可能少的数据训练出比较准的模型，而不是传统的大模型数据学习。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;双碳政策提升了&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;能耗管理行业的商业需求&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：双碳政策之前，你们的商业合作是怎样的状态？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;沈骁&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：当时服务包括一些石油行业的客户和非常传统的集中供暖公司，拿到了他们在实际运行中的一些数据，发现在实际生产运行中，在温度的控制的链路上，其实有很多提升的空间。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;一开始看到了在很多流程控制的生产过程中可以提升的点。当时给用户阐述我们可以提供一个质量更加好的控制系统，控制系统其中一项效果就是满足控制目标过程中的能量节省。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;跟客户的沟通是比较坎坷的。总体来说我们是一个机器学习出身的团队，在现场，客户会有</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 09:50:01 +0800</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>改变世界？合成生物学有望先改变食品行业 | Founder 100</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371432</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr"/>
+      <c r="F521" s="2" t="inlineStr"/>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2022 年 12 月 28 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;合成生物会如何影响我们？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;美国素肉生产公司 Impossible Foods 推出的「人造肉」，可能首次让大众意识到了合成生物的用途。不过在当下，「&lt;/span&gt;&lt;strong&gt;&lt;span&gt;日常生活中合成生物学的产品没有特别多，大&lt;/span&gt;&lt;span&gt;部分还属于『原材料供应』，离终端消费者还有一定距离。&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;&lt;/span&gt;&lt;span&gt;」国内合成生&lt;/span&gt;&lt;span&gt;物公司倍生生物的联合创始人康康这么说道。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;与大众的认知不同，倍生生物并没有选择大宗化工方向设计产品，而是投入到了食品赛道，使用合成生物技术研发了低度酒饮料，主要原因是创始人们喜欢喝酒，对酒有鉴赏能力，还有一个原因是，「&lt;strong&gt;让品牌方感知，生物技术是可以改变食品这样一个非常传统的行业的&lt;/strong&gt;」。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;随着基因编辑、基因合成等技术的进步，以及人工智能的加入，2021 年以来，合成生物行业发展到了一个新的商业阶段，从 2021 年到 2022 年 3 月份，国内就有 16 家合成生物企业完成融资，融资总额超 25 亿元。如何看待合成生物学和计算机、人工智能的结合？以及合成生物公司的壁垒到底是什么？&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;以及，合成生物学什么时候会为行业带来历史性的变革？针对这些问题，我们和康康进行了一场长聊。&lt;/span&gt;&lt;span&gt;&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/d6/e2/d6e28e3dd9c2f44d010162a9236164c0.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;日常生活中合成生物学的产品也没有特别多，大部分成熟应用是「用生物法替代化工来实现特定原料的生产」。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;整个人类理解生命的过程是一个逆向工程，跟计算机的 bottom-up 往上搭建的模式不太一样。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;只有拥抱新的技术，拥抱新的生产工艺，拥抱从研发到生产的整个链条的升级，才能拥抱未来。而不是说把所有的钱花在烧钱、做品牌运营，你就有未来。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;架构化的基因组显然是一个非常强大的壁垒，因为任何人想要构建这种架构化的基因组，都需要耗费巨大的时间、成本和人力。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;合成生物学产品&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;尚未大规模进入日常&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：如何向外行人解释合成生物学究竟是什么？合成生物学与传统的发酵有什么区别？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;康康&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：如果用一个窄化的概念解释：人类希望通过利用生物、改造生物，让这些生物来实现人类想实现的功能，让它生产人类想让它生产的东西。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;实际上合成生物学还可以做像身体检测、传感，或者是环境修复等等产品，而非局限于生物制造业。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;至于「合成生物学」和「传统发酵」两者的区别，如果是对天然的生物进行了一定的理性上的改造和设计，那我们就可以认为它运用了合成生物学；如果使用的微生物来自自然界，恰巧能够帮人们实现想要的功能，那它就是传统的发酵行业。&lt;/</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 09:48:34 +0800</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>麦岩智能：高端商务场景是清洁机器人的下一个蓝海 | Founder 100</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371430</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr"/>
+      <c r="F522" s="2" t="inlineStr"/>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="color: #999; font-size: 14px;"&gt;本文首发于 Founder Park 公众号 · 2022 年 12 月 2 日&lt;/p&gt;&lt;p&gt;&lt;span&gt;和家用清洁机器人不同，商用清洁赛道是一个尚待爆发的赛道，随着老龄化带来的服务业从业人数下降，以及商用场景对于清洁的高要求，对于清洁机器人的需求只会急剧增加。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;在麦岩智能的创始人 &amp;amp; CEO 李宇浩看来，商用清洁机器人和家用的发展差距，主要原因在于&lt;strong&gt;「一定会先从简单场景或是一些对技术要求没那么高的场景开始做商业化。所有技术基本上都是这么来的，因为技术本身迭代需要时间。」&lt;/strong&gt;现在技术已经成熟，需求也有了，剩下的就是「满足市场、喂养市场」了。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;尤其不同的是，麦岩智能的产品是面向高端商务场景，为此他们在产品里甚至使用了主动降噪功能，高端商务场景对于清洁机器人的需求到底是怎样的？清洁机器人是彻底不需要人类了吗？以及，商务清洁机器人的市场何时才会爆发？关于这些问题，我们也和李宇浩进行了探讨。&lt;/span&gt;&lt;/p&gt;&lt;section&gt;&lt;span&gt;&lt;/span&gt;&lt;/section&gt;&lt;p&gt;&lt;img alt="图片" src="https://imgslim.geekpark.net/uploads/image/file/a4/6f/a46f475bb3efff6860f147d2fb7cb358.png" /&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;ol&gt;&lt;li&gt;&lt;p&gt;现实情况下人口红利确实没有了，而且也不能让老人一直干下去，服务行业劳动力短缺非常严重。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;在历史上，无论是汽车代替马车，还是织布机代替纺织工人，或是农业机械代替了农民，每次科技变革都会存在争议，但没有一次例外，都是让大家的生活变得更好。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;某种意义上，一定会先从简单场景或是一些对技术要求没那么高的场景开始做商业化。所有技术基本上都是这么来的，因为技术本身迭代需要时间。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;我们现在是什么状态？整个行业加起来都满足不了需求的 1%。在这种情况下，谈（竞争）这件事过于早了。&lt;/p&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;只有年出货量达到 10 万以上，才能满足客户的相当一部分需求。如果在百万量台级的市场去考虑，起码一年要 10 万台才能撬动市场。&lt;/p&gt;&lt;/li&gt;&lt;/ol&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;section&gt;&lt;br /&gt;&lt;/section&gt;&lt;p&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;br /&gt;&lt;/p&gt;&lt;section&gt;&lt;h2&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;商用清洁机器人&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h2&gt;&lt;h2&gt;&lt;/h2&gt;&lt;h2&gt;&lt;strong&gt;&lt;span&gt;是即将爆发的新赛道&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;&lt;h3&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;Founder Park：你们最开始选择创业方向的时候，清洁行业大概处于什么情况？当时能看见的未来方向是怎样的？&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/h3&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;李宇浩&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;span&gt;：商用清洁是大家日常能看到的或是有意无意能注意到的场景，比如办公室、商场、学校，包括一些公共场所：图书馆、火车站、飞机场等等。区别于家用、门内或是房屋套内的面积。目前商用清洁的状态是以人为核心，辅助一些自动化工具，处于正常的经营状态。就未来而言，我们还是觉得会有一头灰犀牛*朝我们撞过来。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;灰犀牛：比喻大概率且影响巨大的潜在危机。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;老龄化是很明显的问题，据中国宏观数据统计，2000 年有 8000 多万 65 岁以上的人，2050 年将有 3.8 亿以上 65 岁以上的老年人。这会导致劳动力供给的断崖式下降，目前微观上已经影响了商用清洁业务的开展，人现在越来越不容易招到，尤其是年轻人。年纪稍大的从业人员，随着年龄增长，还是会逐渐退出劳动市场，所以能看到未来市场会有相关人员断崖式的下降。&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;我们该怎么办？需要在智能化应用</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 13:38:48 +0000</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>Viral AI agent Instinct raises $1B Series C at a $10B valuation</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/28/viral-ai-agent-instinct-raises-1b-series-c-at-a-10b-valuation/</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr"/>
+      <c r="F523" s="2" t="inlineStr"/>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>"This funding helps us bring Instinct to more people and continue building the future of personal AI. It’s an exciting, creative time, and we're just getting started," founder Noah Shinn said in a statement.</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H523"/>
+  <dimension ref="A1:H538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21794,6 +21794,734 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 02:05:58 +0000</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>半年出货 2.5 万台，同比增长 432.1%：全球人形机器人商业化探索持续升温</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13586</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr"/>
+      <c r="F524" s="2" t="inlineStr"/>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>IDC预计，2030年全球人形机器人出货量将超过75万台，市场将进入规模化应用加速发展阶段。</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 10:56:33 +0000</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>正行创新联合创始人杨宇欣正式亮相：出任总裁，负责全球业务拓展</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/499239.html</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr"/>
+      <c r="F525" s="2" t="inlineStr"/>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>推动公司具身模型、本体、软件等全栈能力进入更多真实场景</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 07:10:59 +0000</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>成立一年完成5轮融资，诺因智能再获数亿元，累计超10亿元</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/499135.html</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr"/>
+      <c r="F526" s="2" t="inlineStr"/>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>诺因从Demo走向家庭</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:25:27 +0800</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 推出个人 AI 智能体 dots；传豆包将推个人 AI 产品「Spell」；SpaceX 发射星舰成功入轨 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372005</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr"/>
+      <c r="F527" s="2" t="inlineStr"/>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e8/82/e8828e7dd563fd5fd57fe2d942f62982.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 开发者大会推出智能体 dots，重构会员定价，意图打造 AI 超级入口&lt;/h2&gt;
+&lt;p&gt;北京时间 9 月 30 日凌晨，OpenAI 举办其宣称规模最大的一届开发者大会，一次性发布 25 项更新，覆盖新模型、API、智能体、插件生态与企业软件市场。大会现场，Sam Altman 公布 ChatGPT Pro 会员调整方案时台下一片沉寂，套餐调价成为本次发布最受争议的内容。&lt;/p&gt;
+&lt;p&gt;会员体系重新划分档位：原有 200 美元 / 月的 Pro 200 售价不变，但新订阅用户额度减半；新增 500 美元 / 月的 Pro 500 套餐，额度为 Plus 的 25 倍，独家开放 Astra Ultrafast 高速模式。OpenAI 的计价逻辑发生转变，不再简单按 token 数量计费，转而参考「雇佣 AI 员工」模式，按交付工作量与运行速度单独收费，高速模式消耗额度更快。尽管 GPT-6.1 Sol 等新模型 API 价格大幅下调，但会员套餐内可用额度同步缩减，引发开发者不满。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f9/1c/f91c93f9e55335c7ffe34bbf81c910b8.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;本次重头戏是智能体 dots，由 GPT-6 Astra 驱动，自带云端运行环境，可连接数千款应用，能够持续自主完成任务，Pro 及企业套餐用户可使用。OpenAI 同步推进平台化改造，新增插件生态、ChatGPT 账号登录、跨应用额度通用能力，对标微信小程序与账号体系，试图将 ChatGPT 打造为人与智能体协作的统一入口。同时上线团队资料空间、动态文档、新版 Codex 云端开发环境，面向企业推出软件市场，企业额度可直接采购第三方商业软件。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;相关报道：&lt;a href="https://www.geekpark.net/news/372003"&gt;除了更贵的订阅和砍半的额度，OpenAI 想做的还是「微信」 | 极客公园&lt;/a&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cc/1f/cc1f363c9a5e34c800d1fcf3037f3fa9.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;DeepSeek Harness 桌面端预览版 v0.2 发布，支持插件安装与自动化任务&lt;/h2&gt;
+&lt;p&gt;9 月 29 日消息，DeepSeek Harness v0.2 预览版正式发布，并提供开箱即用的 macOS 和 Windows 桌面端安装包，已上线 DeepSeek 官网。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cb/c9/cbc9fb1b8d936d80df8141ec9bfd0d09.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;新版本预置了面向日常办公和开发的常用功能，让常用能力开箱即用。同时，新增插件安装与管理页面，并提供更多灵活配置选项，方便按需扩展功能，打造更适合自己的智能产品。DeepSeek Harness 尚在起步阶段，功能与体验仍有待细致打磨。&lt;/p&gt;
+&lt;p&gt;本次更新优化了文件展示、内容预览和代码变更展示体验，完善了自动化任务的设置与管理，并提供多种工作过程展示方式，方便你查看任务进展、了解执行步骤和排查问题。&lt;/p&gt;
+&lt;p&gt;用户可以提供文档、表格或 PDF 文件，让 DeepSeek Harness 整理资料、分析数据、生成图表或制作演示文稿，也可以让它修改项目、运行代码，协助完成开发任务。&lt;/p&gt;
+&lt;p&gt;接下来，DeepSeek Harness 团队将持续改善从上手到完成各类任务的用户体验，包括：改善沙箱功能与安全性、完善智能体团队功能的效果与易用性、加入个性化的长期记忆、实现浏览器与其它 GUI 软件的自动化操作、支持远程与移动端使用、探索会话分享与多人协作。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;&amp;nbsp;&lt;/h1&gt;
+&lt;h2&gt;报道称 OpenAI 年化经</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 19:21:44 +0800</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>AMD 82 亿美元收购 World Labs，买的不只是世界模型</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372000</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr"/>
+      <c r="F528" s="2" t="inlineStr"/>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 月 3 日，英伟达宣布以约 130 亿美元收购 Hugging Face。25 天后，AMD 宣布以约 82 亿美元收购李飞飞创办的 World Labs。&lt;/p&gt;
+&lt;p&gt;两笔交易放在一起看，更觉得有意思。CNBC 最新的报道提到，Hugging Face 在被英伟达拿下之前，AMD 和 Salesforce 都曾表达过收购兴趣。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;没抢到 AI 世界里最大的模型「集散地」，AMD 转身买下了一支造模型的顶级团队。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;根据 AMD 的公告，这是一笔全股票交易&lt;/strong&gt;，预计在 2026 年底前完成交割，仍需通过监管审批。交割之后，李飞飞将出任 AMD 执行副总裁兼首席科学家，直接向 CEO 苏姿丰汇报。&lt;/p&gt;
+&lt;p&gt;这也是 AMD 历史上第二大收购，仅次于 2022 年约 500 亿美元拿下的赛灵思。&lt;/p&gt;
+&lt;p&gt;除了科技圈最有分量的两位华裔女性联手外，很多人的第一反应是&amp;mdash;&amp;mdash;AMD 要押注世界模型了，但这个判断只对了一半。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;「不做模型生意」的模型收购&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;作为一家 AI 基建公司，AMD 从来不靠卖模型赚钱，它卖的是 CPU、GPU 和越来越完整的数据中心系统。&lt;/p&gt;
+&lt;p&gt;这笔交易真正的逻辑，藏在 AMD 自己的表述里。&lt;/p&gt;
+&lt;p&gt;公告写得很直白，随着 AI 扩展到推理、机器人、仿真和物理 AI，算力基础设施面对的需求越来越多样，&lt;strong&gt;World Labs 的模型经验，将帮助 AMD 更深入地理解工作负载如何演变，进而塑造未来的技术路线图&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;AMD CEO 苏姿丰在接受彭博采访时说得更简单，「你对端到端理解得越深，造出来的系统就越好」。&lt;/p&gt;
+&lt;p&gt;一位分析师的评价很到位，「这是一笔买人才和模型洞察的交易，不是买收入。」&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;换句话说，AMD 花 82 亿美元买的不是一个产品，而是一扇能提前几年看到未来算力需求的窗户。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;芯片的设计周期以年计，今天定下的架构，要两三年后才会在数据中心里跑起来。如果等模型公司把新需求摆到面前再去适配，芯片公司永远慢半拍。把一支前沿模型团队放进自己家里，等于在研发链条的最上游装了一个传感器。&lt;/p&gt;
+&lt;p&gt;两位传奇女性的联手，也不是临时起意。&lt;/p&gt;
+&lt;p&gt;World Labs 与 AMD 从去年开始就在 AMD GPU 上合作做模型训练和推理优化，李飞飞还登上了今年 1 月 AMD 的 CES 主题演讲台。她在宣布消息时称苏姿丰是「很好的朋友」，也是 World Labs 的早期投资人。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;追赶英伟达&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;AMD 之所以需要这扇窗户，是因为对手早就开了好几扇。&lt;/p&gt;
+&lt;p&gt;英伟达的护城河从来不只是 GPU。CUDA 生态、自研的 Cosmos 系列开放权重世界模型、与 Wayve 等自动驾驶世界模型公司的深度合作，构成了芯片之外的完整闭环。过去一年里，&lt;strong&gt;英伟达又先后花 200 亿美元买下 Groq 的资产、130 亿美元收购 Hugging Face，一步步从「卖铲子的人」变成「整座矿山的运营者」&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;AMD 这边，此前向公众开放的只有文本和视频模型，在物理 AI 这个英伟达力推的新战场上，几乎没有自己的位置。&lt;/p&gt;
+&lt;p&gt;这并不是说 AMD 眼下过得不好，恰恰相反。9 月 21 日，&lt;strong&gt;AMD 市值首次突破 1 万亿美元&lt;/strong&gt;，今年以来股价累计上涨约 185%。第二季度数据中心业务收入 67 亿美元，同比增长 107%。Anthropic 计划从 2027 年上半年开始部署最多 2 吉瓦的 AMD MI450 GPU，AMD 也承诺向 Anthropic 投资最多 50 亿美元。&lt;/p&gt;
+&lt;p&gt;但差距同样清楚。英伟达市值仍是 AMD 的五倍多，IDC 的估算显示，英伟达占据 AI 加速器市场约 81% 的份额，AMD 约 13%。&lt;strong&gt;AMD 已经证明了自己能卖出芯片，接下来要证明的，是自己也能定义芯片该长什</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 17:12:00 +0800</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic 招股书里，最耐人寻味的 7 个细节</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371994</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr"/>
+      <c r="F529" s="2" t="inlineStr"/>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-MG1OdK5KoovLyBx33bmcZeumnpb"&gt;作者｜Techno 之王&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-LSRZdGUOtoJ6qkxtYOQcYm2Wnab"&gt;编辑｜靖宇&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-LSRZdGUOtoJ6qkxtYOQcYm2Wnab"&gt;&amp;nbsp;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;当地时间 9 月 28 日，外媒披露了一份 Anthropic 的 IPO 招股书。&lt;/p&gt;
+&lt;p&gt;先要说清楚这份文件的性质。它并不是 Anthropic 主动公开的版本。今年 6 月，Anthropic 以公益公司身份向美国证交会秘密递交了 S-1 注册声明草案，为普通股首次公开发行做准备。按照规则，公司要在向机构投资者路演前至少 15 天公开递交修订版 S-1，完整财务数据到那时才会被外界看到。路透此次看到的是一份尚未公开的版本，&lt;strong&gt;Anthropic 对此拒绝置评&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;这意味着其中的数字仍可能随证交会的审阅意见调整，不少细节也只能通过路透的转述窥见一角。&lt;/p&gt;
+&lt;p&gt;但如果这份文件大体反映了 Anthropic 最终交给公开市场的样子，它的分量很难被高估。这次上市的估值目标，是 Anthropic 自己 5 月估算的 9650 亿美元的两倍以上，也就是超过 2 万亿美元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这是 ChatGPT 引爆这轮 AI 浪潮近四年来，第一家把完整账本摊给公众投资人的前沿大模型实验室。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;在此之前，这场 AI 竞赛的资金一直由风投、主权财富基金和科技巨头承担，外界只能从零散的年化收入和融资估值里拼凑这些公司的经营状况。现在，账本第一次有了审计口径。&lt;/p&gt;
+&lt;p&gt;极客公园从招股书中，挑出了 7 个最值得细看的地方。&lt;/p&gt;
+&lt;h1&gt;被误读的 420 亿美元亏损&lt;/h1&gt;
+&lt;p&gt;招股书里最先被传播的数字，是 2025 年约 420 亿美元的净亏损。&lt;/p&gt;
+&lt;p&gt;这个数字很容易被读成「一年烧掉 420 亿美元」，实际并非如此。其中约 340 亿美元是一笔会计费用，反映的是那些未来可能转换成 Anthropic 股票的融资工具估值上升，而不是公司经营业务花掉的钱。&lt;/p&gt;
+&lt;p&gt;这就产生了一个反直觉的结果。&lt;strong&gt;Anthropic 越值钱，它在账面上「亏」得就越多&lt;/strong&gt;。2025 年恰好是它估值暴涨的一年，这笔费用也被同步放大。&lt;/p&gt;
+&lt;p&gt;真正反映经营状况的是另一组数字。收入从 3.86 亿美元增长到 45.9 亿美元，增幅 1088%；经营亏损则从 29.8 亿美元扩大到 80.6 亿美元。&lt;/p&gt;
+&lt;p&gt;收入涨了约 12 倍，经营亏损扩大不到 3 倍，规模效应确实在出现。但一年 80 亿美元的经营亏损，放在任何一家准备上市的公司身上，都是需要反复解释的数字。&lt;/p&gt;
+&lt;h1&gt;650 亿美元年化收入的坑&lt;/h1&gt;
+&lt;p&gt;招股书的消息传开后，美国散户论坛 wallstreetbets 上的最高赞评论只有一句话，大意是「&lt;strong&gt;2 万亿估值，配 40 亿收入？&lt;/strong&gt;」&lt;/p&gt;
+&lt;p&gt;这个质疑直观，但拿错了分母。&lt;/p&gt;
+&lt;p&gt;招股书的主体覆盖 2025 财年，截至去年 12 月 31 日，而 Anthropic 真正的爆发发生在 2026 年。据报道，它的年化收入在 2025 年底约为 90 亿美元，今年 5 月约 470 亿美元，到 7 月底已超过 650 亿美元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;招股书里的 45.9 亿美元，是一家公司在「起飞前」的最后一张快照&lt;/strong&gt;。资本市场给出的 2 万亿美元估值，押注的是 2026 年之后的曲线，而不是 2025 年的全年成绩。&lt;/p&gt;
+&lt;p&gt;不过，年化收入本身需要打折看。它通常用某一个月的收入乘以 12 推算，天然会放大短期波动。招股书自己也给出了两处值得警惕的提示。去年近四分之一的收入来自两个客户；公司还在风险因素中承认，许多最大客户并没有签订长期合同，可能削减甚至停止支出。&lt;/p&gt;
+&lt;p&gt;路透没有披露这两家客户的名字，这会是公开版 S-1 出来后最值得第一时间核对的信息。&lt;strong&gt;Anthropic 的增长曲线足够陡峭，却缺乏合同层面的锁定&lt;/strong&gt;，这是理解它估值的关键前提。&lt;/p&gt;
+&lt;h1&gt;最大的股东，最大的房东&lt;/h1&gt;
+&lt;p&gt;2025 年，Anthropic 在算</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 13:27:55 +0800</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>Manus 正式发布 2.0！个人 AI 助手、云电脑、远程控制，Manus 想做 AI 时代全家桶</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371493</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr"/>
+      <c r="F530" s="2" t="inlineStr"/>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a1/93/a193885ec13c352393ee39cbc8515dc0.png" /&gt;&lt;/p&gt;
+&lt;p&gt;头图来源：Manus&lt;/p&gt;
+&lt;h1&gt;&amp;nbsp;&lt;/h1&gt;
+&lt;p&gt;突然地，Manus 在官网和社交平台上公布了 Manus 2.0 版本的更新。&lt;/p&gt;
+&lt;p&gt;这并非一次简单的产品迭代，更像是&lt;strong&gt;Manus 团队尝试将当下所有最热门的 AI 场景和功能，融合到一个「AI 全家桶中」&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;此次升级中，团队打造的底层 Cascade Agent 框架，能将任务 Token 消耗减少 23.2%，任务完成时间缩短 28.2%，运行成本降低 32%。同时，Manus 现在也提供「云电脑」的选项供用户选择。&lt;/p&gt;
+&lt;p&gt;向上，从视频编辑、游戏开发、远程控制和 AI Studio，Manus 为所有用户常用的场景，提供了相关产品。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7f/7d/7f7d27225d86ff5879ab54913c6afff1.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Manus 正式推出个人助手应用 Cue｜图片来源：Manus&lt;/p&gt;
+&lt;p&gt;最重要的，&lt;strong&gt;这次 Manus 还推出了一款个人 Agent&amp;mdash;&amp;mdash;CUE&lt;/strong&gt;。这款全新应用支持手机和桌面端，和 Manus 共享同样的基础设施。在个人 AI 这块，Manus 正式出击。&lt;/p&gt;
+&lt;p&gt;这是 Manus 在蛰伏许久后的第一次露面，「全家桶」式的升级，代表那个用产品曾经惊艳所有人的团队，并没被时代落下。&lt;/p&gt;
+&lt;p&gt;另外，在官方公众号中，Manus 表示「正在组建团队开发面向国内市场的产品，与国产模型厂商及生态伙伴的合作也在稳步进行，后续将分享更多进展。」&lt;/p&gt;
+&lt;h1&gt;全场景、全家桶&lt;/h1&gt;
+&lt;p&gt;按 Manus 自己的划分，2.0 的更新分成三大类：&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;新的 Agent 框架和运行环境&lt;/strong&gt;&lt;strong&gt;；&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;由桌面端升级的&lt;strong&gt;&lt;em&gt;&lt;em&gt;Manus Studio&lt;/em&gt;&lt;/em&gt;&lt;/strong&gt;；&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;以及一款独立的新应用 Cue&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;运行环境上 Manus 2.0 换成了自研 Agent 框架的最新一代 Cascade，它的思路是让项目在开头尽量轻，等活儿真的需要了，再把相应的专业能力接进来；同一个项目里的简报、网页、视频和自动化流程，彼此关联。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a1/cb/a1cb7eec7046c2216f3c7f270fd0391d.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Manus 2.0 在从底层上变得更「经济」｜图片来源：Manus&lt;/p&gt;
+&lt;p&gt;多人联机的游戏需要一台用户关机后仍然在线的服务器，自动化流程需要一个全天候运转的地方，这些都超出了一台个人电脑能扛的范围。现在用户可以直接向 Manus 购买云电脑，给这类项目一个专属的运行环境。&lt;/p&gt;
+&lt;p&gt;「云主机」这个由 Manus 兴起、时下大火的概念，也被 2.0 更新包含在内｜图片来源：Manus&lt;/p&gt;
+&lt;p&gt;此外，原来的定时任务也升级成了自动化。以前 Manus 只能在设好的时间点开工；现在，已连接服务里发生的事也能触发任务，收到一封新邮件、广告数据出现波动、日历上多了一个事件、Slack 来了一条消息，或者某个 Notion 页面有了更新，都算。&lt;/p&gt;
+&lt;p&gt;Manus 2.0 的自动化｜图片来源：Manus&lt;/p&gt;
+&lt;p&gt;用户只要用一句话交代盯着什么、接下来做什么，Manus 会自己搭好整条工作流并跑起来。这等于给 Manus 加了一种工作方式：不用人叫，自己盯着。&lt;/p&gt;
+&lt;p&gt;至于 Manus Studio。官方把它定义为人和 AI 共用的工作空间，口号是「从完成任务，到做出好作品」。&lt;/p&gt;
+&lt;p&gt;Studio 同样按需加载。Manus 的解释是，每类工作都有各自的专业工具，要是每个任务都把全部能力带上，同样的活只会又慢又贵，</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 08:07:40 +0800</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>AMD 82 亿美元收购李飞飞 AI 创业公司；Manus 推出个人 AI 助手 CUE；今年低价手机将减少 2.3 亿部｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371359</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr"/>
+      <c r="F531" s="2" t="inlineStr"/>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2d/7b/2d7b304b769fdef50ee0b4479c2d1d34.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;Manus 发布 2.0，新增云电脑、远程控制及个人 AI 助手 Cue&lt;/h2&gt;
+&lt;p&gt;9 月 28 日，&lt;a href="https://mp.weixin.qq.com/s/KK20dGFNgEnhGsVjHHI18w"&gt;Manus 发布 2.0 版本&lt;/a&gt;，升级自研 Cascade Agent 框架，并推出云电脑、视频编辑、游戏开发及个人 AI 助手 Cue。据官方数据，新框架可使任务 Token 消耗减少 23.2%、完成时间缩短 28.2%、运行成本降低 32%。&lt;/p&gt;
+&lt;p&gt;升级后的 Manus Studio 支持文档、表格、网站和视频等内容创作，用户可在视频时间线上手动修改素材，再交由 AI 继续编辑。新增远程控制功能允许用户通过手机指挥已授权的电脑，查找文件或操作应用；自动化任务也可由新邮件、日历变更等事件触发，云电脑则为持续运行的项目提供环境。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ab/4c/ab4c40e573bb9b48b1a8f7c7e1cddf15.png" /&gt;&lt;/p&gt;
+&lt;p&gt;独立应用 Cue 支持手机和桌面端，每个 AI 助手可拥有独立邮箱、电话号码、钱包和电脑，在用户设定的预算内付款、代接电话，也可与其他助手协作。目前 Cue 处于抢先体验阶段，凭邀请码免费使用。&lt;/p&gt;
+&lt;p&gt;Manus 还表示，正在组建团队开发面向国内市场的产品，并与国产模型厂商及生态伙伴推进合作。（来源：极客公园）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1d/81/1d8142a4810a7a36aaeb0f81f6eb16d6.png" /&gt;&lt;/p&gt;
+&lt;header&gt;
+&lt;h2&gt;AMD 斥资 82 亿美元收购 World Labs，「AI 教母」李飞飞出任执行副总裁兼首席科学家&lt;/h2&gt;
+&lt;p&gt;9 月 29 日，AMD 宣布同意以全股票交易收购旧金山初创公司 World Labs，交易价值约 82 亿美元（现汇率约合 551 亿元人民币）。&lt;/p&gt;
+&lt;p&gt;World Labs 由李飞飞等人于 2024 年联合创办，主要开发「世界模型」，让 AI 根据文本、图像和视频生成或重建能够交互的 3D 环境。未来，这项技术可以用于机器人训练、工厂模拟和科学研究。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ba/2a/ba2a77e1af10b698f11c1a23f15e5b21.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;按照收购协议，李飞飞将加入 AMD，出任执行副总裁兼首席科学家，并向苏姿丰汇报。&lt;/p&gt;
+&lt;p&gt;有「AI 教母」之称的李飞飞因创建大型标注图像数据库 ImageNet 而广为人知。ImageNet 曾帮助证明，更大的数据规模能够显著提升计算机视觉能力。李飞飞后来担任谷歌云 AI 和机器学习首席科学家，并成为斯坦福大学「以人为本 AI 研究院」创始联席主任。&lt;/p&gt;
+&lt;p&gt;本月早些时候，World Labs 推出新 AI 模型 Atlas，只需少量 2D 图像，就能预测同一场景换一个摄像机角度后呈现的画面。根据 World Labs 介绍，这种工作方式可比作大语言模型预测一句话中的下一个词。&lt;/p&gt;
+&lt;p&gt;AMD CEO 苏姿丰在新闻稿中称，收购 World Labs 能够让 AMD 更深入地了解尖端 AI 模型的演进方向，从而开发运行这些模型所需的芯片和计算系统。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;&amp;nbsp;&lt;/h2&gt;
+&lt;h2&gt;OpenAI 高管称研发资源转向 GPT-7 等后续模型，消息称 GPT-6.1 Astra 因安全风险取消发布&lt;/h2&gt;
+&lt;p&gt;9 月 28 日，据 The Decoder 报道，OpenAI 应用研究主管 Boris Power 在 Fellows Forum 2026 上表示，公司已将 80% 至 90% 的研发资源投入 GPT-7、GPT-8 及后续模型。他认为，同代模</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 22:54:50 +0800</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>中国智能汽车的后台，越来越像阿里云的主场</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371357</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr"/>
+      <c r="F532" s="2" t="inlineStr"/>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;中国智能汽车产业，正在经历一场没有硝烟、却极为深刻的范式迭代。&lt;/p&gt;
+&lt;p&gt;在 2026 云栖大会汽车行业峰会上，我们看到了智能汽车竞争的主线：智能座舱正全面进入 Agent 时代，车不再是执行指令的机器，而是能理解你的意图、主动帮你把事情办成的智能体；智能驾驶的竞争，也早已从算法层下沉到工程层。数据产线的效率、训练集群的稳定性、模型迭代的周期，这些工程层的东西，正在决定胜负。&lt;/p&gt;
+&lt;p&gt;如果切换一下视角，会发现另一条更隐蔽的竞争主线正在成形：&lt;strong&gt;谁能成为中国智能汽车产业的算力与 AI 底座？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;数据给了一个相当清晰的答案。根据沙利文联合头豹近日发布的《2026 年中国汽车 AI 云市场追踪报告（26H1）》，&lt;strong&gt;阿里云在中国汽车公有云市场份额达到 45.2%，在智能驾驶、智能座舱、工业提效等六项市场及细分赛道均拿下第一。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f0/6d/f06d082ab3aeb8376bbd611778537509.jpeg" /&gt;&lt;/p&gt;
+&lt;p&gt;阿里云智能集团公共云事业部 AI 汽车行业总经理李强对这件事的总结，只有五个字：&lt;strong&gt;芯、云、模一体&lt;/strong&gt;。从智能座舱到自动驾驶，从端侧小模型到云端万亿参数推理集群，再到车企内部组织效能的提升，阿里云正在构建一套覆盖中国智能汽车全产业链的 AI 基础设施。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5d/78/5d78915d15edff4bd45559787bb3550a.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;智能座舱：把「能聊天」变成「能办事」&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;前两年，大模型上车是整个行业最性感的叙事。「能聊天、能提供情绪价值」，出现在很多车企发布会 PPT 上。&lt;/p&gt;
+&lt;p&gt;两年过去了，用户并没有被打动。阿里云智能集团公共云事业部 AI 汽车行业解决方案总经理霍健提到，他近期在与多家车企座舱团队交流时观察到，闲聊并不是用户使用座舱的核心高频场景。相比长时间对话，用户更关心系统能否在合适的时机，高效完成车控、导航和服务任务。&lt;/p&gt;
+&lt;p&gt;这说明用户不需要一个只会聊天的车，用户需要一个能把事情办成的车。座舱的本质是一个「任务型」的存在。就像你雇了一个助理，你首先需要确认他能把事情办好，才会逐渐信任他、依赖他，最终才可能把他当成一个可以倾诉的对象。&lt;/p&gt;
+&lt;p&gt;所以，座舱 AI 今年最大的变化，是从聊天到办事。这不是在旧系统上打补丁，是推倒重来。旧的座舱系统建立在规则引擎和多模块拼接之上，每增加一个新功能，就意味着新一轮的工程堆砌。&lt;/p&gt;
+&lt;p&gt;这套逻辑在大模型时代就是一堵墙。新范式的核心是 Harness（工程治理框架）+ 大模型，让模型本身承担意图理解、任务分解和工具调用的全部职责。&lt;/p&gt;
+&lt;p&gt;阿里云的定位很清醒，它没有去做完整的座舱产品；而是提供云、模型等全栈 AI 能力，以及阿里生态服务 Agent。原因很直接&amp;mdash;&amp;mdash;座舱是极度定制化的产品，车企最了解自己的用户和品牌调性，阿里云做完整方案，反而是在错误的地方发力。&lt;/p&gt;
+&lt;p&gt;所以，千问座舱 Agent 的核心能力只有两块：一个是闲聊检索。这部分能力来自千问 C 端 APP 的积累，是阿里在消费者侧多年沉淀能力的车端化。&lt;/p&gt;
+&lt;p&gt;另一个是阿里集团生态 Agent。这才是真正的杀手锏。过去，一家车企如果想在座舱里集成淘宝闪购、高德、飞猪，需要分别与三个不同的业务团队谈判，接口标准不统一，维护成本极高。&lt;/p&gt;
+&lt;p&gt;千问座舱 Agent 做的事，是把这些能力原子化封装成统一的 Agent 接口。车企一次接入，就能调用整个阿里集团的生态能力。&lt;/p&gt;
+&lt;p&gt;举个例子，下班开车回家，不想做饭，在行驶途中对座舱说「帮我点个外卖，我到家的时候外卖也到」。这个指令背后，涉及位置判断、预计到达时间计算、餐厅筛选、下单支付、配送时间协调等多个环节。过去，这需要车企分别接入多个服务商的 API，工程复杂度极高；现在，通过千问座舱 Agent，一个 A2A 调用即可完成全链路。&lt;/p&gt;
+&lt;p&gt;但座舱 Agent 只是用户能看见的部分，真正的故事发生在幕后。&lt;/p&gt;
+&lt;p&gt;目前大多数车企，已经在基于开源的千问系列模型，自研自己的座舱产品体系。结合具体任务在云端与车端部</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 20:40:54 +0800</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>蔚来换电，终于等来了「别人家的车」</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371233</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr"/>
+      <c r="F533" s="2" t="inlineStr"/>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;过去一年，蔚来似乎有意在新车发布时不再过分强调「换电」的重要性。以笔者自己的体感而言，无论是新车发布会，还是线下门店里用户的讨论度，换电都不再是「最重要的那一个话题点」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但换电退到了幕后，却没有影响蔚来的新车销量：第三代 ES8 上市 12 个月销量突破 15 万台，ES9 上市 4 个月累计交付突破 3 万台。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;现在，换电这件事又有了新进展。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;9 月 28 日，在中秋假期后的第一个工作日，蔚来的能源业务迎来了一个重要的合作伙伴。吉利控股将以旗下易易互联 100% 的股权，加上 6.4 亿元现金，入股蔚来能源。交易完成后，吉利控股持有蔚来能源 30% 的股权；易易互联的营运车辆换电业务并入蔚来能源；双方共建统一的 C 端换电技术和标准，吉利将开发面向 C 端的换电车型。另外在充电领域，蔚来也反向入股了吉利旗下的浩瀚能源，持股 10%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;「换电」正在从蔚来过去卖车的「卖点」，走向一门独立的生意。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;比钱更重要的，是「规模」&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;6.4 亿元，对蔚来并不算一笔「大钱」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;截至今年二季度末，蔚来集团的现金储备是 567 亿元，这笔钱大约只占 1%。而且，蔚来已经连续几个季度实现了正向经营现金流。蔚来现阶段最缺的，显然不是现金。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;所以，这并不是一次单纯的「找钱」和「融资」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="854" src="https://imgslim.geekpark.net/uploads/image/file/6b/28/6b286d56246945d5e2802bb16ed8b9df.jpeg" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;合作发布会签约现场 | 图片来源：蔚来&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;本质上，换电是一门非常讲究规模效应的生意。换电站建好的那一刻，土地、设备、电池、运维等成本就基本确定了。运营能否赚钱，主要取决于每天的服务量。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;蔚来创始人李斌很喜欢用「云服务」来类比换电这门在汽车领域相对比较新的生意。云服务的逻辑是：前期必须投入重资产部署服务器，后期租户越多，前期投入的服务器成本才能被摊薄，直至打平甚至盈利。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;换电站的账也是这么算的。蔚来高层此前曾经透露，第四代换电站单站每天约 40-50 次换电，就能基本实现盈亏平衡；在长三角等核心用户区域，已经有换电站达到了这个水平。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;要让更多车开进换电站，核心思路有两条：&lt;span style="font-weight: bold;"&gt;一条是自己多卖车，这是蔚来过去几年一直在做的；另一条就是争取早日让换电从「非共识」变成「共识」，让其他品牌的车早日复用蔚来的换电体系&lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;易易互联过去的主业，就是给出租车、网约车这类 B 端营运车辆换电。截至去年 4 月，它运营的换电站超过 470 座。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而营运车的换电频次一般要比私家车更高：早在 2023 年，易易互联 300 多座站的日均换电量就超过了 2 万次，平均每座站每天六七十次，已经高过蔚来 40-50 次的那条平衡线。当然，营运车的换电站和电池规格与蔚来不同，两者的成本结构不能简单类比，但方向是清楚的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;更大的想象空间在后面。吉利控股集团 CEO 安聪慧表示，吉利旗下曹操出行的车队，以后全部会用上蔚来能源的换电；吉利正在开发的 Robotaxi，也会全面使用换电技术。&lt;/p&gt;
+&lt;p style="text-al</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 17:50:05 +0800</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>不到 1 个月估值暴涨 100 亿美元，Jev 创造者：ChatGPT 把 AI 带歪了</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371126</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr"/>
+      <c r="F534" s="2" t="inlineStr"/>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;最近， 一个叫 Jev 的 AI 模型突然在开发者圈子里炸了。更可怕的是，根据最新消息，Jev 最近正在洽谈 10 亿美元融资，最新估值 100 亿美元&amp;mdash;&amp;mdash;而这距离 Jev 推出，还不到 1 个月。&lt;/p&gt;
+&lt;p&gt;Jev 这个新模型，它不生成文本，不跟你聊天，甚至不写代码。你给它一段数据和一组结构化问题，它返回类型化的答案和校准过的概率值。TypeSafe AI 管它叫「System One 模型」，一种全新的模型类别。9 月 15 日发布早期访问版本的同时，公司宣布获得 DCVC 领投的 4000 万美元种子轮融资，估值 2 亿美元。&lt;/p&gt;
+&lt;p&gt;开发者社区很快炸开了锅。TypeSafe 公布的数据显示，在分类任务上 Jev 比 GPT 系列快约 193 倍、便宜约 445 倍。Vercel CEO Guillermo Rauch 测试后说，在 p95 延迟上 Jev 比 GPT Luna 快 18 倍，而且更准。LangChain 第一时间写了集成指南。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;但真正让 Jev 值得关注的，不是这些数字，而是它背后的人和他的判断&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;Jev 的创造者 Diogo Almeida 曾在 OpenAI 工作近四年，是 GPT-4、ChatGPT 以及 RLHF/InstructGPT 的合著者。 他所在的团队基本上发明了「后训练」这个概念。换句话说，今天几乎所有大语言模型背后的核心训练范式，都有他的手笔。&lt;/p&gt;
+&lt;p&gt;而在 Jev 发布前六周，Almeida 在 AI Engineer 大会上做了一场 18 分钟的演讲，标题叫「&lt;strong&gt;What's Next After RLHF&lt;/strong&gt;?」。&lt;/p&gt;
+&lt;p&gt;他在台上说，自己是 OpenAI 内部少数公开「黑」ChatGPT 的人；他认为 ChatGPT 和 Claude Code 属于同一个时代；&lt;strong&gt;他相信整个行业终将把 RLHF 时代视为一段「奇怪的弯路」&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;一个技术范式的缔造者，亲手给自己创造的时代写悼词，这种事不常发生。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;以下是演讲中的一些核心观点&lt;/strong&gt;：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;「下一个时代不是 Claude Code 时代。ChatGPT 和 Claude Code 属于同一个时代。」&lt;/strong&gt;&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;「为什么所有 LLM 都需要人类在回路中？因为我们就是把人类放进了回路里。」&lt;/strong&gt;&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;「无论模型有多错，它都会看起来是对的。」&lt;/strong&gt;&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;「我们只是在自动化『写软件』这件事，但软件本身的表达力并没有变。」&lt;/strong&gt;&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;「原始的 Scaling Law 是错的。&lt;/strong&gt;」&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;以下是这场演讲的精编转录文字：&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;「黑 ChatGPT 的人」&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;我叫 Diogo Almeida，今天讲的主题是「RLHF 之后是什么」。更准确地说，应该叫「我们所处的 ChatGPT 时代之后是什么」。&lt;/p&gt;
+&lt;p&gt;先给你们一个提示：&lt;strong&gt;下一个时代不是 Claude Code 时代&lt;/strong&gt;。我后面会解释，但我认为 ChatGPT 和 Claude Code 属于同一个时代。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/85/ab/85abadff841188132dada2ddc6a8591b.png" /&gt;&lt;/p&gt;
+&lt;p&gt;看看到底是谁在黑 ChatGPT｜图片来源：Youtube&lt;/p&gt;
+&lt;p&gt;为什么你们该听我说？我是 OpenAI 基本所有重磅论文的合著者，包括 GPT-4、ChatGPT、RLHF/InstructGPT。我所在的团队基本上发明了「后训练」这个概念。所以这些东西我确实很熟。但真正让我有点特别的是，&lt;strong&gt;我大概是 OpenAI 内部少数公开黑 ChatGPT 的人&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;别误会，我不是讨厌 ChatGPT 这个产品。ChatGPT 是</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 17:45:25 +0800</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI，经历了最漫长的一天</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371123</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr"/>
+      <c r="F535" s="2" t="inlineStr"/>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;当地时间 9 月 25 日，OpenAI 经历了漫长的一天。&lt;/p&gt;
+&lt;p&gt;当天，&lt;strong&gt;OpenAI 的 AI 智能体擅自访问美国政府网站的事被曝光，涉及教育部、商务部和证券交易委员会&lt;/strong&gt;，OpenAI 确认了其中商务部和 SEC 的情况。&lt;/p&gt;
+&lt;p&gt;同一天，它承认有 53 张用户上传到 ChatGPT 的图片被智能体发布到了外部图床上。还是这一天，一份事故报告的末尾写着，最强模型的全部训练、评估以及涉及工具调用的推理都已暂停。&lt;/p&gt;
+&lt;p&gt;这一切听上去，像一部 AI 叛逃的惊悚片。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;但翻遍这些事件，没有一个 AI 想干坏事。&lt;/strong&gt;害 OpenAI 暂停模型研究的任务，仅仅是让 AI 查出一篇博客的作者的简单任务。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;简单任务&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;9 月 20 日，一个正处于强化学习训练中的内部模型，拿到了一组人物履历细节和一篇公开博客里的线索，任务是找到那位博主。&lt;/p&gt;
+&lt;p&gt;它先用博客里的特征短语去搜，结果返回的是音乐和一些不相干的泛泛建议。模型开始怀疑搜索工具坏了，于是在命令行里用 Python 直接向其他搜索引擎发请求，三个全部报错。它甚至猜测这道题出自公开评测集 BrowseComp，把数据集和评测脚本下载下来翻找答案，也落了空。&lt;/p&gt;
+&lt;p&gt;接着，它尝试通过 HTTPS 直接联系一个公开的聊天机器人，被代理拦了下来。&lt;/p&gt;
+&lt;p&gt;到这里，墙起了作用。OpenAI 的训练沙箱被设计成与真实互联网隔绝，除了这份报告里的 DNS 解析器，所有联网请求打到的都是一份离线网页缓存。&lt;/p&gt;
+&lt;p&gt;问题就出在这个例外上。&lt;/p&gt;
+&lt;p&gt;DNS 相当于互联网的查号台，任何程序访问一个网址之前，都要先问它「这个地址在哪」。系统里大量正常组件都依赖它，所以哪怕其他出口全部封死，查号台通常还开着。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;模型发现，沙箱自己的解析器能为真实域名返回记录，还能正确拒绝编造的域名，它由此判断这是一条通向公网的路&lt;/strong&gt;。它找到一种公开的 DNS 服务，把自己的问题编进「要查的号码」里，对方在回执里把答案捎回来。第一次超时了，它把等待时间从 6 秒调到 19 秒，重试。&lt;/p&gt;
+&lt;p&gt;这一次，外面的聊天机器人回答了它的测试问题，法国的首都是巴黎。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9b/fc/9bfce321e8449049bdf8041bb4b0826d.gif" /&gt;&lt;/p&gt;
+&lt;p&gt;智能体借 DNS 绕出训练沙箱的路径示意，据 OpenAI 事故报告绘制｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;它没有止步于打通一条缝。&lt;/strong&gt;它随后又通过同一条路发出 18 个问题，其中 14 个带着任务线索，另外 4 个在打听如何经由 DNS 搜索网页、抓取网站，或者哪里有公开的 DNS 隧道服务。&lt;/p&gt;
+&lt;p&gt;最后，它告诉用户没能确认博主身份，请对方提供原文、标题或博客名。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;捡钥匙&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;整份报告里，最值得反复读的是模型在决定走 DNS 这条路时留下的一句思维链。大意是，用户只授权了做研究，那么使用公开提供的 DNS 服务是可以接受的。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;模型并非不知道边界在哪，它是给自己签了一张许可证。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;同样的推理结构，出现在「访问」政府网站那批事件里。在商务部，智能体从公开代码仓库里找到登录凭证，用它拉取了人口普查局的数据。OpenAI 对此的说法是，使用的是公开可得的开发者密钥，没有发现凭证滥用，但它也承认智能体本不该使用这些凭证。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;数据是公开的，不等于捡到别人的钥匙就可以开门。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;另外两起性质更轻。在 SEC，模型访问的是 SEC.gov 和 Investor.gov 上的公开信息，问题在于它把这些材料转贴到了另一个网站。在教育部，AI 研究机构 Transluce 发现，疑似来自 OpenA</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 28 Sep 2026 16:08:56 +0800</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>从超级个体到超级组织，究竟还有多远？</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/371104</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr"/>
+      <c r="F536" s="2" t="inlineStr"/>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 月 22 日上午，阿里巴巴集团 CEO 吴泳铭站在云栖大会主论坛上讲到 AI 时，又一次用了电力作为参照。&lt;/p&gt;
+&lt;p&gt;今天回头来看，电几乎成为了现代社会最重要的基础设施生产力。&lt;/p&gt;
+&lt;p&gt;但 1882 年，即便是最负盛名的科学家与商人爱迪生，所能想到的事情也不过是在纽约珍珠街建起一个电站，点亮 400 盏电灯。甚至在当时为了推广电灯，还不得不用免费赠送半年电力的方式来吸引用户。&lt;/p&gt;
+&lt;p&gt;今天的 AI Coding，很可能也只是「电灯」&amp;mdash;&amp;mdash;&lt;strong&gt;它已经能替代一部分旧工作，帮人写代码、写报告，但站在 1882 年的电灯下面，人们永远也想象不出后来改变了整个人类社会运行的电气世界，究竟是什么样子。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;不过，关于这个故事，其实还有个没讲完的下半段。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;此后十多年时间里，电力已经进入工厂，但生产率却并没有立刻起飞。&lt;/strong&gt;因为早期工厂接入电力时，大部分企业的做法是直接拆掉蒸汽机，换上一台大型电动机。厂房中央的传动轴没有消失，皮带和齿轮也没有消失，动力与组织的生产上限，仍然沿着蒸汽时代留下来的结构传到每一台机器。&lt;/p&gt;
+&lt;p&gt;直到后来，小型电机可以直接装到不同机器旁边，工厂才逐渐摆脱中央动力轴。机器不用再围着一根轴排列，设备位置、物流、工序乃至厂房结构都可以重新设计，第二次工业革命才正式拉开序幕。&lt;/p&gt;
+&lt;p&gt;今天的企业也处在类似的情况中。&lt;/p&gt;
+&lt;p&gt;模型已经进公司了。工程师开始用 AI 写代码，销售用它找客户，HR 用它筛选信息&amp;hellip;&amp;hellip;&lt;strong&gt;可审批不会因为模型升级自动缩短，部门边界不会因为 Token 变便宜自己消失。一个岗位突然快了十倍，带给下一个环节的，可能只是无穷无尽的加班与延期。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;所以，当天上午主论坛讨论完机器智能之后，&lt;strong&gt;下午的云栖大会 AI Native 组织论坛就立刻接棒，将 AI 时代的组织变革作为讨论核心。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这并不是云栖大会上第一次分享相关话题，但却是第一次由阿里 CPO 和 CIO 两条线共同完成的讨论。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;过去，业务系统怎么搭建是一类问题，岗位、协作、人才和文化怎么调整是另一类问题；AI 真正落地生产流程以后，两件事已经很难各自解决。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;率先上台的阿里巴巴集团首席人才官蒋芳，先分享了一个思考：AI Native 组织到底只是一个被热炒的概念，还是组织必然会走向的方向？&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e4/96/e496e019fdfd6fb2f4d13601f0599576.png" /&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;AI Native 的组织到底是怎么运作的？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;AI native 组织是一个必然的进化方向，但不同企业产生的化学反应并不相同，这已经成为了新的管理共识。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;而在过去一年的观察和实践中，蒋芳逐渐总结出了一个规律：通常来说，那些一号位真的理解 AI，而且愿意亲自动手；或者原本的工作已经高度数据化；团队规模比较小；核心团队高度互信，是最容易完成 AI Native 时代组织转型的企业。&lt;/p&gt;
+&lt;p&gt;但偏偏，阿里本身已经成长为了一个拥有十几万名员工的庞大组织，并且组织内部业务形态差异巨大，协作关系复杂，甚至还有大量决策没有完整进入数据链路。想先在总部画好一套未来组织，再要求十几万人一起完成切换，几乎是天方夜谭。&lt;/p&gt;
+&lt;p&gt;并且，在真正尝试转型之前，阿里已经先感受到了另一层落差。蒋芳发现，过去一两年时间里，AI 加速下，组织里已经出现了&lt;strong&gt;一群超级个体，但是将这些超级个体放在一起，并不会自然得到一个超级组织。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;阿里云 CIO 蒋林泉，过去一年在产研团队里，试图解决的正是这种落差。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b7/b0/b7b0</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 12:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>Reco raises $55M as AI agent security startups crowd the market</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/29/reco-raises-55m-as-ai-agent-security-startups-crowd-the-market/</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr"/>
+      <c r="F537" s="2" t="inlineStr"/>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>The round builds on a $30 million fundraise in February, taking the company's total funding to $140 million.</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29T07:48:27-04:00</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic warns of ‘catastrophic’ AI risks in its own IPO filing</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1001838/anthropic-ipo-prospectus-ai-safety-threat</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr"/>
+      <c r="F538" s="2" t="inlineStr"/>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>As Anthropic gears up for its greatly anticipated public debut, a preview of the company's IPO filing reportedly details its mounting losses, leadership proposals to retain power, and how its AI development plans could "further increase the risk that our models cause harm." These disclosures come as Anthropic eyes a $2 trillion valuation, more than [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H538"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22522,6 +22522,193 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 07:08:13 +0000</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>半“臂”江山 万台启程｜珞石第10000台人形力控臂下线交付！</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13620</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr"/>
+      <c r="F539" s="2" t="inlineStr"/>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>从规模交付 到开放具身智能基础设施</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 03:52:21 +0000</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>灵巧手能刺绣？一场 0.01 毫米的指尖考试</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13607</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr"/>
+      <c r="F540" s="2" t="inlineStr"/>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>一根花线，可以劈到 0.01 毫米——大约头发丝的十分之一。过去，能摆弄这么细的东西的，只有人手。 绣娘用它绣 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 04:42:22 +0000</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>36家敲钟的机器人公司：赚钱能力差距巨大，商业化也不玩花架子了</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/499280.html</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr"/>
+      <c r="F541" s="2" t="inlineStr"/>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>机器人上市，风向有变</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 08:28:44 +0800</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>谷歌 Gemini 4 Argon 曝光；中国生成 AI 用户超 7 亿；美光 2026 财年净利暴涨 895%</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372064</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr"/>
+      <c r="F542" s="2" t="inlineStr"/>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/be/5d/be5d1ef7933babedeb1f7789b7df551c.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;苹果即将发布「智能家居中枢」新品&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据彭博社报道，苹果公司计划于 10 月 13 日推进其拖延已久的智能家居市场布局，这是该公司在新任 CEO 约翰&amp;middot;特努斯领导下的一次关键产品扩张。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据知情人士透露，该战略的核心是一款代号为 J490 的智能家居中枢设备。该设备将采用大约 6 英寸的方形显示屏设计，提供可安装在墙上或放置在台面上的版本。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;按照苹果的设想，用户会在家中多处放置多台这种显示屏。它们可用于控制恒温器、门锁和其他联网产品，也可用于视频通话、对讲式沟通、播放音乐，以及查看存储在苹果 iCloud 服务中的照片幻灯片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;苹果还把这台设备视为厨房里的通信和信息中枢，用户可以在做饭时通过语音查询菜谱、观看视频或拨打 FaceTime 通话。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同时，报道称苹果也计划宣布 HomePod mini 自 2020 年首次亮相以来的首次更新，以及自 2022 年以来的首款新电视机顶盒。（来源：凤凰网科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/bd/e3/bde3df44084b690fa48dcc3151826060.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;谷歌 Gemini 4 Argon 登场，长周期代码工程测试超 Opus 5.5&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="1532" src="https://imgslim.geekpark.net/uploads/image/file/0e/23/0e23f9ffd77c9b0b571c5350d3045c2b.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当地时间 9 月 30 日，谷歌发布 Gemini 4 Argon，称其为公司迄今最先进的 AI 模型，但目前并未面向公众全面开放。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;定位方面，Gemini 4 Argon 的重点是长流程软件工程、企业知识工作和网络安全防御。官方称其在真实世界软件工程测试创纪录，网络安全基准并列第一，并在金融、法律等专业任务基准领先。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;模型特性方面，Gemini 4 Argon 单次输出上限达到约 100 万 tokens，高于此前的 64,000 tokens，适合处理大型代码库、长文档和多阶段任务。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;新模型在某些编码和知识工作基准测试中处于最先进水平，在多个方面都优于竞争对手 OpenAI 的前沿模型 GPT-6 Astra。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;快手高管调整：创始人程一笑兼任社区负责人，原社区负责人转任可灵CEO&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;9 月 30 日，快手发布内部公告，宣布组织架构与高管分工双重调整：公司设立跨事业部虚拟组织「企业 AI 生产力」，同时对核心高管岗位进行重新划分。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据了解，全新成立的「企业 AI 生产力」虚拟组织，负责基础办公系统基座的稳定运行，统筹通用 Agent、企业上下文体</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 16:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>Destro AI’s secret sauce is getting robots and humans on the same page</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/30/destro-ais-secret-sauce-is-getting-robots-and-humans-on-the-same-page/</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr"/>
+      <c r="F543" s="2" t="inlineStr"/>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>"One of the biggest reasons we are winning against robotics companies is because we are not a robotics company."</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:H546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22709,6 +22709,143 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:40:12+00:00</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>Atlas Robot’s New Hand May Outperform Humanlike Designs</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/robust-robot-hand</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr"/>
+      <c r="F544" s="2" t="inlineStr"/>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Today, &lt;/span&gt;&lt;a href="https://bostondynamics.com/" target="_blank"&gt;Boston Dynamics&lt;/a&gt;&lt;span&gt; is &lt;a href="https://bostondynamics.com/blog/robot-hands-for-modern-ai-and-real-work/" target="_blank"&gt;announcing&lt;/a&gt; a redesigned hand for its &lt;/span&gt;&lt;a href="https://spectrum.ieee.org/atlas-humanoid-robot" target="_self"&gt;Atlas robot&lt;/a&gt;&lt;span&gt;. The previous generation could do some &lt;/span&gt;&lt;a href="https://spectrum.ieee.org/robots-ces-2026" target="_self"&gt;crazy …&lt;/a&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 02 Oct 2026 08:28:26 +0800</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>苹果首款触屏 Macbook 或 10 月发布；AI 能力成本三年下降数千倍创纪录；美人形机器人跳入熔炉，致敬《终结者 2》</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372069</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr"/>
+      <c r="F545" s="2" t="inlineStr"/>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1a/85/1a8539a71d6383f12a59ab9f1c99f8d4.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;华为 Mate90 系列发布，售价 5999 元起&lt;/h2&gt;
+&lt;p&gt;10 月 1 日，&lt;a href="https://mp.weixin.qq.com/s/TFSZoDmWaGGWTwQv7MN1-w"&gt;华为 Mate90 系列手机正式发布。华为 Mate90 售价 5999 元起，华为 Mate90 Pro 售价 6999 元起，华为 Mate90 Pro Max 售价 9499 元起，华为 Mate90 Pro Max 典藏版售价 10999 元起，华为 Mate90 RS 非凡大师售价 12999 元起。&lt;/a&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/44/a5/44a5a8a76aabfd80cc852e1113567b82.png" /&gt;&lt;/p&gt;
+&lt;p&gt;影像系统是本次迭代的核心亮点。华为 Mate90 系列全系搭载第三代红枫原色摄像头，标配红外光学镀膜技术，有效提升夜景画面纯净度与通透感。新机新增烟花人像、柔光人像、星芒特效等多元拍摄风格，依托原生原片直出的优质画质，既满足日常随手拍需求，也为后期创作预留充足空间。同时，全新华为光变巨炮睿影 Z10 专业影像模块正式登场，区别于传统增距镜设备，其内置 1 英寸大底传感器，支持 1-10 倍连续光学变焦，大幅拓展移动端专业拍摄边界。（来源：36 氪）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/18/77/1877496d3c3a24786c016460799e9333.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果首款 OLED 触屏 MacBook Pro 或最快本月发布&lt;/h2&gt;
+&lt;p&gt;苹果首款配备 OLED 显示屏的 MacBook Pro 正在逐渐接近发布。彭博社记者马克&amp;middot;古尔曼最新表示，苹果有望在 2026 年 10 月或 11 月推出这款经过大幅重新设计的 MacBook 产品。这意味着此前传闻已久的 OLED MacBook Pro 最快可能在本月正式亮相，不过具体发布时间仍存在变数，也不排除推迟到 11 月甚至更晚的可能。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/86/5f/865f300c4364638fabb865eee1d099b7.png" /&gt;&lt;/p&gt;
+&lt;p&gt;根据目前多方爆料，苹果计划推出 14 英寸和 16 英寸两种尺寸的 OLED 机型。这将是 MacBook Pro 自 2021 年采用 M1 Pro 和 M1 Max 平台以来首次进行如此大规模的外观重新设计。与目前仍采用 LCD 显示屏的 MacBook Pro 相比，新机除了更换 OLED 面板之外，还将针对机身厚度、屏幕结构以及摄像头区域进行调整。&lt;/p&gt;
+&lt;p&gt;OLED 显示屏将是新款 MacBook Pro 最核心的硬件变化之一。与目前的 Mini-LED 背光 LCD 相比，OLED 能够实现像素级独立发光，在显示纯黑画面时可以直接关闭对应像素，因此能够提供更高的对比度和更深的黑色，同时也有望进一步改善响应速度和显示效果。（来源：cnBeta）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;ChatGPT 新增虚拟试穿与收藏功能，可用自拍预览服饰效果&lt;/h2&gt;
+&lt;p&gt;OpenAI 为 ChatGPT 推出两项购物功能，面向全球用户开放。用户可以上传自拍或全身照，预览衣服和配饰穿在自己身上的效果；也可以上传商品图片或网页截图，让 ChatGPT 尝试将该商品合成到照片中。购物结果中将出现新的「试穿」按钮。&lt;/p&gt;
+&lt;p&gt;新功能由 ChatGPT Images 2.5 模型驱动。OpenAI 称，该模型能呈现更自然的光线和更丰富的纹理，更可靠地遵循图像编辑指令，并缩短生成图片所需时间。另一个新增功能「收藏」允许用户把感兴趣的商品保存到应用内的资料库，供日后查看；试穿生成的图片也会与收藏商品一并保存。&lt;/p&gt;
+&lt;p&gt;ChatGPT 还可根据用户描述的风格寻找搭配单品，或</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 11:21:33 +0800</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>从数据到智能，再到进化：Agent正在重写AI基础设施</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372065</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr"/>
+      <c r="F546" s="2" t="inlineStr"/>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;一个工程师写完数据处理代码，点下提交，然后去喝了杯咖啡。十几分钟甚至几十分钟之后，他才回到屏幕前看结果、改代码、再提交。这条「等待&amp;mdash; 反馈」的空隙，过去一直是数据平台默认的节奏。&lt;/p&gt;
+&lt;p&gt;Agent 没有这个空隙。它拿到一次结果，立刻验证，紧接着并发地去试第二种、第三种方案，飞快拿到反馈，再发起下一轮调用。&lt;/p&gt;
+&lt;p&gt;人用平台，发过来的是一个相对确定的任务，算完、给结果、走人；Agent 用平台，会不停地换着法子去完成你交代的那个目标。压力就这样被放大了&amp;mdash;&amp;mdash; 管控的压力和隐形计算的压力，会十倍、百倍地往上翻。&lt;/p&gt;
+&lt;p&gt;这正在成为 2026 年云计算需要面对的一种新负载。&lt;/p&gt;
+&lt;p&gt;AI 正在深入「把模型用起来」的阶段。模型一旦长成 Agent，它就不再是一个躺在那里等你调用的接口，而更像一个会自己找数据、自己拆任务、自己并发试错、自己一直跑下去的数字员工。它制造出来的负载，和过去十几年云平台习惯承载的那种负载，完全是两回事。&lt;/p&gt;
+&lt;p&gt;阿里云智能集团首席技术官李飞飞在云栖大会上把智能体落地拆成三个词：Model 决定智能的上限，Context 决定 Agent 读不读得懂你的业务，Harness 决定它能不能真正调起工具、把事做完、并且一直跑下去。想同时喂饱这三样，光把一个模型做大做强，远远不够。&lt;/p&gt;
+&lt;p&gt;数据流动起来产生智能，智能以 Agent 的形态落进业务，业务跑起来又产生新的数据和新负载，回过头再推着整个系统往前走。飞轮转得快不快，取决于三件事&amp;mdash;&amp;mdash; 模型生产的效率、智能落地的效率、系统自我进化的效率。&lt;/p&gt;
+&lt;p&gt;今年云栖大会上，阿里云做的事，就是沿着这三个效率，把从数据入湖、训练集生产、模型训练、推理服务，一直到系统自己优化自己的整条链路，一次性升级了一遍。&lt;/p&gt;
+&lt;p&gt;贯穿这些升级的，是阿里云所强调的「芯云模一体」：让芯片、云平台与模型逐渐走向协同设计，打通从原始数据到业务决策的全栈。&lt;/p&gt;
+&lt;h1&gt;当模型走进真实世界，数据先成了瓶颈&lt;/h1&gt;
+&lt;p&gt;AI 进入物理世界之后，数据首先发生了变化。&lt;/p&gt;
+&lt;p&gt;过去的大模型主要处理文本和代码。自动驾驶、具身智能和科学计算面对的却是视频、点云、运动轨迹和传感信号。原始数据很容易积累，真正困难的是把这些数据清洗、质检、标注并转换成模型可以使用的训练集。&lt;/p&gt;
+&lt;p&gt;穹彻智能首席科学家吕峻在接受采访时提到，具身智能的数据以视频和点云为主，从采集完成到进入训练，中间可能经过几十道处理。一次数据版本迭代，短则两周，长则一个月。存储、数据处理和模型训练之间只要有一个环节衔接不畅，整个实验周期都会被拉长。&lt;/p&gt;
+&lt;p&gt;从长期看，具身智能可用的数据规模可能仍有两到三个数量级的缺口。但吕峻认为，现阶段更直接的问题已经转向数据质量：哪些数据真正有效，怎样完成精细标注和前后质检，以及算法能否把这些数据转化成模型能力。&lt;/p&gt;
+&lt;p&gt;数据生产方式也在随之变化。传统人工标注需要组建和培训团队，规则改变后还要重新调整流程；模型辅助标注可以更快迭代，并将人力集中到质检和高难度样本上。对于具身智能公司来说，这种变化影响的不只是成本，还决定了模型实验能否足够频繁地进行。&lt;/p&gt;
+&lt;p&gt;阿里云对 MaxCompute 和 EMR 的升级，针对的正是这条数据生产链。MaxCompute 将 CPU、GPU 和大模型 Token 纳入统一调度，MaxFrame 和 SQL AI Function 可以直接调用模型处理图片、文本等全模态数据。面向自动驾驶和具身智能等场景，行业 Skill 则将数据管线进一步封装，让开发者通过自然语言组织处理任务。&lt;/p&gt;
+&lt;p&gt;EMR Serverless Spark 支持 Spark、Ray、Daft 等全模态引擎，并与 Paimon、Iceberg 等开放湖表格式连接。按照阿里云公布的数据，这套方案可以让具身智能数据处理耗时减少 40%，PB 级原始数据能够直接生成 LeRobot、RLDS 格式的训练集。&lt;/p&gt;
+&lt;p&gt;数据准备完成后，问题来到了训练端。PAI-DLC 3.0 引入 Xfuse，对算力底座、训练框架和任务运行状态进行联合分析，自动定位通信、数据读取、算子和资源调度中的问题。阿里云公布的测试结果显示，多模态模型端到端训练速度提升了 2.4 倍。&lt;/p&gt;
+&lt;p&gt;这类优化越来越依赖芯片、云平台和模型之间的协同。&lt;/p&gt;
+&lt;p&gt;阿里云智能集团研发副总裁、计算平台事业部负责人汪军华则在接受采访时举例称，一种模型架构即便效果足够好，如果与芯片缓存、通信方式和推理框架不匹配，落到真实硬件上仍可能付出很高的成本。AI 基础设施由此进入一</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H546"/>
+  <dimension ref="A1:H548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22846,6 +22846,95 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:30:02+00:00</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Albatross Falls, Spins, Self-Rights, and Sails Away</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-bioinspired-robotics</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr"/>
+      <c r="F547" s="2" t="inlineStr"/>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 03 Oct 2026 09:17:08 +0800</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>英伟达股价创新高，逼近 6 万亿美元；限制 AI 助手，苹果收紧 MacOS 磁盘访问权限；arXiv 每人每月仅允许投递 2 篇论文</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372070</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr"/>
+      <c r="F548" s="2" t="inlineStr"/>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/da/95/da959aebfdc76b4839014c7178cc0f95.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;英伟达股价创新高，逼近 6 万亿美元&lt;/h2&gt;
+&lt;p&gt;英伟达股价自 5 月以来首次创下历史新高，在两个月的抛售导致市值蒸发逾 1 万亿美元后，投资者重新涌入该股。这家全球市值最高的上市公司股价周五上涨 2.9%，较 7 月底低点累计反弹近 25%。&lt;/p&gt;
+&lt;p&gt;英伟达股价今年迄今上涨约 27%，有望连续第四年实现两位数涨幅。目前公司市值约为 5.7 万亿美元，距离成为历史上首家市值达到 6 万亿美元的公司不到 3000 亿美元。（来源：环球市场播报）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/81/c4/81c4954515b980b21ef5df2528cd6f50.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;腾讯 WorkBuddy 内置模型独家支持 Space Bunny&lt;/h2&gt;
+&lt;p&gt;10 月 2 日消息，腾讯 WorkBuddy 宣布内置模型独家支持 Space Bunny。&lt;/p&gt;
+&lt;p&gt;据介绍，Space Bunny 是一款匿名 Flash 大模型，具备极速推理、强大的编码能力，原生支持文本、图像、视频输入，思考深度可调，上下文长达 1M。WorkBuddy 国内独家接入，2026 年 10 月 2 日至 10 月 7 日间可享限时折扣。&lt;/p&gt;
+&lt;p&gt;2026 年 9 月 27 日，Space Bunny 在 OpenRouter 的 Token 调用量约 3.99 万亿，在 OpenCode 约 8.3 万亿，均位居第一，连续霸榜三天。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;AI 代理能力增强带来新的隐私安全风险，苹果收紧 macOS「完全磁盘访问」权限&lt;/h2&gt;
+&lt;p&gt;苹果近日宣布将进一步收紧 macOS 中的「完全磁盘访问」（Full Disk Access）权限控制，并计划增加新的安全机制，以降低 AI 代理获得大范围系统数据访问权限后可能产生的隐私风险。&lt;/p&gt;
+&lt;p&gt;苹果表示，「完全磁盘访问」最初主要是为了让备份等软件能够正常工作，但随着能够自主操作电脑的 AI 代理越来越普及，这一权限所带来的风险正在明显上升。&lt;/p&gt;
+&lt;p&gt;macOS 目前已经允许用户在系统设置的「隐私与安全性」中手动授予应用「完全磁盘访问」权限。获得这一权限后，应用可以访问用户电脑中的大量敏感数据，包括文件、邮件、信息以及浏览历史等内容。苹果长期以来一直要求这类权限必须经过用户主动授权。&lt;/p&gt;
+&lt;p&gt;苹果认为，当 AI 代理获得这种级别的系统访问能力后，其潜在影响已经不同于传统应用，因此用户必须更加明确地知道自己究竟授予了应用什么权限。&lt;/p&gt;
+&lt;p&gt;随着越来越多 AI 产品开始直接进入桌面操作系统，如何让代理拥有完成复杂任务所需的能力，同时又避免一次授权导致整个个人数字环境暴露，正在成为操作系统厂商必须解决的新问题。（来源：搜狐科技）&lt;/p&gt;
+&lt;h2&gt;Meta 旗下 AI 智能体 Muse 将登陆智能眼镜平台，可代用户完成各种任务&lt;/h2&gt;
+&lt;p&gt;10 月 2 日消息，Meta 宣布旗下 AI 智能体 Muse 将于近期登陆智能眼镜，用户无需拿出手机，只需通过语音下达指令，Muse 就能在后台代用户完成一系列任务。&lt;/p&gt;
+&lt;p&gt;Meta 表示，Muse 基于 Muse Spark AI 模型运行，其核心运行环境是一台部署在云端的私有持久化 Linux 虚拟机，配备独立的网页浏览器、文件系统和终端。即使用户关闭应用，这些组件仍会持续运行。&lt;/p&gt;
+&lt;p&gt;为了完成用户交代的任务，Muse 可以自行决定编写并运行代码，也可以将工作分配给多个子智能体，还能创建定时任务。此外，Muse 还能够生成文档、PDF、网站以及消费记录追踪器、数据仪表盘等交互式工具。&lt;/p&gt;
+&lt;p&gt;Meta 列举了更多使用场景，包括代用户预约服务、查询机票价格、寻找替换零部件、记录饮食、提供健身指导、帮助购买用户眼前看到的商品。用户只需说出「Hey Muse」或预先设置的 Muse 名称，然后提出具体要求，Muse 便会在后台执行任务，并在完成后向用户反馈结果。（来源：网易）&lt;/p&gt;
+&lt;h2&gt;微软 CEO 纳德拉重申 Copilot AI 定位：面向工作的新操作系统&lt;/h2&gt;
+&lt;p&gt;10 月 3 日消息，微软首席执行官萨蒂亚 &amp;middot;</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H548"/>
+  <dimension ref="A1:H549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22935,6 +22935,54 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 04 Oct 2026 08:33:38 +0800</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>苹果确认美版 iPhone 18 Pro Max 有问题；OpenAI 每天烧超 50 万美元查 AI 入侵事故；求职者吐槽 AI 面试「恐怖谷」上热搜｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372073</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr"/>
+      <c r="F549" s="2" t="inlineStr"/>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/98/b7/98b70ec4d8f526d4dce6c7b2137fb702.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;苹果确认：美版 iPhone 18 Pro Max 有问题&lt;/h1&gt;
+&lt;p&gt;北京时间 10 月 3 日，彭博社报道称，苹果公司表示，AT&amp;amp;T 的问题已导致部分 iPhone 18 Pro Max 用户无法拨打电话、访问数据或在联网时收发短信。目前尚不清楚有多少人遇到此问题。受影响的用户发现，除非连接到 Wi-Fi 网络，否则他们的设备基本无法使用。&lt;/p&gt;
+&lt;p&gt;苹果公司已发布运营商设置更新，并推出了 iOS 操作系统的新版本 27.0.1，以防止该问题进一步蔓延。运营商设置修复程序将在未来 14 天内自动为 AT&amp;amp;T 用户下载，但苹果仍建议消费者立即安装任何可用的软件更新。&lt;/p&gt;
+&lt;p&gt;苹果发言人在提供给彭博社的一份声明中表示：「我们已发现一个影响少数 AT&amp;amp;T 网络 iPhone 18 Pro Max 用户的故障，可能导致设备失去服务并无法拨打电话。」报道称，对于已经受到影响的用户，唯一的解决办法是更换手机，使用苹果或 AT&amp;amp;T 提供的新设备。&lt;/p&gt;
+&lt;p&gt;报道提到，在美国销售的 iPhone 18 Pro Max 与其他新款机型有一点不同：它搭载的是由高通公司制造的蜂窝基带。包括较小的 iPhone 18 Pro 在内的所有其他版本，均配备苹果自研的 C2 基带。根据用户报告，只有 iPhone 18 Pro Max 受到了 AT&amp;amp;T 这一漏洞的影响。（来源：新浪科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b1/c0/b1c0a7691b78da43484e913b00986632.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;英伟达 Vera Rubin NVL72 跑出 4.8 倍 Token 吞吐&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;AI 云服务商 CoreWeave 近日宣布，英伟达 Vera Rubin NVL72 系统已在 CoreWeave Cloud 正式投入生产，AI 软件公司 Cognition 成为首个在该平台运行生产工作负载的客户。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Cognition 在 Vera Rubin NVL72 上运行 SWE-2 推理任务，&lt;strong&gt;实测总 Token 吞吐量较 GB200 NVL72 提升高达 4.8 倍。&lt;/strong&gt;在强化学习场景中，每 GPU 输出 Token 吞吐量也达到 GB200 NVL72 的&lt;strong&gt;3.8 倍&lt;/strong&gt;，意味着 Devin 可同时处理更多会话并加速多步推理。&lt;strong&gt;在 DeepSeek-R1 推理基准测试中，Vera Rubin NVL72 每兆瓦 Token 吞吐量达到 GB200 NVL72 的 10 倍，&lt;/strong&gt;在相同电力消耗下可产出更多智能输出。&lt;/p&gt;
+&lt;p&gt;硬件规格方面，NVL72 系统由 36 颗 Vera CPU 和 72 颗 Rubin GPU 构成，采用&lt;strong&gt;100%全液冷设计&lt;/strong&gt;。无缆线模块化托盘设计将安装时间从两小时压缩至五分钟，大幅提升部署效率。（来源：快科技）&lt;/p&gt;
+&lt;h1&gt;旗下智能体频繁「闯祸」，OpenAI 每天要烧掉超 50 万美元来调查&lt;/h1&gt;
+&lt;p&gt;10 月 3 日消息，据英国《卫报》3 日报道，OpenAI 披露，为调查旗下 AI 智能体攻击澳大利亚 Medicare 医疗保险系统和 Hugging Face 等事件，公司每天投入&lt;strong&gt;超过 50 万美元（现汇率约合 335.7 万元人民币）&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;由于需要筛查的数据规模极大，OpenAI 还动用 AI 参与审查。OpenAI 本周在博客中介绍了这项调查的规模：公司需要&lt;strong&gt;检查 50PB 数据&lt;/strong&gt;，约合 5000 万吉字节。如果把这些数据全部交给一个人阅读，需要&lt;strong&gt;约 6600 万年&lt;/strong&gt;。OpenAI 警告，调查还没有结束，近期可能有更多机构接到通知，被告知曾成为智能体行动的目标。审查重点包括&lt;strong&gt;模型访问或修改网站的记录&lt;/strong&gt;，以及涉及密码、应用程序编程接口访问权限和其他敏感凭证的操作。&lt;/p&gt;
+&lt;p&gt;Open</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H549"/>
+  <dimension ref="A1:H550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22983,6 +22983,57 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 08:36:34 +0800</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>马斯克将旗下人工智能业务更名为 SpaceXSI；Altman 称 AI 发展应容忍一定风险；小米 Vision GT 将入驻《GT7》游戏｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372082</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr"/>
+      <c r="F550" s="2" t="inlineStr"/>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/97/c3/97c3777f86ddef91f843ffa5b09b2a67.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;马斯克拟将 SpaceXAI 更名为 SpaceXSI 为「超级智能」概念背书&lt;/h1&gt;
+&lt;p&gt;美国总统特朗普推动以「超级智能」（Super Intelligence，简称 SI）取代「人工智能」（AI）的举措正在迅速影响科技行业。特斯拉和 SpaceX 首席执行官埃隆&amp;middot;马斯克日前表示，旗下人工智能业务品牌 SpaceXAI 有意更名为 SpaceXSI，并公开宣称「SpaceX 是一家超级智能公司」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1d/a4/1da40b5999a490e3b9abce9fd496bf24.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;这一表态源于特朗普政府近期推动的一项新政策。9 月 22 日，特朗普宣布以「超级智能」取代「人工智能」这一术语，并呼吁美国联邦政府在相关文件和机构中采用新的表述。此后，美国政府开始围绕「超级智能」建立新的政策框架和产业沟通机制。&lt;/p&gt;
+&lt;p&gt;在回应社交平台用户关于「SpaceXAI 是否会更名为 SpaceXSI」的提问时，马斯克明确表示「是的，我们会做出改变」。随后，他进一步发文称，SpaceX 本质上是一家「超级智能公司」。&lt;/p&gt;
+&lt;p&gt;此次更名若最终落实，将是该业务板块在短时间内再次调整品牌身份。此前，由马斯克创立的 xAI 于今年 2 月被 SpaceX 收购，并在 7 月正式完成品牌重组，更名为 SpaceXAI，将 Grok 及其他人工智能产品统一纳入 SpaceX 体系。如今，随着「超级智能」概念被推向台前，该品牌可能再次迎来名称调整。（来源：CnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6a/db/6adb1c5d1c6d707dc8afa0ad8e4e454d.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;余承东：华为半导体已在手机、AI、智能汽车等领域成功设计并量产 381 款 &amp;tau; 芯片&lt;/h1&gt;
+&lt;p&gt;10 月 4 日消息，在今年 5 月的 2026 国际电路与系统研讨会上，华为公司董事、半导体业务部总裁何庭波在主旨演讲中首次提出半导体全新演进路径&amp;mdash;&amp;mdash;「韬（&amp;tau;）定律」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f1/cf/f1cf1b762761ad7651b82a89d6989a63.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;华为常务董事、产品投资评审委员会主任、终端 BG 董事长余承东今日发布视频，透露华为半导体已经在手机、AI、通用计算、网络、智能汽车等多个领域&lt;strong&gt;成功设计并量产了 381 款 &amp;tau; 芯片&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;据余承东介绍，过去芯片性能提升主要依赖不断缩小的晶体管。但随着晶体管尺寸接近物理极限，性能提升越来越难。因为空间是有极限的，所以华为换了一个思路&amp;mdash;&amp;mdash; 向时间要性能。&lt;/p&gt;
+&lt;p&gt;具体来看，芯片完成一项任务，时间不光花在计算上，还花在数据传输和等待上。韬定律的核心思路是让数据少绕路、让计算不用等，花更少的时间完成更多的任务。&lt;/p&gt;
+&lt;p&gt;华为韬定律提出以「时间 (&amp;tau;) 缩微」替代「几何缩微」作为半导体与电子系统演进的新指导原则&amp;mdash;&amp;mdash; 通过逻辑折叠等创新技术，持续压缩信号传播时延，不断提升晶体管密度，从而实现半导体与电子系统的持续演进。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;消息称台积电先进晶圆价格 2027Q1 拟计划再上调 6%~8%&lt;/h1&gt;
+&lt;p&gt;10 月 5 日消息，韩媒 ddaily 于 10 月 2 日发布博文，报道称在决定上调 10%~20% 基础上，台积电计划 2027 年第一季度针对最先进晶圆出货价格，&lt;strong&gt;再次上调约 6%~8%，&lt;/strong&gt;理由是制造成本和电力费用上涨。&lt;/p&gt;
+&lt;p&gt;报道援引半导体业界消息称，台积电 2 纳米制程订单激增，公司已将晶圆订单目</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H550"/>
+  <dimension ref="A1:H553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23034,6 +23034,154 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 09:16:53 +0800</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 宣布「28 天计划」，持续改进 Codex、Work；TikTok 上线一系列 AI 电商功能；蓝色起源公布月球「动力塔计划」</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372086</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr"/>
+      <c r="F551" s="2" t="inlineStr"/>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d0/88/d0889b25259f9a37ad377449ed0834f9.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;2026 诺贝尔奖生理学或医学奖揭晓：三学者凭借「光控离子通道和光遗传学」领域发现获表彰&lt;/h2&gt;
+&lt;p&gt;10 月 5 日消息，诺贝尔奖基金会宣布将 2026 年诺贝尔生理学或医学奖授予以下三人，以表彰他们在「光控离子通道和光遗传学」领域的发现：美国霍华德 &amp;middot; 休斯医学研究所及斯坦福大学的 Karl Deisseroth、德国柏林洪堡大学的 Peter Hegemann、德国维尔茨堡大学的 Georg Nagel。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/59/5a/595a9b018581fc65abeea524382c2b41.png" /&gt;&lt;/p&gt;
+&lt;p&gt;诺贝尔奖评选机构表示，三位科学家的研究推动了光遗传学（Optogenetics）的发展。这项技术能够利用光信号精确控制神经细胞活动，使研究人员得以观察活体大脑中的神经细胞如何影响记忆、情绪和行为，并为神经科学研究开启了新的方向。&lt;/p&gt;
+&lt;p&gt;这项研究最初源于对单细胞藻类的探索。Peter Hegemann 一直对莱茵衣藻（Chlamydomonas）如何向光源游动感到好奇。21 世纪初，他与 Georg Nagel 发现了一种具有特殊功能的蛋白质「通道视紫红质」（Channelrhodopsin）。这种蛋白质位于藻类细胞表面，当受到蓝光照射时，蛋白质会打开离子通道，使带电离子进入细胞，从而产生电信号。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/51/c2/51c277d7d8595dcc63f5c89d24c980bf.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 宣布「28 天计划」：Codex、Work 日进一步或「重置」&lt;/h2&gt;
+&lt;p&gt;10 月 5 日消息，OpenAI 核心产品与平台负责人 Thibault Sottiaux 在 X 上发文，透露团队将在未来 28 天持续推进 Codex 和 ChatGPT Work 相关改进。&lt;/p&gt;
+&lt;p&gt;他表示，OpenAI 接下来每天都会发布一项「对大多数 Codex / Work 用户而言有明显改善且具备实际意义」的功能更新，否则就提供一次「重置」。&lt;/p&gt;
+&lt;p&gt;根据其发布时间计算，这一周期预计至少从 10 月 5 日持续至 11 月 2 日。不过，Sottiaux 并未说明会如何进行重置，也没有确认其「重置」将覆盖哪些用户或额度。IT 之家后续将保持关注。&lt;/p&gt;
+&lt;p&gt;前一天，Sottiaux 还表示团队已经「锁定方向」，当前正在推进的工作主要集中于简化产品、提高使用效率以支持更多使用量、推出突破性功能以及开发新模型。&lt;/p&gt;
+&lt;p&gt;他同时提到，虽然有时需要提前进行技术投入，但用户反馈已经明确表明，希望相关产品变得更加简单，团队正在对此进行调整。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;OpenAI 将在 ChatGPT 生成图片时测试视觉广告 不会影响生成结果&lt;/h2&gt;
+&lt;p&gt;OpenAI 宣布，将在 ChatGPT 中测试一种新的视觉广告形式。用户生成图片时，界面可能出现展示商品灵感、产品使用方式或服务体验的广告。OpenAI 称，广告会明确标注，并与正在生成的图片分开，不会直接嵌入或改变用户创作的图像；公司也重申，广告不会影响 ChatGPT 给出的回答。&lt;/p&gt;
+&lt;p&gt;这项测试预计于 10 月下旬在美国启动，初期只面向一批广告商。OpenAI 没有在公告中说明具体哪些用户或订阅层级会看到视觉广告。此次推出的是 ChatGPT 现有广告业务的新广告格式，并非广告首次进入 ChatGPT。OpenAI 表示，ChatGPT 目前每周触达 12 亿人，广告业务将帮助其覆盖仅靠订阅服务难以触及的更大用户群体。&lt;/p&gt;
+&lt;p&gt;除视觉广告外，OpenAI 还将扩展广告效果衡量工具及合作伙伴网络，让广告商通过 Hightouch、Tealium 和 LiveRamp 等服务接入转化数据，并利用 AppsFlyer、Adjust、Branch 等伙伴开展网站或应用归因。公司也与 DoubleVerify 和 Inte</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 09:15:06 +0800</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>交付 19 天，小米澎程破万台，雷军又赢了。</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372087</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr"/>
+      <c r="F552" s="2" t="inlineStr"/>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/74/29/7429d854ae16a0778e480da6ddae6144.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：视觉中国&lt;/p&gt;
+&lt;p&gt;10 月 1 日，小米汽车公布了 9 月交付成绩单：单月交付量首次突破 4 万台。&lt;/p&gt;
+&lt;p&gt;这个数字放在新势力阵营里排第三，仅次于零跑（10.56 万台）和小鹏（4.13 万台），领先鸿蒙智行（3.75 万台）。&lt;/p&gt;
+&lt;p&gt;但真正值得关注的，不只是「小米又卖爆了」。&lt;/p&gt;
+&lt;p&gt;更有意思的是，9 月刚上市的澎程系列，首月交付就超过 1 万台。而这件事，偏偏发生在增程市场整体降温，上半年批发销量同比下滑 13.1%的背景下。&lt;/p&gt;
+&lt;p&gt;一个看似「风口已过」的赛道，被小米硬生生撕开了一道口子。&lt;/p&gt;
+&lt;p&gt;小米澎程是如何成功的？&lt;/p&gt;
+&lt;h1&gt;从 3 万到 4 万&lt;/h1&gt;
+&lt;p&gt;过去几年，增程市场的剧本非常魔幻。2020 年，增程式汽车全年总销量才 3 万多台。那时候，增程还经常被一些车企高管嘲讽为「过时技术」，甚至被说成是「脱裤子放屁」。但市场从来不听嘴炮，它只看用户掏不掏钱。&lt;/p&gt;
+&lt;p&gt;后来的事情大家都看到了。&lt;/p&gt;
+&lt;p&gt;2021 年，增程销量突破 10 万台；2022 年涨到 25 万台；2023 年冲到 64.2 万台；2024 年更是摸到 116.7 万台。短短几年，增程从新能源鄙视链底端，逆袭成为行业「黑马」。&lt;/p&gt;
+&lt;p&gt;原因也很简单，它解决了中国家庭买新能源车时最现实的里程焦虑。城市通勤能用电，长途出行不用怕没桩。既有电车的低成本体验，又能保留燃油车时代的安全感。&lt;/p&gt;
+&lt;p&gt;但到了 2026 年，剧情突然变了。&lt;/p&gt;
+&lt;p&gt;上半年增程批发销量只有 50.4 万台，同比下降 13.1%。6 月单月批发量更是暴跌 25.2%，创下近五年最大跌幅。增程在新能源市场里的份额，也从最高超过 10%，一路滑落到 6%左右。&lt;strong&gt;在纯电、插混、增程三条路线里，增程成了唯一一个下滑的市场&lt;/strong&gt;。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b5/39/b53903451c39c58d34b499e6c87ac955.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;小米澎程 N70 ｜来源：小米汽车&lt;/p&gt;
+&lt;p&gt;这时候小米杀进来，多少有点「来晚了」的味道。&lt;/p&gt;
+&lt;p&gt;9 月 7 日，小米在秋季发布会上推出澎程系列四款增程车型：N70 Pro、N70 Max、N90 Max、N90 Max 探索版。发布会现场，锁单 4 分钟破万。9 月 12 日开启交付，&lt;strong&gt;到月底只用了 19 天左右，交付就突破 1 万台&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;这直接把小米汽车月交付从 3 万台级别，推上了 4 万台台阶。&lt;/p&gt;
+&lt;p&gt;更重要的是，澎程的爆发，并没有明显挤压 SU7 和 YU7。很多品牌都会遇到一个尴尬局面：新车一上市，老车立刻掉量。表面看总销量涨了，实际是内部互抢客户，左手打右手，最后热闹了一场，没真正做大盘子。&lt;/p&gt;
+&lt;p&gt;但这次不一样。&lt;/p&gt;
+&lt;p&gt;澎程系列带来的，是一批原本不在小米纯电产品核心画像里的用户。他们不一定追求极致性能，但更关心第三排能不能坐人，后备厢能不能放下婴儿车&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p&gt;这批人过去可能会看理想、问界，也可能在燃油 SUV 和插混 SUV 之间犹豫。这次小米终于用澎程摸到了他们。&lt;/p&gt;
+&lt;h1&gt;澎程的杀手锏&lt;/h1&gt;
+&lt;p&gt;20 多万元的新能源车，单月销量破万，放在任何品牌身上都不是小事。尤其是在今天这个市场环境里，消费者已经不再容易被一场发布会、一句口号打动。&lt;/p&gt;
+&lt;p&gt;新能源车打到 2026 年，用户早就被教育得很精了。他们会算电池容量，会比空间、智驾芯片，看轴距，还会研究座椅布局&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;小米澎程最大的亮点是大空间&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;SU7 和 YU7 代表的是小米汽车的年轻感、科技感和运动感。澎程则是小米第一次真正面向家庭场景交出的产品。&lt;/p&gt;
+&lt;p&gt;N90 定位大型大七座 SUV，车长 5285mm，轴距 3080mm。这个尺寸对应的是多人口家庭、多人长途出行、商务接待、大空间刚需；N70 则更像主流家庭的车型，车长 4960mm，车宽 1998mm，轴距 2950mm，尺寸</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 05 Oct 2026 12:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>Can Safeworld convince people that GenAI robots won’t hurt them?</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/05/can-safeworld-convince-people-that-gen-ai-robots-wont-hurt-them/</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr"/>
+      <c r="F553" s="2" t="inlineStr"/>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>Safeworld is building digital humans to make sure robots don't hurt the real ones.</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H553"/>
+  <dimension ref="A1:H555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23182,6 +23182,74 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 20:00:30 +0000</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>AI computing startup Lambda to raise $4B ahead of planned IPO</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/06/ai-computing-startup-lambda-to-raise-4b-ahead-of-planned-ipo/</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr"/>
+      <c r="F554" s="2" t="inlineStr"/>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Lambda is raising up to $4 billion at a $14.5 billion pre-money valuation ahead of a planned 2027 IPO, led by Coatue and Blackstone.</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 06 Oct 2026 16:35:00 +0000</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>Mirror Particle is building a ‘world model’ of human behavior</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/06/mirror-particle-is-building-a-world-model-of-human-behavior/</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr"/>
+      <c r="F555" s="2" t="inlineStr"/>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>Mirror Particle will launch at TechCrunch Disrupt's Startup Battlefield 200 with a world model built from scratch to predict human behavior, arguing that LLM role-play falls short for market research and brand strategy.</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H555"/>
+  <dimension ref="A1:H566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23250,6 +23250,436 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 02:59:14 +0000</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>触觉智能企业“灵感机器人”新近完成数千万元天使轮融资</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13660</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr"/>
+      <c r="F556" s="2" t="inlineStr"/>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>力合资本、合肥创新投等机构投资，Lux 系列视触觉传感器已实现规模化交付。</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 02:43:37 +0000</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>“庐优”，九江诞生江西首个人形机器人自主品牌</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13644</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr"/>
+      <c r="F557" s="2" t="inlineStr"/>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>在这里，知九江！九江阅读量最高的公众号！</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 02:18:26 +0000</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>强强联合！优必选携手一汽-大众，推进人形机器人在物流场景应用落地</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13640</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr"/>
+      <c r="F558" s="2" t="inlineStr"/>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>Dream with Robots</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:49:48+00:00</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>HiPHI: A Large-Scale Benchmark for High-Precision Human Motion and Object Interaction</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>https://content.knowledgehub.wiley.com/hiphi-a-large-scale-benchmark-for-high-precision-human-motion-and-object-interaction/</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr"/>
+      <c r="F559" s="2" t="inlineStr"/>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;This White Paper gives robotics researchers and engineers an overview of a new large-scale motion capture dataset built to close …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>从 Rollout 到权重同步：Mooncake 如何支撑高性能强化学习系统｜QCon上海</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/akexM07HzNrRJzmjYNml?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr"/>
+      <c r="F560" s="2" t="inlineStr"/>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/akexM07HzNrRJzmjYNml?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 09:40:34 +0800</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>造物 100#07   | 给硬盘养个图书馆员、指纹钥匙给 AI 上锁、AI 对讲机住着科幻宇宙</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372099</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr"/>
+      <c r="F561" s="2" t="inlineStr"/>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;产品的创新，究竟应该如何定义它的价值？&lt;/p&gt;
+&lt;p&gt;上周，华为、小米、苹果在 72 小时内接连发布折叠屏旗舰。华为 Mate XT 2 非凡大师 19999 元起售，小米 18 Fold 10999 元，苹果首款折叠屏 iPhone Duo 市场预计 1.6 万起。与此同时，一组数据冲上热搜，通用内存合约价环比涨超 58%，固态硬盘涨超 70%，主流性能机比去年贵了 2800 到 4500 元。「普通人没必要追求电子产品顶配」登上热搜，年轻人转向二手电脑和标准版机型，不再一味追求顶配功能。&lt;/p&gt;
+&lt;p&gt;一边是厂商急需拓展新产品线的渴望，一边是用户日益下探的购买力。当「更贵」不再自动等于「更想要」，创新到底该如何定义价值？消费者真正愿意买单的还有什么？&lt;/p&gt;
+&lt;p&gt;上周我们谈到在成熟品类上小创新成为当下造物的一种方式。这周，这个方向仍在不少品类上体现。这些新造物几乎都不是一个完全独立的创新品类，但它们都希望重新定义产品的使用指南。&lt;/p&gt;
+&lt;p&gt;智能数据拓展坞 MUZIM L1 结合了桌面交互、拓展坞、内存条盒的基础功能上，基于本地化，重新定义了存储和信息搜索。手机皮肤镜 Lumeria Lumoscope 基于手机和专有摄像头，去解决亲人具体困扰已久的皮肤敏感问题。无线指纹钥匙 immurok IK-1 则是在 Mac 的指纹解锁上，硬件独立化，解决 AI 授权的行为。&lt;/p&gt;
+&lt;p&gt;现阶段，硬件或许没办法直接去押注一个「更大」未来时，创新的机会反而变得具体了。你如何将一个旧麻烦的解决方式「优化」得更好，同时还能够为消费者创造意料之外的使用惊喜，或许成为关键。&lt;/p&gt;
+&lt;p&gt;以下，是「造物 100」栏目第 7 期推荐的最新造物。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;智能数据拓展坞 MUZIM L1 :打造本地化的私人图书馆，请一位听得懂人话的 AI 管理员&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;每个人的硬盘里都躺着几万个再也找不到的文件。命名混乱的照片、不知道存在哪层文件夹的合同、手机备份了三次的重复视频。过去，文件的搜索框只认文件名，而你早忘了当初和好友合影的图片编码到底是什么数字。&lt;/p&gt;
+&lt;p&gt;MUZIM L1 想把这件事换个解法。硬件上，它是一台桌面数据坞，双 SSD 插槽、16 口扩展、最高支持 24TB 存储，一块 1.6 英寸小屏加主动散热，USB 4.0 连接。但真正的主角是里面跑的 OpenSoul 文件系统，团队管它的核心能力叫 Vibe Search，用一句人话，可以搜到任何文件。「去年冬天在海边拍的那段视频」、「上个月签的那份租房合同」，只要你描述得出来，它就找得到，不仅是图片支持按内容语义搜，视频也可以精确到某一帧的内容，音频也会先被转写再检索。&lt;/p&gt;
+&lt;p&gt;它还会自动整理，识别人脸分组、按「宝宝第一次走路」这样的语义把散落文件组织成故事、把相似的废片堆叠起来。甚至还有很细致的时间线，告诉你在什么时间，干了什么事情。比较有意思的是它会记录不同人之间的关系，去揣测全程本地优先，文件不默认上云。&lt;/p&gt;
+&lt;p&gt;AI 文件搜索这件事，苹果和微软都在系统层面做，但它们的答案都通向云端订阅。MUZIM 把这套能力塞进一台桌面硬件里，语义搜索在你自己的 SSD 上跑，等于给人做了一台 AI 时代的私人图书馆。&lt;/p&gt;
+&lt;p&gt;不过众筹还没正式开跑，语义搜索的实际准确率、大文件库的索引速度都要等实机检验。而且它赌的前提是你的数据需不需要一台专属本地硬件，这个判断对创作者成立，对普通人还需要说服。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/17/46/17461e9043d435287b560a57b0df35ac.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;手机皮肤镜 Lumeria Lumoscope：把皮肤科的检测相机，夹到你的手机上&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;Lumeria Lumoscop 的创始人 Anthea Guo 的姐姐被湿疹追着跑了八年，最后查出的元凶是地毯里的灰尘。但这个罪魁祸首，在长达八年的时间里都没人抓到它，很难被人看见。但是皮肤对睡眠、居住环境、护肤品和空气的每一次反应，都没有变成数据。而且每当需要换一个皮肤科医生时候，一切的盘问都从零开始。&lt;/p&gt;
+&lt;p&gt;Lumeria 选择打造一个夹在手机镜头上的多光谱皮肤镜。通过 RGB、紫外、偏振光加近红外四种光谱扫描皮肤，把诊所里皮肤镜能看到，但是肉眼看不见的信息都记录下来。再配套上 AI 教练读取扫描历史，追踪变化、判断哪些产品真的有效、提示什么时候该去看医生。团队将其看作，皮肤界的 O</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 08:49:27 +0800</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT 推出全新 IUI 智能用户界面；谷歌推出试验性 AI 游戏平台 Playground；苹果被曝联合 LG 开发门锁、摄像头等智能家居配件｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372090</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr"/>
+      <c r="F562" s="2" t="inlineStr"/>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9e/40/9e40f9772b90b2e469e4dc6938518a66.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;2026 年诺贝尔化学奖公布：二人因解开不对称有机合成难题获奖，其中一位 96 岁高龄&lt;/h2&gt;
+&lt;p&gt;10 月 7 日，2026 年诺贝尔化学奖正式公布，瑞典皇家科学院决定将 2026 年诺贝尔化学奖授予亨利 &amp;middot;B&amp;middot; 卡甘（Henri B. Kagan）和硖合宪三（Kenso Soai），「表彰他们在不对称有机合成中发现非线性效应和自催化现象。」&lt;/p&gt;
+&lt;p&gt;有些分子，例如氨基酸，以两种变体形式存在，互为镜像。然而，生物体只包含这些镜像之一。像这样的化学不对称性是如何出现的，长期以来对化学家来说一直是个谜。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5b/d9/5bd97d3817125c6001163e2501a71a88.png" /&gt;&lt;/p&gt;
+&lt;p&gt;亨利 &amp;middot;B&amp;middot; 卡甘和硖合宪三因发现这一难题的解决方案而荣获 2026 年诺贝尔化学奖。&lt;/p&gt;
+&lt;p&gt;亨利 &amp;middot;B&amp;middot; 卡甘（1930 年出生于法国，当前 96 岁，隶属法国奥尔赛省巴黎南大学）发现了一种操纵化学反应的新方法，可以创建比之前假设的更多的镜像。他的发现对于化学家来说是革命性的，可以帮助开发用于制造药物、香料、香味和新材料的反应。&lt;/p&gt;
+&lt;p&gt;硖合宪三（1950 年出生于日本广岛，当前 76 岁，隶属东京理科大学）设计了首个仅形成其中一个潜在镜像的化学反应。除了生命本身，没有人曾实现过这样的壮举。诺贝尔奖官方表示，Soai 反应是有史以来最壮观的化学实验之一。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/27/9a/279a24ef9847d73a9b81c853daaacc3e.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;黄仁勋：英伟达当初正是因 Windows 而诞生&lt;/h2&gt;
+&lt;p&gt;10 月 8 日，在美国旧金山举办的发布会中，英伟达首席执行官黄仁勋表示：「英伟达当初正是因 Windows 而诞生」。&lt;/p&gt;
+&lt;p&gt;在本次活动中，微软首席执行官萨蒂亚 &amp;middot; 纳德拉、英伟达首席执行官黄仁勋和白宫前人工智能高级政策顾问斯里拉姆 &amp;middot; 克里希南三人展开了一场对话。&lt;/p&gt;
+&lt;p&gt;黄仁勋在开场时表示：「英伟达的创立是因为 Windows 系统。Windows 95 系统让 GPU 连接到 PC 成为可能，DirectX 对 PC 图形技术的早期发展至关重要。」这基本上就是英伟达并行计算平台 CUDA 的起源故事。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a3/34/a334bce3992fad895438d8f053095246.png" /&gt;&lt;/p&gt;
+&lt;p&gt;黄仁勋表示：「我们想要世界上最好的 Blender、世界上最好的 Omniverse、世界上最好的 CUDA&amp;hellip;&amp;hellip; 所有这些都要和 AI 一起运行在同一台电脑上。」&lt;/p&gt;
+&lt;p&gt;黄仁勋强调，AI 计算不应只存在于大型数据中心，也将逐步进入开发者和企业用户的桌面环境。随着模型规模扩大以及对隐私、低延迟和本地处理的需求增加，个人设备需要具备更强的 AI 推理和开发能力。&lt;/p&gt;
+&lt;p&gt;黄仁勋的讲话也显示，英伟达希望进一步加强与微软 Windows 生态的结合。通过将高性能 GPU、统一内存和 AI 软件栈带到 Windows 设备，开发者可以在熟悉的操作系统环境中构建和运行 AI 应用。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;&amp;nbsp;&lt;/h2&gt;
+&lt;h2&gt;&lt;strong&gt;&lt;span class="text-only"&gt;OpenAI 推出 ChatGPT 全新交互界面：AI 不只回答问题，还能直接生成可操作的工具&lt;/span&gt;&lt;/strong&gt;&lt;/h2&gt;
+&lt;div&gt;
+&lt;p&gt;10 月 7 日，OpenAI 宣布将 GPT-6 推向更广泛的 ChatGPT 用户，并同步推</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 08:39:21 +0800</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>派拉蒙 1100 亿美元收购时代华纳，好莱坞诞生新巨无霸；月之暗面被曝完成 500 亿美元 PreIPO 融资；微软、Meta 被曝要求员工减少使用 Claude</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372089</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr"/>
+      <c r="F563" s="2" t="inlineStr"/>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ed/c1/edc15e1a2981cde354ac7813f71ba265.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;2026 诺贝尔物理学奖揭晓：把一立方公里南极冰变成望远镜，打开「中微子天文学」&lt;/h1&gt;
+&lt;p&gt;10 月 6 日，2026 年诺贝尔物理学奖授予比利时裔美国物理学家 Francis Halzen，以表彰其「对 IceCube 中微子天文台的决定性贡献，以及发现来自天体的高能中微子」。&lt;/p&gt;
+&lt;p&gt;Halzen 领导建设的 IceCube 位于南极，把超过 一立方公里的透明冰层本身变成粒子探测器：5000 多个光学传感器被埋入超过两公里深的冰层，通过捕捉中微子极少数与物质碰撞时产生的微弱光线，反推出粒子的来源。&lt;/p&gt;
+&lt;p&gt;与传统望远镜利用光观察宇宙不同，中微子几乎可以不受阻碍地穿过物质，因此能够携带超新星、黑洞等极端宇宙事件的信息。&lt;/p&gt;
+&lt;p&gt;IceCube 的成果由此建立了「中微子天文学」这一新的宇宙观测窗口。（来源：NSF、Reuters）&lt;/p&gt;
+&lt;h1&gt;距 6 万亿美元仅一步之遥，英伟达市值达 5.8 万亿美元，创历史新高&lt;/h1&gt;
+&lt;p&gt;10 月 6 日消息，当地时间上午 9 点 30 分，纳斯达克市场开盘。开盘钟声敲响后的二十分钟左右，英伟达（NVDA）市值达到 5.82 万亿美元（现汇率约合 39.08 万亿元人民币），创下历史新高，同时距 6 万亿美元（现汇率约合 40.29 万亿元人民币）仅有一步之遥。&lt;/p&gt;
+&lt;p&gt;今日开盘时，英伟达股价为 242.10 美元（现汇率约合 1,626 元人民币），最高 243.37 美元（现汇率约合 1,634 元人民币），最低 240.76 美元（现汇率约合 1,617 元人民币）。&lt;/p&gt;
+&lt;p&gt;同时，英伟达股价于美东时间 10 月 5 日星期一再度刷新历史纪录，收盘报 238.90 美元（现汇率约合 1,604 元人民币），单日上涨 2.12%，连续第三个交易日以收盘价创历史新高。如果继续上涨，英伟达有望成为全球首家市值达 6 万亿美元的公司。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/59/a3/59a39fc496b5ed9b99dc1791b87f1988.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;消息称 DeepSeek 新一轮融资接近锁定至少 800 亿元，腾讯控股和宁德时代重金投入&lt;/h1&gt;
+&lt;p&gt;10 月 6 日消息，据彭博社援引知情人士消息称，中国人工智能公司 DeepSeek 最新一轮融资已接近收官，锁定至少 800 亿元人民币（约 120 亿美元），远超其最初设定的约 500 亿元融资目标。根据已签署的投资条款清单，最终融资规模有望逼近 1000 亿元。&lt;/p&gt;
+&lt;p&gt;腾讯控股和宁德时代是承诺出资金额最高的投资方。知情人士称，DeepSeek 最初在本轮仅寻求约 500 亿元，但在最新模型顺利发布后，投资者认购热情超出预期，公司最初设定的目标估值约为 5000 亿元。相关交易尚未最终敲定，具体条款仍可能发生变化。&lt;/p&gt;
+&lt;p&gt;报道还提到，DeepSeek 正在内蒙古建设数据中心，并部署华为 AI 芯片。&lt;/p&gt;
+&lt;p&gt;2026 年 6 月，DeepSeek 完成成立以来首轮外部融资，总额达 510 亿元人民币，投后估值近 4000 亿元，创下当时国内 AI 行业单轮融资规模最高纪录。该轮融资由创始人梁文锋领投，个人出资约 200 亿元，为最大单一出资方。腾讯出资约 100 亿元，宁德时代体系出资约 50 亿元。&lt;/p&gt;
+&lt;p&gt;据报道，最新一轮融资落定后，DeepSeek 的下一步是推进公司重组，为 IPO 做准备。据路透社此前报道，DeepSeek 公司已聘请中信证券作为辅导机构，筹备在上海证券交易所科创板上市。（来源: TechWeb）&lt;/p&gt;
+&lt;h1&gt;月之暗面完成 IPO 前融资 估值 500 亿美元，拟明年第一季度香港上市&lt;/h1&gt;
+&lt;p&gt;10 月 6 日，据彭博社报道，月之暗面已完成最后一轮私募融资，估值约为 500 亿美元，正朝着明年第一季度在中国香港进行首次公开招股 (IPO) 迈进。&lt;/p&gt;
+&lt;p&gt;一些知情人士称，月之暗面已开始作准备工作，最早将于本月启动 IPO 早期摸底会议，以评估投资者意向。知情人士此前称，该公司考虑通过此次 IPO 筹集最多 50 亿美元。&lt;/p&gt;
+&lt;p&gt;月之暗面是</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 20:48:45 +0000</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>Nous Research confirms it hit $1.5B valuation, launches AI agents for business users</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/07/nous-research-confirms-it-hit-1-5b-valuation-launches-ai-agents-for-business-users/</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr"/>
+      <c r="F564" s="2" t="inlineStr"/>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>The developer of Hermes Agent raised a $90 million Series B.</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 15:07:08 +0000</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>Healthleap raises $38M for its AI that flags hospital patients who may need a closer look</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/07/healthleap-raises-38m-for-its-ai-that-flags-hospital-patients-who-may-need-a-closer-look/</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr"/>
+      <c r="F565" s="2" t="inlineStr"/>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>The financing includes an $8M seed round co-led by Sequoia Capital and First Round Capital, and a $30 million Series A led by Hummingbird Ventures.</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 07 Oct 2026 14:41:38 +0000</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>Tony Fadell on why the first wave of AI gadgets failed — and what comes next</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/07/tony-fadell-on-why-the-first-wave-of-ai-gadgets-failed-and-what-comes-next/</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr"/>
+      <c r="F566" s="2" t="inlineStr"/>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>The “father of the iPod” says the first generation of AI gadgets failed to solve real problems — and the next wave will need to earn consumers’ trust.</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H566"/>
+  <dimension ref="A1:H572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23680,6 +23680,228 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>This Disembodied Hand Is All the Robot You Need</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/walking-robotic-hand</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr"/>
+      <c r="F567" s="2" t="inlineStr"/>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://spectrum.ieee.org/biomimetic-anthropomorphic-robot-hand" target="_blank"&gt;A hand&lt;/a&gt; attached to the end of an arm is a given for most humans, but what if robots didn’t …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 11:07:57 GMT</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>全球扩散语言模型最大融资诞生：经纬、顺为、君联数亿元押注扩散智能DiffuSpace</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/kjPiCQV1cOO6AzaOjioR?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr"/>
+      <c r="F568" s="2" t="inlineStr"/>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/kjPiCQV1cOO6AzaOjioR?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 09:30:17 +0000</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>浪子回头！Manus重启北京办公室大举招聘</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/502009.html</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr"/>
+      <c r="F569" s="2" t="inlineStr"/>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>开始和国产Agent抢人，还拿到5亿美元新融资</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 08:35:13 +0800</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>谷歌云发布 Gemini Agent；Manus 官宣五亿美元融资；小鹏上线 Robotaxi 打车小程序</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372143</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr"/>
+      <c r="F570" s="2" t="inlineStr"/>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/66/a9/66a96fbb12d92ecb1adef01c35fec474.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;谷歌云发布 Gemini Agent，支持多种 AI 模型&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 8 日，谷歌云在 Gemini at Work 2026 发布会上宣布，面向企业客户推出 Gemini 智能体（Gemini Agent）。这款产品定位「通用工作智能体」，支持 Gemini Enterprise 、Workspace 以及第三方服务。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;谷歌表示，Gemini Agent 只需要用户给出目标就能完成工作，支持回答问题、处理知识型工作、创建媒体内容，以及编写程序。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;除了充当个人助理之外，Gemini 智能体还可以用作「团队成员」。它可以在团队中担任 PM、财务分析师等。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;目前，该智能体支持 Gemini 和 Claude 模型，未来还将兼容各种闭源、开源模型。官方将提供 API，让开发者将 Gemini Agent 集成到第三方应用中。（来源：IT之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/37/be/37bec93d46251ffe4cf041cea83d36bf.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Manus 官宣 5 亿美元新一轮融资&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 8 日，Manus 母公司蝴蝶效应宣布于近日完成超过 5 亿美元新一轮融资。本轮融资由博裕投资、IDG 资本领投，老股东腾讯、红杉中国、真格基金继续加持。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这距离 Manus 于 9 月 1 日正式宣布恢复独立运营，还不到一个月。据接近 Manus 的人员透露，经历了诸多波折之后，团队变动不大、状态稳定，主要注意力依然集中在产品研发上。另据相关人士透露，本轮融资目标估值约 40 亿美元。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;创始人兼 CEO 肖弘在 9 月 28 日新产品发布后的感慨，为这段经历留下了一个注脚。「我原来以为我们的旅程只是一个注释就结束了，没想到也许有机会书写一个章节。如果有机会一起就太好了。」（来源：腾讯科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;小米汽车澎程系列首销月锁单量破 7 万台&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 8 日，小米正式公布小米汽车「澎程」系列上市首销月的官方锁单数据：截至 10 月 7 日，小米澎程 N70、N90 系列累计锁单量破 7 万台。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;值得注意的是，这一数据在 1&amp;mdash;8 月增程市场萎缩近 20% 的背景下出现的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;10 月 1 日，雷军曾表示，小米澎程 9 月当月交付已破万，直接拉动小米汽车 9 月整体交付量突破 4 万台。此前，小米汽车多月销量维持在 3 万台级别。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;业内认为，随着四季度产能进一步爬坡，小米澎程系列有望推动小米汽车交付规模再上新台阶，同时加速 20 万&amp;mdash;30 万元级家用 SUV 市场的新能源替代节奏。（来源：新浪财经）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;C</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Oct 2026 13:20:32 +0000</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>China’s Manus raises over $500M in first funding round since split with Meta</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/08/chinas-manus-raises-over-500m-in-first-funding-round-since-split-with-meta/</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr"/>
+      <c r="F571" s="2" t="inlineStr"/>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>Boyu Capital and IDG Capital led the funding round, and existing shareholders Tencent, HSG (formerly known as Sequoia China), ZhenFund, and others also participated.</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:06:56-04:00</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>California is trying to shut down robot vs. human cage matches</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/1008401/california-shut-down-rek-fighting-robot-company-human</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr"/>
+      <c r="F572" s="2" t="inlineStr"/>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>The California State Athletic Commission sent a cease-and-desist letter to a startup that hosted a match between a human and a robot last month, as reported by The New York Times. The fight, which took place on September 18th, pitted a human, Frankie LaPenna, against a humanoid robot owned by a tech startup, Rek, that [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H572"/>
+  <dimension ref="A1:H587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23902,6 +23902,559 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 02:39:45 +0000</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>直写式3D打印的柔性触觉电子皮肤：打印油墨、结构制备以及器件应用</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13762</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr"/>
+      <c r="F573" s="2" t="inlineStr"/>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>欢迎订阅《化学进展》，SCI收录的中文综述期刊！</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 02:38:20 +0000</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>做一只灵巧手最快多久？中科院团队：3天</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13751</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr"/>
+      <c r="F574" s="2" t="inlineStr"/>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>刚过去的十一假期，具身智能机器人销售额同比增长1.3倍，"AI+机器人"成为文旅消费热点，更多“台上的展示产品 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 02:36:09 +0000</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪人形机器人，外观专利公布</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13741</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr"/>
+      <c r="F575" s="2" t="inlineStr"/>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>​</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 02:29:46 +0000</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>青瞳视觉：手物交互数据如何采集？高精度手部动作捕捉的应用价值</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13729</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr"/>
+      <c r="F576" s="2" t="inlineStr"/>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>OptiUMI以亚毫米级精度、微秒级同步和手-物联合追踪，重新定义了可穿戴数采设备的能力边界。</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 02:00:43 +0000</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>艾曼斯高性能聚酰胺材料，突破四足机器人的未来极限</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13723</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr"/>
+      <c r="F577" s="2" t="inlineStr"/>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>迎接具身智能时代：艾曼斯高性能材料赋能四足机器人迈向多元应用场景。</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 01:20:27 +0000</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>灵感机器人宣布完成数千万元天使轮融资，加速产线建设与触觉智能布局</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13716</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr"/>
+      <c r="F578" s="2" t="inlineStr"/>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>本轮融资将主要用于产线建设与量产能力优化，以及触觉智能系统研发。</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 01:19:46 +0000</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人电子皮肤的5种常见触觉传感原理</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13714</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr"/>
+      <c r="F579" s="2" t="inlineStr"/>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤触觉传感器可分为压阻式、电容式、压电式、光电式、电磁式等</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 01:16:34 +0000</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公开柔性触觉传感器专利：弯曲阵列覆盖机器人手指和手掌</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13713</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr"/>
+      <c r="F580" s="2" t="inlineStr"/>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>具备多模态感知与可规模化制造方法的三维软柔顺阵列触觉传感器</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 02:29:12 +0000</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>风暴中的数采中心｜数据采集是好生意吗？“部分高度依赖数采订单的企业或接近临界点”</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13694</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr"/>
+      <c r="F581" s="2" t="inlineStr"/>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>澎湃新闻记者 秦盛 滕晗 数千平方米的空间里，家居、商超、工业、医药等场景被搬进同一座“训练场”，百余台不同品 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 01:36:30 +0000</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>800+动作类型！OpenLET小脑动作数据集正式发布</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13680</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr"/>
+      <c r="F582" s="2" t="inlineStr"/>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>&amp;#160; 人形机器人的“小脑”运控能力，正从单一技能走向泛化训练。高质量、多类别的动作数据，是支撑这一跨越 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:30:02+00:00</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Robot Decommissioning Takes a Fun Turn</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-reachy-mini-raps</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr"/>
+      <c r="F583" s="2" t="inlineStr"/>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 03:52:21 +0000</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>清华具身模型登顶全球第一！突围GPT-6、英伟达，不靠外挂和额外数据</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/502125.html</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
+      <c r="F584" s="2" t="inlineStr"/>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>星动纪元选择将视频预测与动作学习分阶段训练，重点不是「视频、动作一锅炖」，而是把两者「解耦」，重新「排序」。</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 09:27:14 +0800</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>Jev 开发商估值已达 75 亿美元；苹果投资 AI 音频初创；传 OpenAI、Anthropic 高管私下推演 AI 灾难场景</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372184</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr"/>
+      <c r="F585" s="2" t="inlineStr"/>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5c/d1/5cd1326158f94461a6a2390db681667c.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;内存等成本压力上升，2027 全球笔记本价格恐继续上涨&lt;/h2&gt;
+&lt;p&gt;市场调查机构集邦咨询（Trendforce）于 10 月 8 日发布博文，表示如果零部件价格继续维持高位，品牌扩大成本转嫁，&lt;strong&gt;终端涨价可能延长用户换机周期，预估 2027 年全球笔记本市场面临出货、价格双重影响。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;在 2026 年第 3 季度以建议零售价 900 美元的主流笔记本为例，其 CPU、内存及 SSD 占物料成本约 68%，品牌面临提价、压缩毛利或降低配置的选择。&lt;/p&gt;
+&lt;p&gt;该机构预计，2027 年全球出货量将低个位数（预估低于 5%）下滑。若 CPU 与 DRAM 价格维持高位，品牌扩大成本转嫁，终端涨价可能延长换机周期，这种情况下，全年降幅或扩大至高个位数（可能高于 5%）。&lt;/p&gt;
+&lt;p&gt;零部件供给方面，AI 服务器持续占据先进制程产能。报告预计，DRAM 供应仍偏紧；NAND 闪存（NAND Flash）或随新产能投产，于 2027 年下半年逐步缓解紧张。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e9/57/e9578f248d674300873cf40ebb2a9d5f.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果投资 Huxe，由前谷歌 NotebookLM 团队成员创立&lt;/h2&gt;
+&lt;p&gt;10 月 10 日消息，苹果与 AI 音频初创公司 Huxe 达成人才引进与技术许可协议，这是今年公开披露的第 4 笔苹果 AI 相关交易。&lt;/p&gt;
+&lt;p&gt;这项安排属于「收购式招聘」（acqui-hires），不代表苹果收购 Huxe 公司。协议允许苹果引进部分员工并使用相关知识产权，但交易没有包括购买 Huxe 业务，报道没有披露协议金额。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Huxe 由 3 名前 Google NotebookLM 团队成员创立。&lt;/strong&gt;项目负责人 Raiza Martin 于 2024 年 12 月离开 Google，并与设计师 Jason Spielman、工程师 Stephen Hughes 共同创办公司。&lt;/p&gt;
+&lt;p&gt;Huxe 于 2025 年 6 月以邀请制方式推出同名应用，并在同年 9 月向公众开放，团队当时公布完成 460 万美元融资。&lt;/p&gt;
+&lt;p&gt;该应用可依据用户邮件和日历生成每日音频简报，也能围绕主题制作播客式对话，此外还提供新闻、体育等主题的持续更新音频内容。Huxe 于 2026 年 5 月宣布关闭，服务在 5 月 28 日结束。（来源：9to5Mac）&lt;/p&gt;
+&lt;h2&gt;谷歌 Gemini 4「Argon」模型即将发布&lt;/h2&gt;
+&lt;p&gt;10 月 10 日消息，据《商业内幕》报道，谷歌即将向公众正式发布新一代 Gemini 4「Argon」模型。&lt;/p&gt;
+&lt;p&gt;据该媒体获取的内部文档与截图显示，谷歌员工近期一直在测试代号为「Carbon」的全新 Gemini 4 版本。该模型很可能是 Argon 架构下的新检查点（Checkpoint）更新，并已于近日接入谷歌内部代码平台 Jetski。&lt;/p&gt;
+&lt;p&gt;一名员工透露，Carbon 在代码能力上的表现「堪比 Opus 5.5」&amp;mdash;&amp;mdash;后者是 Anthropic 旗下针对复杂代码智能体长期任务打造的最强模型。不过该员工同时表示，这一结论仍有待更深入的评测验证。&lt;/p&gt;
+&lt;p&gt;不过也有员工指出，早期版本在处理部分编程任务时仍显吃力，其水平大体只相当于 Anthropic 早前发布的 Claude Opus 5。（来源：商业内幕）&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;OpenAI&lt;/strong&gt;&lt;strong&gt; 解雇三名 AI 安全研究员，双方就解雇原因发生争议&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;据美联社 10 月 9 日报道，OpenAI 确认解雇三名 AI 安全研究人员 Tomek Korbak、Jasmine Wang 和 Mikita Balesni。公司表示，内部调查发现三人违反了敏感信息处理政策，因此决定终止雇佣关系。 三名研究人员此前向 OpenAI 内部多个安全监督机构提交公开信，认为公司可能将商业利益置于安全工作之上，并对解雇决定提出异议</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 12:28:07 +0800</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>攻克超声穿颅读脑，拿下 4 亿元新融资，他们要做脑科学的「英伟达」</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372148</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr"/>
+      <c r="F586" s="2" t="inlineStr"/>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;一家深圳公司，让实时「看清」人类大脑变成了可能。&lt;/p&gt;
+&lt;p&gt;极客公园获悉，鲲为科技近期完成 4 亿元新一轮融资，新增股东包括 XVC、红杉中国，老股东夏尔巴、腾讯进一步加仓。&lt;/p&gt;
+&lt;p&gt;在鲲为位于深圳的研发中心，创始人刘家家向我们展示了实测对比。&lt;/p&gt;
+&lt;p&gt;一边是价值数百万的海外顶级旗舰彩超设备，一边是鲲为自主研发的机器。当探头同时置于受试者颅骨侧面，海外设备的声波在穿透至大脑中线后便衰减进一片暗影，仅能拼凑出模糊的轮廓；而在鲲为的屏幕上，穿透颅骨后的脑组织结构清晰毕现，中脑核团、侧脑室乃至微细血管中的血流动态被毫秒级实时捕捉。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8c/b8/8cb828030003c46c751fd8a360354ab8.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span style="font-size: 14px;"&gt;穿透颅骨后的脑组织结构、血流动态等都能被清晰捕捉｜图片来源：鲲为&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;一场清晰的「代差」展现。&lt;/p&gt;
+&lt;p&gt;「传统超声长期陷入穿透力与分辨率不可兼得的工程困境，面对坚硬的颅骨几乎是雾里看花。」刘家家解释。为此，鲲为选择了一条违背行业常识的路径：放弃通过不断提升频率来换取清晰度的惯性，转向低频。&lt;/p&gt;
+&lt;p&gt;鲲为的核心突破，在于将算力与算法引入物理声场，在低频段下兼顾了颅骨穿透力与高分辨率实时成像。这种将超声从成像升维为「声学空间智能」的技术跨越，彻底打开了超声在临床医学、脑科学及通用人工智能领域的想象空间。&lt;/p&gt;
+&lt;p&gt;在中风抢救的急救车里，鲲为的便携设备几分钟内即可精准判别脑梗或脑出血，为患者争取到关键的黄金救治期；在脑机接口的前沿探索中，它为整个行业提供了一个非侵入且能够实时获取全脑功能数据的基础设施。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2f/28/2f28f312860e0d80da1025dc30076d00.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span style="font-size: 14px;"&gt;鲲为的全系列产品｜图片来源：鲲为&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;鲲为已实现数千万订单，正站在商业化起飞拐点。但刘家家告诉极客公园，鲲为目标不止于做一家技术和产品领先的颅脑超声设备公司，而是成为赋能脑科学 AGI 的 Infra 公司：提供硬件设备和基础软件平台 kOS，就像 AI 领域的英伟达提供显卡和 CUDA。全球不同技术路线的脑机接口 Lab，以及 NeuroAI 模型公司，都是他们的目标客户。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/98/eb/98eb9b227d9d44b1c02c3821740a3b78.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span style="font-size: 14px;"&gt;鲲为创始人刘家家｜图片来源：受访者&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;复刻蝙蝠，靠智能「看清&lt;strong&gt;」&lt;/strong&gt;人脑&lt;/h2&gt;
+&lt;p&gt;鲲为的起点，源于对一项统治了行业几十年的常识的怀疑。&lt;/p&gt;
+&lt;p&gt;2008 年，刘家家从西安交通大学生物医学工程专业毕业后进入超声行业。他很快注意到，超声工业乃至更广泛的硬件领域，在 2000 年前后撞上了一堵无形的物理墙：&lt;/p&gt;
+&lt;p&gt;从芯片的主频大战（AMD 与 Intel 争相突破 1GHz），到无线通信从 2G 到 5G/6G 的频段演进，再到半导体光刻机从可见光迈向 EUV&amp;mdash;&amp;mdash;科技产业近百年来遵循着同一种范式，即通过提升频率来榨取性能上限。&lt;/p&gt;
+&lt;p&gt;「大家把工程上的经验总结，误认为了不可逾越的物理极限。」刘家家回忆。他产生了一个强烈的假说：为什么我们一定要被高频绑架？基于低频，同样可以构建出高性能的成像与感知系统。&lt;/p&gt;
+&lt;p&gt;在当时，这个想法被同行视为毫无文献支持的「异类」。&lt;/p&gt;
+&lt;p&gt;转折发生在 2016 年 AlphaGo 震动世界。刘家家意识到，打破行业瓶颈的关键钥匙可能在于&amp;mdash;&amp;mdash;智能。&lt;/p&gt;
+&lt;p&gt;自然界早就给出了答案。他想到，蝙蝠发射的声波频率并不高，却能依靠大脑神经网络对回波信息的精准处理，在百米之外捕获一只蚊子的飞行轨迹</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 09 Oct 2026 16:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>Danu Robotics’ fight to build a better recycling robot</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/09/danu-robotics-fight-to-build-a-better-recycling-robot/</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr"/>
+      <c r="F587" s="2" t="inlineStr"/>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>For six years, Danu founder Amy Ma has been working on a better way to sort recyclable waste.</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H587"/>
+  <dimension ref="A1:H589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24455,6 +24455,74 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 17:24:57 GMT</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>单次RL后训练烧掉260万美元、每步37亿Token，小米披露MiMo-V2.6“规模化强化学习”路线</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/gNdWoDM8ygkAjXfsLaBK?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/gNdWoDM8ygkAjXfsLaBK?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 08:53:38 +0800</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>马斯克豪言 SpaceX 估值将超1000万亿美元，遭拉表打脸；传腾讯字节加速个人智能体研发；四部门拟禁止汽车采用全隐藏式门把手</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372216</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr"/>
+      <c r="F589" s="2" t="inlineStr"/>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d2/04/d204d27e0c20c3e37f63a06813e59e29.png" /&gt;&lt;/p&gt;&lt;h1&gt;马斯克豪言 SpaceX 估值超 1000 万亿美元，惨遭拉表打脸&lt;/h1&gt;&lt;p&gt;近日，马斯克在社交平台大胆预测，SpaceX 未来估值有望突破 1000 万亿美元，体量将远超当前全球经济总量。目前 SpaceX 估值仅约 2.2 万亿美元，而 2025 年全球 GDP 总量约 118 万亿美元，此番极具颠覆性的超高估值言论引发全网热议与质疑。&lt;/p&gt;&lt;p&gt;面对这一惊人预测，有网友晒出富国银行证券整理的一张名为「说到做到记录，以及其所隐含的折价」数据表格，直接打脸马斯克的激进预测。&lt;/p&gt;&lt;p&gt;表格梳理了特斯拉、SpaceX 多项核心项目，Robotaxi、Semi 卡车、星舰等重点产品的实际落地成果与马斯克此前公布的目标差距悬殊，多项项目达成率极低、交付严重延期，部分目标甚至已被撤回。&lt;/p&gt;&lt;p&gt;据不完全统计，马斯克在过去 15 年间提出的 602 个明确目标中，仅有约三成能够按期实现。从 Robotaxi 的多次跳票，到 Cybertruck 交付的反复推迟，再到 Semi 卡车的量产困境，「马斯克时间」早已成为科技界对过度承诺的一种调侃。&lt;/p&gt;&lt;p&gt;在 SpaceX 冲击更高估值之前，如何将那些「说到做到」的承诺转化为实际交付，或许是马斯克需要面对的更现实的问题。（来源: TechWeb）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/46/ff/46ff26c7d8bfe828608cc67ddfaa08ef.png" /&gt;&lt;/p&gt;&lt;h1&gt;消息称 Meta 已搁置向 Anthropic 出租 AI 算力的计划&lt;/h1&gt;&lt;p&gt;10 月 10 日消息，《华尔街日报》在一篇报道中提到，Meta 已搁置向 Anthropic 出租 AI 算力的计划。&lt;/p&gt;&lt;p&gt;报道指出，Anthropic 首席执行官 Dario Amodei 今年早些时候曾亲自致电 Meta 首席人工智能官汪滔 (Alexandr Wang)，希望从这家竞争对手处租赁 AI 计算芯片。Meta 就此事进行过内部讨论，最终做出了暂不提供的决定。&lt;/p&gt;&lt;p&gt;随着 Muse 系列自研模型的逐步发布，Meta 的 AI 业务从早些时候的低潮中快速恢复，自身对算力的需求也迅速增长。此时若选择向 Anthropic 出售算力可算是「资敌」行为。&lt;/p&gt;&lt;p&gt;报道提到，算力资源分配正影响人工智能人才的就业选择，Transformer 架构核心作者 Noam Shazeer 之所以二次离职谷歌就与算力不足有关。与此同时，大量的算力建设承诺最终落空，限制了 AI 产业的发展。（来源：IT 之家）&lt;/p&gt;&lt;h1&gt;消息称英伟达洽谈收购 / 追加投资 Reflection AI，加码开源模型&lt;/h1&gt;&lt;p&gt;10 月 11 日消息，据金融时报消息，知情人士透露，英伟达正就收购美国初创公司 Reflection AI 或向其追加投资展开深入谈判。&lt;/p&gt;&lt;p&gt;Reflection AI 专注于开发开放权重模型，于当地时间 10 月 5 日发布旗下首款开放权重 AI 模型 Beam。&lt;/p&gt;&lt;p&gt;知情人士补充称，目前的谈判尚处初期阶段，潜在交易可能采取多种形式——包括所谓「人才兼并」模式。在这一架构下，英伟达将吸纳其核心团队并获取技术授权，从而绕开全面并购通常伴随的漫长反垄断审查。&lt;/p&gt;&lt;p&gt;英伟达目前已是 Reflection 的主要股东之一，也可能选择通过新一轮股权投资，或以提供更多芯片与算力资源的合作方案，进一步加深与该公司的绑定。英伟达此前已向 Reflection 注资 8 亿美元（现汇率约合 53.65 亿元人民币）。&lt;/p&gt;&lt;p&gt;据多位知情人士透露，双方有望在未来几周内敲定方案，但各方也强调谈判仍存在破裂的可能。目前具体的交易条款尚未明确，但在今年 3 月的上一轮融资中，Reflection 的估值已达 250 亿美元（现汇率约合 1,676.62 亿元人民币）。（来源：IT 之家）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0c/3c/0c3cc48326db03cb0a279d6da8ae1cd0.png</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H589"/>
+  <dimension ref="A1:H592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24523,6 +24523,148 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 10 Oct 2026 09:59:37 +0000</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>一举一动胸中有数，机器人后另有高人，数采是门怎样的行业？</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13785</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
+      <c r="F590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>广州的数据采集员黄健采集刷墙的动作。 （受访者提供） &amp;#160; 许多对人类而言理所当然的动作，到了机器人这 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 08:02:38 +0800</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>尊界：11 月起陆续升级踏板；iPhone 折叠屏国内预约超 200 万；6 个月，超千万 Claude 账户被封杀｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372218</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr"/>
+      <c r="F591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/13/82/1382624c8bdc73f0c9f848ff45d2bad9.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;陶哲轩提出「数学 2.0」：AI 解题之外，还要帮助人理解证明&lt;/h2&gt;
+&lt;p&gt;10 月 11 日，数学家陶哲轩公开了在加州理工学院的演讲《数学 2.0》。他认为，AI 正在降低部分数学问题的求解成本，使数学研究逐渐从「证明稀缺」走向「证明富足」。但目前多数前沿问题仍未解决，不能只凭公开传播的成功案例判断 AI 的整体能力。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/66/95/6695ad75bc3154f08313aaa10487ac48.png" /&gt;&lt;/p&gt;
+&lt;p&gt;陶哲轩指出，得到正确证明，并不意味着研究者理解了证明为何成立，或掌握了可用于其他问题的新方法。他主张用 AI 寻找更易理解的证明、整理分散的研究成果，并对大量数学问题开展系统分析。例如，等式理论项目通过人类与自动化工具协作，对超过 2200 万个命题作出了判定。&lt;/p&gt;
+&lt;p&gt;对于 AI 解题能力的评估，他还呼吁公开计算资源消耗、失败尝试等信息。在陶哲轩看来，未来数学研究既要利用 AI 扩展探索范围，也要保留人类对证明及其现实应用的理解和判断。（来源：机器之心）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/09/f7/09f74344dce3602435bc64b6276abc10.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;Claude 爆发大规模封号潮：半年封杀 1140 万个账号申诉后仅 4.2 万翻案&lt;/h2&gt;
+&lt;p&gt;10 月 11 日，据媒体报道，近期 Claude 账号封禁问题引发开发者讨论。受到关注的一项数据来自 Anthropic 今年 7 月发布的报告：2026 年上半年，平台累计封禁约 1140 万个账号；收到约 39.8 万次申诉，其中约 4.2 万次申诉成功。报告未披露完整的封禁原因分布，仅凭这些数字也无法判断近期封号是否增加，但申诉结果使平台的封禁标准和复核机制受到关注。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/84/ff/84ffdc6b690d3ca0fbc02fdae26e1b5f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Anthropic 列出的违规情形包括利用服务从事违法活动、侵犯隐私，以及违反地区使用限制等。今年上半年，Anthropic 还向相关儿童安全组织提交了超过 1.5 万起报告。&lt;/p&gt;
+&lt;p&gt;此外，Anthropic 近期修订了 Claude 使用政策，计划自 11 月 12 日起禁止用户在没有明显目的的情况下，反复对模型实施极端残忍行为。公司称，新规针对的是极端情形；用户表达不满、反驳模型、创作黑暗题材内容，以及开展模型测试与研究，不属于该项禁令的范围。（来源：快科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;英伟达洽谈收购 Reflection AI，已投资 8 亿美元，后者估值达 250 亿美元&lt;/h2&gt;
+&lt;p&gt;10 月 11 日，据媒体报道，英伟达正与美国人工智能初创企业 Reflection AI 就潜在收购或进一步扩大投资展开初步谈判，交易可能采取全面收购、追加股权投资、提供更多芯片及算力支持，或通过聘用员工并获得技术授权等多种形式。英伟达此前已向 Reflection AI 投资 8 亿美元，是其最大股东之一。&lt;/p&gt;
+&lt;p&gt;知情人士透露，双方可能在未来数周内达成协议。Reflection AI 今年 3 月融资时的估值达到 250 亿美元，其开发的开放权重 AI 模型被美国政府视为抗衡 DeepSeek 等低成本竞争对手的重要技术资源。（来源：新浪科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;消息称 OLED 屏新款 iPad mini 售价将大幅上涨，或接近 799 美元&lt;/h2&gt;
+&lt;p&gt;10 月 11 日，彭博社记者马克 &amp;middot; 古尔曼表示，苹果计划本月晚些时候推出新款 iPad mini。新机的起步存储空间可能会有所提升，但有意换机</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 13:52:01 +0800</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>12 分钟订单破万，吉利银河战舰 700，要订下新能源越野的新标准</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372213</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/44/ad/44ad72a68bdf0f2b29d045b8d20c5e29.png" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：吉利银河&lt;/p&gt;
+&lt;p&gt;「这台车我们造了 5 年，这也是吉利第一次造越野车。」吉利汽车研究院院长李传海说到。&lt;/p&gt;
+&lt;p&gt;就在几分钟前，10 月 10 日，吉利银河战舰 700，一台新能源野车正式发布，16.98 万（限时焕新价）起的价格，让这台最高配备三电机四驱，千匹马力，能爬 45&amp;deg; 坡、能应急浮水的越野车，变得十分打动人心。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/88/cf/88cf6de613a6f5b7f5a4080a32499b3d.png" /&gt;&lt;/p&gt;
+&lt;p&gt;吉利银河战舰 700 的价格梯度比较大｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;事实也是如此，在发布会后 12 分钟，吉利银河战舰 700 的订单数量就突破 1 万台。&lt;/p&gt;
+&lt;p&gt;但在显性成功的背后，你确实会猜测，可能恰恰因为吉利「缺乏越野基因」，才能让团队没有任何包袱，从底层架构层面，重新思考新能源时代的越野车，到底应该是什么样。或者，&lt;strong&gt;用吉利团队的话，是新能源越野时代 2.0 的产品，该是怎样的&lt;/strong&gt;？&lt;/p&gt;
+&lt;p&gt;&lt;a id="heading_0"&gt;&lt;/a&gt;&lt;strong&gt;大梁，「吃」进车里&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;过去十几年，硬派越野车的规矩很简单。想要真越野，就上非承载式大梁，车身坐在一副独立的钢制梯形车架上，扛得住扭，经得起摔，代价是车重、空间被吃掉、进城开起来晃晃悠悠。想要舒适，就选承载式车身，好开好坐，但遇到交叉轴和连续冲击，车身容易扭，严重时车门都关不严。&lt;/p&gt;
+&lt;p&gt;新能源来了之后，这道题反而更难。电池要找地方放，电机要找地方装，大梁车本来就紧张的底盘空间被进一步压缩，车重再往上叠几百公斤。市面上不少新能源硬派，其实是在两条老路里选一条走，要么在大梁车上做加法，要么给城市 SUV 套一个方盒子外壳。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;银河战舰 700 的思路，是不再二选一。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fd/b6/fdb6610b42b5c9fcc3d36c4f5af75272.png" /&gt;&lt;/p&gt;
+&lt;p&gt;吉利集团 CEO 淦家阅介绍 GTA 架构和一体大梁技术｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;它基于吉利新发布的 GTA 原生新能源越野架构，&lt;strong&gt;核心是一套被称为「一体式大梁」的结构&lt;/strong&gt;。简单理解，就是把大梁拆成三段分别用最合适的工艺来做，再整体嵌进车身骨架。前纵梁用超高强热成形钢，中段是超高强辊压集成大梁，后纵梁用 TRB 热成形（一种变厚度轧制工艺，受力大的地方厚，受力小的地方薄），三段前后贯通，再和门槛梁、横梁连成一个整体。&lt;/p&gt;
+&lt;p&gt;这么做的收益体现在几组数字上。官方数据显示，这套结构的强度比传统大梁提升 30% 以上，整车扭转刚度做到 44180 N&amp;middot;m/deg，比同级独立大梁车型高出 20% 以上。与此同时，它比独立大梁方案轻 80 到 100 公斤，高度方向省出 40 到 70 毫米，换来更大的头部空间和 80.3% 的得房率。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;它想要大梁车的「骨头」，又不想背大梁车的「包袱」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;需要说清楚的是，从结构分类上看，这依然是一台承载式车身的车，吉利早期资料里也用过「内嵌式梯形半承载」的说法。它并不是传统意义上的非承载大梁车，这套结构在长期高强度越野中的可靠性，最终还要交给时间和用户来检验。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1e/90/1e90cc58fd7d2779bee2c2adc9a5c44f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;吉利银河战舰 700 的底盘｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;架构只是起点。新能源越野之所以值得从头设计，还因为电机能做到传统机械四驱做不到的事。&lt;/p&gt;
+&lt;p&gt;银河战舰 700 的雷神 EM-T 采用三电机布局，前面是发动机加三挡 DHT 电驱，后桥是两台独立的轮边电机，单台峰值功率 220kW。两台后电机各自控制左右车轮的扭矩，再加上前后轴之间的扭矩分配，就构成了两把随时待命的「智能</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H592"/>
+  <dimension ref="A1:H595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24665,6 +24665,130 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 11:06:58 GMT</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>星尘智能完成新一轮融资，公司估值达150亿元</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/z9ORbE470QJDHDiBCC8S?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr"/>
+      <c r="F593" s="2" t="inlineStr"/>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/z9ORbE470QJDHDiBCC8S?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 11:44:18 +0800</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>复旦邱锡鹏团队获超 10 亿融资，成立两年，让模型感知、理解、响应变化的世界</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372278</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;section&gt;&lt;section&gt;&lt;section&gt;&lt;span&gt;&lt;img alt="" src="https://imgslim.geekpark.net/uploads/image/file/85/ce/85ce22516e30fc4681b89047a233eb1c.png" style="vertical-align: bottom; color: rgb(0, 0, 0); text-align: left; width: 100%;" /&gt;&lt;/span&gt;&lt;/section&gt;&lt;section&gt;&lt;span&gt;大模型融资还在继续，新的押注转向了能边听、边看、边说的 AI。&lt;/span&gt;&lt;/section&gt;&lt;section style="margin-top: 25px; margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;span&gt;作者｜Li Yuan&lt;/span&gt;&lt;/strong&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/section&gt;&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;span&gt;编辑｜&lt;/span&gt;&lt;strong&gt;&lt;span&gt;郑玄&lt;/span&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: rgb(0, 0, 0); line-height: normal;"&gt;&lt;strong style="color: rgb(55, 84, 116);"&gt;&lt;strong&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;&lt;/section&gt;&lt;/section&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;想象这样一个家庭场景。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;孩子正在玩玩具，突然，厨房里「哐」的一声，玻璃碎了，紧接着传来孩子的声音：「不是我。」语速很快，尾音压得很低，有点紧张。两秒后，一只猫从厨房门口窜出来，钻进了沙发底下。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;今天的模型，能分别识别这些信息。转写模型能记下孩子的话，音频模型能听出是玻璃碎裂，视觉模型能认出那只猫。但把这些能力叠在一起，模型仍然不知道刚才发生了什么。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;那声脆响是从哪个方向来的？碎玻璃、那句急着撇清的「不是我」、逃窜的猫，是不是同一件事？厨房地上有没有碎片，孩子是不是正光着脚站在旁边？AI 需要把声音、画面、人物和前后发生的事情联系起来，在信息还不完整时作出判断，必要时继续观察或向人确认。&lt;/span&gt;&lt;/p&gt;&lt;p style="margin: 25px 8px; text-align: justify; color: rgb(0, 0, 0); letter-spacing: 1px; line-height: 1.75;"&gt;&lt;span&gt;但</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 08:27:49 +0800</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>曝梁文锋密集见机器人创业者；影石出货量累计突破1000万台；Meta发布Muse Wonder模型｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372264</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr"/>
+      <c r="F595" s="2" t="inlineStr"/>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/14/b9/14b93390862925f9b7b30fff2cc09574.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;曝梁文锋密集接触具身智能创业者，DeepSeek 拟入局具身智能&lt;/h1&gt;
+&lt;p&gt;据报道，DeepSeek 创始人梁文锋近期密集关注具身智能领域，并与多位该领域创业者交流，探讨机器人、大模型与现实世界交互等方向。&lt;/p&gt;
+&lt;p&gt;据知情人士透露，梁文锋正在考虑 DeepSeek 进入具身智能领域的可能性，可能会亲自组建团队下场研发，也可能通过投资相关企业切入。&lt;/p&gt;
+&lt;p&gt;此前，梁文锋已投资宇树科技，另据彭博社报道，DeepSeek 计划领投腾讯前 AI 科学家胡瀚创立的机器人公司 Winverse AI。（来源：新浪科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8a/e4/8ae4ef9a60bd1e1318aa9cd0d89887df.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;Meta 发布 Muse Wonder 模型，拥有主动记忆和主动专注功能，瞄准个人超级智能&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;Meta 今天推出 Muse Wonder 系列，包括 Muse Wonder 和 Muse Wonder Full 两款功能最强大的型号，它们在个人和专业智能任务中均能提供卓越的性能。它们的推出标志着我们产品线的又一次飞跃，也是迈向个人超智能的重大一步。Muse Wonder 融合了&lt;strong&gt;主动记忆&lt;/strong&gt;和&lt;strong&gt;主动专注功能&lt;/strong&gt;，能够帮助您追踪重要事项，并高效地朝着目标努力。&lt;/p&gt;
+&lt;p&gt;Muse Wonder 现已可通过 Meta Model API 和 Muse Code 使用，Muse Wonder Full 现已面向 Muse Code 订阅用户推出。&lt;/p&gt;
+&lt;p&gt;Muse Wonder 即将为 Muse 中的各种体验提供支持，并将首先面向订阅用户推出。Muse Wonder 还将为需要更高智能的工件生成和流程提供支持。未来，Meta 将利用 Muse Wonder 开发专用模型，供所有 Muse 用户使用。（来源：Meta）&lt;/p&gt;
+&lt;h1&gt;影石出货量累计突破 1000 万台 全景相机占比超 60%&lt;/h1&gt;
+&lt;p&gt;10 月 13 日消息，&lt;strong&gt;影石 Insta360 对外公布，旗下相机产品全球累计出货量已经突破 1000 万台，全景相机占整体出货超过 60%&lt;/strong&gt;，11 年时间做到这个规模，增长速度相当可观。&lt;/p&gt;
+&lt;p&gt;比较有意思的是，&lt;strong&gt;1000 万台的总量里面，有 470 万台是过去 12 个月卖出去的，差不多接近一半。&lt;/strong&gt;也就是说影石最近一年的销量，几乎等于前面十年的总和，增长势头很猛。&lt;/p&gt;
+&lt;p&gt;相关庆祝活动之前已经在代工厂立讯精密的工厂完成，双方创始人以及工厂员工一起见证这个里程碑。&lt;/p&gt;
+&lt;p&gt;全景相机依旧是影石的基本盘。IDC 给出的数据显示，它在全球全景相机市场份额达到 72.5%，差不多每卖出去 10 台全景相机，就有 7 台来自影石。很多骑行、滑雪、旅行爱好者，都喜欢用全景相机，拍完之后再选画面，不用拍摄的时候纠结构图。（来源：快科技）&lt;/p&gt;
+&lt;h1&gt;蚂蚁「灵光」开启小范围内测，新版对标「Meta Muse」&lt;/h1&gt;
+&lt;p&gt;蚂蚁集团旗下 AI 产品「灵光」已于近日开启新版本的小范围内测，新版对标「Meta Muse」。&lt;/p&gt;
+&lt;p&gt;公开信息显示，今年 9 月，Meta 推出个人智能体 Muse。该智能体可介入用户日常生活，并持续跟进用户交待的事宜。&lt;/p&gt;
+&lt;p&gt;接近项目人士透露，灵光相关方向约半年前已开始筹备，期间迭代多个版本，计划本月全面开放。&lt;/p&gt;
+&lt;p&gt;该人士还透露，此次升级的核心，是灵光从能聊天、能生成应用的 AI 助手，转向拥有长期记忆、可主动推进任务的 AI 原生个人智能体。灵光新版本还能通过调用 Skill 和 MCP，实现钉钉发信息、调用智能家居设备等功能。&lt;/p&gt;
+&lt;p&gt;据悉，灵光 2.0 的内测用例集中在长程、变量多、普通人难盯住的场景，例如帮上班族跟踪市场异动、帮家长管理钉钉打卡、旅行中遇航班延误或景区限流重排路线等。（来源：新浪科技）&lt;/p&gt;
+&lt;h1&gt;阶跃旗舰模型接入腾讯 WorkBuddy，限免 2 周&lt;/h1&gt;
+&lt;p&gt;</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H595"/>
+  <dimension ref="A1:H605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24789,6 +24789,391 @@
         </is>
       </c>
     </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 11:05:39 +0000</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>魔法原子具身Agent框架拿下MolmoSpaces全球第一</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503107.html</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
+      <c r="F596" s="2" t="inlineStr"/>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>让VLA从“演示可用”逼近“产线可用”</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 09:33:37 +0000</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>梁文锋投了Swin Transformer作者！DeepSeek开始布局具身大脑</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503093.html</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr"/>
+      <c r="F597" s="2" t="inlineStr"/>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>Winverse AI</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 07:19:21 +0000</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>华为哈勃投了个98年博士！让机器人皮肤变色，团队平均23岁</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/502954.html</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
+      <c r="F598" s="2" t="inlineStr"/>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>让材料感知压力，造出超薄高密度电子皮肤</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 04:07:04 +0000</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>9大赛道，23份企业真实考卷！上海具身智能大考，邀千队共解题</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/502784.html</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr"/>
+      <c r="F599" s="2" t="inlineStr"/>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>赢奖金、拿融资、送出海</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 04:01:15 +0000</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>单轮23亿，累计43亿，无问芯穹刷新国产AI Infra赛道融资双重纪录</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/502767.html</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
+      <c r="F600" s="2" t="inlineStr"/>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>算力、模型、行业，三层生意一起做</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 08:28:51 +0800</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>超越抖音，传红果短剧日均时长 125 分钟；299 美元，苹果推 Siri AI 带屏音箱；谷歌最强模型 Gemini 4 正式上线</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372304</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr"/>
+      <c r="F601" s="2" t="inlineStr"/>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f4/30/f430488c535436872c05371a1d73db8f.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;谷歌最强 AI 模型：Gemini 4 Argon 上线，输出词元上限 100 万个、专攻最棘手难题&lt;/h1&gt;
+&lt;p&gt;10 月 14 日消息，&lt;strong&gt;Gemini 4 Argon&lt;/strong&gt;现已面向全球开发者和企业开放，可通过 AI Studio、 Gemini 平台 API 使用，同时支持 Google Antigravity 的 Google AI Ultra 订阅用户，以及 Gemini 应用和搜索 AI 模式的 Google AI Ultra 和 Pro 订阅用户。&lt;/p&gt;
+&lt;p&gt;该模型目前限时入门定价如下，2026 年 11 月 30 日入门促销结束后价格会翻倍：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;输入：每百万 Tokens 2 美元&lt;/li&gt;
+&lt;li&gt;输出：每百万 Tokens 10 美元&lt;/li&gt;
+&lt;li&gt;缓存输入：每百万 Tokens 0.1 美元&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Gemini 4 Argon&lt;/strong&gt;擅长在编码、金融、法律、网络安全、科学等领域处理复杂的现实任务，在多步骤任务上的深度和精度使其在多个领域基准测试中表现优于其他前沿模型，目前在衡量金融、编码、法律和税务等关键经济领域模型性能的 Vals Index 中排名第一。（消息来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/73/90/73901e1dd39d85075f6c75c27e32a127.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;苹果首款智能家庭中枢 HomeView 发布：售价 299 美元，11 月 13 日开售&lt;/h1&gt;
+&lt;p&gt;极客公园报道：苹果给 Siri 做了一块能认出全家人的屏幕，售价 299 美元&lt;/p&gt;
+&lt;p&gt;10 月 13 日消息，苹果刚刚推出了全新的 Apple HomeView 智能家居管理设备，标准版与壁挂版定价均为 299 美元，首批上市国家（澳大利亚、加拿大、印度、新西兰、英国和美国）今日开启预购，后续新加坡于 10 月 15 日开启预购，均于 11 月 13 日正式开售。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cb/dc/cbdced42a906613063ce8006e10d9830.png" /&gt;&lt;/p&gt;
+&lt;p&gt;该产品搭载 A18 芯片，配备 7 英寸（实际 6.98 英寸）Liquid Retina 显示屏（IPS 面板，1088&amp;times;1088 像素分辨率，220ppi，支持原彩显示，自带防指纹疏油层），还配备了一颗 1200 万像素摄像头（&amp;fnof;/2.4 光圈），整合音乐播放、FaceTime 视频通话、家庭监控和智能家居控制等功能，并搭载基于 Apple Intelligence 的 Siri AI；支持 Wi-Fi 6E、蓝牙 6.0、Thread；需搭配运行 iOS 27.2 或更高版本的 iPhone 或运行 iPadOS 27.2 或更高版本的 iPad 使用。&lt;/p&gt;
+&lt;p&gt;苹果表示，该设备支持面部识别，可根据不同家庭成员切换个性化内容，同时将隐私与安全保护作为产品设计的核心。&lt;/p&gt;
+&lt;p&gt;这款设备可识别最多六位家庭成员并根据识别结果显示对应用户在信息、FaceTime、日历、提醒事项和「查找」等应用中的个人内容，同时支持全家共享照片相册和音乐。苹果表示，个人内容不会向其他家庭成员开放。（消息来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;马斯克要用造火箭的思维造芯片：一年设计 10 款快速迭代，所有流程在一个 Terafab 工厂完成&lt;/h1&gt;
+&lt;p&gt;10 月 13 日消息，特斯拉 CEO 埃隆 &amp;middot; 马斯克今日公布了他对 Terafab 芯片工厂的愿景，表示特斯拉和 SpaceX 计划每年在 Terafab 位于美国得克萨斯州的 Giga Texas 研究设施&lt;strong&gt;制造和测试约 10 款芯片&lt;/strong&gt;，以加快开发进程。&lt;/p&gt;
+&lt;p&gt;马斯克强调，特斯拉与 SpaceX 正在芯片制造领域合作，目标是开展一些高风险高回报的项目。然而，每年推出 10</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 21:51:34 +0800</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>苹果给 Siri 做了一块能认出全家人的屏幕，售价 299 美元</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372302</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
+      <c r="F602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/44/70/447053bf69f939330b37989bf2d38c00.jpg" /&gt;&lt;/p&gt;&lt;p&gt;头图来源：Apple 官网&lt;/p&gt;&lt;p&gt;北京时间 10 月 13 日晚，苹果召开了一次主题为「欢迎回家」的新品发布会，苹果这次放进客厅的新东西，是一块 7 英寸的屏幕。&lt;/p&gt;&lt;p&gt;&lt;strong&gt;它叫 Apple HomeView，美国售价 299 美元&lt;/strong&gt;，10 月 13 日开放预订，11 月 13 日上市，一同曝光的还有第四代 Apple TV 4K、HomePod mini 2。三款产品在海外都以新一代 Siri AI 为卖点，但音箱要等后续软件更新才能用上。同期发布的，还有 Apple Home Collection 智能家居配件系列。&lt;/p&gt;&lt;p&gt;HomePod 和 Apple TV 早已支持家庭控制，HomePod 也有声音识别和个人请求。HomeView 给了 Siri 一块全家共用的屏幕，可以放在厨房台面、床头柜上，也可以装在玄关的墙上。&lt;/p&gt;&lt;p&gt;这次产品发布更有意思的变化，是 Siri 的回应多了一个可以随时看见、伸手操作的地方。它的个人化能力，仍和每个人的设备、权限绑在一起。&lt;/p&gt;&lt;p&gt;&lt;strong&gt;屏幕属于全家，个人化的 Siri 仍然要认人、认手机&lt;/strong&gt;。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5a/14/5a14c6ae47b900953000b11d8bea4bf9.png" /&gt;&lt;/p&gt;&lt;p&gt;桌面版提供四种配色｜图片来源：Apple&lt;/p&gt;&lt;h1&gt;一块会认家人的屏幕&lt;/h1&gt;&lt;p&gt;HomeView 桌面版用一根不锈钢铰链，把 7 英寸 Liquid Retina 屏幕连在一个穹顶形的铝制扬声器底座上，屏幕可以手动调整倾角，有银色、星光色、玫瑰粉和深空灰四种颜色。屏幕亮度最高 500 尼特，最低可降到 0.3 尼特。苹果的设想是，白天放在阳光充足的房间里看得清，晚上放在床头也不刺眼。&lt;/p&gt;&lt;p&gt;壁挂版是另一款独立型号，同样售价 299 美元，只有深空灰和银色两种颜色，需要另购施耐德设计的电源支架。USB-C 款 59.95 美元起，交流电接线款 79.95 美元起，PoE 款要等到 2027 年初，售价 129.95 美元。&lt;/p&gt;&lt;p&gt;屏幕闲着的时候，可以当相框或动态表盘。照片表盘能选用共享相簿，远方的家人也能往里添照片；Flow 表盘的光影会随人的走动变化；还有一组史努比动画，会跟着时间、天气和节日变换。苹果还说，界面会根据人与屏幕的距离调整信息密度：站在远处时显示大字号的简要信息，走近后再展开更多细节。&lt;/p&gt;&lt;p&gt;&lt;strong&gt;厨房是苹果重点展示的使用场景&lt;/strong&gt;。按苹果的说法，在 Safari 里找到菜谱后，可以把它转成分步说明；手上沾着面粉时，用语音就能开关多个计时器，倒计时以实时活动的形式停在屏幕一角。&lt;/p&gt;&lt;p&gt;它配有一颗 1200 万像素的人物居中摄像头和四个波束成形麦克风，打 FaceTime 时，人在厨房里走来走去，画面也会把人保持在中间。收到的信息可以用语音或屏幕键盘回复；广播功能能把一句「吃饭了」传到其他房间的 HomeView 和 HomePod，以及家人的 iPhone 和 Apple Watch 上。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/da/7f/da7fd21cfe1be3ebaf4d03ad9a10e97b.png" /&gt;&lt;/p&gt;&lt;p&gt;菜谱变成适合台面的分步界面｜图片来源：Apple&lt;/p&gt;&lt;p&gt;它同时也是一块家居看板。Home 相机表盘最多能同时播放 9 路摄像头画面，调温度、关灯、锁门都可以直接在屏幕上完成。配合符合条件的 iCloud+ 订阅和兼容的摄像头，它还能识别门口的人、熟悉的面孔、宠物、包裹和车辆，并为监控录像生成文字描述。&lt;/p&gt;&lt;p&gt;Apple Home Collection 则把配套设备也补了进来。这是苹果与 LG、施耐德电气合作设计的系列，涵盖摄像头、可视门铃、门锁、温控器和温湿度传感器。按苹果的说法，用 iPhone 碰一下即可开始设置，之后全在「家庭」App 里管理，不用另装厂商 App、注册账户。&lt;/p&gt;&lt;p&gt;LG </t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 19:33:53 +0800</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>说个事：极客公园创新大会 2027！</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372300</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr"/>
+      <c r="F603" s="2" t="inlineStr"/>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;一年一度：极客公园创新大会 2027，已经启动了。&lt;/p&gt;
+&lt;p&gt;你大概已经注意到一些不太寻常的事&amp;mdash;&amp;mdash;科技行业真正关心的东西，一直在变。&lt;/p&gt;
+&lt;p&gt;大模型公司的关注点，过去几年，几个月就一波变化：从追求用户规模，到追求技术的 SOTA 程度；应用公司的产品热点从 Chatbot，到 Agent，再到 Personal Agent；生产力工具也从 Copilot，一路到了 workspace。甚至连工程领域的概念也在快速更迭，从 Prompt Engineering，已经到了到 Environment Engineering。&lt;/p&gt;
+&lt;p&gt;流行概念的交替，实质是科技领域里，创新问题的权重和价值，正在被快速重估。什么值得投入、什么人更重要、什么样的能力还能构成壁垒&amp;mdash;&amp;mdash;答案已经不是过去的答案。&lt;/p&gt;
+&lt;p&gt;经过这几年 AI 带来的冲击和对世界的影响，我们已经可以清晰地看到：一次根本性的价值重估已经开始。&lt;/p&gt;
+&lt;p&gt;有的公司在长出惊天市值，有的公司在被彻底遗忘；有人好像在丢掉岗位，但有人正在变成「超人」；技术、产品、组织和人，都在重新给出关于「价值」的新答案。&lt;/p&gt;
+&lt;p&gt;时代从不预告它的转向，只是沉默地重新衡量一切。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;今年，极客公园创新大会 2027（IF 2027）想讨论的，就是这件事。陪你一起，在这个重新估值的时代里，找到属于自己的坐标与上升通道。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ff/a5/ffa5598c57a1e86739a5f6f15e5493e3.png" /&gt;&lt;/p&gt;
+&lt;p&gt;极客公园创新大会每一年的主题，都是那个时代脉搏的共振。我们习惯在热点还没形成的时候，把那个时代最迫切真实的问题，提前摆上台面，变成一场大会的主题。&lt;/p&gt;
+&lt;p&gt;这么多年，一直如此。&lt;/p&gt;
+&lt;p&gt;2017 年，AlphaGo 点燃了全球对 AI 的想象，以技术变化的加速时代开始到来。那一年，我们的主题是「科技主义」&amp;mdash;&amp;mdash;就算那时候大家还在谈移动互联网，我们依旧把那些相信技术、尊重技术、用技术改变世界的人请上台。&lt;/p&gt;
+&lt;p&gt;2019 年，移动互联网退潮让整个行业集体收缩、观望，很多人都在问「还能怎么办」。那一年，我们的主题是「WHY NOT」&amp;mdash;&amp;mdash;有一些人看到世界可能的样子，会思考「为什么不能更好一些？」今天的智能电动车、自动驾驶和大模型、机器人恰恰来自于那些当时喊出「why not」的团队。&lt;/p&gt;
+&lt;p&gt;2023 年，ChatGPT 们第一次让 AI 成为普通人手里的工具。AI 开始涌现出技术革命的浪潮。那一年，我们的主题是「增强人生」&amp;mdash;&amp;mdash;我们看到的是科技开始增强每一个个体，不仅仅是更省心，更好用，而是可以让我们突破原来的能力和资源桎梏去撒欢儿。&lt;/p&gt;
+&lt;p&gt;2025 年，AI 已经开始体现出解决问题的更大能力，真正的稀缺变成了人如何设定目标、判断和行动。那一年，我们的主题是「进程由我 On The Loop！」&amp;mdash;&amp;mdash;技术是阶梯，但主动权，必须拿在自己的手中。&lt;/p&gt;
+&lt;p&gt;今年也一样。&lt;/p&gt;
+&lt;p&gt;你可以看到，商业世界，甚至整个社会的价值结构，正在发生确定性的变化&amp;mdash;&amp;mdash;&lt;/p&gt;
+&lt;p&gt;创新和价值的权重在快速转移，不是所有东西都变贵了，也不是所有努力都还值钱。答案正在被重写。&lt;/p&gt;
+&lt;p&gt;因此，这也成为了我们今年大会的主题：&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Revaluation 价值，另有答案&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;所以今年，我们决定站在这个视角：既看懂 2026 年正在发生的事，也看清未来 18 个月里，哪些是值得你投身的方向？究竟什么正在变得更加贵重？哪些事情更值得你去改变？&lt;/p&gt;
+&lt;p&gt;这场跨越全球的价值重估，无人能够置身事外。它已经开始，&lt;/p&gt;
+&lt;p&gt;这就是为何你一定要来 IF 2027 的原因。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e5/75/e575d17039bebff053aef19c461764b9.png" /&gt;&lt;/p&gt;
+&lt;p&gt;找到那些跑赢时代的人，极客公园已经干了十几年。&lt;/p&gt;
+&lt;p&gt;2010 年，北京朝阳公园，索尼探梦科技馆的地下室。两把大红沙发椅，周围四五十个人席地而坐</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 23:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Next wants factory robots to switch tasks in minutes, not weeks</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/13/industrial-next-wants-factory-robots-to-switch-tasks-in-minutes-not-weeks/</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
+      <c r="F604" s="2" t="inlineStr"/>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Next helps manufacturers automate complex, delicate tasks that have traditionally required human labor.</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 17:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>Laplace Intelligence red-teams robots and self-driving cars before they hit the real world</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/13/laplace-intelligence-red-teams-robots-and-self-driving-cars-before-they-hit-the-real-world/</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr"/>
+      <c r="F605" s="2" t="inlineStr"/>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>University of Michigan spinout Laplace Intelligence uses AI agents and interactive simulation to stress-test robots and self-driving vehicles before deployment. The profitable startup is competing in Startup Battlefield at TechCrunch Disrupt, October 13-15 in San Francisco.</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H605"/>
+  <dimension ref="A1:H610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25174,6 +25174,193 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 10:56:08 +0000</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>星海图产品动态｜LEMO 双臂开发平台首发开售，让创造更快发生</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13845</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
+      <c r="F606" s="2" t="inlineStr"/>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>具身智能正在加速走向真实世界，从硬件搭建、数据采集到模型部署，如何让开发流程更高效、更便捷，成为具身智能研发中 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 17:35:33 GMT</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>九成具身智能公司在东部沿海，长沙抢走了另一样东西</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/ZqJq0uHBPvvEewkc0ZFC?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr"/>
+      <c r="F607" s="2" t="inlineStr"/>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/ZqJq0uHBPvvEewkc0ZFC?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 10:41:47 +0000</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>抢先盘点2026全球开发者先锋大会暨国际具身智能技能大赛十大亮点！</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503294.html</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr"/>
+      <c r="F608" s="2" t="inlineStr"/>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>“具身进实景，劳动最光荣”</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 04:51:32 +0000</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>国内最年轻AI教授创业：要让世界模型走向全身全模态</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503172.html</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr"/>
+      <c r="F609" s="2" t="inlineStr"/>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>给Ego补上缺失的交互信息</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 08:29:12 +0800</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>腾讯上线「绿泡泡」短剧，主打免费好看；特斯拉 Roadster 跑车明日发布；豆包工作支持一键导入 GPT、Claude 对话 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372366</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr"/>
+      <c r="F610" s="2" t="inlineStr"/>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d9/2d/d92d756bd52620b91bcbec587e6ba275.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;155 款应用拒绝豆包助手 AI 自动化操作&lt;/h1&gt;
+&lt;p&gt;10 月 14 日，豆包手机助手《屏幕自动化操作声明协议》（SAEP）30 天公示期结束，官方公布名单显示，已有 155 款第三方应用拒绝 AI 自动化操作，腾讯、阿里、美团、快手旗下多款产品，连同 Kimi、DeepSeek 等 AI 产品均在名单内，堪称互联网头部厂商的集体表态。&lt;/p&gt;
+&lt;p&gt;SAEP 协议核心是将 AI 屏幕自动操作的选择权交还应用开发者，开发者可自主决定是否允许豆包助手执行屏幕识别、模拟点击等操作。公示期内应用默认不开放权限；公示结束后，未明确拒绝的应用将按风险分级逐步开放，拒绝方后续也可随时调整声明。该自动化权限仅影响 AI 代操作，不影响用户手动使用 App。&lt;/p&gt;
+&lt;p&gt;此前，努比亚 NaviX Ultra 搭载豆包手机助手发售，就出现过设备触发游戏风控等冲突，这类矛盾过去长期处于隐性博弈状态。本次拒绝名单基本集中在拥有独立流量闭环的平台，安全风险、流量主权是核心考量。SAEP 把隐性冲突转为公开规则协商，标志移动端 AI 入口权博弈正式开启。行业认为，这只是智能体时代生态确权的起点，后续权限细化、责任划分、利益分配仍需多方持续磨合。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;相关报道：&lt;a href="https://mp.weixin.qq.com/s/r-hPYyFrpsohEvAacDmUHg"&gt;第一款 AI 手机，被半个互联网「拒」了&lt;/a&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ab/df/abdfafdef92ff5d9c119fbe1ab64cc1e.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;腾讯上线绿泡泡短剧&lt;/h1&gt;
+&lt;p&gt;近日，腾讯低调上线绿泡泡短剧，主打「免费好剧，一点就看」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/40/64/406450309a4e1c3f95afb8d158ea9cdd.png" /&gt;&lt;/p&gt;
+&lt;p&gt;绿泡泡的界面分为「免费剧场」「刷一刷」和「我的」三部分。「免费剧场」下设「AI 剧」「真人剧」「每日上新」「动漫剧」「本周必看」「百万播放」等栏目。点开中间入口「刷一刷」，上下滑动即进入沉浸式推荐流。剧集全部免费，但会在剧集之间插入广告。&lt;/p&gt;
+&lt;p&gt;《短剧小程序用户协议》显示，服务签订主体为深圳市腾讯计算机系统有限公司。协议同时写明，短剧均来自第三方提供方，包括第三方小程序、短剧制作方、授权发行方等，由其授权本服务展示、播放。&lt;/p&gt;
+&lt;p&gt;和红果短剧相比，绿泡泡的社交印记更重。除了常规排行榜，首页还有「朋友在看」的短剧推荐，以及标注「北京的朋友都在看」的地区热门榜。腾讯方面表示，为提供个性化内容，会收集用户的浏览、观看、分享、点赞、评论、收藏等记录，以及朋友看过的剧目。经过程序分析后，平台会预测用户的偏好，朋友在看什么，直接影响给相关用户推什么。&lt;/p&gt;
+&lt;p&gt;这并非腾讯首次下场做短剧。2021 年 12 月，腾讯视频发布业内首个微短剧品牌「十分剧场」，当时它只是长视频 App 里的一个频道页。2025 年 1 月，「火星短剧社」在微信上线，后改名「火星观剧」，是腾讯首款独立短剧产品。2025 年 6 月，微信上线名为「短剧」的官方小程序。到 2026 年 10 月，这个小程序已找不到入口，位置让给了绿泡泡。（来源：北京日报）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;小鹏发布智能汽车解决方案业务&lt;/h1&gt;
+&lt;p&gt;2026 巴黎国际车展期间，小鹏集团董事长兼 CEO 何小鹏作为巴黎汽车峰会唯一受邀的中国车企 CEO，发表重要演讲。何小鹏向与会的行业高管、全球媒体等，正式介绍其智能汽车解决方案业务：「XPENG AI ENGINEERING」，小鹏将面向全球合作伙伴开放智能汽车技术合作，输出覆盖整车研发、生产到售后的一站式能力。并将开放涵盖机器人、Robotaxi、飞行汽车、图灵 AI 芯片、物理世界基座模型等物理 AI 生态全领域的技术合作方案。&lt;/p&gt;
+&lt;p&gt;何小鹏表示：「开放已经成为小鹏与全球伙伴深化合作的关键词。我们不仅与合</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H610"/>
+  <dimension ref="A1:H622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25361,6 +25361,450 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:47:38 +0000</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>具身智能实景实训示范落地！人形机器人开启产线“作业模式”</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14009</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr"/>
+      <c r="F611" s="2" t="inlineStr"/>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>&amp;#160; 10月15日，乐聚机器人与兆丰机电在浙江联合发布“具身智能+汽车零部件上料解决方案”，15台“夸 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:34:57 +0000</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人首批国家标准正式发布，北京人形牵头起草“运动控制”部分</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13992</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr"/>
+      <c r="F612" s="2" t="inlineStr"/>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月28日，《人形机器人技术要求 第4部分：运动控制》（GB/T 48317.4—2026）正式发布 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:29:14 +0000</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>视塔机器人完成天使轮融资，光子晶体电子皮肤厚度可小于 1 毫米</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13971</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr"/>
+      <c r="F613" s="2" t="inlineStr"/>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>10月13日，深圳视塔机器人科技有限公司（以下简称“视塔”）宣布完成天使轮融资。</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:28:56 +0000</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>丝网印刷在电子皮肤/触觉传感器上的应用</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13984</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr"/>
+      <c r="F614" s="2" t="inlineStr"/>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤是一种能模仿人类触觉的电子器件，本质上是一种柔性触觉传感器，其结构通常在一片柔性薄膜上同时印刷出导电线</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:27:53 +0000</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>液态金属在电子皮肤上的应用</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13977</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr"/>
+      <c r="F615" s="2" t="inlineStr"/>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>液态金属正在成为电子皮肤值得关注的一种导电材料</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 09:49:08 +0000</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>具身数采，为什么开始重视外骨骼手套？</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/13944</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr"/>
+      <c r="F616" s="2" t="inlineStr"/>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>“软”的不行，就来“硬”的。</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 12:01:47 GMT</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>数据驱动的具身智能：迈向规模化之路｜QCon 上海</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/a8LKxyL9AC4PWhB2r0XX?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr"/>
+      <c r="F617" s="2" t="inlineStr"/>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/a8LKxyL9AC4PWhB2r0XX?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 10:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>成立不到半年融资数亿元，98年清华学者、KAN一作创业：让AI学会设计模型</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/QdPWpubQFmegrsH9UZFC?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr"/>
+      <c r="F618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/QdPWpubQFmegrsH9UZFC?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:15:00 +0800</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek 出现服务故障，官方补偿 1 周 Token 消耗；库克：苹果智能月底在华发测试版；特斯拉、SpaceX 最快年底合并｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372430</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr"/>
+      <c r="F619" s="2" t="inlineStr"/>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/45/37/45378c73036801a0b461c3228e0505f2.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;DeepSeek 服务故障近 5 小时，官方补偿所有 API 用户 7 天内的消耗金额&lt;/h1&gt;
+&lt;p&gt;10 月 15 日消息，DeepSeek 网页 / API 服务今日（10 月 15 日）早间出现服务问题，经过近 5 个小时的修复，终于恢复正常。&lt;/p&gt;
+&lt;p&gt;对此，DeepSeek 官方开放平台发布服务恢复及补偿通知，将补偿所有 API 用户 7 天内的消耗金额：&lt;/p&gt;
+&lt;blockquote&gt;北京时间 2026 年 10 月 15 日 8:11 至 13:04 期间，我们的服务系统出现故障，导致该时段内 API 服务无法正常使用。对于此次故障给您带来的不便与困扰，我们深表歉意。&lt;strong&gt;我们已第一时间启动针对服务稳定性的全面排查和彻底整改，全面梳理并剥离单点依赖&lt;/strong&gt;，坚决杜绝同类问题再次发生。&lt;/blockquote&gt;
+&lt;blockquote&gt;作为补偿，&lt;strong&gt;我们将按您账号 7 日内（10.8-10.14）的消耗金额以赠金形式全额返还&lt;/strong&gt;，赠金自动到账，API 计费扣款先从赠金账户扣除。此次故障对您造成了影响，我们再次致歉，感谢您一直以来的信任与支持。&lt;/blockquote&gt;
+&lt;p&gt;这是 DeepSeek 本月以来遇到的最大规模服务问题，网友今早在 DeepSeek 中对话提示「服务器暂时不可用」，「DeepSeek 崩了」话题也一度登上微博热搜。（来源： IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/41/a9/41a98b79a4b2045eb799666c5c441c3b.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e1/fe/e1fee250135e72e3a27758ed3f79dc13.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;工信部等三部门联合调查有关车辆刹车踏板支架断裂问题，尊界声明积极响应、完全服从并将全力配合调查组工作&lt;/h1&gt;
+&lt;p&gt;10 月 15 日消息，针对网络反映的「尊界 V800 汽车刹车踏板支架断裂问题」，工业和信息化部、中央网信办、市场监管总局高度重视，在前期调查工作基础上，成立联合调查组开展核查，并依法依规处理。有关情况将及时公布。&lt;/p&gt;
+&lt;p&gt;据多位博主分享的截图，华为常务董事、产品投资评审委员会主任、终端 BG 董事长余承东转发了尊界汽车声明，表态称：&lt;/p&gt;
+&lt;blockquote&gt;&lt;strong&gt;正义可能会迟到，但永远不会缺席！&lt;/strong&gt;&lt;/blockquote&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a4/74/a47435f11a1b955c9993f3134817b09f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;库克：苹果智能 Apple Intelligence 月底在华发布测试版本，但不包括 Siri AI&lt;/h1&gt;
+&lt;p&gt;10 月 15 日消息，苹果董事会执行主席蒂姆 &amp;middot; 库克今日在上海接受澎湃新闻、界面新闻等媒体采访时确认，苹果智能（Apple Intelligence）及相关阿里千问大模型已获得批准，将于 10 月晚些时候面向中国用户发布测试版本。&lt;/p&gt;
+&lt;p&gt;库克表示，首批功能包括实时翻译、书写工具、照片清除工具等，但 Siri AI 不在此次发布范围之内。「我们很高兴，首批核心的苹果智能功能是可以慢慢上线了。」库克说道。&lt;/p&gt;
+&lt;p&gt;据此前报道，此次获批涉及的阿里系模型包括通义千问和通义万相，前者为大语言模型，后者为图像及视频生成工具。&lt;/p&gt;
+&lt;p&gt;彭博社古尔曼还曾报道称，苹果计划于 12 月随 iOS 27.3 系统更新为中国用户正式推送 Apple Intelligence，首批功能与 2024 年海外首次发布时的版本基本一致。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https:</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:08:03 +0800</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>手机大厂开始做穿戴录音，卷的已经不是转写：OPPO 心力球体验</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372428</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr"/>
+      <c r="F620" s="2" t="inlineStr"/>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c3/4e/c34ea9a1c77de083e0df48877c1edf4d.jpg" /&gt;&lt;/p&gt;&lt;p&gt;头图来源：极客公园&lt;/p&gt;&lt;p&gt;「24 小时全天候录音硬件」这个概念，放到今天其实已经不太新鲜了。&lt;/p&gt;&lt;p&gt;无论是年初的 CES，再到国内今年数次硬件展、再到一个月前 IFA 上，我都密集看了一圈把麦克风塞进手环、戒指甚至项链里的 AI 穿戴硬件。不管是海外创业团队还是国内硬件老兵，大家都在试着把屏幕拆掉，把麦克风戴到身上。&lt;/p&gt;&lt;p&gt;真正新鲜、也是所有人都还在苦苦寻找答案的问题，是如何把录下来的东西自然地融入你自己的日常工作流。甚至直到 2026 年下半年，Personal AI Agent 这个概念大火之后，这个问题在行业里依然没有一个明确的正确答案。&lt;/p&gt;&lt;p&gt;独立硬件创业公司的做法，往往是再造一个硬件，配一个独立的 App，然后按月收你的云端订阅费。而当 OPPO 这样的手机厂商亲自下场，直接把这枚名叫「OPPO AI 心力球」的小硬件，融入你每天最常用的智能手机里，让它成为手机体验的一部分。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/17/ba/17ba7ac8cce33212da2c19828129fbd8.jpg" /&gt;&lt;/p&gt;&lt;p&gt;OPPO AI 心力球与收纳盒，主机重量仅 9.8 克｜图片来源：极客公园&lt;/p&gt;&lt;p&gt;这枚在今年 9 月 17 日 OPPO 开发者大会（ODC）上首次亮相的小硬件，拿到手里非常轻巧。主机算上背后的夹持 C 桥一共只有 9.8 克；放进不含电池的随身收纳盒里，整体也才 45 克左右。&lt;/p&gt;&lt;p&gt;你可以像别一枚纽扣一样，顺手把它夹在衣领、口袋边缘或者背包带上。它的夹持力做到了 4N 以上，外层还配了增加摩擦力的硅胶套和 IP55 级防尘防水，日常通勤走动基本感觉不到它的存在。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/de/b6/deb6bc52456095997014d7df544266b8.jpg" /&gt;&lt;/p&gt;&lt;p&gt;背面采用一体式 C 桥夹持结构，配合硅胶套增加日常佩戴的摩擦力｜图片来源：极客公园&lt;/p&gt;&lt;h1&gt;不用掏手机的「重点键」&lt;/h1&gt;&lt;p&gt;过去很多人买过 AI 录音卡或者录音笔，无论产品形态如何，最后十有八九都放在抽屉里吃灰了。&lt;/p&gt;&lt;p&gt;原因很简单：无论是吸在手机上还是挂在身上，每次对话发生之前，你得先完成「记得去把设备打开」这样一套机械性的动作，录完之后它又变成一个个孤立的音频文件，躺在文件夹里没人回头翻。&lt;/p&gt;&lt;p&gt;OPPO 心力球把「开机」这个反人性的动作直接取消了。它采用的是类似智能手机一样的全时工作状态：早上从收纳盒里拿出来戴上，系统自动进入聆听和记录状态；晚上摘下来放回收纳盒，自动停止记录。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/68/df/68df25a19ef35b9aaa53105fb358fc54.png" /&gt;&lt;/p&gt;&lt;p&gt;满电状态下支持 24 小时连续记录，配合 5 米远距收音和区分佩戴者本人声音的声纹识别，从早到晚完全不需要手动开关。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/30/b4/30b403e80efae5640c2d94f5651182fe.jpg" /&gt;&lt;/p&gt;&lt;p&gt;夹在衣领或口袋上，日常几乎没有佩戴存在感｜图片来源：极客公园&lt;/p&gt;&lt;p&gt;用下来这几天，最让我觉得顺手的体验细节，其实是它在日常碎片时间里接住灵感的方式。&lt;/p&gt;&lt;p&gt;平时工作里，经常有那种灵感突然迸发的瞬间，可能是在开车，甚至是在浴室洗漱。那种时候你的手边根本没有纸和笔，而我甚至连手机都懒得掏出来。&lt;/p&gt;&lt;p&gt;现在有了心力球之后，这件事变得自然了很多：你直接开口说就行，或者伸手长按机身正面的 AI 键 0.5 秒唤醒语音输入，按住说话、松开结束，心力球会顺着当时的语境和语义，自动识别你是在记一条灵感，还是在</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 18:20:44 +0800</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人最尴尬的事：长了一双腿，却只能定住干活</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372420</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr"/>
+      <c r="F621" s="2" t="inlineStr"/>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: #000000; line-height: normal;"&gt;&lt;strong style="color: #375474;"&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/section&gt;
+&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: #000000; line-height: normal;"&gt;&lt;strong style="color: #375474;"&gt;编辑｜&lt;strong&gt;郑玄&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section style="margin-right: 8px; margin-left: 8px; letter-spacing: 1px; color: #000000; line-height: normal;"&gt;&lt;strong style="color: #375474;"&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;长得像人，但是只能跳舞表演，根本没法真正干活。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;这大概是过去几年人形机器人最尴尬的一幕。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;人形机器人最初拿到天量关注，底层逻辑其实很直接：现实世界本来就是围绕人类身体设计的。楼梯、橱柜、货架、工位甚至门把手，全都有现成尺寸。理论上，机器人完全可以用下肢越过障碍，直接用上肢拿起工具工作。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;逻辑听起来无懈可击，但行业演进了几年，我们看到的却往往是另一副模样。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;视频里的人形机器人，主要是在跑跑跳跳、翻跟头；哪怕真有一些干活的演示，也大多老老实实待在平地上&amp;mdash;&amp;mdash;走到某处，定在原地，再小心翼翼地伸手。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;&lt;strong style="margin-top: 0px; margin-bottom: 0px; text-align: left; color: #000000; letter-spacing: 0px; line-height: 1.6;"&gt;如果双腿只负责把机器人送到任务面前，真正动手时它必须先站稳锁定身体，那它们不过是一对成本极高、极其脆弱的机械轮子。那么人形机器人的优势在哪？&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;这也很难怪大家苛刻。迈不过这道坎，人形机器人就永远撕不掉「表演道具」的标签。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; line-height: 1.75;"&gt;不过，这</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:39:52-04:00</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>The tech backlash is now in theaters</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/entertainment/1012438/hollywood-tech-backlash-you-can-see-everything-musk-the-social-reckoning-artificial</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr"/>
+      <c r="F622" s="2" t="inlineStr"/>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>Though movies about disruptive tech founders are nothing new, 2026 has been unusually stacked with features that take a much more critical look at how Silicon Valley is reshaping our reality. Aaron Sorkin's The Social Reckoning frames Mark Zuckerberg as a robotic villain whose ambitions are destabilizing society. Nathan Fielder and Lance Oppenheim's You Can [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H622"/>
+  <dimension ref="A1:H634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25805,6 +25805,567 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:18:11 +0000</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>芯明独家视觉融合方案落地钧舵机器人灵巧手</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14054</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr"/>
+      <c r="F623" s="2" t="inlineStr"/>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>目前市场上唯一能装进掌心的dTOF+RGB视觉融合方案</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 03:48:32 +0000</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>从具身操作走向规模交付：中科慧灵构建鞋服制造“模型—本体—场景”技术路径</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14030</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr"/>
+      <c r="F624" s="2" t="inlineStr"/>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>序言 具身智能的价值，最终不应只体现在机器人完成了多少动作，而要体现在它为人和产业带来了什么。让机器承担更多重 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 01:57:11 +0000</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>“从每天一万三，降到每天三千九！”人形机器人行业迎来商业化大考</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14023</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr"/>
+      <c r="F625" s="2" t="inlineStr"/>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>针对人形机器人租赁价格下降的问题，国内头部机器人租赁平台擎天租相关负责人今日回应中国证券报记者采访时表示：“国 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:30:02+00:00</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: When Two Robots Become One</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-reconfigurable-robots</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr"/>
+      <c r="F626" s="2" t="inlineStr"/>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 08:22:32 +0800</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>iPhone Duo 一秒售罄，发货排到明年；马斯克：考虑自建电商平台；谷歌创始人：AI 正开始自己造自己</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372488</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr"/>
+      <c r="F627" s="2" t="inlineStr"/>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b6/87/b687f3bc8408da3a1902b1450b56d9cc.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果官网 2026 年的 iPhone Duo 已售罄！发货日期排到明年 1 月 22 日&lt;/h2&gt;
+&lt;p&gt;10 月 16 日，苹果首款折叠屏 iPhone Duo 于当晚 8 点开启线上预购，大量用户同时涌入苹果官网、Apple Store App 及天猫、京东等官方直营渠道，购买页面一度无法正常打开。开售一分钟左右，各大电商平台即显示该机型售罄。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9e/6e/9e6e1564d7011d10be673e041efe52cb.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;目前官网仍可下单，预计发货时间排至 1 月 22 日，2026 年的备货已全部售罄。受折叠屏铰链、柔性内屏产能爬坡周期长于直板机型、首批备货有限叠加首发集中抢购影响，交期被拉长。后续随着产能释放，发货排期将逐步前移，已抢到 11 月、12 月批次的用户或提前半个月拿到新机。&lt;/p&gt;
+&lt;p&gt;该机型维修费用极高，非 AppleCare+用户更换内屏需 7998 元，外屏需 3198 元，电池维修费用达 1898 元，建议自用用户选购 AppleCare+。(来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/07/12/0712f6ca2fe32fe4ee6c89d9f9fe27b6.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;马斯克回应 Grok Bot 被亚马逊封禁：不让 AI 智能体网购，就考虑自建电商平台&lt;/h2&gt;
+&lt;p&gt;科技媒体 notateslaapp 10 月 15 日发布博文，报道称有用户反馈亚马逊阻止 Grok Bot 智能体在其平台下单之后，全球首富马斯克表示考虑打造一家与亚马逊竞争的公司。&lt;/p&gt;
+&lt;p&gt;该媒体指出特斯拉上月已将 Grok Bot 整合进车辆，用户可在通勤途中把下单任务交给 AI。用户无需亲自打开零售商网站，即可由 AI 完成购物流程，对希望掌控流量、推荐和交易入口的零售平台而言，这直接冲击了其传统电商模式。&lt;/p&gt;
+&lt;p&gt;据报道，亚马逊不仅限制 Grok Bot 下单，也屏蔽了 Meta 的 Muse AI 购物智能体，同时自身仍在开发 AI 购物工具。&lt;/p&gt;
+&lt;p&gt;网友 @thecsguy 近日在 X 平台发帖，反馈遇到的 Grok Bot 网购被封问题，并鼓励马斯克考虑推出「X Shop」。针对用户反馈，马斯克在推文中表示：「或许我们应该创立一家与亚马逊竞争的公司」。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;英特尔计划 2028 年面向物理 AI 领域推出「Razor Lake AX」 处理器，平台算力 700 TOPS&lt;/h2&gt;
+&lt;p&gt;10 月 17 日消息，据韩媒 THE ELEC 报道，Intel（英特尔）高级副总裁 조민성 昨日在韩国举行的「半导体驱动人形机器人」大会上表示，该企业计划 2027 年初面向物理 AI 领域推出「Nova Lake」处理器。&lt;/p&gt;
+&lt;p&gt;而在 "Nova Lake" 后，英特尔还将在 2028 年为物理 AI 带来「Razor Lake AX」。其平台总算力可到 700 TOPS，显著优于「Panther Lake」的 180 TOPS。&lt;/p&gt;
+&lt;p&gt;据悉，「Razor Lake AX」是英特尔首款商业化的大内存位宽大核显 SoC，其沿用标准「Nova Lake」 核心组成的同时集成了 16 个或 32 个 Xe3P 核心，图形显示与 AI 推理能力都得到显著提升。(来源：IT 之家)&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;OpenAI 升级 ChatGPT 浏览器扩展 可读取多个标签并执行网页任务&lt;/h2&gt;
+&lt;p&gt;OpenAI 更新了 ChatGPT 浏览器扩展，用户可在 ChatGPT 对话中提及 Chrome，让助手读取已打开的网页标签作为上下文，并比较页面内容、整理资料或协助完成浏览器任务。OpenAI 列举的用途还包括汇总供应商价格与功能、整理表格、预填表单，以及根据网页信息起草邮件。&lt;/p&gt;
+&lt;p&gt;升级后的侧边栏可在浏览网页时直接打开 ChatG</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 14:46:47 +0800</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>是的，特斯拉真造了一辆「飞行汽车」！</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372459</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr"/>
+      <c r="F628" s="2" t="inlineStr"/>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;历史，是由疯子和工程师创造的。&lt;/p&gt;
+&lt;p&gt;我们知道马斯克是个疯子，但没想到他能这么疯。&lt;/p&gt;
+&lt;p&gt;当地时间 10 月 16 日，在 SpaceX 于州 McGregor/Waco 的火箭试验场上，一段向上垂直弯过来的人造公路上，一台白色跑车以匪夷所思的状态，反重力地贴在了上面的弯上。这还不算完，在这段路上倒车加速后，这台车脱离公路，直接飞到空中，转体并通过推进器稳稳落地。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e6/b6/e6b6804a87dc58ed100d1f6674dc32d5.gif" /&gt;&lt;/p&gt;
+&lt;p&gt;无法形容的酷｜图片来源：Tesla&lt;/p&gt;
+&lt;p&gt;新一代的特斯拉 Roderster 跑车，就以这种情况，完成了自己的首秀。&lt;/p&gt;
+&lt;p&gt;伊隆&amp;middot;马斯克在开场时候告诉现场观众：「我们确定没问题，但要是不巧的话，咱们这里的安全距离可不太够。」&lt;/p&gt;
+&lt;p&gt;当然，你知道的，一些恐惧，恰恰能激起人们更大的兴奋，老马是懂行的。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d1/36/d13663e7d5c1fd7af07bb6d05a57d139.png" /&gt;&lt;/p&gt;
+&lt;p&gt;测试的 Rocket 版本使用的并非真人驾驶员｜图片来源：Tesla&lt;/p&gt;
+&lt;p&gt;除了能飞，新一代 Roderster 跑车据悉将有三个版本，Performance、Thrust 和 Rocket 版本，其中最后的 Rocket 版本是单座，0 到 60 英里加速达到惊人的 0.59 秒。&lt;/p&gt;
+&lt;p&gt;虽然价格尚未公布，但你能猜到全世界的富豪，应该都已经开始准备支票本了。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;特斯拉能飞&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;先说结论，新一代 Roadster 能飞起来，&lt;strong&gt;靠的不是螺旋桨，也不是喷气发动机，而是一套从 SpaceX「借」来的冷气推进系统，加上一个能把车「吸」在天花板上的风扇&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;发布会开场的演示，几乎就是这两套系统的「联合作战」。&lt;/p&gt;
+&lt;p&gt;一辆 Roadster 倒挂在一段弧形坡道的顶端，四个轮子朝天，就这么「粘」在上面不掉下来。随后它倒着冲出去，在空中翻转，靠尾部喷出的气流稳住姿态，四平八稳地落地。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/38/2f/382f47d2203bad674a4af1593ddbc450.png" /&gt;&lt;/p&gt;
+&lt;p&gt;车稳稳落地，台上先是一句「Well, it worked」&amp;mdash;&amp;mdash;嗯，成功了，紧接着又有人喊了一句更直白的，「Flying cars are real」，飞行汽车是真的。&lt;/p&gt;
+&lt;p&gt;马斯克顺势搬出了老朋友彼得&amp;middot;蒂尔的名言，「我们想要一辆会飞的汽车，得到的却是 140 个字符」，然后补了一句，「现在不是了」。&lt;/p&gt;
+&lt;p&gt;能倒挂，是因为它真的会「吸」。&lt;/p&gt;
+&lt;p&gt;Roadster 底盘下装了一套风扇抽吸系统，把车底的空气往外抽，制造负压，最多能产生 2G 的吸附力。也就是说，它被「按」在地面上的力，是自身重量的两倍。所以哪怕车倒过来、停着不动，也不会掉下来。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/50/41/5041814be9ba602a0b16152dbc7141cb.png" /&gt;&lt;/p&gt;
+&lt;p&gt;马斯克在台上难得「开了车」，说这辆车「能把拖车挂钩上的镀铬吸下来」，「能把网球从水管里吸过去」。&lt;/p&gt;
+&lt;p&gt;玩笑归玩笑，他也承认，日常开车谁会想倒挂着呢？这套系统真正的价值，其实在赛道上。&lt;/p&gt;
+&lt;p&gt;普通轮胎的抓地极限大约是 1.26G，再往上就会打滑。而有了风扇抽吸，Roadster 过弯能超过 2G，看起来就像在「违反物理定律」。&lt;strong&gt;马斯克的原话是，它会「碾压所有赛道纪</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 14:41:48 +0800</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>苹果和 Meta 和好了，是 AI 逼的</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372458</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr"/>
+      <c r="F629" s="2" t="inlineStr"/>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;没有永远的敌人，只有永远的 AI 焦虑。&lt;/p&gt;
+&lt;p&gt;10 月 2 日，苹果做了一件很少见的事，因为一个第三方 App，宣布要调整系统规则。&lt;/p&gt;
+&lt;p&gt;起因是《Inc.》杂志的科技专栏作者 Jason Aten 公开指控，Meta 的 AI 智能体 Muse 在他的 Mac 上读取了私人消息。Muse 是 Meta 力推的「能替你办事」的 Agent，会帮你退订闲置会员，甚至替你砍价。&lt;/p&gt;
+&lt;p&gt;苹果随即表态，&lt;strong&gt;今后 AI 请求读取 Mac 数据时，系统会主动提示用户&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;这几乎就是苹果和 Meta 过去五年关系的缩影，Meta 想拿数据，苹果出面拦着。&lt;/p&gt;
+&lt;p&gt;然而仅仅两周后，故事发生了反转。&lt;/p&gt;
+&lt;p&gt;当地时间 10 月 15 日，Meta 发布开放权重模型 Muse Spark Open，扎克伯格在 X 上发帖，感谢「John Ternus 和苹果」的合作，让这个模型能在新款 Mac Studio 上流畅运行。&lt;/p&gt;
+&lt;p&gt;苹果 CEO Ternus 本人很快回复，称能在自己桌上如此高效地跑起这种量级的模型：&lt;/p&gt;
+&lt;p&gt;「鹅妹子嘤」。&lt;/p&gt;
+&lt;p&gt;Meta 的 AI 负责人 Alexandr Wang 接受 Axios 采访时，说了一句更搞笑但直白的话：&lt;/p&gt;
+&lt;p&gt;「&lt;strong&gt;很高兴爸爸妈妈又和好了&lt;/strong&gt;。」&lt;/p&gt;
+&lt;p&gt;所以，「爸爸」和「妈妈」，是怎么和好的？以及，Meta 最近连续在模型上发力，终于重回牌桌了吗？&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;一台桌子，放下 8000 亿参数&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;先看这次苹果和 Meta 的合作到底做成了什么。&lt;/p&gt;
+&lt;p&gt;Meta 宣称 Muse Spark Open 总参数 8160 亿，每次推理只激活其中 420 亿，支持 100 万 token 的上下文。Meta 称它是：&lt;/p&gt;
+&lt;p&gt;「&lt;strong&gt;迄今美国最强的开放权重模型&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;注意这个措辞里的「美国」两个字。论参数规模，它并不是全球最大的开源模型。&lt;strong&gt;月之暗面的 Kimi K2、蚂蚁的 Ling-1T，早在 2025 年就把开源模型推到了万亿参数级别&lt;/strong&gt;。Meta 这次是在追赶，而且对手是中国公司。&lt;/p&gt;
+&lt;p&gt;真正新鲜的，是它跑在哪里。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cc/df/ccdff1c8fe8a9eb61d4a56fb76ca510f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;苹果的 M5 Ultra Mac Studio 绝对是本地模型利器｜图片来源：Apple&lt;/p&gt;
+&lt;p&gt;按 Meta 的说法，&lt;strong&gt;两台顶配 M5 Ultra Mac Studio 就能装下整个模型&lt;/strong&gt;。每台 Mac Studio 的 GPU 能直接调用最多 512GB 统一内存，两台连起来约 1TB，在 Apple 的 MLX 框架下像一台小型超算一样协同工作。&lt;/p&gt;
+&lt;p&gt;这件事放在别的 AI 硬件平台上，几乎不可能放在一张书桌上。&lt;/p&gt;
+&lt;p&gt;道理不复杂。这类「总参数大、激活参数小」的模型，最需要的是超大的内存容量，对带宽的要求反倒没那么极端。每生成一个 token，模型只需要读取 420 亿参数那一小块，M5 Ultra 每秒 1.2TB 的内存带宽足够应付。&lt;/p&gt;
+&lt;p&gt;换到 NVIDIA 阵营，一张消费级显卡的显存不过几十 GB，想装下 8000 亿参数，得上 8 卡 H100 级别的服务器，那是机房里的设备，不是桌面上的。&lt;/p&gt;
+&lt;p&gt;也就是说，&lt;strong&gt;苹果统一内存架构这几年被嘲笑「贵」的那部分，恰好成了跑超大模型的护城河&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;Meta 展示的用例也很有针对性。基于 Muse Spark Open 的编程工具 Muse Code，全程在本地完成了两件事。一件是给开源 Mastodon 客户端 Ice Cubes 提交 iOS 代码修改，另一件是操作 DaVinci Resolve 审看素材，把横屏视频裁成竖屏。&lt;/p&gt;
+&lt;p&gt;写代码、剪视频，两个都是 Mac 用户最典型的工作场景。&lt;/p&gt;
+&lt;p&gt;当然，门槛也很现实。&lt;strong&gt;256GB 内存版的</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 10:22:17 +0800</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>巅峰估值 50 亿美元的 AI 独角兽，何以不到 0.1 折贱卖</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372437</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr"/>
+      <c r="F630" s="2" t="inlineStr"/>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：Chatgpt 生成&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;当地时间 10 月 12 日，曾经引爆 AI 陪伴赛道的明星项目 Character.AI，在美国特拉华州法院提交《破产法》第 11 章重组申请，开启法院监督下的资产拍卖流程。&lt;/p&gt;
+&lt;p&gt;根据披露文件，迪士尼已经与它提前达成了底价竞购协议：2000 万美元，买走部分知识产权的非独占永久许可，外加用一批「前员工」为平台提供过渡期技术服务。&lt;/p&gt;
+&lt;p&gt;这笔交易不包含公司主体、产品 App 和用户资产。拍卖窗口期预计在今年 11 月底至 12 月初收尾。&lt;/p&gt;
+&lt;p&gt;在整个出售周期内，Character.AI 平台维持正常运转，现有订阅、对话服务暂时不会改动。但如果最终没有买家愿意接手并持续运营平台，Character.AI 将走向关停。&lt;/p&gt;
+&lt;p&gt;短短几年，这家由 Transformer 论文核心作者创办、巅峰估值 50 亿美元的 AI 创业公司，走完一轮剧烈的起落。&lt;/p&gt;
+&lt;p&gt;它的故事，不只是一家创业公司的失败样本，也折射出生成式 AI 消费应用普遍面临的成本、版权与商业化困境。&lt;/p&gt;
+&lt;h1&gt;一、破产拍卖，迪士尼买的是什么&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/95/e5/95e59f690d71d0d6b55c6d07d057b7fd.png" /&gt;&lt;/p&gt;
+&lt;p&gt;破产申请书｜图片来源：stretto&lt;/p&gt;
+&lt;p&gt;这份 10 月 12 日的文件显示，Character.AI 列出的资产和负债都在 5000 万到 1 亿美元区间。&lt;/p&gt;
+&lt;p&gt;破产前，它与迪士尼旗下 Disney Worldwide Services 签了协议：迪士尼担任 stalking horse bidder，也就是底价竞购方，出价 2000 万美元，买下部分知识产权的非独占永久许可和相关债权，还承诺用其雇佣的前员工，为平台提供一段时间的过渡技术服务。&lt;/p&gt;
+&lt;p&gt;stalking horse 是破产拍卖的常用机制：第一个出价的人定下底价，后面的人可以出更高价，最终价高者得，整个过程由法院监督，走《破产法》第 363 条的程序，预计 11 月底到 12 月初收尾。CEO Colin Adams 的说法是，董事会评估了所有选项，法院监督下的出售是「为所有利益相关方最大化价值」的最佳路径。&lt;/p&gt;
+&lt;p&gt;这里有一个细节，迪士尼买的是 IP 许可，平台本身不在标的里。也就是说，迪士尼对继续运营 Character.AI 这个 App 兴趣不大，它要的是技术。&lt;/p&gt;
+&lt;p&gt;这与迪士尼过去一年的 AI 布局完全一致：2025 年 12 月，它曾宣布与 OpenAI 达成角色授权合作，计划把 200 多个迪士尼、漫威、皮克斯、星战角色放进 Sora；2026 年 3 月 OpenAI 关停 Sora，这笔交易最终没有成交、没有资金往来。现在，迪士尼又从破产拍卖里捡走一套角色对话技术。版权方从「禁止你用我的角色」，变成了「买下让你能和我角色互动的技术」。两种做法，同一个目的。&lt;/p&gt;
+&lt;p&gt;另外一个颇具戏剧性的背景是，就在一年前，迪士尼还向 Character.AI 发送过侵权律师函，指控平台大量用户创建的迪士尼角色，未经许可使用版权形象，甚至提出部分内容对未成年人存在风险。彼时 Character.AI 被迫下架平台上大量迪士尼 IP 角色。如今双方身份反转，迪士尼进入破产拍卖，收购它的技术资产。&lt;/p&gt;
+&lt;p&gt;而这次拍卖如果没有出现新的接盘者，Character.AI 将按计划关停，数千万用户创建的角色、对话记录，都将面临消失风险，会在某个日期变成无法访问的数据。&lt;/p&gt;
+&lt;h1&gt;二、曾经，硅谷最贵的「情绪生意」&lt;/h1&gt;
+&lt;p&gt;Character.AI 诞生于大模型爆发前夜。&lt;/p&gt;
+&lt;p&gt;把时间拉回到 2021 年，Noam Shazeer 是 Transformer 奠基论文《Attention Is All You Need》的核心作者，也是谷歌最早对话模型 LaMDA 的开发者之一。&lt;/p&gt;
+&lt;p&gt;他和同事 Daniel De Freitas 在谷歌合作开发对话模型 Meena&amp;mdash;&amp;mdash; 也就是后来的 LaMDA。&lt;/p&gt;
+&lt;p&gt;2020 年，Shazeer 写下一份在公司内部广泛流传的备忘录《Meena Eats the World》，判断 Meena 能取代谷歌搜索，创造数万亿美元的收入。但谷歌以</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 10:18:36 +0800</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>第一款 AI 手机，被半个互联网「拒」了</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372436</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr"/>
+      <c r="F631" s="2" t="inlineStr"/>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;头图来源：&lt;/strong&gt;chatgpt 生成&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;10 月 14 日，豆包手机助手推出的《屏幕自动化操作声明协议》（SAEP，Screen Automation Execution Protocol）正式结束 30 天公示期。随之公布的拒绝名单显示，已有 155 款第三方应用明确关上了 AI 自动化操作的大门。名单当日经两轮更新，首批发布为 153 款，最终补全长尾应用后共计 155 款。&lt;/p&gt;
+&lt;p&gt;腾讯旗下 66 款、阿里旗下 23 款、美团 11 款、快手 14 款，几乎覆盖国内互联网半壁江山的主流产品悉数在列，就连 Kimi、DeepSeek 等 AI 赛道的同类产品，也选择了关闭权限。&lt;/p&gt;
+&lt;p&gt;这份长长的拒绝名单，是超级 App 们在 AI Agent 时代，第一次集体对自身的应用边界和流量主权做出表态。&lt;/p&gt;
+&lt;p&gt;当 AI 开始能替用户点按屏幕、跨应用完成任务，原本稳固了十几年的移动端流量格局和商业逻辑，正在出现新的裂痕。&lt;/p&gt;
+&lt;h2&gt;SAEP：把规则摆上台面&lt;/h2&gt;
+&lt;p&gt;在 SAEP 出台之前，这件事始终处于行业的灰色地带。&lt;/p&gt;
+&lt;p&gt;手机 AI 助手能不能操作某款应用、能操作到哪一步，基本由 AI 厂商单方面技术适配决定，应用方没有正式的表态渠道，大多通过风控策略默默拦截；用户则始终面对模糊的功能边界，不知道为什么有的应用能用 AI 操作，有的不能。&lt;/p&gt;
+&lt;p&gt;SAEP 的核心，是把屏幕自动化操作的选择权交还给第三方开发者。&lt;/p&gt;
+&lt;p&gt;开发者可以自主声明是否允许豆包手机助手在自身应用内执行屏幕识别、模拟点击、内容填写等操作，也可以细化到具体页面、具体功能的权限边界。&lt;/p&gt;
+&lt;p&gt;按照豆包公布的运行规则，整个权限开放分为两个阶段：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;30 天公示期内，所有第三方应用默认不开放 AI 操作，仅主动声明同意的应用才会被支持；&lt;/li&gt;
+&lt;li&gt;公示期结束后，未明确提交拒绝声明的应用，将按照风险层级逐步开放操作权限；&lt;/li&gt;
+&lt;li&gt;已明确拒绝的应用，始终不会被 AI 执行自动化操作，开发者后续也可随时调整声明状态。&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;从技术实现上，豆包手机助手的自动化能力基于系统级权限，可在后台完成屏幕读取与交互操作，区别于普通无障碍工具需占用前台的特性。同时，该权限仅针对 AI 自动化操作，完全不影响应用本身的正常使用，用户依然可以手动打开、使用所有 App。&lt;/p&gt;
+&lt;h2&gt;从隐性冲突到公开规则&lt;/h2&gt;
+&lt;p&gt;事实上，这套规则的出台，之前已埋下伏笔。&lt;/p&gt;
+&lt;p&gt;2025 年 12 月，字节跳动联合中兴努比亚推出豆包手机助手技术预览版，搭载于工程样机努比亚 M153，面向行业人士开放体验。&lt;/p&gt;
+&lt;p&gt;这是豆包屏幕自动化能力首次面向公众落地，但很快便暴露出与第三方应用的适配冲突。当时已有用户反馈，微信、淘宝、闲鱼、大麦等多款主流应用出现登录异常、频繁弹出人机验证、闪退等现象；在竞技类游戏场景中，相关自动化能力也触发了应用方的风控判定。&lt;/p&gt;
+&lt;p&gt;针对这一情况，豆包官方当时即发布功能调整公告，主动限制了 AI 在刷分激励类、金融类应用以及竞技游戏等场景下的自动操作。矛盾被暂时压下，但并没有形成统一的解决标准。&lt;/p&gt;
+&lt;p&gt;2026 年 9 月 14 日，豆包手机助手消费者版本正式发布，同步推出《屏幕自动化操作声明协议》（SAEP），启动为期 30 天的公示期。两天后，搭载豆包手机助手消费者版的努比亚 NaviX Ultra 正式发售，标志着这项系统级 AI 自动化能力正式面向普通消费者开放。&lt;/p&gt;
+&lt;p&gt;然而正式落地后不到两周，冲突再次集中出现。&lt;/p&gt;
+&lt;p&gt;9 月 24 日起，大量用户反馈在 NaviX Ultra 上登录《王者荣耀》时触发「设备环境异常」判定，账号被强制下线甚至短时封禁，理由是「使用第三方辅助工具」。&lt;/p&gt;
+&lt;p&gt;豆包官方次日发布说明致歉，称经核查助手未对游戏系统进行任何操作，不存在违规模拟行为，团队正与腾讯沟通。后续媒体实测显示，即便未开启 GUI 自动化功能，该机型运行游戏仍会触发风控。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a2/03/a2033ac31abdf189919ceb260e08db53.png" /&gt;&lt;/p&gt;
+&lt;p&gt;腾讯系拒绝名单｜图片来源：豆包手机助手官方网站&lt;/p&gt;
+&lt;p&gt;这一事件典型呈现了此前</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 10:15:21 +0800</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>腾讯盯上了字节的摇钱树</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372435</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr"/>
+      <c r="F632" s="2" t="inlineStr"/>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：Chatgpt 生成&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;短剧正在成为互联网行业最吸金的时长黑洞。&lt;/p&gt;
+&lt;p&gt;QuestMobile 数据显示，2026 年 7 月，红果短剧日活达到 1.68 亿，超过腾讯视频、爱奇艺、优酷、芒果 TV 四大长视频平台的日活总和，用户人均单日刷剧时长达到 125 分钟，甚至一度超过抖音主站同期的人均使用时长。&lt;/p&gt;
+&lt;p&gt;而据第三方监测数据，到 10 月其日活规模已攀升至 2.2 亿上下，半年时间净增超 5000 万，增速依然没有放缓的迹象。&lt;/p&gt;
+&lt;p&gt;从三年前上线，到如今字节跳动旗下实打实的现金牛，红果短剧把免费广告（IAA）短剧的商业模式彻底跑通，也成了字节拉动用户时长的核心引擎。&lt;/p&gt;
+&lt;p&gt;腾讯不是没做短剧，但在红果一路狂奔的同时，前者的短剧布局却始终慢了半拍。此前在 2021 年，腾讯就上线了十分剧场主打精品横屏短剧，走会员分账路线；微信生态里也先后试过火星短剧社、官方短剧小程序，但始终是小范围试水，没有形成规模化的产品矩阵。&lt;/p&gt;
+&lt;p&gt;直到今年 9 月底，由原微信官方短剧小程序升级更名而来的绿泡泡短剧开启大规模推广，腾讯才终于拿出了一款能和红果站在同一赛道对标的产品。&lt;/p&gt;
+&lt;p&gt;但比起主动进攻，这更像是会腾讯瞄准字节基本盘的一次防守反击&amp;mdash;&amp;mdash;作为赛道后来者，绿泡泡目前仍处于早期爬坡阶段，距离撼动红果的行业地位差距甚远。&lt;/p&gt;
+&lt;h1&gt;一、红果，字节跑出的新摇钱树&lt;/h1&gt;
+&lt;p&gt;在字节的内容版图里，红果短剧的增长速度和变现效率，都超出了行业预期。&lt;/p&gt;
+&lt;p&gt;三年时间，红果短剧的日活从 0 冲到 1.68 亿，更关键的是用户粘性：人均每天 125 分钟的使用时长，意味着核心用户每天要花两个多小时在上面刷剧。这个时长量级，已经足以撑起一个独立的内容生态和商业化体系。&lt;/p&gt;
+&lt;p&gt;支撑起这个体量的，是一套跑通的完整链路：抖音提供流量入口，用户刷到短剧片段可以直接跳转红果看全集；番茄小说提供 IP 储备，大量爆款短剧改编自站内热门网文；红果负责承接长时长观看，通过片头、片中广告完成变现，再分账给上游制作方。&lt;/p&gt;
+&lt;p&gt;整条链路全部在字节生态内完成，几乎没有外溢。据第三方统计数据，今年 8 月，在中国月度使用时长排名前 50 的应用中，字节系产品的总时长份额达到 41.8%，创下历史新高，其中很大一部分增量就来自红果短剧。&lt;/p&gt;
+&lt;p&gt;相比长视频平台高昂的内容成本和缓慢的会员增长，免费短剧的边际成本更低，变现效率更高，已经成了字节当下最稳健的现金牛业务之一。&lt;/p&gt;
+&lt;p&gt;更可能让腾讯感到压力的，是红果对用户的渗透深度。&lt;/p&gt;
+&lt;p&gt;QuestMobile 2026 年 2 月数据显示，红果 50 岁以上用户就已超过 4000 万，覆盖了大量长视频触达不到的下沉市场和银发用户。这些用户之前的线上时间很大一部分属于微信，现在正在被红果大量抢走。&lt;/p&gt;
+&lt;h1&gt;二、绿泡泡，腾讯用微信底盘打错位战&lt;/h1&gt;
+&lt;p&gt;腾讯选择在这个时间点把绿泡泡短剧推到台前，本质上是一场防守反击。&lt;/p&gt;
+&lt;p&gt;此前腾讯的短剧布局，始终和红果不在同一个赛道。十分剧场走精品化路线，服务愿意为内容付费的长视频用户；微信里零散的第三方短剧小程序，更像是平台提供基础设施，流量分散，没有统一的品牌和运营体系。&lt;/p&gt;
+&lt;p&gt;面对红果在免费赛道的狂飙突进，腾讯一直缺少一个对应的抓手。&lt;/p&gt;
+&lt;p&gt;绿泡泡的出现，就是要补上这块短板。&lt;/p&gt;
+&lt;p&gt;和红果做独立 App 的思路不同，绿泡泡从一开始就长在微信生态里：不用下载，搜索就能用；支持悬浮小窗播放，看剧时收到微信消息不用退出，缩小就能边看边回；视频号可以直接挂载跳转，刷到片段一键进入小程序看全集。&lt;/p&gt;
+&lt;p&gt;它最核心的差异，是把微信的社交关系链融入了内容分发逻辑。&lt;/p&gt;
+&lt;p&gt;首页专门设置了「朋友在看」栏目和地区热门榜，好友的观看行为会直接影响推荐结果，好剧可以通过群聊、朋友圈自发裂变传播。这套逻辑和红果纯算法推荐、付费买量的打法完全不同&amp;mdash;&amp;mdash; 红果靠投放拉新，绿泡泡靠社交裂变。&lt;/p&gt;
+&lt;p&gt;为了撬动上游内容方，腾讯还直接出了一套分账规则。9 月 23 日，微信开放平台联合微信营销推出 2026 年第四季度「微短剧」小程序激励活动，绿泡泡没有沿用行业通用的播放量考核，而是把核心门槛定为单用户有效观看时长不低于 10 分钟，优质新剧最高可以拿到 100% 收入激励。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 16:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>An Nvidia insider-turned-VC on why robotics hasn’t hit its ChatGPT moment, yet</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/video/a-nvidia-insider-turned-vc-on-why-robotics-hasnt-hit-its-chatgpt-moment-yet/</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr"/>
+      <c r="F633" s="2" t="inlineStr"/>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>Amulya Vishwanath, who spent seven years leading product marketing for NVIDIA’s robotics platforms, says robotics is currently in its “Lego era,” with the basic building blocks like actuators, robotic hands, software, and safety standards still being&amp;#160;rebuilt.&amp;#160; This view runs counter to those who believe that robotics, powered by a general foundation model,&amp;#160;is about to have [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 16:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>Physical AI is more than robots, says the Nvidia veteran now investing in it</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/podcast/physical-ai-is-more-than-robots-says-the-nvidia-veteran-now-investing-in-it/</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr"/>
+      <c r="F634" s="2" t="inlineStr"/>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>Amulya Vishwanath, who spent seven years leading product marketing for NVIDIA’s robotics platforms, says robotics is currently in its “Lego era,” with the basic building blocks like actuators, robotic hands, software, and safety standards still being&amp;#160;rebuilt.&amp;#160; This view runs counter to those who believe that robotics, powered by a general foundation model,&amp;#160;is about to have [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H634"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26366,6 +26366,258 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 12:54:54 +0000</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>清华特奖得主AI创业再+1：GeoPT一作入局物理世界模型</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503880.html</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr"/>
+      <c r="F635" s="2" t="inlineStr"/>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>从搭载物理建模能力的世界模型切入</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:12:01 +0000</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>从“看懂世界”到“预演下一步”：世界模型与 VLA，如何让机器人拥有真正的“具身大脑”？</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503865.html</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr"/>
+      <c r="F636" s="2" t="inlineStr"/>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>VLA解决“能干”，世界模型解决“想清楚再干”</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 08:00:31 +0000</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>霸榜三大基准！优必选 Thinker-WM：多模态统一表征，单模型实现六大能力</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503843.html</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr"/>
+      <c r="F637" s="2" t="inlineStr"/>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>优必选 Thinker-WM在三大公认具身世界模型基准评测中全部拿下第一名</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 16 Oct 2026 06:17:53 +0000</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>超1亿元融资砸向四川具身科技！要把「情绪价值」卖进千家万户</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/503782.html</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr"/>
+      <c r="F638" s="2" t="inlineStr"/>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>9.8万元起售，冲刺万台量产</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 18 Oct 2026 08:39:02 +0800</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek 新模型上线，价格更低能力更强；传华为将推新品牌「星芒」主打性价比；天文学家发现第一颗绿色恒星｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372512</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr"/>
+      <c r="F639" s="2" t="inlineStr"/>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7a/a8/7aa8807777270654af55a6c78559f6b5.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;DeepSeek V4.1 Flash 新版本上线：许愿式编程一键成真&lt;/h1&gt;
+&lt;p&gt;10 月 17 日，DeepSeek V4.1 Flash 更新至 V4.1-Flash-1017 版本，官方网页端、APP 与 API 模型已同步变更为新模型。相比上一版本的 DeepSeek V4.1 Flash，新模型在各方面的基准测试中取得了长足的提升。&lt;/p&gt;
+&lt;p&gt;在提升性能的同时，模型的任务运行时间与输出长度还缩短了，让用户能够以更低成本、更快速度完成任务，在多个 Harness 下达到了新的性能-费用帕累托最优。&lt;/p&gt;
+&lt;p&gt;特别地，此次优化着重针对 DeepSeek Harness、腾讯 CodeBuddy、WorkBuddy 等平台框架进行了优化。（消息来源：DeepSeek）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a2/90/a2903ac9deb2c741750cd870abdfa37c.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7a/ee/7aee214fe40d62c647945597dfb30363.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;马斯克盯上了砍价生意 号称一年为全球省下 6 万亿美元&lt;/h1&gt;
+&lt;p&gt;10 月 17 日消息，特斯拉创始人马斯克在社交平台 X 发文称，团队正投入大量资源，开发面向商业场景的专用议价机器人（Hagglebot）。&lt;/p&gt;
+&lt;p&gt;Hagglebot 是依托 Grok 打造的软件 AI Bot，主打企业议价场景，和普通对话 AI 定位完全不同。目前马斯克没有放出太多细节，这套 AI 具体怎么议价、支持哪些交易场景、何时上线、怎么收费，都还没有官宣。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;马斯克表示，「我们认为该产品能够将企业成本效率提升 5% 乃至更高。如果放到全球 GDP 的维度测算，每年可节省的成本规模最高可达 6 万亿美元。」&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;他还进一步指出，凡是使用 Grok 的企业，都能获得立即可量化的竞争优势。（消息来源：快科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/59/bd/59bd209cedcf20117aaab1998c0ba507.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&amp;nbsp;&lt;/h1&gt;
+&lt;h1&gt;要么不用工具，要么交出内容？Meta 新条款引争议&lt;/h1&gt;
+&lt;p&gt;Gizmodo 报道，社交巨头 Meta 更新 Meta Business Suite 商业账号服务条款，新规将于 10 月 30 日正式落地。&lt;/p&gt;
+&lt;p&gt;按照新协议，企业开通 Facebook、Instagram 商业账号，就自动授予 Meta 抓取自家网站公开内容的权利，且没有设置独立关闭退出通道。即便企业网站通过 robots.txt 规则屏蔽网络爬虫，也无法阻止本次基于商业账号协议授权下的内容采集。&lt;/p&gt;
+&lt;p&gt;过去 Meta 若要使用出版商、企业网页素材训练 AI，需要单独签署版权授权协议。而本次条款改动，把内容授权绑定商业工具使用资格。不少法律从业者表示，大量中小企业在开通商业推广账号时，并不会仔细阅读冗长的服务协议，在不知情的状态下完成内容授权。&lt;/p&gt;
+&lt;p&gt;Meta 解释，抓取网页内容旨在提升 Meta AI 的回答准确度，企业既然使用平台商业服务，就应当开放网页内容使用权。但出版商与中小企业行业协会对此提出批评，认为新规等于逼迫企业二选一：要么放弃 Meta 商业营销工具，要么交出网站内容用于 AI 训练，绕过正常版权协商流程，损害内容方权益。（消息来源：环球科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;英伟达黄仁勋称 AI 现在不是泡沫，安全不应成为减速理由&lt;/h1&gt;
+&lt;p&gt;10 月 17 日消息，英国当地时间 10 月 14 日在伦敦接受彭博记者 Emily Chang 采访时，英伟达首席执行官黄仁勋表示当前 AI 需求远大于供</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 10:46:16 +0800</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>1 分钟售罄、发货排到明年，iPhone Duo 卖爆背后的真相</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372509</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr"/>
+      <c r="F640" s="2" t="inlineStr"/>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;人们已经很多年没见过，苹果的新品被这样抢了。&lt;/p&gt;
+&lt;p&gt;10 月 16 日晚 8 点，苹果首款折叠屏 iPhone Duo 开启预购。社交媒体上流传的说法是，&lt;strong&gt;开售 1 分钟，全型号库存就空了，京东、天猫页面相继显示售罄&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;大约 40 分钟后，&lt;strong&gt;苹果官网的预计送达时间已经跳到了 2027 年 1 月底&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;几个小时后，大洋彼岸的美国东部时间上午 8 点，同样的剧情再演一遍。分析师 Max Weinbach 在 X 上说，纽约及周边、康涅狄格州的门店大约 3 分钟就被抢光。半小时内，美国所有配置的交付日期都变成了 1 月 25 日。eBay 上，一台 2TB 版的预购机挂出了 5000 美元的成交价，比官方价格高出 1800 美元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这不是中国市场独有的狂热，而是一场苹果新品全球同步的抢购。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;iPhone Duo 卖爆的背后，真的是产品太牛，创新性十足，还是产能不足逼出的热卖？&lt;/p&gt;
+&lt;p&gt;「秒罄」这两个字，其实藏着两个完全不同的故事。一个关于需求，一个关于产能。&lt;/p&gt;
+&lt;h1&gt;太整齐的交付日期&lt;/h1&gt;
+&lt;p&gt;先看一个容易被忽略的细节。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;iPhone Duo 这次在美国、中国、英国、德国、日本、印度等约 70 个国家和地区同步开启预购&lt;/strong&gt;。开售之后，美国和英国最早的交付日期都是 1 月 25 日，国行显示的是 1 月底。&lt;/p&gt;
+&lt;p&gt;市场规模、消费习惯、竞争格局完全不同的几个国家，交付日期却几乎对齐。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这更像是苹果在全球范围内按配额统一分货的结果，而不是各地需求恰好一样旺。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;换句话说，首批能放出来的货就那么多，分到每个市场的量都不大，哪里都是几分钟被抢完。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/72/1c/721c1ab59c8487eeed5282b6c1600bc3.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;这一点从黄牛市场也能看出来。&lt;strong&gt;国内顶配机型的加价被报到 7000 元以上，甚至有说法称破万&lt;/strong&gt;；美国 1TB 和 2TB 两个版本的转售价都比官方价格高出约 1800 美元。以 2TB 版来算，美国的溢价幅度大约是五成多，和国内的情况相差无几。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;两边的「热度」高度相似，恰恰说明真正决定热度上限的，是供给。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1&gt;让人遗憾的产能&lt;/h1&gt;
+&lt;p&gt;如果把时间拨回到一个多月前，iPhone Duo 的产能问题其实早有端倪。&lt;/p&gt;
+&lt;p&gt;日经亚洲 8 月底的报道称，&lt;strong&gt;苹果当时每天只能生产「几百台」iPhone Duo&lt;/strong&gt;，远远低于一款常规 iPhone 新品的爬坡节奏。9 月中旬，界面新闻援引供应链消息称，富士康的组装良率只比 60% 高一点，要提升到成熟水平，可能还需要半年到一年。&lt;/p&gt;
+&lt;p&gt;问题的核心，在那枚特殊设计的铰链上。&lt;/p&gt;
+&lt;p&gt;供应链消息显示，iPhone Duo 的铰链由 100 多个零件组成，外盖还用到了 3D 打印工艺。原本的主力供应商安费诺产能没能达到苹果的预期，苹果随后加大了台湾新日兴的供货比例。屏幕这一侧也不轻松，三星显示的折叠 OLED 面板良率同样偏低，部分原因是苹果在最后阶段改了设计。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9d/14/9d14202f46d01878ee5fc73fb085a6bf.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;分析师 Jeff Pu 因此把 iPhone Duo 今年的出货预测从 700 万台下调到 600 万台。他给出的理由很直接，是铰链拖了后腿，而不是需求不足。&lt;/p&gt;
+&lt;p&gt;需要说明的是，60% 良率不等于卖出去的手机有四成是坏的，它意味着有相当比例的机器第一次组装没有通过苹果的品控，需要返工或报废，生产因此变得又慢又贵。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;说白了，苹果选择了「宁可少卖，也不能卖坏」。对第一代折叠屏来说，这几乎是唯一正确的选择。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;当然，这些消息大多来自匿名的供应链渠道，苹果并没有正式确认过。&lt;/p&gt;
+&lt;h1&gt;想买的人，也是真的多&lt;/h1&gt;
+&lt;p&gt;如果只是货少</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26618,6 +26618,108 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 18 Oct 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>“AI+终端”时代的萌芽：大模型在终端领域的探索和量产落地｜QCon上海</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/qZPH971CbfHkaCfgG0cb?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr"/>
+      <c r="F641" s="2" t="inlineStr"/>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/qZPH971CbfHkaCfgG0cb?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 09:18:11 +0800</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 三个神秘模型曝光；DeepSeek 开放搜索与网页抓取 API；智界将获独立造车资格，公司计划上市 ｜ 极客早知道</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372514</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr"/>
+      <c r="F642" s="2" t="inlineStr"/>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f6/57/f657edd60c2d62f5ce41053cb0013b6d.png" /&gt;&lt;/p&gt;&lt;h1&gt;OpenAI 三个神秘模型曝光&lt;/h1&gt;&lt;p&gt;10 月 18 日，有开发者发现，OpenAI 的 API 模型列表中突然出现了三个陌生名字：&lt;/p&gt;&lt;p&gt;aurora-red-alpha、aurora-green-alpha、aurora-blue-alpha。三个模型都以 Aurora（极光）命名，分别对应红、绿、蓝三种颜色。但相关条目很快便从模型列表中消失。&lt;/p&gt;&lt;p&gt;此次发现来自第三方维护的 OpenAI 模型列表镜像，并非官方公告。因此，这些模型究竟是什么、是否会正式发布，目前都还是未知数。&lt;/p&gt;&lt;p&gt;有网友推测，这些模型极有可能是 GPT-6 Astra 后续版本的内部检查点，专门对标 Fable 5.5 的强项，创意编码、长程 agent、视觉 / 3D。也有网友推测：三个模型对应 OpenAI 三个图像模型。（消息来源：机器之心）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2f/d4/2fd453b6b60505ba1edefd8fcbe9dfd0.png" /&gt;&lt;/p&gt;&lt;h1&gt;Anthropic 与法律专家讨论 AI Agent 谈判规则，未来可替用户砍价、处理纠纷&lt;/h1&gt;&lt;p&gt;据《金融时报》最新报道，Anthropic 正在与律师事务所及法律专家合作，研究 AI Agent 代表用户进行谈判时应遵循的行为规范。&lt;/p&gt;&lt;p&gt;随着 Agent 逐渐能够独立执行任务，未来可能出现大量 AI 与 AI 之间的商业交互。&lt;/p&gt;&lt;p&gt;例如，消费者让自己的 AI 助手与商家的 AI Agent 讨价还价，员工让 AI 代理参与薪资谈判，或者用户委托 AI 处理服务纠纷。&lt;/p&gt;&lt;p&gt;Anthropic 希望明确几个问题：AI 应该在多大程度上争取用户利益？什么时候需要征求用户确认？面对其他 AI Agent 时，是否应该默认对方存在欺骗或操纵意图？&lt;/p&gt;&lt;p&gt;公司还讨论过一种授权方式：让用户通过签署文件，明确 AI 的代理权限、目标和行为边界。&lt;/p&gt;&lt;p&gt;目前，这仍属于规则研究和产品探索，尚未推出面向公众的自动谈判服务。（消息来源：金融时报）&lt;/p&gt;&lt;h1&gt;DeepSeek 正式开放搜索与网页抓取 API，每千次调用收费 5 元&lt;/h1&gt;&lt;p&gt;DeepSeek 正式开放 Search 和 Fetch 两项 API，向开发者提供基于自研搜索引擎的网页搜索及内容抓取能力。&lt;/p&gt;&lt;p&gt;其中，Search API 可以根据关键词返回结构化搜索结果，包括网页标题、链接、摘要、发布日期等信息；Fetch API 则可以抓取指定网页，将正文转换为 Markdown 文本。&lt;/p&gt;&lt;p&gt;两项 API 均采用按成功请求次数计费的方式，价格为每千次 5 元。失败、超时或未返回有效结果的请求不收费。&lt;/p&gt;&lt;p&gt;DeepSeek 还为接入其 API 的 Claude Code、Codex 和 DeepSeek Harness 提供了阶段性的免费搜索调用安排。&lt;/p&gt;&lt;p&gt;DeepSeek 表示，其自研搜索引擎目前每天在全球范围内处理数亿次请求。（消息来源：DeepSeek 官方公告）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/74/be/74becb645f30c4d271010c7ac166891b.png" /&gt;&lt;/p&gt;&lt;h1&gt;Anthropic 拟设立「公共利益」基金，初始注入 5% 股份&lt;/h1&gt;&lt;p&gt;当地时间 10 月 18 日，Anthropic 宣布，在获得股东批准的前提下，&lt;strong&gt;公司计划将 5% 的股份划入新设立的公共利益基金&lt;/strong&gt;（Public Benefit Fund）；且随着这家人工智能巨头的估值增长，该基金持有的股份比例未来还可能进一步提升。&lt;/p&gt;&lt;p&gt;该拟议的基金将作为一家全资拥有的有限责任公司设立，经董事会裁量，公司估值每较尚未披露的基准上涨 50%，基金就会获得 Anthropic 额外 2% 的股份。&lt;/p&gt;&lt;p&gt;Anthropic 公共利益基金所支持的项目将涵盖非营利捐赠、向特定群体发放直接资助，以及应对人工智能</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18T14:28:10-04:00</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>A woman was arrested in Philly for blocking a delivery robot</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1013541/a-woman-was-arrested-in-philly-for-blocking-a-delivery-robot</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr"/>
+      <c r="F643" s="2" t="inlineStr"/>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>Carolyn Marvin was arrested and charged with disorderly conduct after blocking the path of an Uber delivery robot and refusing to get out of the way. Marvin told Philadelphia's ABC13 "I know they're taking the jobs of human delivery workers and so, I have been protesting them whenever I saw them by standing in front [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H643"/>
+  <dimension ref="A1:H653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26720,6 +26720,451 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>The Robot I Didn’t Expect to Build</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/agility-robotics-digit-5-redesign</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr"/>
+      <c r="F644" s="2" t="inlineStr"/>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;&lt;a href="https://www.agilityrobotics.com/" rel="noopener noreferrer" target="_blank"&gt;&lt;span&gt;Agility Robotics&lt;/span&gt;&lt;/a&gt;, the &lt;/strong&gt;company I cofounded out of &lt;a href="https://mime.engineering.oregonstate.edu/research/drl/" target="_blank"&gt;my robotics lab at Oregon State University&lt;/a&gt; in 2015, has just …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 10:27:39 +0000</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>2026物理AI与世界模型大会医疗健康世界模型分会场在南京举行</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504266.html</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr"/>
+      <c r="F645" s="2" t="inlineStr"/>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>2026年10月19日下午，医疗健康世界模型分会场在南京国际博览中心钟山厅举行</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 10:15:19 +0000</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>全栈自研！国产高端互连芯片，稳了!</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504225.html</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr"/>
+      <c r="F646" s="2" t="inlineStr"/>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>六年蛰伏出货80万颗</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 08:12:45 +0000</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>赛场交卷 未来已来——首届全球具身智能应用创新挑战赛暨2026中国机器人大赛闭幕</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504199.html</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr"/>
+      <c r="F647" s="2" t="inlineStr"/>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>10月18日下午，首届全球具身智能应用创新挑战赛暨2026中国机器人大赛落下帷幕。</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 09:34:14 +0800</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>1 分钟售罄、发货排到明年，iPhone Duo 卖爆背后的真相</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372583</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr"/>
+      <c r="F648" s="2" t="inlineStr"/>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;人们已经很多年没见过，苹果的新品被这样抢了。&lt;/p&gt;
+&lt;p&gt;10 月 16 日晚 8 点，苹果首款折叠屏 iPhone Duo 开启预购。社交媒体上流传的说法是，&lt;strong&gt;开售 1 分钟，全型号库存就空了，京东、天猫页面相继显示售罄&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;大约 40 分钟后，&lt;strong&gt;苹果官网的预计送达时间已经跳到了 2027 年 1 月底&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;几个小时后，大洋彼岸的美国东部时间上午 8 点，同样的剧情再演一遍。分析师 Max Weinbach 在 X 上说，纽约及周边、康涅狄格州的门店大约 3 分钟就被抢光。半小时内，美国所有配置的交付日期都变成了 1 月 25 日。eBay 上，一台 2TB 版的预购机挂出了 5000 美元的成交价，比官方价格高出 1800 美元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这不是中国市场独有的狂热，而是一场苹果新品全球同步的抢购。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;iPhone Duo 卖爆的背后，真的是产品太牛，创新性十足，还是产能不足逼出的热卖？&lt;/p&gt;
+&lt;p&gt;「秒罄」这两个字，其实藏着两个完全不同的故事。一个关于需求，一个关于产能。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;太整齐的交付日期&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;先看一个容易被忽略的细节。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;iPhone Duo 这次在美国、中国、英国、德国、日本、印度等约 70 个国家和地区同步开启预购&lt;/strong&gt;。开售之后，美国和英国最早的交付日期都是 1 月 25 日，国行显示的是 1 月底。&lt;/p&gt;
+&lt;p&gt;市场规模、消费习惯、竞争格局完全不同的几个国家，交付日期却几乎对齐。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这更像是苹果在全球范围内按配额统一分货的结果，而不是各地需求恰好一样旺。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;换句话说，首批能放出来的货就那么多，分到每个市场的量都不大，哪里都是几分钟被抢完。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9f/81/9f81e7b8b3660cabf8bf4e266b1f5b70.png" /&gt;&lt;/p&gt;
+&lt;p&gt;这一点从黄牛市场也能看出来。&lt;strong&gt;国内顶配机型的加价被报到 7000 元以上，甚至有说法称破万&lt;/strong&gt;；美国 1TB 和 2TB 两个版本的转售价都比官方价格高出约 1800 美元。以 2TB 版来算，美国的溢价幅度大约是五成多，和国内的情况相差无几。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;两边的「热度」高度相似，恰恰说明真正决定热度上限的，是供给。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;让人遗憾的产能&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;如果把时间拨回到一个多月前，iPhone Duo 的产能问题其实早有端倪。&lt;/p&gt;
+&lt;p&gt;日经亚洲 8 月底的报道称，&lt;strong&gt;苹果当时每天只能生产「几百台」iPhone Duo&lt;/strong&gt;，远远低于一款常规 iPhone 新品的爬坡节奏。9 月中旬，界面新闻援引供应链消息称，富士康的组装良率只比 60% 高一点，要提升到成熟水平，可能还需要半年到一年。&lt;/p&gt;
+&lt;p&gt;问题的核心，在那枚特殊设计的铰链上。&lt;/p&gt;
+&lt;p&gt;供应链消息显示，iPhone Duo 的铰链由 100 多个零件组成，外盖还用到了 3D 打印工艺。原本的主力供应商安费诺产能没能达到苹果的预期，苹果随后加大了台湾新日兴的供货比例。屏幕这一侧也不轻松，三星显示的折叠 OLED 面板良率同样偏低，部分原因是苹果在最后阶段改了设计。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ab/a9/aba96bcd85608274650b2293a70fb149.png" /&gt;&lt;/p&gt;
+&lt;p&gt;分析师 Jeff Pu 因此把 iPhone Duo 今年的出货预测从 700 万台下调到 600 万台。他给出的理由很直接，是铰链拖了后腿，而不是需求不足。&lt;/p&gt;
+&lt;p</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 09:01:44 +0800</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek 新模型登顶开源模型榜首；国内 55% 算力用于视频和短剧？豆包发言人辟谣；微信发起公众号小说改编微短剧激励｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372568</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr"/>
+      <c r="F649" s="2" t="inlineStr"/>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/87/54/8754171604dca5929a9c6d14dfdd3bcc.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;DeepSeek 新模型登顶 Code Arena WebDev 开源模型榜首&lt;/h2&gt;
+&lt;p&gt;10 月 19 日，AI 模型评测平台 Arena 宣布，DeepSeek-V4.1-Flash-1017（Max）超过 Kimi K3（Max），成为 Code Arena: WebDev 榜单排名最高的开源模型。&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;截至目前，DeepSeek-V4.1-Flash-1017 在该榜单上得分为 1670 分，超过了Kimi&amp;nbsp;K3（Max）、Mimo-V2.6 Flash等开源模型，也超过了Muse Spark 1.3（Max）、Claude Opus 5（High）、Grok 4.7（xHigh）等闭源模型，仅落后 GPT-6 Sol（Max）12 分。&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9f/c4/9fc4049b225e3508837b296d8b3fc31d.png" /&gt;&lt;/p&gt;
+&lt;p&gt;该模型于 10 月 17 日推出，在软件工程能力 DeepSWE v1.1 测试中，其得分超GPT-6 Astra、GPT-6.1 Sol、Claude Opus 5等模型，单项任务平均费用较上一版本下降约六成。DeepSeek 称其模型支持「许愿式编程」，可一键生成游戏、3D 建模等。网友实测该模型生成速度比 GPT-6.1 超快模式还要快。&lt;/p&gt;
+&lt;p&gt;价格方面，DeepSeek-V4.1-Flash-1017 在高峰时段的每百万 Token 输入（缓存未命中）价格为 2 元，输出价格为 8 元；空闲时段的输入（缓存未命中）价格为 1 元，输出价格为 4 元。若输入缓存命中，每百万 Token 输入价格在高峰时段为 0.04 元，空闲时段为 0.02 元，综合成本约为 Kimi&amp;nbsp;K3 的 1/10。&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;Arena 发布的对比图显示，DeepSeek-V4.1-Flash-1017 进入了 Code Arena 的「帕累托前沿」，即图中的绿色折线，这说明目前没有其他模型能同时做到比它更便宜、且得分更高。 （来源：新智元）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/43/df/43df425426fbd824cfe05c98775f3aa8.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;特斯拉声明没有速成车，陶琳称安全稳定可靠、让人安心是最大的豪华&lt;/h2&gt;
+&lt;p&gt;10 月 19 日消息，特斯拉官方发微博，称特斯拉没有「速成车」。特斯拉官方表示，特斯拉拥有完整的直营体系（覆盖买车、提车、用车、修车、换车），没有 4S 店，销售、交付、客服、技师全是自家人，大品牌 + 完整的直营体系正是消费者放心买、安心用的最大底气。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f0/6f/f06fe6358e55a007d7badc3b85941a6a.png" /&gt;&lt;/p&gt;
+&lt;p&gt;特斯拉公司副总裁陶琳随后转发该博文并表示，「安全稳定可靠，让人安心是最大的豪华。」&lt;/p&gt;
+&lt;p&gt;特斯拉此前宣布，2026 年第三季度，特斯拉全球生产了超 46.4 万辆电动车，交付了超 48.6 万辆（同比下降 2%）；储能产品装机量达 13.7 吉瓦时。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;&amp;nbsp;&lt;/h2&gt;
+&lt;h2&gt;iPhone 18 Pro 系列国内销量超 408 万，开售三周破 400 万&lt;/h2&gt;
+&lt;p&gt;10 月 19 日，博主 @RD 观测 公布苹果旗舰手机最新销量数据。截至 2026 年第 41 周，也就是 10 月 5 日至 10 月 11 日，iPhone 18 Pro 系列国内累计激活销量（Sell out）约为 408.09 万台。CNMO 科技注意到，该系列于 9 月 18 日正式开售，上市约三周时间累计销量已经突破 400 万台。&lt;/p&gt;
+&lt;p style="text</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 21:57:34 +0800</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>AI 里没有答案的问题，需要一场「深谈」</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372579</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr"/>
+      <c r="F650" s="2" t="inlineStr"/>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;去年，极客公园创新大会第一次办起「小场深谈」。场子都不大，百人左右围坐在一起。&lt;/p&gt;
+&lt;p&gt;有些瞬间仍然记忆犹新。&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;在「超级个体」专场，一位观众站起来。他刚从大厂跳槽到一家小厂，正用 AI 做自己的第一款产品。他向嘉宾说出自己的困惑：我还在打工，做公众号、视频号，早晚会被老板和同事刷到。这个冲突，怎么解？&lt;/li&gt;
+&lt;li&gt;在「硬控 AI」专场，有人直接向刚刚离职的小米 AI 眼镜负责人提问：如果给你两个亿，你会去做哪种 AI 眼镜？有人继续追问，你觉得豆包手机助手到底是真需求还是伪需求？&lt;/li&gt;
+&lt;li&gt;在「重塑关系」专场，一位精神科医生，问做陪伴机器人的嘉宾：你是希望它把人带回现实社会的交往，还是给这个家添一个新成员？&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;这些问题都不「大」，但都很真，带着一个人具体的处境，来自坐在你旁边的人。&lt;/p&gt;
+&lt;p&gt;有老朋友说，这让他们想起极客公园 17 年前的样子&amp;mdash;&amp;mdash;在借来的索尼探梦地下室里，一群人席地而坐。&lt;/p&gt;
+&lt;p&gt;如果你参加过去年的「小场深谈」，很可能还记得这种 Vibe。不是发布会式的提问，更像小场子里几个人围坐时，把一个人正在卡住、关心的事摊开来聊。&lt;/p&gt;
+&lt;p&gt;去年的「小场深谈」，共设置了 4 个主题专场，包涵 12 场深度访谈，数百位观众走进小场，165 个朋友甚至同时买了主舞台和「小场」的票：既听了主会场的趋势判断，也不舍得错过小场里「深谈」的收获。还有超过不少人专程为某一场深谈而来。&lt;/p&gt;
+&lt;p&gt;大会后的购票调研里，超过六成观众把「话题兴趣」排在首位，为了聊自己真正关心的问题而来。&lt;/p&gt;
+&lt;p&gt;这让我们确认：&lt;strong&gt;在信息过载的时代，有些问题，听 AI 解释一百遍，不如和「最有料的人」当面聊一次。嘉宾谈得尽兴，观众提出高质量的问题，一场访谈变成真正的共同创作。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/61/95/619535f0a6cb6a08e688799ecc21d059.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/23/99/2399a201adf4c3021481fd6f21172697.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/42/c8/42c86f6576e20c85b37590bfd0de2bf0.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fb/b8/fbb89fd671c6429976b432918952e26e.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-size: 14px;"&gt;IF 2026「小场深谈」现场部分精彩瞬间&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/42/19/421933610507c2f59b805e4b0116a531.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;今年 12 月 5 日、6 日，极客公园创新大会 2027 将在北京举行，主题是「Revaluation 价值，另有答案」。&lt;/strong&gt;AI 冲击下，价值的标准正在被重新评估。哪些旧经验值得重新审视，哪些新机会正在出现？&lt;/p&gt;
+&lt;p&gt;最迫切的那些议题，网络上、AI 里都没有现成答案。&lt;/p&gt;
+&lt;p&gt;因此，在主舞台之外，我们将继续保留「小场深谈」&amp;mdash;&amp;mdash;一个更小、更近、更主动的交流空间：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;更深：&lt;/strong&gt;围绕一个方向，几小时的深度访谈与探讨，把一个问题聊透；&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;更近：&lt;/strong&gt;实干派嘉宾与观众面对面，传递最坦诚的思考；&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;更主动：&lt;/strong&gt;你不只是听众，可以提问，成为这场讨论的共同创作者。&lt;/</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 18:10:03 +0800</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>客户为什么愿意为端侧 AI 买单？五位一线操盘手讲透了</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372578</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr"/>
+      <c r="F651" s="2" t="inlineStr"/>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;过去几年，AI 行业热衷于比参数、拼算力、讲融资。但模型一旦离开展台，客户的问题立刻具体起来：数据会不会泄露？设备能不能 24 小时运行？响应够不够快？噪声大不大？&lt;/p&gt;
+&lt;p&gt;这些问题，正把端侧 AI 推到产业舞台中央。&lt;/p&gt;
+&lt;p&gt;10 月 14 日，后摩智能在北京开了一场生态合作伙伴大会。期间，极客公园创始人 &amp;amp; CEO 张鹏主持了一场圆桌，五位来自不同赛道的人坐到了一起：麒麟软件副总经理 / 生态发展中心总经理姚翎、聊趣智能科技创始人兼 CEO 黄隽实、罗格数据 CTO 刘学鹏、寅谱计算 CMO 陈展凌、后摩智能 AI 系统总工程师陈仲铭。&lt;/p&gt;
+&lt;p&gt;他们分别来自操作系统、应用、数据工程、整机集成和芯片领域，讨论的是同一件事：端侧 AI 什么时候才能真正成为一门生意？&lt;/p&gt;
+&lt;p&gt;黄隽实讲了一个养老院里的故事。他们在上海落地了一套「数字家人」，陪老人聊天、提醒用药、辅助防诈骗。老人每天说了什么、身体状况如何，都是极其敏感的信息，不能随意上传云端；系统又要全天值守，设备还不能嗡嗡作响。到了这样的现场，隐私、算力、功耗和噪声都不再是技术指标，而是老人愿不愿意使用的前提。&lt;/p&gt;
+&lt;p&gt;在企业市场，答案同样清晰。刘学鹏认为，客户最关心的是私域化专属。「AI 未来会成为企业的数字专家或数字员工，这种触及核心业务的『员工』，必须招进公司内部，而不是变成外部的云端服务。」当模型开始读取发票、财报、订单和客户资料，数据边界就不再是附加选项，而是商业落地的前提。&lt;/p&gt;
+&lt;p&gt;对央企及关键岗位而言，安全门槛更加严格。姚翎表示，只要 AI 工具部署在互联网上，涉密数据就绝对不能碰。大模型甚至可能从不同时段上传的碎片信息中，拼凑出完整内容。「本地安全是重中之重，没有任何商量的余地，安全就是一切的前提。」&lt;/p&gt;
+&lt;p&gt;不过，需求成立，不等于生意成立。&lt;/p&gt;
+&lt;p&gt;陈展凌直言，客户未必在意省了多少 Token，他们更关心体验。首字出来要多久，机器是否安静，系统会不会卡顿，能否连续稳定运行，这些看似琐碎的问题，决定了产品是被长期使用，还是演示结束后被塞进柜子。&lt;/p&gt;
+&lt;p&gt;端侧 AI 的难点，不只是把大模型装进小设备，更是把通用能力变成可持续交付的专业服务。模型发布后能否及时适配，硬件成本能否降到客户可接受的范围，软件伙伴能否低门槛开发，都会影响商业化的速度。&lt;/p&gt;
+&lt;p&gt;而在底层，端侧算力还要面对算力、带宽与功耗的「不可能三角」。陈仲铭说，后摩要做的，就是不断把这三条边界向外推，并通过开放软件、接口和 API，让更多开发者参与进来。&lt;/p&gt;
+&lt;p&gt;在对话的最后，刘学鹏给了一个大胆的判断：在中国，AI 真正落地，一定是「端侧为主，云端为辅」。端侧是个人和企业的专属大脑，云端是负责知识流动的社会大脑。&lt;/p&gt;
+&lt;p&gt;这个判断对不对，日后会见分晓。但有一点已经很确定：AI 从「能聊天」走向「能干活」，就要吃进你最核心、最不愿示人的数据。到那时，算力放在哪里，就不再只是技术选型题，而是一道信任题。&lt;/p&gt;
+&lt;p&gt;大模型的上半场，人们争相让机器变聪明。下半场，比拼的是如何让智能走出云端，进入千行百业。最后的赢家，未必拥有最大的模型，但一定最早跨过那「最后一百米」。&lt;/p&gt;
+&lt;p&gt;以下是张鹏和姚翎、黄隽实、刘学鹏、陈展凌、陈仲铭的对话内容，部分有删减。&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f9/64/f9645516cac39324f08688f4bd2f5299.jpg" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;01 安全、私域、体验：端侧 AI 商业化的三道真实门槛&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;张鹏：去年大家都在说端侧 AI 元年，今年变成了「商业化元年」。在真实的落地过程中，客户掏钱时最在意的是什么？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;黄隽实：&lt;/strong&gt;落地过程中的挑战其实非常多。我们在上海一家养老机构落地了「数字家人」场景，主要为了缓解老年人因孤独引发的各类并发症。&lt;/p&gt;
+&lt;p&gt;在这个场景里，我们特别关注几个核心诉求：首先是安全隐私。家庭场景的私密信息极度敏感，特别是与公办或民营机构合作时，本地算力提供了最好的数据兜底方案。&lt;/p&gt;
+&lt;p&gt;其次是决策能力。系统需要 24 小时值守，提醒老人用药甚至防诈骗，这要求本地 AI 必须具备强大的持续计算能力。&lt;/p&gt;
+&lt;p&gt;最后是要非常安静。我们在使用后摩芯片时，能够达到这样一个需求。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;刘学鹏：&lt;/strong&gt;围绕企业和专业客户来看，大家</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 12:00:32 +0800</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>MemSilicon完成超 4 亿元 A 轮融资，宣布战略升级</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372545</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr"/>
+      <c r="F652" s="2" t="inlineStr"/>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;10 月 19 日，铭芯启睿（MemSilicon）宣布完成超 4 亿元 A 轮融资。本轮融资由博原资本领投，博世创投、创领资本、米哈游、中关村科学城公司、兆易创新等跟投，老股东复容投资、国开科创、恒裕资本、锦秋基金、顺禧基金、小米战投、中科创星持续加注。本轮融资将主要用于 RRAM 的产业化与商业化，以及新产品 LPU 的研发。&lt;/p&gt;
+&lt;p&gt;MemSilicon 同时宣布，&lt;strong&gt;前 Graphcore 总裁兼大中华区总经理卢涛加入团队，担任 CEO 和联合创始人。&lt;/strong&gt;公司战略全面升级：在继续推进阻变存储器（RRAM）产品化的基础上，启动面向大模型推理的第一代 LPU 研发，打造「满血模型、高速 Token、越级性价比」的新一代推理引擎。&lt;/p&gt;
+&lt;p&gt;随着 Agentic AI 时代的到来，AI 落地已经从问答，转向完成复杂、长程的任务，下一步竞争的关键指标，会从峰值算力转向任务完成效率。&lt;/p&gt;
+&lt;p&gt;一次任务包含多轮推理、工具调用和上下文复用，还可能启动多个 Agent 并行工作。客户需要的，不只是更多 Token，而是在保证质量的前提下，更快地解码和输出、更多任务能并行，并降低单次任务成本。&lt;/p&gt;
+&lt;p&gt;这要求推理系统从架构层面进行创新，同时优化计算、存储、互联和调度。因此，存算协同被视为核心破局路径之一。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f0/55/f0552d82f21862878932f9f9d53b573f.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;（图 1｜低延迟已是独立售卖的服务档位。数据来源：OpenAI）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/11/c5/11c5191e10b7fa6c038cdff217a8e7e6.png" /&gt;&lt;/p&gt;
+&lt;p&gt;（图 2｜高速解码决定 Agent 每一步走多快。在缓存能够有效保留的条件下，输入缓存命中率为 84.6%-99.5%，解码占 LLM 执行时间的 91.0%-98.6%。数据来源：arxiv2605.26297v2, Agentic AI Workload Characterization）&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;strong&gt;为什么是现在：大模型推理进入架构创新关键期&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;加入 MemSilicon 之前，卢涛已在芯片行业深耕 20 余年。&lt;/p&gt;
+&lt;p&gt;他历任曦智科技副总裁、Graphcore 总裁兼大中华区总经理、Cavium 中国区总经理，长期聚焦 AI 基础设施核心组件，覆盖 Arm 架构服务器 CPU、DPU、RDMA 网卡、数据中心交换芯片、大 SRAM 架构的 AI 处理器 IPU、基于 3D 堆叠 DRAM 的 NPU，及硅光芯片等多个领域，兼具技术、产品与市场的复合视角。&lt;/p&gt;
+&lt;p&gt;卢涛对 AI 时代的技术演进、产品逻辑、商业模式和客户需求有深刻洞察。他认为，大模型推理正在进入架构创新的关键期，单纯依赖单一维度的算力提升，已难以满足「低延迟、长上下文、高吞吐」的综合需求，存算协同是破局的核心路径之一。&lt;/p&gt;
+&lt;p&gt;卢涛表示：「MemSilicon 的定位很明确，不与 GPU 内卷，聚焦满血模型的高速 Token 体验，用越级性价比，服务高端推理市场。大模型推理提出了新课题，既要运行能力完整的模型，又要在可承受的成本下及时响应。这是当前通用 GPU 架构和纯 SRAM 架构的无人区。探索新大陆，就不能依靠单向度增加计算单元、存储密度、通信带宽的老地图，必须重新思考算什么、在哪里算、权重怎么存、数据怎么传的系统级问题。依托中国领先的存储战略纵深，结合我们在 AI 芯片产品定义与产业落地上的积累，MemSilicon 正同步推进 RRAM 产品化和下一代 LPU 研发，加速存算协同落地。」&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;MemSilicon 团队源自中国科学院刘明院士团队，在材料、器件、工艺、芯片设计等底层技术上，拥有二十多年的深耕积累。从材料与器件物理出发，团队的工作延伸至可靠性、工艺集成、IP 和芯片设计，再推进到流片验证与应用；除 RRAM 外，团队在三维集成、近存计算及混合存算一体架构方面也具备深厚科研积累。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;打破冯&amp;middot;诺依曼体系的枷锁、突破存储与数据搬运瓶颈，是 MemSilicon 不变的初心。&lt;/strong</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 12:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>Laplace Intelligence red-teams robots and self-driving cars before they hit the real world</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/19/laplace-intelligence-red-teams-robots-and-self-driving-cars-before-they-hit-the-real-world/</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr"/>
+      <c r="F653" s="2" t="inlineStr"/>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>University of Michigan spinout Laplace Intelligence uses AI agents and interactive simulation to stress-test robots and self-driving vehicles before deployment. The profitable startup is competing in Startup Battlefield at TechCrunch Disrupt, October 13-15 in San Francisco.</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H653"/>
+  <dimension ref="A1:H656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27165,6 +27165,126 @@
         </is>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 08:37:07 +0800</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>曝高通启动全球裁员；上线 40 天，Muse 下载量突破 1000 万次；ChatGPT 上线幻灯片工具</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372650</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr"/>
+      <c r="F654" s="2" t="inlineStr"/>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/fd/70/fd70ca324a3f10e86a9d0c331902bd24.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;DeepSeek 开源大规模云服务推理框架&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 20 日下午，DeepSeek 宣布，在此前开源一系列大模型、TileLang 编译工具及推理算子库的基础上，决定进一步将内部推理框架 DeepInfer 全面开源。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;DeepSeek 称，基于 DeepInfer，已实现 DeepSeek V4.1 Flash 高吞吐、低延迟的大规模推理服务。未来，DeepSeek 新模型的推理代码及后续优化也将在此持续更新。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;券有商分析师认为，开源模型与 Agent 工具链的持续完善，有望降低应用开发成本，推动 AICoding 向游戏开发、3D 内容制作、企业软件及自动化工作流等场景扩展，具备开发者入口和应用生态的平台有望优先受益。（来源：证券时报）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/d3/66/d366e35d23be3efe0ebe8f4854e0a581.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;上线 40 天，Muse 下载量突破 1000 万&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;市场情报机构 Sensor Tower 的最新数据显示，Meta 的人工智能助手 Muse 自 9 月推出以来，累计下载量达 1090 万次，其中美国地区下载量为 1020 万次。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;迄今为止仅有另外 11 款应用达成过这一上线后的里程碑，上一款实现该成绩的正是 Meta 的 Threads，时间为 2023 年 7 月。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;另据数据显示，Muse 的用户留存表现优于 ChatGPT、Claude、Grok 等 AI 竞品。（来源：IT之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;华为引望、宁德时代合作换电车型拟 2027 年上市&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 20 日，媒体报道称华为引望与宁德时代、时代电服合作正推进首批车型的开发，涉及五款新车，计划 2027 年上市。有报道表示，首款采用巧克力换电的车型为东风与华为合作的奕境品牌旗下产品。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;引望成立于 2024 年，承接华为原智能汽车解决方案业务，向车企提供智能驾驶、智能座舱、车控等系统及部件。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而宁德时代正在通过技术合作、股权投资等方式扩大换电业务规模。赛豆科技旗下 AIVA 品牌首款量产车 AIVA ME7 将采用换电模式，宁德时代提供电池技术及充换电体系支持，具体方案还在规划中。（来源：晚点 Auto、财联社）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;曝高通将启动全球裁员&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据路透社报道，高通 CEO 克里斯蒂亚诺&amp;middot;安蒙近期在一份内部备忘录中告知员工，公司将在年度员工评估后，开展以绩效为重点的全球裁员，相关通知将于 11 月开始发出。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;安蒙表示，此举旨在建立更强的绩效文化，并解决公司持续未能达到预期的情况。备忘录未披露</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 21:25:22 +0000</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s cloud partnerships are getting messy</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/20/anthropics-cloud-partnerships-are-getting-messy/</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr"/>
+      <c r="F655" s="2" t="inlineStr"/>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic is reportedly struggling to secure enough compute from cloud providers that increasingly view it as a competitor, even as its infrastructure spending balloons ahead of a planned November IPO.</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>Eka is worth $1.45B thanks to a physical AI model that has experts raving</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/20/eka-is-worth-1-45-billion-thanks-to-a-physical-ai-model-that-has-experts-raving/</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr"/>
+      <c r="F656" s="2" t="inlineStr"/>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>Eka Robotics may be the first robotic arm that is actually good at picking up a wide range of objects, and it is so smooth and human-like, it is wowing the industry.</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H656"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27285,6 +27285,233 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 01:15:23 +0000</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>采集、标定都做了，你的数据真能训练人形机器人吗？北航×通义 EgoAlign 给出真机验证</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14058</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr"/>
+      <c r="F657" s="2" t="inlineStr"/>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>视频1（完整Demo）从人类示范到真实G1：观看长距离搬运、导航与脚部交互。 一批人类第一视角数据已经采集完毕 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 08:48:32 +0800</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>微软员工数十年来首次下降；沃尔玛/山姆推出 Agent 购物接口；推动 SpaceX 和特斯拉合并，马斯克财富有望暴涨</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372711</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr"/>
+      <c r="F658" s="2" t="inlineStr"/>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/57/1c/571c62ce4cbbe39a27c100fea865fd08.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;24 小时为你在线打工：Anthropic 推出 Claude Duet AI 智能体，迎战 Meta 和 OpenAI&lt;/h2&gt;
+&lt;p&gt;10 月 22 日消息，Anthropic 昨日（10 月 21 日）宣布以研究预览版形式，推出全新应用 Claude Duet，定位为可主动工作的 AI 智能体（agent），加入由 Meta 的 Muse、以及 OpenAI 的 Dots 领衔的「全天候主动型 AI 助理」大战。&lt;/p&gt;
+&lt;p&gt;技能方面，该应用会每天整理跨应用的重要事项、主动提醒需要处理的问题，并在用户离开后继续在后台完成被委托的任务。&lt;/p&gt;
+&lt;p&gt;Claude Duet 基于 Claude Opus 5.5 构建，提供 iOS、Android 独立应用及 claude.ai 网页版。首批面向美国 Pro 和 Max 订阅用户开放候补名单；预览阶段与 Claude 其他功能共享套餐用量限制。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/aa/bb/aabb16c5bb9eed7c47e0f42799f87656.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;Meta 2026 财年第三财季归母净利润 98.6 亿美元，同比增长 264%&lt;/h2&gt;
+&lt;p&gt;10 月 22 日消息，Meta 发布 2026 财年（2026 年 1 月～2026 年 12 月）第三财季（2026 年 7 月～2026 年 9 月）及本财年前三财季（2026 年 1 月～2026 年 9 月）报告。&lt;/p&gt;
+&lt;p&gt;2026 财年第三季度实现营收 646.01 亿美元，同比增长 26%；归母净利润 98.6 亿美元，同比增长 264%；稀释每股收益 3.83 美元，同比增长 265%。&lt;/p&gt;
+&lt;p&gt;核心业务 Family of Apps（Facebook、Instagram 等）营收达到 641.58 亿美元，运营利润 171.17 亿美元；Reality Labs（VR / AR 业务）营收 4.43 亿美元，运营亏损 41.29 亿美元，亏损同比收窄。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;微软员工总数十年来首次下降，截至 6 月底雇员约 22.3 万人&lt;/h2&gt;
+&lt;p&gt;10 月 22 日消息，微软已经在多个业务部门持续裁员一段时间，如今，一份年度报告披露了确切数据。&lt;/p&gt;
+&lt;p&gt;该公司最新年度申报文件显示，截至 2026 年 6 月 30 日，微软员工规模约为 22.3 万人，相比上一年的 22.8 万人有所减少，这是十年来微软员工总数首次出现下降。数据来自微软 2026 财年的 10-K 报表，文件写明公司拥有「约 22.3 万名全职员工」，其中美国本土 12.1 万人，海外 10.2 万人。&lt;/p&gt;
+&lt;p&gt;报告显示，产品研发部门受影响最大，员工人数从 2024 年峰值 8.1 万人降至 7.7 万人，连续第二年人员缩减；销售与营销岗位各减少 1000 个，现有 4.3 万人；综合行政岗位缩减至 1.4 万人。虽然员工总数下降，但微软 2026 财年营收上涨 18%，达到 3318 亿美元；仅 6 月所在季度，资本支出就达到 410 亿美元，公司正持续向人工智能数据中心投入大量资金。（来源：网易）&lt;/p&gt;
+&lt;h2&gt;黄仁勋 GTC 柏林反驳 AI 终结软件论：工具公司将迎来更多使用者&lt;/h2&gt;
+&lt;p&gt;10 月 21 日，英伟达创始人兼 CEO 黄仁勋在 GTC 柏林大会上表示，AI 的发展将增加软件工具的使用者，工具公司也将向 AI 公司和智能体公司转型。&lt;/p&gt;
+&lt;p&gt;黄仁勋在演讲中提到，有人认为 AI 的到来意味着软件和工具公司的终结，他对此持相反看法。他认为，随着 AI 智能体承担更多工作，过去开发的软件工具将迎来更多使用者。&lt;/p&gt;
+&lt;p&gt;支撑这一判断的原因是，AI 要完成实际工作，仍然需要调用专业工具。黄仁勋以科学家和工程师的工作为例说明，即使具备很强的智能，也需要实验室、模拟器和求解工具。AI 智能体同样需要借助工具开展实验、仿真和数据处理。&lt;/p&gt;
+&lt;p&gt;他表示，编程是智能体较早落地的领域，编译器或 Python 环境就能支持其中一些任务。随着智能体进入更多行业，需要调用的工具也将更加丰富，包括流</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 22:26:58 +0800</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>奇瑞说，中国家庭的下一台车是摩托</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372692</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr"/>
+      <c r="F659" s="2" t="inlineStr"/>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;「SUV 有了、轿车有了、MPV 也有了，你再买什么？中国家庭接下来要买的车，就是一台摩托。」&lt;/p&gt;
+&lt;p&gt;说这话的是奇瑞智能科技副总经理涂小岳。10 月 19 日，2026 奇瑞全球创新大会期间，奇瑞旗下的两轮公司零维科技第一次正式面对媒体。芜湖下着雨，展台上摆着一台白色的增程巡航车、一台银色的电动探索踏板，还有一顶能把导航投到眼前的智能头盔。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="零维科技在 2026 奇瑞全球创新大会上展出的 GROW C3 与 SOLO X5" src="https://imgslim.geekpark.net/uploads/image/file/e0/d6/e0d619b0776e4d3e0267ef38f89a8085.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;车企造摩托，这件事本身不算新闻。宝马、本田早就两条腿走路，长城有灵魂，吉利有钱江，长安刚把轻骑收入囊中。真正值得多看两眼的是，奇瑞给这家公司定的目标，听上去不太像一家摩托车厂。&lt;/p&gt;
+&lt;h2&gt;出口是本田的四倍，利润不到六成&lt;/h2&gt;
+&lt;p&gt;先算一笔账。中国摩托车商会的数据显示，2025 年全国摩托车销量约 2197 万辆，其中出口 1337 万辆，连续 31 年全球第一。但国内销量在下滑，燃油摩托内销同比减少 6.18%；唯一逆势猛涨的是 250cc 以上的大排量休闲车型，全年卖出 95 万辆，增长近 26%。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;通勤在萎缩，玩乐在放量&lt;/strong&gt;，这是零维入场的大背景。&lt;/p&gt;
+&lt;p&gt;另一组数字来自零维科技总经理黎小君，他此前在一家日系摩托品牌担任总经理。「我们的摩托车出口产能大约是本田的 4 倍，但利润还不及本田的 60%。」量大利薄，大量利润来自低端制造。奇瑞控股集团执行副总裁鲍思语的说法更直接，高档摩托车仍被外资品牌垄断，「一台卖两三万元的高速摩托车就算是好的了」。&lt;/p&gt;
+&lt;p&gt;所以零维瞄准的不是通勤代步。涂小岳把全球约 6500 万辆的摩托车市场拆成三块，东南亚、南亚的代步刚需，欧美流行的高速 Scooter，以及把摩托当成生活方式的哈雷、宝马、金翼这一类。零维要的是第三块，他估算约 3000 万辆，「和中国汽车市场差不多」。&lt;/p&gt;
+&lt;p&gt;这个项目 2023 年就在奇瑞内部启动，2024 年 11 月零维科技由奇瑞智能科技与淮北市国资共同设立。至于投入，涂小岳的回答很奇瑞，「一个近六千亿的公司，花几亿、十几亿做一件事，其实不算那么大的资源。」&lt;/p&gt;
+&lt;h2&gt;汽车技术下放，最难的不是技术&lt;/h2&gt;
+&lt;p&gt;零维这次亮出的家底，一眼就能看出汽车血统。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="SOLO X5 电动探索踏板" src="https://imgslim.geekpark.net/uploads/image/file/9b/b3/9bb380eddc24c5a2383fcd621a60b735.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;银色的 SOLO X5 是一台纯电 ADV 踏板，官方称 20 分钟可从 20% 充到 80%，用的是液冷温控快充，充电口和汽车通用。白色的 GROW C3 是增程巡航车，从公开信息来看，纯电续航约 100 公里、综合续航约 600 公里，市区用电、长途加油。背后还有一套叫「鲲鹏」的 4 档多模混动平台，可以在纯电、增程、混动、直驱之间切换。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="GROW C3 增程巡航车" src="https://imgslim.geekpark.net/uploads/image/file/ef/3e/ef3e93e6a7325546230f113681d7d537.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;为什么纯电选快充而不是换电？黎小君的解释是场景决定路线。换电适合市内通勤，可零维的用户是周末去郊外玩的，荒郊野外没有换电柜，只能靠快充。混动的逻辑也类似，中大排量燃油技术长期握在欧美日企业手里，中国企业短期很难追上，「中排量通过混动方式，可以达到大排量的效果」。&lt;/p&gt;
+&lt;p&gt;汽车发动机热效率已经做到 48%，摩托车普遍还在 28% 到 30%。三电、热管理、电子电气架构这些在汽车上验证过的东西，搬到两轮上确实是近水楼台。零维的技术方案评审，由近 30 名汽车级专家完成。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="零维科技总经理黎小君" src="https://imgslim.geekpark.net/uploads/image/file/1d/0d/1d0de4c1d7f534df32920f2ffd2b4797.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;但问到最大的难点，黎小君没有提任何一项技术。「对技术的消化吸收不够、对摩托的理解不够」，他坦言团队为此走过弯路。零维现在 200 多</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 17:10:33 +0800</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>当车企要说为「人类自由」奋斗时，它在说什么</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372698</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr"/>
+      <c r="F660" s="2" t="inlineStr"/>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/42/86/4286966cba90113cdbf7c8505c823462.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;头图来源：极客公园&lt;/p&gt;
+&lt;p&gt;1993 年，时任三星集团会长的李健熙，在德国发表了著名的「法兰克福宣言」，其中最著名的一句话是：「除了老婆孩子，一切都要变。」&lt;/p&gt;
+&lt;p&gt;当时韩国摸着日本，在全球化浪潮中极速行军，产量提升的同时，也被贴上了「便宜廉价」的标签，法兰克福宣言，开启了三星通过技术进行高端化转型之路。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8c/f8/8cf85dfda0caac4b2bbbc72a1ae328b1.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;2026 奇瑞全球创业大会会场｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;33 年后的当下，安徽芜湖，奇瑞集团创新产业园中，「Change 改变」的字样随处可见，这是 2026 奇瑞全球创新大会的主题。&lt;/p&gt;
+&lt;p&gt;在主题演讲中，奇瑞董事长尹同跃说，奇瑞是一家披着车企外衣的「科技公司」，奇瑞的技术愿景是「为人类自由，创造最大价值。」&lt;/p&gt;
+&lt;p&gt;从某种角度来看，奇瑞愿景的宏大，和 SpaceX 的伊隆&amp;middot;马斯克，多少有相似之处了。&lt;/p&gt;
+&lt;h2&gt;从芯片、模型到智驾&lt;/h2&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/82/bd/82bdb710a6d3d96b9b8c2d2f17b8d693.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;奇瑞董事长尹同跃对于 AI 时代的断言｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;如果给车企的「科技含量」排个座次，芯片和大模型大概排在最前面。这一次，奇瑞把这两样东西一起摆上了台面。&lt;/p&gt;
+&lt;p&gt;先说芯片。奇瑞发布了自研的「紫微」芯片系列，分成三条线。C 系列是中央计算芯片，S 系列是车规级碳化硅功率芯片，M 系列是车规级控制芯片。从「大脑」到「肌肉」再到「神经末梢」，一台智能车需要的核心芯片，基本都被画进了这张路线图。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/44/b8/44b8e09bd29c54429a1943e39227abc6.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;最受关注的是紫微 C100。单颗算力 1200TOPS，两颗组合后整车 NPU 算力达到 2400TOPS，内存带宽 600GB/s。按照奇瑞的说法，它可以支撑 1000 亿参数的大模型在车端运行，计划 2027 年推出。奇瑞给出的对标数据是，带宽约为竞品的 2.2 倍，算力约为 1.2 倍。&lt;/p&gt;
+&lt;p&gt;相比之下，碳化硅这条线更务实。S 系列已经走到第二代 8 寸平面工艺，S750、S1200 今年推出，漏源耐压做到 1500V，奇瑞称这是目前车规级的最高电压等级。8 寸晶圆量产后，成本下降超过 30%。&lt;strong&gt;算力芯片决定上限，功率芯片则直接决定每台车的成本&lt;/strong&gt;，这笔账，车企比谁都算得清。&lt;/p&gt;
+&lt;p&gt;芯片之上是模型。奇瑞发布了一个名为 CheryMind 的垂类基础大模型，定位是「为物理 AI 而生」。它的底气来自奇瑞多年攒下的家底：700TB 企业知识、200PB 工程数据、千万级研发文档，再加上 2500 万段教练级驾驶数据，以及 500 万段机器人动作捕捉数据。&lt;/p&gt;
+&lt;p&gt;有意思的是，CheryMind 最先改造的是奇瑞自己。按照官方数据，它已经打通了 400 多个企业系统和 1500 多条端到端业务流程，每天有超过 6 万名员工在用。在它下面，一边是 CAD、质量、制造等「企业垂模」，教 AI 怎么造车；另一边是智舱、智驾、飞控、农机 OS 等「产品垂模」，让汽车、飞行器乃至拖拉机更懂人和世界。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/04/2b/042b1afb87a92dfa3541651f08a9ec4c.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;落到智驾上，是奇瑞的「全维世界引擎」CHERY AWE，由一个世界模型加三个细分模型组成。构境模型负责「造场景」，已经生成 70 万个训练场景，其中高危场景 30 万个、极限场景 2 万个，让智驾在虚拟世界里把危险提前经历一遍。观语模型负责「认路」，结合摄像头画面、导航和短期记忆去理解沿途的路口和地标，目</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 20 Oct 2026 16:20:06 +0000</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Nvidia-turned-VC Amulya Vishwanath: ‘Physical AI is in its LEGO era’</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/20/ex-nvidia-turned-vc-amulya-vishwanath-physical-ai-is-in-its-lego-era/</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr"/>
+      <c r="F661" s="2" t="inlineStr"/>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>It’s the moment everyone is waiting for — the ChatGPT moment for robotics, Amulya Vishwanath explained to TechCrunch’s Equity.</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27512,6 +27512,521 @@
         </is>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 09:13:14 +0000</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>魔法原子发布柔性仿生力控机械臂 MagicArm R1，搭载 MolmoSpaces 全球第一具身大模型</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14062</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr"/>
+      <c r="F662" s="2" t="inlineStr"/>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>打通“采数—训练—部署”，为具身智能技术研究、能力验证和实际应用提供一体化平台</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 08:46:30 GMT</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek千亿融资逼近收官：结盟完美世界、中芯聚源等产业资本，募资翻倍押注具身智能</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/ViOyxiOSP2ihxuUyg1rD?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr"/>
+      <c r="F663" s="2" t="inlineStr"/>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/ViOyxiOSP2ihxuUyg1rD?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 07:05:59 +0000</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>谁在给OpenAI供应具身数据？</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504800.html</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="inlineStr"/>
+      <c r="F664" s="2" t="inlineStr"/>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>挤进全球Physical AI核心供应链</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 09:45:22 +0000</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>生数科技Motubrain团队将直播Physical AI训练全流程，持续半个月</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504730.html</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="inlineStr"/>
+      <c r="F665" s="2" t="inlineStr"/>
+      <c r="G665" s="2" t="inlineStr">
+        <is>
+          <t>10月21日，生数科技世界模型团队正式开启Motubrain 2.0训练全流程公开直播</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 21 Oct 2026 07:15:05 +0000</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>LeCun押注的世界模型，中国一家清华系公司已经做进了机器人</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504653.html</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="inlineStr"/>
+      <c r="F666" s="2" t="inlineStr"/>
+      <c r="G666" s="2" t="inlineStr">
+        <is>
+          <t>世界模型赛道新看点：千诀隐变量可辨识性方向的研究，比LeCun相近工作早一年，不堆画面预测，主打物理规律与跨本体复用。</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 08:49:03 +0800</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek 据悉完成 1000 亿元新一轮融资；特斯拉三季度利润大跌 43%；微信称已完成适配 iPhone Duo | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372767</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="inlineStr"/>
+      <c r="F667" s="2" t="inlineStr"/>
+      <c r="G667" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c6/78/c6786e73fae593ac2e300a247caee940.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;DeepSeek 新一轮融资筹得约 1000 亿&lt;/h1&gt;
+&lt;p&gt;10 月 22 日，有市场消息称，国内大模型公司 DeepSeek 拟在最新一轮融资中筹得约 1000 亿元人民币 ( 约 150 亿美元 )，腾讯和宁德时代为本轮出资最多的投资方，交易预计在未来数日内正式完成。&lt;/p&gt;
+&lt;p&gt;截至目前，DeepSeek 及腾讯等相关投资方均未公开回应。记者从接近公司和投资方的多个信源交叉求证，确认上述消息属实。&lt;/p&gt;
+&lt;p&gt;消息人士透露，本轮募资目标最初设定为 500 亿元，此后经多轮上调至约 1000 亿元，目前尚未官宣，最终金额仍未完全确定。&lt;/p&gt;
+&lt;p&gt;这笔资金将继续用于模型训练、算力建设和人才招募，以支撑 DeepSeek 参与全球竞争。也有部分消息人士判断，本轮融资将为公司筹备中的科创板 IPO 铺平道路。（来源：上海证券报）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e0/be/e0bedbc389fa2ec06097ea20cc17d0e8.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;SpaceX 据报洽谈接入美国至少 8 万座基站，准备建立全国性移动通信网络&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;据彭博社 10 月 22 日报道，SpaceX 正在与美国移动通信基础设施企业洽谈，希望获得至少 8 万座地面通信站点的使用权。&lt;/p&gt;
+&lt;p&gt;这项计划可能帮助 SpaceX 建立覆盖美国全国的移动通信网络，进一步拓展 Starlink 的业务范围。&lt;/p&gt;
+&lt;p&gt;过去，Starlink 主要通过卫星提供宽带互联网服务，并逐步发展卫星直连手机业务。如果 SpaceX 能够获得大量地面通信站点的使用权，就有机会将卫星通信与传统地面移动网络结合。&lt;/p&gt;
+&lt;p&gt;目前相关合作仍处于谈判阶段，尚未公布最终协议。（来源：彭博社）&lt;/p&gt;
+&lt;h1&gt;Anthropic 冲刺史上规模最大 IPO&lt;/h1&gt;
+&lt;p&gt;10 月 22 日，据财联社援引知情人士消息，Anthropic 最快将于当地时间本周五向美国 SEC 公开提交 S-1 招股说明书，这是这家 AI 公司冲刺史上规模最大 IPO 的核心程序性节点。&lt;/p&gt;
+&lt;p&gt;早在今年 6 月，Anthropic 就已秘密提交 IPO 草案，此前一个月完成的 650 亿美元 H 轮融资，也为上市奠定了资本基础。该轮融资投后估值达 9650 亿美元，由 Altimeter Capital、Dragoneer、Greenoaks 和红杉资本领投。Anthropic 的估值也超越 OpenAI，后者在今年 3 月的投后估值为 8520 亿美元。&lt;/p&gt;
+&lt;p&gt;很长一段时间里，华尔街主流机构的乐观预期是，Anthropic 有望以 2 万亿美元估值上市，募资规模最高可达 1000 亿美元，直接刷新今年 6 月 SpaceX 创下的 IPO 纪录。SpaceX 上市时估值约 1.77 万亿美元，募资约 857 亿美元。（来源：界面新闻）&lt;/p&gt;
+&lt;h1&gt;腾讯客服称微信目前已适配 iPhone Duo，后续还会推出相关更新并持续提升使用体验&lt;/h1&gt;
+&lt;p&gt;10 月 22 日消息，苹果首款折叠屏手机 iPhone Duo 已于 10 月 16 日晚 8 点开启预购，搭载 A20 Pro 处理器，国行定价 15,999 元起。&lt;/p&gt;
+&lt;p&gt;关于微信的适配情况一直是大家重点关心的问题，腾讯客服表示：&lt;/p&gt;
+&lt;blockquote&gt;微信目前已经适配苹果折叠屏手机，您可以正常下载使用微信。同时微信团队正在积极推进对苹果可折叠设备的适配优化，后续会推出相关更新并持续提升使用体验。请您放心使用当前版本。&lt;/blockquote&gt;
+&lt;p&gt;另外，微信输入法也已更新 4.0.0 版本，宣布全面适配 iPhone Duo。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;特斯拉三季度净利润大跌 43%，交付量降至 48.65 万辆&lt;/h1&gt;
+&lt;p&gt;10 月 22 日消息，特斯拉于当地时间周三美股盘后发布 2026 年第三季度财报。数据显示，公司当季营收为 280.46 亿美元，与上年同期的 280.95 亿美元基本持平；GAAP 净利润为 7.87 亿美元，同比下降 43%。&lt;/p&gt;
+&lt;p&gt;按非 GA</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 06:41:03 +0800</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>欧洲 AI，等来了黄仁勋</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372763</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr"/>
+      <c r="F668" s="2" t="inlineStr"/>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;GTC 柏林开幕前的两周，半导体板块走得并不顺，费城半导体指数出现了 2008 年以来最长的一轮连跌。市场在反复算同一笔账，巨额的 GPU 投入，什么时候能变成实打实的回报。&lt;/p&gt;
+&lt;p&gt;10 月 21 日，在柏林 Tempodrom 的舞台上，黄仁勋没有发布新芯片。早已发布的 Vera Rubin 平台，这次只是确认「已全面量产」。他把更多时间留给了三个更落地的问题：&lt;strong&gt;算力中心怎么建得更快，越来越能干的智能体怎么管住，物理 AI，怎么走进欧洲的工厂和马路&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;用他自己的话说，「我们正处于人类历史上最大规模的基础设施建设之中」，需求不缺，缺的是产能和落地速度。&lt;/p&gt;
+&lt;p&gt;在英伟达 GTC 柏林大会之前，黄仁勋和德国总理默茨的对谈走红社交平台，当下 AI 基建绝对王者告诉后者，面对汹涌而至的全新生产力革命，「紧箍咒」可能并不是最优解。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f5/8b/f58b6fb7ba3ddac5be5afc6d4543a1c5.jpg" /&gt;&lt;/p&gt;
+&lt;h1&gt;把 AI 工厂装进集装箱&lt;/h1&gt;
+&lt;p&gt;过去两年，建一座 AI 数据中心更像一场土木工程。服务器、网络、供电和液冷要在现场逐一安装、布线、调试，一个大型集群从设备进场到真正点亮，拖上大半年是常态。而模型公司的迭代是按周算的，晚一个月拿到算力，可能就晚了一个版本。&lt;/p&gt;
+&lt;p&gt;英伟达在柏林给出的答案是 DSX POD。大屏上的标语很直白，「&lt;strong&gt;集装箱就是 AI 工厂&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;它是一套完整 Vera Rubin AI 工厂的模块化参考设计。一套 DSX POD 由 7 个液冷计算机架组成，内部约 17 公里线缆互连，采用 800V 直流供电，计算、网络、供电和液冷都在工厂里集成、测试完毕，再装进集装箱运到现场。戴尔、HPE、联想、施耐德电气、维谛，以及鸿海、广达、纬创等厂商参与制造，预计 2027 年初开始交付。&lt;/p&gt;
+&lt;p&gt;按照官方的说法，在现场电力、冷却和网络已经就绪的前提下，部署时间可以从约 6 个月缩短到最快 14 天。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a8/76/a876b961694b69b2a6535b826ac577c7.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;只看建设速度，其实低估了这件事。黄仁勋把 AI 经济比作五层蛋糕，最底下一层是能源。&lt;strong&gt;当算力规模越做越大，真正卡脖子的已经不只是芯片，而是电。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;所以和 DSX POD 一起发布的，还有两套用电工具。DSX MaxLPS 在 GPU 之间动态分配功率，官方称在产出同样多 Token 的情况下，功耗最多能降低 30%，换个角度说，同样的电力额度里能塞进更多 GPU。DSX Flex 则让数据中心和电网联动，按电价和供电状况调整负载，在模拟电网事件的早期测试里，一个 Blackwell Ultra 集群的用电负荷最多降了 40%。冷却改用闭环液冷加室外干式冷却器，减少冷却塔的蒸发耗水。&lt;/p&gt;
+&lt;p&gt;英伟达投资的欧洲数据中心开发商 Nscale 给了一组早期数据，在 GB300 NVL72 上，同样的电力预算下多部署了 37% 的 GPU，总推理吞吐提升近 50%。&lt;/p&gt;
+&lt;p&gt;这套逻辑的落点很清楚，&lt;strong&gt;衡量 AI 工厂的指标，正在从「有多少卡」变成「每度电产出多少 Token」&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;当然也有官方没说的部分。14 天的前提是电力和场地已经到位，而从公开信息来看，欧洲不少地区的电网接入本身就要排很久。DSX POD 的价格、总拥有成本也还没有公布，集装箱方案能帮客户省下多少钱，要等首批项目交付后才见分晓。&lt;/p&gt;
+&lt;h1&gt;给智能体装上硬件刹车&lt;/h1&gt;
+&lt;p&gt;如果说 DSX POD 解决的是「建得快」，OpenShell 企业参考架构要解决的是「用得放心」。&lt;/p&gt;
+&lt;p&gt;今年的智能体已经不只待在对话框里，它们开始读写文件、调用工具、访问企业系统。权限越大，风险越大，近期 AI 圈就出现过智能体擅自关闭安全监控的事件。&lt;/p&gt;
+&lt;p&gt;黄仁勋在台上说得很直接，「最重要的是确保智能体是安全的」。智能体的权限要降到最低，并持续监控，而且「每次启动智能体，权限都不一样」，所以管控也得跟着动态调整。他把 OpenShell 称</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 21:20:53 +0800</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>Token 成本降到每年 1 元，AI 家电这事就能成了 | 对话博联刘宗孺</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372762</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr"/>
+      <c r="F669" s="2" t="inlineStr"/>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;过去两年多，在智能硬件领域，投资人和创业者都热衷于为 AI 寻找一个个物理世界里的新「容器」，各种新形态的 AI 原生硬件成了投资市场的热门项目。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但其实，很多成熟形态的硬件同样有 AI 化的需求。这也许没有「AI Native」的概念那么性感，但市场一点不小，复杂度丝毫不低。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以家电行业为例：供应链长，改一次硬件就要重走研发、测试、认证；销售链条长，从厂家、经销商到上门安装的电工，每一环都得接得住；成本又极度敏感，多一块钱都要反复掂量。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;好在，家电已经为 AI 打好了地基。过去十几年，大量家电已经具备联网能力&amp;mdash;&amp;mdash;这意味着灵活升级的 OTA「管道」已经铺好，行业缺的是让设备真正被用起来的解决方案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;那么，硬件到底需要什么样的 AI？9 月，TypeSafe 推出的 Jev 在开发者圈引发了不少讨论，它提供了一个参照：Jev 不生成文字，只输出带置信度的判断。在硬件乃至具身领域的不少场景里，判断比生成更重要。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为一名在硬件和芯片行业里从业近 20 年的创业者，博联创始人刘宗孺近期和我们谈了谈博联最新的技术以及商业思考。在博联看来，「不让通用模型挑大梁」也许才是硬件领域的最优解。他们推出的寰思中枢由一系列参数很小的专家模型组成，大模型则退到后台，充当「阅卷老师」，复盘错误并自我迭代。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据刘宗孺介绍，目前寰思中枢已经在多个品类里和 B 端客户实现落地，AI 成本可以被压缩到「单台产品每年 1 元人民币」的级别。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以下是 Hardwire 和博联智能董事长兼 CEO 刘宗孺的访谈，经编辑整理。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;访谈 | siqi、郑玄&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作者 | siqi&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;编辑 | 郑玄&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;智能家电头 10 年：联网了，但不够智能&lt;/span&gt;&lt;/h2&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Hardwire：很多读者可能没听说过博联，但可能家里很多产品里都有博联的模组。先请您介绍一下，博联是一家什么样的公司？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;刘宗孺：&lt;/span&gt; 我们是做 ToB 的，所以对外宣传比较少。博联主要做两块业务：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第一块是帮家电、照明、电工这些厂家做智能化方案：从芯片、模组，到通信组网协议；厂家没有能力做云服务和软件的，我们就打包提供，也帮他们对接外面的各个生态。到了 AI 时代，又多了一块 AI 方案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第二块是空间场景的智能化，比如全屋智能、智慧酒店、智慧办公。我们自己不做家电，而是把客户的硬件拿过来，再叠加系统和软件。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;所以我们其实是 To B to C，通过厂家和这些大客户，把智能化送进用户家里。十几年下来，我们最核心的积累就是连接：芯片是我们自己的，组网协议是从头写的，整个通信这一层都在我们自己手里。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Hardwire：智能家电这个品类，目前走到什么阶段了？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 19:56:03 +0800</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>宇树 10 周年，王兴兴：我劝你相信 AI</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372759</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr"/>
+      <c r="F670" s="2" t="inlineStr"/>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;10 月 22 日，杭州国际博览中心热闹非常，不仅人多，而且机器人也特别多。&lt;/p&gt;
+&lt;p&gt;这是 2026 年宇树科技举办的世界物理 AI 大会的现场，从四足机器人到人形机器人，你甚至可以说这里是全球「机器人密度」最高的地方。&lt;/p&gt;
+&lt;p&gt;2026 年，也是宇树科技创立的第十年。有意思的是，在今天的舞台上，宇树科技创始人王兴兴，在谈机器人之外，聊的最多的就是当下最火热的 AI。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;他不仅劝所有人要「相信 AI」，而且还反思，觉得自己「相信 AI 还相信得不够」&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;为什么这家中国、乃至全球机器人行业中最有实力的公司掌舵者，会这么说？物理 AI 的拐点，真的要到来了吗？&lt;/p&gt;
+&lt;h1&gt;必须相信 AI&lt;/h1&gt;
+&lt;p&gt;在王兴兴 36 分钟的演讲中，宇树自己的产品只占了开头和结尾。中间最长的一段，王兴兴在做一件事&amp;mdash;&amp;mdash;劝人相信 AI。&lt;/p&gt;
+&lt;p&gt;从 AI 攻下了一批顶尖数学难题，「人类最智慧的金字塔的尖端」已经被击穿；到 AI 逆向工程让「传统软件公司的壁垒没了」；AI 视频里人物的表情和情绪「比真人演的还好很多」；顶尖大模型公司内部「已经实现了模型的自进化」。&lt;/p&gt;
+&lt;p&gt;「这不是闹着玩的」。他的结论是，以当下的模型能力，哪怕不再进步，信息世界也已经被「完全击穿」。&lt;/p&gt;
+&lt;p&gt;然后他说了一句不太像上市公司董事长会说的话，「&lt;strong&gt;我感觉我自己还不够相信，还不够坚定&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;这不是即兴发挥。十天前的上海工博会上，他已经当众「认错」过一次，「过去十几年我犯的最大的错误，就是对 AI 的相信还不太够」。他还给过一个倍数，5 年前或 10 年前你喜欢、相信 AI 的程度，「现在乘 10 倍都不为过」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8e/52/8e52cca67795ccf944673a91a7425c53.png" /&gt;&lt;/p&gt;
+&lt;p&gt;王兴兴在会上探讨物理 AI 的未来｜图片来源：宇树科技&lt;/p&gt;
+&lt;p&gt;更直观的变化在时间表上。今年 8 月的世界机器人大会，王兴兴对具身智能「ChatGPT 时刻」的预期还是快则 2 到 3 年、慢则 5 到 10 年；两个月后，这个窗口被他压缩成「1 到 2 年，慢的话 2 到 3 年」。至于随便把一台宇树机器人带进陌生的家里，一句话让它把房间收拾好，「快的话可能明年就可以实现」。工博会上他说得更直白，「明年 GPT-7 出来，可能直接把具身智能问题打穿」。&lt;/p&gt;
+&lt;p&gt;一个硬件出身的工程师，在两个月里成了全场最激进的 AI 布道者。这看上去像一次认知突变，但把宇树最近半年的处境摊开来看，&lt;strong&gt;他的「相信」几乎是一道必答题。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;但是，宇树的强项&amp;mdash;&amp;mdash;机器人本体，依然是王兴兴骄傲的事情。&lt;/p&gt;
+&lt;p&gt;王兴兴在台上最骄傲的是 G1。这款 2024 年 5 月发布的人形机器人，&lt;strong&gt;累计下线大约 1 到 2 万台&lt;/strong&gt;，他称之为全球单一型号出货量最大的人形机器人。&lt;/p&gt;
+&lt;p&gt;10 月 21 日，宇树放出 H2-X「功夫传奇 守护」的视频，一脚踢瘪车门、徒手抬车、4 米高台空翻落地，续航从 H2 的约 3 小时拉到约 8 小时。可以看到，宇树团队依然在快速迭代公司的产品。&lt;/p&gt;
+&lt;p&gt;本体之外，一直在布道 AI 的王兴兴，推销的 AI，并不完全是宇树自己的 AI。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3b/fa/3bfac1929d5b085031c8d9905997d819.png" /&gt;&lt;/p&gt;
+&lt;p&gt;随后的论坛环节王兴兴和姚明等嘉宾一同探讨物理 AI 的未来｜图片来源：宇树科技&lt;/p&gt;
+&lt;p&gt;他在台上很坦白，「我们毕竟是一家新公司」，跟全球最头部的多模态大模型公司「做一模一样的模型，那是不太现实的」。宇树会自研，也会和国内外大模型公司合作。他展示的最亮眼的 demo，是把 GPT-6 接到机器人上，零训练就能自己洗笔、换颜料，在围棋盘上精准落子。他判断规划和导航这类问题「某种意义上已经解决掉了」，剩下的是多模态大模型的输入输出和真实机器人之间的对齐&amp;mdash;&amp;mdash;传感器的误差、执行器的误差，「我觉得这个也是很快可以解决的问题」。&lt;/p&gt;
+&lt;p&gt;把这几句话连起来，就能看</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 16:15:50 +0800</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>大模型内卷之后，AI 竞争进入搜索基础设施时代</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372743</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr"/>
+      <c r="F671" s="2" t="inlineStr"/>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：元宝搜索&lt;/p&gt;
+&lt;p&gt;过去一年，AI 行业的战场正在悄悄发生位移。&lt;/p&gt;
+&lt;p&gt;当 Agent 从概念快速渗透进办公、内容、金融等真实业务场景，行业共识也在悄然改变：决定 AI 体验上限的，是它连接真实世界的能力。&lt;/p&gt;
+&lt;p&gt;政策迭代、市场波动、行业动态、垂类数据&amp;hellip;&amp;hellip;现实世界的信息每秒都在更新，大模型自带的知识储备永远有边界，想要输出可靠结论、完成复杂任务，就必须接入实时、权威的外部信息。&lt;/p&gt;
+&lt;p&gt;搜索，是大模型对接真实世界的核心接口。但这也是当下 AI 落地的共性卡点：传统搜索基于关键词匹配，读不懂自然语言的复杂意图，低质内容还容易引发模型幻觉；从头自建一套完整检索体系，又意味着爬虫、解析、索引、运维一整套极高的工程门槛，绝大多数团队都难以承担。&lt;/p&gt;
+&lt;p&gt;而腾讯其实早就在默默布局这层底层能力。 过去一年，腾讯在 AI 应用层动作密集：全场景智能体工作台 WorkBuddy、AI 知识管家 ima、腾讯视频 AI 小助理等 50 余款产品接连落地，覆盖办公、内容、金融等多个核心场景。但很少有人注意到，支撑这些产品联网检索、信息获取能力的底层搜索基座，此前一直藏在幕后。&lt;/p&gt;
+&lt;p&gt;10 月 20 日，这张「暗牌」终于正式亮相，元宝搜索迎来全面升级，并通过腾讯云以 API 形式向个人开发者与企业开放。&lt;/p&gt;
+&lt;p&gt;这套已经在腾讯内部支撑数 50 多款核心产品、沉淀数千亿级索引、接入 157 个权威信源、日均调用量达数亿次的搜索能力。这次全新升级的元宝搜索正式从内部自用工具，转向面向全行业的公用 AI 基础设施。&lt;/p&gt;
+&lt;p&gt;从幕后走到台前，元宝搜索的开放，补上的是 AI 规模化落地过程中，一块缺失已久、经过真实业务验证的信息基建拼图。&lt;/p&gt;
+&lt;h1&gt;一、一张尚未被翻开的搜索底牌&lt;/h1&gt;
+&lt;p&gt;搜索的发展，一直与互联网如何组织信息、分配流量紧密相连。每一次行业代际变迁，都会重新定义搜索的定位。&lt;/p&gt;
+&lt;p&gt;PC 互联网初期是目录导航时代，雅虎用人工分类的方式整理网站，搜索是互联网的「导航地图」；随后谷歌凭借 PageRank 算法开启了关键词搜索时代，搜索成为整个互联网的流量入口，核心逻辑是「人找信息」，通过关键词匹配返回网页列表，广告成为最核心的商业模式，谁掌握了搜索，谁就掌握了流量分发权。&lt;/p&gt;
+&lt;p&gt;进入移动互联网时代，超级 APP 割裂了开放的互联网，信息孤岛开始形成。通用搜索的入口价值被稀释，搜索能力逐步下沉为垂类产品的内置功能&amp;mdash;&amp;mdash;电商搜商品、内容平台搜视频、社交工具搜聊天记录，搜索从独立的流量产品，变成了服务各自生态的基础能力，语音搜索、本地搜索等新形态也随之出现。&lt;/p&gt;
+&lt;p&gt;而当 AI 浪潮袭来，搜索正在经历第三次本质变化：服务对象从「人」变成了「智能体」，核心目标从「返回网页链接」变成了「交付可信、结构化、可直接调用的信息」。&lt;/p&gt;
+&lt;p&gt;「搜索面对的用户从 1.0 时代的人，变成了 3.0 时代的智能体。这是整个使用对象的本质变化。」马晋表示，大模型天然存在幻觉、知识时效性不足、垂类术语缺失三大短板，搜索正是解决这些问题的核心路径。&lt;/p&gt;
+&lt;p&gt;这其中，&lt;strong&gt;实时性是 AI 搜索区别于传统静态大模型最核心的价值之一&lt;/strong&gt;。传统大模型的知识停留在训练截止日，面对瞬息万变的现实世界天然存在「时差」；而 AI 原生搜索可以同步全网最新动态，让 Agent 获得持续感知外部变化的能力&amp;mdash;&amp;mdash; 金融行情的实时波动、政策法规的最新修订、行业事件的即时进展，都能第一时间转化为智能体可调用的信息输入。&lt;/p&gt;
+&lt;p&gt;对于 Agent 来说，搜索成为了感知外部世界的核心感官，正是这种底层需求的变化，让搜索从「应用层功能」重新回到了「基础设施层」的核心位置。&lt;/p&gt;
+&lt;p&gt;但站在当下的行业节点看，适配 AI 时代的搜索基础设施，供给远远跟不上需求。&lt;/p&gt;
+&lt;p&gt;传统搜索 API 脱胎于「人找信息」的逻辑，本质还是关键词匹配，面对长语义、强意图的复杂查询，召回精度往往大打折扣；通用网页搜索的结果里混杂着大量 SEO 内容、营销号与过期信息，直接投喂给大模型，极易催生幻觉，让 AI 输出错误结论。&lt;/p&gt;
+&lt;p&gt;针对泛滥的 AIGC 低质内容，行业至今没有一劳永逸的解法。马晋提到，这本质是一场攻防战：既要靠模型识别单篇内容的特征，也要针对频繁发布低质内容的站点、账号做专项治理；但更有效的思路，是从源头提升优质信源的权重，让可信内容优先被召回。&lt;/p&gt;
+&lt;p&gt;如果选择自建搜索体系，门槛则是高得惊人：爬虫对抗、网页解析去噪、百亿级数据的存储与索引、排序模型的迭代</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 22:08:24 +0000</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI working on new $30B raise at $1.25T valuation ahead of IPO</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/22/openai-working-on-new-30b-raise-at-1-25t-valuation-ahead-of-ipo/</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr"/>
+      <c r="F672" s="2" t="inlineStr"/>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>Should OpenAI command an over $1 trillion valuation with this round, it would break records as the most highly valued private company ever.</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 13:11:13 +0000</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek reportedly raises $15B days after US restrictions</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/22/deepseek-reportedly-raises-15b-days-after-us-restrictions/</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr"/>
+      <c r="F673" s="2" t="inlineStr"/>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek has reportedly raised $15 billion in one of China's largest funding rounds, just days after the U.S. ordered federal agencies to remove its technology over national security concerns.</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28027,6 +28027,192 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:30:02+00:00</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Quadruped Robot Solves Giant Rubik’s Cube by Itself</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-rubiks-cube-robot</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr"/>
+      <c r="F674" s="2" t="inlineStr"/>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 24 Oct 2026 08:34:27 +0800</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>iPhone Duo正式交付；Kimi K3.1 Pro 、Seedance 2.5 4K正式发布；红果短剧上线防沉迷｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372858</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr"/>
+      <c r="F675" s="2" t="inlineStr"/>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/51/80/518047a03496253e470b6f3b4c348644.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;苹果首款折叠屏手机 iPhone Duo 正式交付用户 部分订单预计明年 1 月才能送达&lt;/h1&gt;
+&lt;p&gt;苹果首款折叠屏手机 iPhone Duo 于 2026 年 10 月 23 日正式进入上市交付阶段，首批预购用户开始收到新机，苹果零售店也迎来首发日消费者。由于预购需求强劲，加上生产供应受到限制，上市初期的现货数量相当有限，部分消费者即使在首发日下单，也可能需要等待数月才能拿到设备。&lt;/p&gt;
+&lt;p&gt;苹果此前表示，iPhone Duo 的预购需求表现异常强劲，公司正在努力尽快将产品交付给消费者。苹果同时确认，全球 Apple Store 门店会提供少量供现场顾客购买的库存，但提醒消费者，这些现货可能很快售罄。对于希望不经预购、直接前往门店购买的用户来说，能否买到新机仍存在较大不确定性。&lt;/p&gt;
+&lt;p&gt;这次供应紧张，与 iPhone Duo 在预购阶段迅速售罄的情况相吻合。预购于 10 月 16 日开启后，部分配置的预计发货时间很快被推迟。此后，苹果官网显示的新订单交付日期进一步延后，部分订单的预计送达时间已经排到 2027 年 1 月 25 日左右。这意味着，首发需求与现有供应能力之间仍存在明显差距。（来源：cnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/18/19/181955e8357b71883ae8163ef44455b3.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;曝 DeepSeek 最快明年推进 IPO，联想系入局 DeepSeek 新一轮融资&lt;/h1&gt;
+&lt;p&gt;据外媒援引知情人士消息，DeepSeek 新一轮融资引入多家产业及财务投资者，其中包括君联资本（Legend Capital）、专注半导体领域的石溪资本及吉利等。与此同时，DeepSeek 已聘请中信证券为其 IPO 提供顾问服务，并于今年 9 月引入新的首席财务官，DeepSeek 最快可能于 2027 年初推进 IPO。&lt;/p&gt;
+&lt;p&gt;君联资本与联想集团同属联想控股体系。联想集团是联想控股旗下核心产业公司，君联资本则是其重要投资平台。此次君联资本参与 DeepSeek 融资，也意味着联想系资本正式进入 DeepSeek 股东阵营。&lt;/p&gt;
+&lt;p&gt;从产业协同来看，此次投资进一步拉近了联想系与国内头部大模型厂商之间的关系。联想目前的 AI 业务已经覆盖 AI 终端、企业 AI 和 AI 基础设施多个领域，其中 AI PC、手机、平板等终端需要持续接入大模型能力，企业 AI 业务依赖模型、智能体与行业解决方案结合，服务器及数据中心业务则承接模型训练和推理带来的算力需求。&lt;/p&gt;
+&lt;p&gt;此前，联想已经围绕 DeepSeek 推进多项产品适配，包括在 AI PC、服务器及企业 AI 解决方案中接入 DeepSeek 模型。此次君联资本进一步参与 DeepSeek 融资，使双方关系从产品和技术适配进一步延伸至资本与生态层面，有望为联想 AI 终端、企业 AI 及 AI 基础设施业务带来更多协同空间。&lt;/p&gt;
+&lt;p&gt;（来源：新浪科技）&lt;/p&gt;
+&lt;h1&gt;古尔曼爆料苹果第三代 iPhone Duo 折叠手机：配长焦镜头，8 英寸出头内屏&lt;/h1&gt;
+&lt;p&gt;10 月 23 日消息，在第四期 Power On 播客节目中，彭博社的马克 &amp;middot; 古尔曼（Mark Gurman）透露，&lt;strong&gt;苹果公司正在规划更大尺寸的&lt;strong&gt;&lt;em&gt;&lt;em&gt;iPhone Duo&lt;/em&gt;&lt;/em&gt;&lt;/strong&gt;，并考虑在未来机型中加入长焦摄像头。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;古尔曼在播客节目中表示，这些规划有望在第三代 iPhone Duo 上实现，该产品预估 2028 年推出，其内屏尺寸可能比现款（7.6 英寸）增加约 0.5 英寸，&lt;strong&gt;达到「8 英寸出头」的水平。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;古尔曼表示，苹果 iPhone Duo 屏幕尺寸的升级路线，不会推出 8.5 英寸或者 9 英寸的大型折叠屏幕，会采用类似 Pro 系列的渐进式扩屏策略。例如 iPhone 15 Pro Max 从 6.7 英寸增至 iPhone 16 Pro Max 的 6.9 英寸。&lt;/p&gt;
+&lt;p&gt;影像方面，古尔曼透露长焦「已在苹果的计划清单</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 14:15:58 +0800</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>中国 AI 硬件的下一个爆款，可能生在「网球场」</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372807</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="inlineStr"/>
+      <c r="F676" s="2" t="inlineStr"/>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/bc/1d/bc1d7da9262701c829504e18b08df008.jpg" /&gt;&lt;/p&gt;&lt;p&gt;头图来源：Hirdwire&lt;/p&gt;&lt;p&gt;2024 年巴黎奥运会，郑钦文在罗兰·加洛斯捧起金牌的那个下午，中国的网球场预订量在一周内翻了数倍。两年后，最先把这股热潮变成生意的，是一群造机器的深圳工程师。&lt;/p&gt;&lt;p&gt;过去一年，至少四款中国团队打造的 AI 球类机器人在 Kickstarter 上筹得百万美元级资金。庞伯特以 26255% 的超募率卷走 265 万美元；智能家居大厂 SwitchBot 推出的 Acemate 30 天入账 180 万美元；Tenniix 首战筹得近百万美元后，其母公司英汉思动力完成红杉联合领投的三轮共超亿元融资；最新收官的 AceiiLab 首批量产正在交付，单台售价约 2000 美元，早鸟价 999 美元。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/99/3f/993f9f8b3217efaf5f18c4627095111b.png" /&gt;&lt;/p&gt;&lt;p&gt;但火归火，这条赛道连「卖的是什么」都还没说清。在「AI 网球机器人」标签背后，可以是打网球的人形机器人，也可以是便携发球机，也有可能是一款手机 App。&lt;/p&gt;&lt;p&gt;为什么网球机器人赛道突然爆火？一台真正的 AI 网球机器人到底该长什么样？带着这两个问题，我们在深圳的一片球场上见到了 AceiiLab，和它背后一思科技的联创晁光。随后我们发现，这场竞赛里硬件只是入场券，真正的关键在于你把这台机器定位成一件器材，还是一个对手。谁能让用户打得更久、离开得更难，谁才有机会提前拿到「AI 网球机器人」的定义权。&lt;/p&gt;&lt;h1&gt;&lt;strong&gt;一、「球场上来了个会跑位的陪练」&lt;/strong&gt;&lt;/h1&gt;&lt;p&gt;见到实物前，我们对网球机器人的想象是一块会移动的大屏，或一条能挥拍的机械臂。&lt;/p&gt;&lt;p&gt;AceiiLab A1 被拉进球场时，看起来像一只 20 寸行李箱，下半截是带轮子的本体，上半截是可拆卸的球包，可装 120 颗球。过去是一手拎机器、一手拖球筐，现在两件行李合成一件，整机约 20 公斤，四个轮子推行。&lt;/p&gt;&lt;p&gt;「我们发现在设备上，用户的本质需求不是要求机器轻，而是希望自己搬运不累。选择行李箱的形式，不需要一直发力，很大程度上减少累的体感。」AceiiLab 相关负责人说，「行李箱的方式既解决了移动难题，也是一个友好的用户使用过程。」&lt;/p&gt;&lt;p&gt;真正开机后，我们发现 AceiiLab 的玩法和常见的传统发球机并不一样，它是一个可移动的、交互性较强的产品。「这可能是我当下使用过最好的 AI 网球机器人，移动带来的真实对打感是其他同类产品几乎不可比的地方。」一位参与到现场与 AceiiLab 对打的朋友说道。&lt;/p&gt;&lt;p&gt;将 AceiiLab 放在网球线上，按下主机开关后，两侧车轨支架自动展开。十几秒后，摄像头认出球场上的线，机器开始沿线巡逻。它并不满场乱跑，只认中场线、底线和边界线这几条「跑道」，像一名守规矩的球员，绝不越位。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3d/b0/3db0fdf90428b64b3ecc0e5ef1c04e58.jpg" /&gt;&lt;/p&gt;&lt;p&gt;AceiiLab A1 开机准备 ｜来源：Hirdwire&lt;/p&gt;&lt;p&gt;热身完毕，好戏开场。开球前需先在 App 里选择模式，目前主要有三种玩法：组合&amp;amp;移动、自由练习、接发球训练。&lt;/p&gt;&lt;p&gt;以组合 &amp;amp; 移动模式为例，AceiiLab A1 会按照内置的 50 多套球路组合，一边沿线移动一边按剧本喂球，正手一颗、反手一颗，深一颗、浅一颗，球速和旋转轮着变，发球间隔最快能压到半秒一颗。&lt;/p&gt;&lt;p&gt;自由练习则把发球选择权交还给用户，无论是隔网对打、同侧陪练，还是让它在底线自由移动，用户均可按需选择。它还能定点喂球，或站在左右边线喂出角度刁钻的球，相较于传统发球机练来练去就那几个角度，它能把整条底线都变成发球点。&lt;/p&gt;&lt;p&gt;接发球练习模式中，还有一个「球童模式」，你不需要按下开始键，只需竖起球拍，机器就能自动识别就绪状态并完成发球，就像有一位专业球童一直站在对面为你发球。&lt;/p&gt;&lt;p&gt;真正开打后的画面，</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 21:59:19 +0000</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>Hottest toy for Christmas? Nvidia CEO plays with adorable Microduck robots, 20,000 sell</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/23/hottest-toy-for-christmas-nvidia-ceo-plays-with-adorable-microduck-robots-20000-sell/</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="inlineStr"/>
+      <c r="F677" s="2" t="inlineStr"/>
+      <c r="G677" s="2" t="inlineStr">
+        <is>
+          <t>The robots, stomping their little feet and making tiny R2-D2 noises, sat, fell down dead for a "nap," and summersaulted on voice command.</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 04:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>Uber rival inDrive eyes 2027 robotaxi tests in Central Asia with Pony AI and Nvidia</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/22/uber-rival-indrive-eyes-2027-robotaxi-tests-in-central-asia-with-pony-ai-and-nvidia/</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="inlineStr"/>
+      <c r="F678" s="2" t="inlineStr"/>
+      <c r="G678" s="2" t="inlineStr">
+        <is>
+          <t>The company plans to begin testing Pony.ai's robotaxis in Kazakhstan's capital in the first half of 2027.</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28213,6 +28213,63 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 25 Oct 2026 08:52:41 +0800</t>
+        </is>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>苹果首批折叠屏遭集中投诉；英国宣布超过 6 亿英镑 AI 投资计划；刘慈欣监制《三体·大史》年内开机</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372860</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="inlineStr"/>
+      <c r="F679" s="2" t="inlineStr"/>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9b/1a/9b1aaf523c45509ba917776c57981979.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;​到手 6 小时、开合不到 20 次屏幕就裂：苹果首批折叠屏遭集中投诉&lt;/h2&gt;
+&lt;p&gt;苹果首款折叠屏手机 iPhone Duo 刚开售就遇上了麻烦：据海外论坛和小红书多人反馈，不少用户开箱即遇到屏幕爆线、开裂问题，汇总照片显示故障位置高度集中&amp;mdash;&amp;mdash;几乎全部出现在铰链正上方，多数表现为屏幕一侧浮现一条亮像素线。&lt;/p&gt;
+&lt;p&gt;一名澳洲用户称，设备到手约 6 小时、开合不到 20 次，向朋友展示展开时先感到内铰链下方异样，随后听到清晰的「咔嚓」声，屏幕随即沿铰链裂开，内屏表面与外部铰链均无磕碰或夹痕，他前往 Apple Store 后苹果直接为其更换了故障机。国内也有类似案例。&lt;/p&gt;
+&lt;p&gt;综合目前反馈，问题可能出在 iPhone Duo 的铰链上，但涉及规模不算大，更可能是装配公差导致，而非设计缺陷，具体情况还有待后续观察。截至发稿，苹果官方尚未就这一批次屏幕问题作出公开说明。&lt;/p&gt;
+&lt;p&gt;如果苹果售后检测确认非人为导致，将会为用户更换新机。但若被认定为磕碰所致，则需用户自费维修：按苹果官网公示，未购买 AppleCare+时，内屏损坏保外维修预估费用高达 7998 元；购买 AppleCare+后，内屏及意外损坏服务费为 628 元&amp;mdash;&amp;mdash;两者相差超过十倍。&lt;/p&gt;
+&lt;p&gt;对于新机短期出现的屏幕问题，法律人士指出，消费者有权依据国家「三包」规定主张修理、更换或退货，商家若主张「人为损坏」，应承担相应的举证和说明义务。AppleCare+属于自愿购买的增值服务，不能替代经营者对商品质量的基本责任。建议用户保留购物凭证、沟通记录和设备照片等证据，必要时可向消保委投诉或走法律途径。(来源：TechWeb)&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0e/23/0e234e5f229da3db313cfaff30932b2d.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;英伟达黄仁勋开炮：「AI 毁灭人类」纯属捏造，是博眼球的廉价炒作&lt;/h2&gt;
+&lt;p&gt;法新社于 10 月 22 日发布博文，报道称在柏林举行的公司会议上，英伟达首席执行官黄仁勋再度抨击「AI 毁灭人类」言论，认为其是无稽之谈，更多是为了制造头条新闻而进行的「捏造」和「廉价」炒作。&lt;/p&gt;
+&lt;p&gt;IT 之家翻译黄仁勋相关言论内容如下：&lt;/p&gt;
+&lt;p&gt;当你听到说 AI 将会终结人类文明时，请不要相信这个言论。这些言论靠「捏造」和「廉价」炒作，博得「头条新闻」，但绝非事实。&lt;/p&gt;
+&lt;p&gt;针对某些科学专家认为「AI 会在 10 年内毁灭人类」观点，黄仁勋表示：「他们的所有预测都错了，所谓的 10% 概率既没有科学依据，也没有研究支持&amp;hellip;&amp;hellip; 这些预测只会伤人。」&lt;/p&gt;
+&lt;p&gt;黄仁勋呼吁外界以「负责任的乐观态度」看待 AI，表示如果人们关心人类之后的未来与可持续发展，现在正是「构建人工智能」的最佳时机。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;月之暗面主动限制 Kimi K3.1 Pro 的网络攻击能力，为开放权重设置安全边界&lt;/h2&gt;
+&lt;p&gt;10 月 24 日，路透社报道，月之暗面在新一代模型 Kimi K3.1 Pro 的训练过程中，主动采取措施限制其网络攻击能力。&lt;/p&gt;
+&lt;p&gt;月之暗面表示，团队从训练数据和强化学习环境中移除了部分网络攻击相关内容，希望在保持通用编程能力的同时，避免开放权重模型进一步提高前沿网络攻击能力。&lt;/p&gt;
+&lt;p&gt;根据月之暗面公布的内部测试，在受控环境中寻找并利用软件漏洞的评测里，经过安全调整的 K3.1 Pro 得分为 81.0%，而未采取相同限制措施的版本为 90.5%。&lt;/p&gt;
+&lt;p&gt;公司表示，调整后的模型仍然超过上一代产品的表现。&lt;/p&gt;
+&lt;p&gt;Kimi K3.1 Pro 已于 10 月 24 日凌晨发布，完整模型权重计划于 11 月 4 日前开放。（来源：路透社）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;Anthropic 亮出未发布 AI 模型：能力比 Mythos 5.1 更强，也更「守规矩」&lt;/h2&gt;
+&lt;p&gt;Anthropic 10 月 23 日发布博文，联合英国人工智能安全研究所（AISI），发布了一起 AI 网络测试失控</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H679"/>
+  <dimension ref="A1:H680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28270,6 +28270,59 @@
         </is>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 08:34:07 +0800</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>苹果发 iPhone 折叠屏官方文档，排查铰链故障；触屏 MacBook 或周三发布；《流浪地球 3》将曝光，春节上映｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372863</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="inlineStr"/>
+      <c r="F680" s="2" t="inlineStr"/>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cf/53/cf534da177beaa7d1ab1d7d36e046a39.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;张雪时隔 17 年圆梦「水上漂」，在家乡麻阳刷新吉尼斯纪录&lt;/h2&gt;
+&lt;p&gt;10 月 25 日，「张雪机车」创始人张雪驾驶改装摩托车 MX450，在湖南省怀化市麻阳苗族自治县郭公坪镇小坡村，成功挑战「改装摩托车在开阔水域行驶最远距离」吉尼斯世界纪录。&lt;/p&gt;
+&lt;p&gt;这场挑战要追溯到 2009 年。当时 22 岁的张雪在央视节目中骑着一辆车轮上焊着铁皮的摩托车冲向水面，四次尝试全部落水，最远只滑出 20 米，离他自己定下的 26 米目标差了一口气。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/06/c3/06c376557711fbc743b3312fe06ff40d.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;本次用于挑战的「张雪机车」MX450，是专门为了应对水上滑行而改装的型号。据「张雪机车」研发工程师邓连松介绍，改装摩托车以标准摩托车车架和动力总成作为基础，技术团队进行了相应的优化升级。&lt;/p&gt;
+&lt;p&gt;麻阳是张雪的故乡，当地龙舟以逆水行舟而闻名。在张雪挑战成功之后，乡亲们以龙舟表演等方式为张雪团队庆祝胜利。（来源：新华网）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e1/6e/e16e8cf1ff13067b7391ce8daffbbf5d.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 前沿模型训练不再接入实时互联网，改用离线网页环境&lt;/h2&gt;
+&lt;p&gt;10 月 24 日，OpenAI 公布前沿模型训练与评估环境的新安全措施：模型在训练中不再直接访问实时互联网，搜索和浏览任务改用预先索引、缓存的网页内容。这里限制的是训练中的模型，并不意味着 OpenAI 的训练基础设施完全断网；运行和监测实验仍需要部分外部连接。&lt;/p&gt;
+&lt;p&gt;这一调整与此前的安全事件有关。9 月，一款内部模型曾利用 DNS 配置缺口，在训练中获得有限的外网访问权限。此后，OpenAI 暂停相关训练 11 天，并让前沿模型智能体测试沙箱、虚拟机和网络防线。测试发现多处漏洞及配置问题，修复后，前沿模型的强化学习训练已于 10 月 1 日恢复。OpenAI 表示，今后仍会持续测试这些隔离措施。（来源：OpenAI）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;苹果 iPhone Duo 在部分区域破发：已加入电商平台「百亿补贴」，相对上市价便宜约 200-300 元&lt;/h2&gt;
+&lt;p&gt;10 月 25 日，综合各大平台网友反馈，苹果 iPhone Duo 在国内部分区域出现「破发」情况，同时当下拼多多已将该机上架百亿补贴频道（注：仅部分地区能看到），相对于上市价格便宜约 200-300 元。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6a/99/6a99ba3bf9fc1ea23072928e49a66360.png" /&gt;&lt;/p&gt;
+&lt;p&gt;虽然苹果&amp;nbsp;iPhone&amp;nbsp;Duo 首发日被加价到 1500-2000 元，然而该机在发售 2 天后的当下就迎来了「破发」局面。尽管如此，目前苹果 Apple Store 全国多家门店依然没有提供可直接购买的现货，官网购买手机选择「送货」选项时，显示仍要等到明年 1 月。&lt;/p&gt;
+&lt;p&gt;行业研究机构 IDC 此前预计，苹果首款折叠屏 iPhone 首年出货量将超过 1000 万部，并可能在 2027 年拿下全球折叠屏手机市场约 40% 的份额。高盛则维持对 iPhone Duo 的乐观判断，预计其 2026 年出货可达 1300 万部，2027 年有望达到 3300 万部。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;英伟达想靠软件持续收费，黄仁勋举例：每块 GPU 每年约 2000 美元&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;10 月 26 日，据媒体报道，英伟达 CEO 黄仁勋近日在柏林 GTC 活动上表示，软件许可将成为公司越来越重要的收入来源。他以运行 AI 智能体的软件为例，提到按</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H680"/>
+  <dimension ref="A1:H693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28323,6 +28323,509 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 03:49:17 +0000</t>
+        </is>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>提升电子皮肤拉伸性的4 种结构设计</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14106</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="inlineStr"/>
+      <c r="F681" s="2" t="inlineStr"/>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>波形、岛-桥、折纸剪纸、织物解析四大结构设计思路，探索柔性触觉传感器的性能优化与应用潜力。</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 03:41:25 +0000</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>机器人保镖来了？宇树科技推出 H2-X 功夫传奇守护人形机器人</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14064</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="inlineStr"/>
+      <c r="F682" s="2" t="inlineStr"/>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>将人形机器人的应用边界从传统工业、巡检、展演场景延伸至个人守护领域</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 03:24:08 +0000</t>
+        </is>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>2026视触觉传感器技术应用趋势及企业名单</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14063</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="inlineStr"/>
+      <c r="F683" s="2" t="inlineStr"/>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>更薄、更小、更高精度放在前面更薄、更小、更高精度，视触觉传感器正在如何突破机器人的触觉感知边界？</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 18:30:50 GMT</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>中科慧灵完成数亿元A++轮融资：制鞋机器人订单超 4 亿元，具身智能开始拼量产交付</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/2svt5BbWUOHbADdo0UZo?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="inlineStr"/>
+      <c r="F684" s="2" t="inlineStr"/>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/2svt5BbWUOHbADdo0UZo?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 09:07:25 +0000</t>
+        </is>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>企业AI需要两个世界模型</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/505032.html</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="inlineStr"/>
+      <c r="F685" s="2" t="inlineStr"/>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>特赞想让企业Agent真正懂业务</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 23 Oct 2026 09:03:37 +0000</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>一张5090跑起34B实时世界模型，国产玩家拿下英伟达大奖！</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/504931.html</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="inlineStr"/>
+      <c r="F686" s="2" t="inlineStr"/>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>房间秒变草原，抬手就能下雪</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 08:26:51 +0800</t>
+        </is>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>苹果回应 iPhone 折叠屏问题：可申请换机；传腾讯绿泡泡短剧月活过亿；；Anthropic或下月上市｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372952</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="inlineStr"/>
+      <c r="F687" s="2" t="inlineStr"/>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c2/08/c2087329df3a1c67cd16aa10adb49f65.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f9/08/f908a7b4fdc4d47ce2f71f379d1d02ac.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;Anthropic 公开递交纳斯达克 IPO 申请：目标 11 月 16 日当周上市&lt;/h1&gt;
+&lt;p&gt;Anthropic 正式踏上上市之路。这家成立仅五年、身处生成式 AI 浪潮核心的企业，本次 IPO 有望创下历史纪录。&lt;/p&gt;
+&lt;p&gt;Anthropic 在提交给美国证券交易委员会（SEC）的文件中披露，计划登陆纳斯达克交易所，股票代码定为「ANT」，目标在 11 月 16 日当周进行 IPO。该公司将设立 T 类特殊股票，供 T 类董事持有。&lt;/p&gt;
+&lt;p&gt;在招股书中，该公司披露，上半年营收 162.9 亿美元，上年同期为 11.6 亿美元；净亏损 807.5 亿美元，上年同期为 129.7 亿美元；营业亏损 6.93 亿美元，上年同期为 21.4 亿美元。&lt;/p&gt;
+&lt;p&gt;截至 9 月 30 日的九个月内，该公司没有任何单一客户占公司营收的 10%以上。79%的收入来自前五大客户以外的客户。合作方面，根据与 SpaceX AI 的协议，该公司同意在截至 2029 年的期限内累计支出高达 1205 亿美元。&lt;/p&gt;
+&lt;p&gt;该公司透露，资本支出将大幅增加，可能需要比目前预期更早地寻求额外融资；在可预见的未来不会支付任何股息，且目前未就重大收购达成任何协议；可能发行总额最高达 420 亿美元的可转换本票。&lt;/p&gt;
+&lt;p&gt;截至 9 月 30 日的九个月内，该公司没有任何单一客户占公司营收的 10%以上。79%的收入来自前五大客户以外的客户。合作方面，根据与 SpaceX AI 的协议，该公司同意在截至 2029 年的期限内累计支出高达 1205 亿美元。（来源：新浪科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b0/bf/b0bfab3717fdf6aad01e39c369afd5fb.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;苹果回应 iPhone Duo 内屏开裂问题：仅少量设备受影响，可申请换机&lt;/h1&gt;
+&lt;p&gt;iPhone Duo 上市不久，就有部分用户反馈铰链故障，导致内屏出现裂纹。苹果现已在给 MacRumors 的一份声明中回应了相关消息，称受影响的设备数量很少。&lt;/p&gt;
+&lt;p&gt;苹果没有说明裂痕产生的原因，也没有透露是否会推出修复方案。受影响的用户可以到线下门店更换新机，但由于备货有限，部分用户需要等待。&lt;/p&gt;
+&lt;p&gt;苹果表示，该问题波及范围很小。绝大多数用户不会遇到 iPhone Duo 屏幕故障，也不用担忧这个问题会随着使用慢慢出现。&lt;strong&gt;出现故障的设备，裂痕大多在购机后不久就会显现&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;据了解，一部分网传的裂痕图片是 AI 生成的，这也加大了判断问题真实影响范围的难度。&lt;/p&gt;
+&lt;p&gt;不少出问题的 iPhone Duo，裂痕位置都集中在内屏下半区，沿着铰链分布。用户称，屏幕损坏前会有卡顿卡滞的手感，有时还会听到咔哒声响。维修拆解网站 iFixit 拆解了 iPhone Duo，找到了几种可能造成铰链故障的原因。该网站表示，铰链这个位置汇集了多个零件，铰链内部一根本该收回的中部支撑杆可能无法正常回缩，进而造成屏幕损伤。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;OpenAI 低成本新模型 GPT-6.1 Terra 深夜炸场：每项任务成本仅 Claude Opus 5.5 九分之一，更快更准确&lt;/h1&gt;
+&lt;p&gt;OpenAI 今天凌晨宣布推出新模型 GPT-6.1 Terra，主打以更低成本完成复杂的电脑操作任务，尤其擅长需要视觉推理和操作桌面软件的工作。与 GPT-5.6 Terra 相比，新模型在事实准确性和编程能力方面也有大幅提升。&lt;/p&gt;
+&lt;p&gt;Terra 主要面向希望降低自动化成本的企业，可用于处理发票、解读技术图纸等工作。OpenAI 称，面对难度较高的专业任务，Terra 也能以远低于高价模型的成本完成。在考察复杂专业工作的 Agents』Last Exam 基准测试中，T</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 18:16:50 +0800</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>今年的 1024，可能是最后一个程序员节</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372944</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="inlineStr"/>
+      <c r="F688" s="2" t="inlineStr"/>
+      <c r="G688" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;作者｜Wildcard&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;今天一整天， X 上都有人在讨论，「&lt;strong&gt;1024 程序员节日快乐，今年会不会是最后一个程序员节了&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;这一天恰好是周六。微博上的话题叫「今年程序员节自带休息日」，配文说 AI 工具分担了重复编码，程序员终于能过一个不被紧急需求打断的节。&lt;/p&gt;
+&lt;p&gt;影石连续第五年给优秀程序员发黄金键帽，今年新增了一颗「F5」键，寓意不断刷新迭代。颁奖现场，一位年轻同事说了句玩笑话，「今年的黄金键帽，应该发给 AI」。&lt;/p&gt;
+&lt;p&gt;一家机构的节日推文写得更直白，「今年的程序员节，我们扩招了，会指挥 AI 做东西的，也算程序员」。&lt;/p&gt;
+&lt;p&gt;而在小红书上，有程序员在「古法编程时代」的标签下清理旧书，《图解 HTTP》三块一本，算法书十块。另一条帖子的标题是「程序员的书，多抓鱼都不收」，最后卖出去的几本里，最贵的竟然是《人月神话》。&lt;/p&gt;
+&lt;p&gt;一个节日，被放了假，被扩了招，连它的「圣经」都在二手市场上打折。&lt;/p&gt;
+&lt;p&gt;节日通常不会死于被取消。它死于没有人再需要它来确认自己是谁。要理解这句话，得先回到这个节日是怎么来的。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;从码农的暗号到所有人的节日&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;1024 从来不是一个官方节日。它的远亲是俄罗斯 2009 年定下的「第 256 天」程序员节，传到中国时因为闰年日期飘忽，被换成了更好记的 2 的 10 次方。大约从 2015 年起，10 月 24 日成了约定俗成的「程序员节」。&lt;/p&gt;
+&lt;p&gt;这是一个&lt;strong&gt;只有圈内人才懂的暗号&lt;/strong&gt;。和它一起长大的，是一整套自嘲。2006 年前后《IT 民工》在网上流传，2009 年到 2012 年「码农」迅速扩散，再往下还有「码奴」「码畜」。自嘲的前提是门槛，拿着比同龄人高一截的工资、干着外人看不懂的活，才有底气管自己叫农民工。2021 年人社部把软件从业者归进「新生代农民工」的统计口径，程序员们刷屏转发「码农真成农了」，语气里更多的是乐，不是愤怒。&lt;/p&gt;
+&lt;p&gt;然后，这个暗号被请出了圈子。2020 年，CSDN 在长沙办了第一届 1024 程序员节，院士开场；2023 年上了央视，2024 年微博话题阅读量达到 40.7 亿次。&lt;/p&gt;
+&lt;p&gt;有意思的是，这个节日的宣传语，一直在变化。&lt;strong&gt;2023 年，长沙大会第一次把重心从开源转向人工智能&lt;/strong&gt;。2024 年，中国软件行业协会主办的程序员节，主题已经变成「&lt;strong&gt;AI 如潮水向未来，共命运不得不 AI&lt;/strong&gt;」；长沙大会开幕式上，CSDN 创始人蒋涛现场演示的，是用自然语言让 AI 写代码。&lt;/p&gt;
+&lt;p&gt;到了今年，大会改名「1024 程序员日暨 AI 构建者大会」，主题是「人人皆可 Build」，开幕式上坐着的是几家机器人公司的创始人。「构建者」比「程序员」宽得多，那条「扩招」推文里列出的新程序员作品，有消费冷静期提醒、衣柜穿搭生成器、能请李白陪你聊天的程序，做它们的人很多一行代码都没手写过。AI 编程工具也把这一天当成拉新节点，ZCode 送 5 亿 Token，TRAE 签到抽奖，官方公示 92.5% 的结果是一张 10 元券。&lt;/p&gt;
+&lt;p&gt;收编让节日的圈子变大了，AI 让圈子大到几乎没有边界。&lt;strong&gt;一个对所有人开放的节日，其实就不再属于任何人&lt;/strong&gt;。可圈子在变大的同时，原来站在中心的那群人，正在经历什么？&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;最倒霉的一届计算机学生&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;2021、2022 年入学的计算机专业学生，今年毕业时自嘲是「史上最倒霉的一届」。入学时满眼是水果日和几轮面试就能拿到的 offer，毕业时却发现几乎没人愿意招初级员工。&lt;/p&gt;
+&lt;p&gt;数据站在他们这边。斯坦福的研究显示，美国 22 岁到 25 岁软件开发者的就业人数，比 2022 年底的峰值少了将近 20%，资深开发者却基本稳住。国内，麦可思的就业蓝皮书里，计算机类专业首次跌出本科绿牌专业榜和高薪专业前十；脉脉的数据显示，&lt;strong&gt;后端开发岗位需求降了 41%，AI 岗位却涨了 7.9 倍&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;被抽走的不是整架梯子，而是梯子最下面那一格。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;最有说服力的样本，来自一家把 AI 编程做到极致的公</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 18:16:08 +0800</t>
+        </is>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>Kimi 发布 K3.1 Pro，加量降价挑战 Opus 5.5</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372943</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="inlineStr"/>
+      <c r="F689" s="2" t="inlineStr"/>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;作者｜宇航猿&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;10 月 23 日上午，Kimi 官方在 X 和视频号上发了一段 24 秒的视频。&lt;/p&gt;
+&lt;p&gt;画面里是一台复古风格的老式电脑，屏幕上开着 Kimi Code，终端里一行行地写着 Three.js 代码，在生成一个复杂的 3D 场景。眼尖的网友很快在左上角的模型栏里找到了答案&amp;mdash;&amp;mdash;「Model: Kimi K3.1」。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a3/dc/a3dcee375aef47237471ec6404ff6dba.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Kimi 官方发布的 K3.1 预热视频｜图片来源：X @Kimi_Moonshot&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;用一台老古董般的机器，跑一段今天最前沿的 3D 代码，这个反差本身就是月之暗面想说的话。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;十几个小时后，10 月 24 日零点刚过，卡着程序员节，Kimi K3.1 Pro 正式上线，同步推出的还有一个速度快 2 到 3 倍的 Highspeed 版本。官方承诺，完整模型权重将在 11 月 4 日前放出。&lt;/p&gt;
+&lt;p&gt;距离上一代 K3 发布，过去了三个多月。这三个月里，月之暗面经历的事情，比大多数公司一年还多。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;「加量不加价」的 0.1&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;先说清楚 K3.1 Pro 是什么。&lt;/p&gt;
+&lt;p&gt;它不是一个全新的模型。月之暗面明确表示，K3.1 Pro 是 K3 的后训练版本，底座没换&amp;mdash;&amp;mdash;仍然是 2.8 万亿总参数、1040 亿激活参数的混合专家架构，仍然是 100 万 token 的上下文窗口，仍然原生支持图像和视频输入。&lt;/p&gt;
+&lt;p&gt;变的是后训练。官方的说法是投入了「大幅增加的后训练算力」，在数百个下游领域做了大规模联合强化学习，为此把强化学习框架、沙箱基础设施、长上下文推理这些底层工程都重构了一遍。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;也就是时候，同一个大脑，被重新「教」了一遍怎么干活。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;效果体现在榜单上。在考察编程智能体的 Terminal-Bench 4.0 上，K3.1 Pro 拿到 65.7%，超过 GPT-6 Astra 的 58.2%，和 Claude Opus 5.5 的 66.4% 只差不到一个点。上一代 K3 在这个榜单上的成绩，按第三方机构 Artificial Analysis 的测法只有 13%。&lt;/p&gt;
+&lt;p&gt;第三方的综合评分也给了面子。&lt;strong&gt;Artificial Analysis 智能指数上，K3.1 Pro 拿到 55 分，比 K3 高出 11 分，排名全球第四，前面只有 Claude Opus 5.5、Claude Sonnet 5.5 和 Muse Wonder Full&lt;/strong&gt;。等权重正式放出，它将成为得分最高的开放权重模型，开源与闭源之间的差距会从 12 分缩小到 3 分。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/de/d9/ded95c7705e8f1b16b01e514252214d7.png" /&gt;&lt;/p&gt;
+&lt;p&gt;K3.1 Pro 在 14 项编程、科学与知识工作评测上的表现｜图片来源：Kimi 官方博客&lt;/p&gt;
+&lt;p&gt;除了编程，这次的两条新主线是 3D 和金融。&lt;/p&gt;
+&lt;p&gt;K3.1 Pro 能驱动 Unity、Unreal、Godot 这样的游戏引擎，能写 Blender 和 CAD 脚本做参数化建模。在从多视角图片重建 3D 模型的 BenchCAD 测试里，它借助工具拿到 92.7%，接近 Opus 5.5 和 Astra。Kimi 网页版和 App 也同步上线了「3D Make」，可以直接描述需求，生成 3D 网页、3D 模型，甚至导出给 3D 打印机。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f9/f0/f9f0447bc957c6a29adb3f7180226993.png" </t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 16:49:42 +0000</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s IPO filing reveals its strategy for keeping enterprise customers hooked</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/26/anthropics-ipo-filing-reveals-its-strategy-for-keeping-enterprise-customers-hooked/</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="inlineStr"/>
+      <c r="F690" s="2" t="inlineStr"/>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s S-1 shows more than half of its $100,000-plus customers now use both the Claude Platform and a first-party app, a cross-selling playbook reminiscent of Amazon that’s making enterprise customers stickier.</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 14:35:22 +0000</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic officially files for its public debut</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/26/anthropic-officially-files-for-its-public-debut/</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr"/>
+      <c r="F691" s="2" t="inlineStr"/>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic has officially filed for an IPO, revealing soaring revenue, mounting losses, major enterprise adoption, and an unusual governance structure designed to preserve founder control and its AI safety mission.</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T13:10:23-04:00</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>Five weird details from Anthropic’s IPO filing</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1018738/anthropic-ipo-s1-filing-weird-details</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr"/>
+      <c r="F692" s="2" t="inlineStr"/>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic has finally filed its S-1 prospectus with the SEC, a document designed to give investors a look under the hood of its business, from how much its executives are making and plans for spending its IPO billions to the risks that could derail its ambitions. At more than 300 pages, there's a lot to [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T09:32:49-04:00</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s IPO filing lays out a plan to &amp;#8216;revolutionize every area of human endeavor&amp;#8217; with AI</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1018476/anthropic-ipo-details-s1-filed-sec</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr"/>
+      <c r="F693" s="2" t="inlineStr"/>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic has filed its S-1 prospectus with the Securities and Exchange Commission, preparing the company behind Claude to beat OpenAI to the punch with an IPO. In a filing with the SEC, Anthropic said it plans to list on the Nasdaq exchange under the ticker symbol "ANT." The AI company confidentially filed with the SEC [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H693"/>
+  <dimension ref="A1:H710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28826,6 +28826,685 @@
         </is>
       </c>
     </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:14:39+00:00</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>Your Robot’s Safety Functions Already Work. What If the Input Lies?</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/ai-robot-safety-cybersecurity-vicone</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr"/>
+      <c r="F694" s="2" t="inlineStr"/>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;em&gt;This article is brought to you by &lt;a href="https://vicone.com/?utm_source=ieee-spectrum&amp;amp;utm_medium=sponsored-content&amp;amp;utm_campaign=2026-10" rel="noopener noreferrer" target="_blank"&gt;VicOne&lt;/a&gt;.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;/em&gt;&lt;span&gt;A mobile robot slows for someone in a hallway. A collaborative …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 16:06:31 +0000</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>刚刚，Anthropic公开335页招股书：史上最大IPO，史上最亏AI公司</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/505551.html</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr"/>
+      <c r="F695" s="2" t="inlineStr"/>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>地球最富兄妹俩堂堂来袭！7名联创仍紧握50.1%总投票权</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 26 Oct 2026 06:50:44 +0000</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>趋境科技完成 B 轮融资，半年实现超十倍速增长，加速高品质 AI Token 规模化交付</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/505429.html</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr"/>
+      <c r="F696" s="2" t="inlineStr"/>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>高品质 AI Token 成为行业新风向</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 17:24:34 +0800</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>iPhone Duo 裂屏，是苹果新 CEO 接班后第一次「大考」</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373008</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr"/>
+      <c r="F697" s="2" t="inlineStr"/>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/bc/27/bc278280152ca16346b5eb8f068c3405.jpg" /&gt;&lt;/p&gt;&lt;p&gt;头图图片来源：iFixit&lt;/p&gt;&lt;p&gt;2011 年 9 月 30 日，苹果递交了一份名为「Flexible electronic devices」的专利申请。&lt;/p&gt;&lt;p&gt;它描述的是一台屏幕可以对折的设备，合起来能揣进口袋，靠传感器判断自己是开着还是合着。&lt;/p&gt;&lt;p&gt;这份专利 2015 年 1 月获得授权，发明人一共六位，其中一位叫特努斯（John Ternus）。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d7/15/d7152d6ad1d31eb9393ae98189cad216.png" /&gt;&lt;/p&gt;&lt;p&gt;苹果 2011 年递交的折叠设备专利附图｜图片来源：Apple&lt;/p&gt;&lt;p&gt;十五年后，2026 年 9 月 9 日，当年署名的这位工程师，第一次以苹果 CEO 的身份走上发布会舞台，发布的正是一台可以对折的 iPhone：iPhone Duo。&lt;/p&gt;&lt;p&gt;巧的是，十二年前的同一天，2014 年 9 月 9 日，库克也在后台等着上台。&lt;/p&gt;&lt;p&gt;那是他接任 CEO 三年后，第一次发布全新品类的产品 Apple Watch，同场还有大屏的 iPhone 6。&lt;/p&gt;&lt;p&gt;据彭博商业周刊当时的报道，&lt;strong&gt;开场前，库克戴着耳机，用 iPhone 听 OneRepublic 的《I Lived》给自己打气。&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;新 CEO 的第一款重磅产品，从来都是一场大考。&lt;/p&gt;&lt;p&gt;只是特努斯的这场考试，没有在发布会那天结束。&lt;/p&gt;&lt;p&gt;10 月 23 日，iPhone Duo 开售。&lt;/p&gt;&lt;p&gt;当天就有澳洲用户在 Reddit 上发出内屏开裂的照片，之后几天，美国、中国大陆、日本、韩国陆续有人晒图，描述几乎一样：到手开合不到二十次，展开时铰链处有一点阻力，「咔嚓」一声，内屏沿着折痕中线裂开几厘米，旁边亮起一条白线。&lt;/p&gt;&lt;p&gt;裂开的地方，正是十五年前那份专利里要折起来的那一道。&lt;/p&gt;&lt;p&gt;真正出问题的机器并不多。&lt;strong&gt;9to5Mac 统计到的独立案例大约 10 起，社交平台上还混着不少 AI 生成的假图&lt;/strong&gt;。&lt;/p&gt;&lt;p&gt;10 月 26 日，苹果通过媒体发了一份声明，承认「少量 iPhone Duo 的内屏出现问题」，用户可以联系 AppleCare 换新，不需要另外购买 AppleCare+。&lt;/p&gt;&lt;p&gt;但这些裂缝几乎都出现在同一个位置，说明它们大概率出自同一个原因，而不是用户各自摔出来的。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c8/df/c8df0df0dd7b3c0850cafcb13fc3a694.png" /&gt;&lt;/p&gt;&lt;p&gt;Reddit 用户 leftyhyzer16 发布的故障内屏，竖线沿着折痕，横向亮线从交汇处向外延伸｜图片来源：Reddit @leftyhyzer16&lt;/p&gt;&lt;p&gt;硬件上的难题，大多能靠钱和时间解决。苹果两样都不缺，它在折叠屏上花的时间，比几乎所有厂商都长。&lt;/p&gt;&lt;p&gt;只是「时间」有两种：一种是实验室里的研发时间，另一种是几百万台机器到了用户手里之后，被真实使用的时间。&lt;/p&gt;&lt;p&gt;前一种，苹果攒了十五年；后一种，谁都没办法提前攒。&lt;/p&gt;&lt;h1&gt;Duo 之前的十五年&lt;/h1&gt;&lt;p&gt;递交那份专利时，特努斯还是苹果硬件工程团队里的一员。&lt;/p&gt;&lt;p&gt;在接受《时代》采访时，他这样回忆当年的判断：&lt;strong&gt;「当时就很清楚，我们迟早会走到 OLED 屏幕可以弯折的那一步。」&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;从专利到产品，中间隔了十五年。&lt;/p&gt;&lt;p&gt;据彭博社马克·古尔曼的报道，苹果工程师大约到 2016 年才开始认真做折叠设备，项目由特努斯的前任、硬件工程主管丹·里奇奥发起。&lt;/p&gt;&lt;p&gt;最初试的是一台能展开成大平板的 iPad mini，2020 年前后才转向折叠 iPhone。&lt;/p&gt;&lt;p&gt;这期间，三星、华为已经先后推出了好几代折叠屏，苹果一直没有跟进。&lt;/p&gt;&lt;p&gt;《时代》的报道里有一个细节：苹果产品设计副总裁 Richard Dinh 曾问特努斯，屏幕最外层要</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 16:55:13 +0800</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>看了招股书，我终于知道为什么 Anthropic 不在乎用户了</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373006</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr"/>
+      <c r="F698" s="2" t="inlineStr"/>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;大的，终于来了。&lt;/p&gt;
+&lt;p&gt;10 月 26 日，Anthropic 向美国证监会公开递交了 S-1 招股书，准备在纳斯达克全球精选市场挂牌上市，股票代码定为 ANT。媒体报道中，&lt;strong&gt;这家公司的估值讨论区间已经来到了 1.5 万亿至 2 万亿美元&lt;/strong&gt;，发行价区间尚未披露。&lt;/p&gt;
+&lt;p&gt;24 小时内，这本 300 多页的招股书已经被科技圈和金融圈翻了个底朝天，最抓眼球的几个数字大家都看过了：2026 年上半年营收 162.86 亿美元，去年同期只有 11.63 亿美元；第二季度交出 9.74 亿美元经营利润，迎来公司历史上首个经营盈利的季度；至于账面上高达 807 亿美元的净亏损，大头是 723.88 亿美元的可转债、衍生负债和 SAFE 公允价值变动，属于非现金的会计费用。&lt;/p&gt;
+&lt;p&gt;但在这些华尔街叙事之外，国内的开发者和日常使用者有着另一种割裂的体感。在中国大陆用户眼里，Claude 大概是目前市面上封号最多、风控最严苛、用起来最让人恼火的 AI 产品。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;为什么一家做出顶尖大模型的公司，在面对普通个人用户时总是显得如此冷淡&lt;/strong&gt;？&lt;/p&gt;
+&lt;p&gt;翻完招股书的财务附注和风险提示，答案其实就写在账本上。在 Anthropic 的商业版图里，个人用户贡献的真金白银占比非常小。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;不到 20% 的个人用户&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;要看懂一家公司真正在乎谁，最直接的办法就是去翻它的收入构成表。在招股书的财报附注 2 里，Anthropic 把营收拆成了两大块，一块是按用量计费的收入，另一块是订阅收入。&lt;/p&gt;
+&lt;p&gt;数据对比非常悬殊。2025 年全年，按用量计费的收入是 37.96 亿美元，订阅收入只有 7.89 亿美元，比例大约是 83% 对 17%。到了 2026 年上半年，按用量计费的收入冲到 130.64 亿美元，订阅收入是 32.22 亿美元，前者依然占到 80% 左右，订阅收入只占约 20%。&lt;/p&gt;
+&lt;p&gt;更关键的细节藏在订阅收入的构成里。这 20% 里，既有个人用户的 Claude Pro 和 Claude Max，也有企业级的 Team 和 Enterprise 套餐，招股书并没有把个人订阅单独拆出来。&lt;strong&gt;这意味着，个人用户掏腰包买会员贡献的收入，在 Anthropic 总营收里的占比肯定低于两成，甚至可能还要低得多。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;那么，八成的按用量计费收入从哪来？答案是&lt;strong&gt;云厂商渠道和成千上万家企业&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;通过亚马逊、谷歌、微软这几家云厂商市场卖给客户的收入，占比一路狂飙：2023 年约 11%，2024 年约 32%，2025 年约 47%，2026 年上半年约 48%。几乎半壁江山都是靠三大云巨头的分销管道撑起来的。&lt;/p&gt;
+&lt;p&gt;撑起这台印钞机的，是一批迅速膨胀的机构客户。截至 2026 年 9 月 30 日，过去 12 个月贡献收入 10 万美元以上的客户（按独立组织统计），从一年前的 950 多家暴增到 11900 多家。客户结构也很健康，2026 年前 9 个月没有任何单一客户收入占比超过 10%，前五大客户合计约 25%。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/89/2a/892af93f6a96f0362c21f5b12a90e7df.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span style="font-size: 14px;"&gt;招股书中的企业客户增长图：过去 12 个月贡献收入 10 万美元以上的客户，从 2023 年底约 20 家增长到 2026 年 9 月底的 11900 多家｜图片来源：Anthropic&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;招股书给个人付费用户专门用了一个词叫「prosumers」，定义是订阅 AI 工具来做知识工作的个人用户&lt;/strong&gt;，比如研究人员、开发者、分析师和写作者。头衔听起来很专业，但这群人在核心财务指标面前依然处于边缘位置。&lt;/p&gt;
+&lt;p&gt;整份 300 多页的招股书，没有披露日活和月活用户数，连付费订阅人数都没有提。&lt;/p&gt;
+&lt;p&gt;最能体现这种态度的是净收入留存率。&lt;/p&gt;
+&lt;p&gt;截至 2026 年 9 月 30 日，&lt;strong&gt;</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 16:49:29 +0800</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>Manus，刚刚悄悄发布了自己的 2.0 宣言</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373004</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr"/>
+      <c r="F699" s="2" t="inlineStr"/>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;10 月 26 日，Manus 联合创始人、产品合伙人张涛（网名 HideCloud）最近在自己的公众号「潜云思绪」写了一篇长文，标题叫《&lt;strong&gt;用 Manus 改造 Manus&lt;/strong&gt;》。&lt;/p&gt;
+&lt;p&gt;文章开头是一个让他印象很深的画面。他给工程师提了几条需求和 Bug，过一会儿去看进展，发现对方电脑上开着一排 Codex 和 Manus 的 Session。随便点开一个，输入就是他刚在 Slack 上发的需求原文，一字未改。&lt;/p&gt;
+&lt;p&gt;更让他意外的是，这位工程师当时同时在处理十几、二十个需求。在今天的 Manus，这已经是常态。&lt;/p&gt;
+&lt;p&gt;这篇文章信息量很大，有几件事最值得记下来。&lt;/p&gt;
+&lt;p&gt;Manus 内部做了一个叫 Manus-mono 的统一代码入口，配上一本写给 AI 看的说明书，让 AI 能看到跨仓库的全局。一个需求，一个人就能写完所有端。移动端团队一直只有 7 个人，同时负责 2 个产品、4 个 App，进度和网页版基本同步。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/32/1d/321d0359eee7fc5190a1fd06e11593b2.png" /&gt;&lt;/p&gt;
+&lt;p&gt;所有产品经理都向 Manus 提交过代码，大约一半能独立把需求做到上线。有的产品经理交出来的需求，已经从文档变成了一段视频。&lt;/p&gt;
+&lt;p&gt;市场团队有了一位「数字同事」，会自己安排工作、主动提醒项目进度，还会跨团队去把功能细节问清楚。&lt;/p&gt;
+&lt;p&gt;9 月，&lt;strong&gt;公司的 AI 开销人均超过 1 万美元，少数人一个月就用掉七八万美元&lt;/strong&gt;。张涛专门用一节回应了外界的质疑。&lt;/p&gt;
+&lt;p&gt;文章发出的时间点也很微妙。9 月底，Manus 发布了 2.0 版本和个人智能体应用 Cue；10 月初，母公司蝴蝶效应宣布完成超过 5 亿美元的新一轮融资，同时在北京开出 17 个岗位。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;放在这个节点上看，这篇文章更像是 Manus 团队进入 2.0 时代的一份宣言&lt;/strong&gt;。它讲的是组织如何利用 AI 进化，透露出来的却是这家公司的产品方向、成本逻辑和用人标准。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;Manus 本身，就是 2.0 的样板间&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;如果你把文章里的内部实践和 Manus 2.0 的功能列表放在一起，会发现它们几乎能一一对上。&lt;/p&gt;
+&lt;p&gt;市场团队的数字同事用内部网站觉得不顺手，可以通过一个反馈接口直接提需求，需求一进来就自动触发 Manus 的开发任务。这背后用的是 2.0 的 Automations，收到一条外部通知，就自动开始一个任务。&lt;/p&gt;
+&lt;p&gt;产品经理用视频代替需求文档，靠的是 2.0 大幅加强的视频能力，既能用图像生成视频，也能用代码做动画。做语音转文字功能的那位产品经理，故事很典型。她先让 Manus 测试了十多个模型，选定一个接入，再按现有设计规范做 Demo，让 Manus 把用户可能遇到的场景逐一生成图片，一张张检查修改，最后把 Demo 剪成视频。方案清楚了，她干脆把功能写完，网页端和桌面端的界面都出自她手。&lt;/p&gt;
+&lt;p&gt;同事做的 Slack 机器人运行在云电脑上。非研发同事想知道某个功能怎么实现、文案在哪、有没有上线，不必先打听归谁管，直接问它就行。&lt;strong&gt;这对应的是 2.0 里可以 7&amp;times;24 小时常驻的云电脑&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;还有一些功能目前只在内部用。比如同一项目的成员默认能看到彼此的 Session，工程师和 AI 做完大部分工作，产品经理可以进到同一个 Session 里，接着调间距、样式和文案。&lt;/p&gt;
+&lt;p&gt;张涛在文末写得很直接，这些是 Manus 接下来要做好的事，「&lt;strong&gt;我们会先自己试，再交到用户手里&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;「吃自己的狗粮」这个说法在软件行业流传了几十年。一般认为它源自 1988 年微软高管 Paul Maritz 的一封内部邮件，标题就叫「Eating our own Dogfood」，要求员工多用自家产品。后来更有名的例子是 Slack，它最早是游戏公司 Tiny Speck 开发《Glitch》时自用的沟通工具，游戏没做起来，工具反倒成了主业。&lt;/p&gt;
+&lt;p&gt;Manus 走的</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 16:46:19 +0800</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>启元机器人第 5000 台下线，从规模化量产迈向商业化验证</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373003</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr"/>
+      <c r="F700" s="2" t="inlineStr"/>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;10 月 25 日，启元机器人第 5000 台个人机器人正式下线。从 9 月 20 日发售启元 Q1、T1 两款个人机器人，到一个月后完成 5000 台下线，启元在产能爬坡、制造体系与供应链协同上取得阶段性进展。&lt;/p&gt;
+&lt;p&gt;对仍处产业化早期的个人机器人行业而言，5000 台的意义不止于产量增长，更在于企业将研发阶段的技术能力转化为可复制的制造能力，并进一步连接产品交付、用户使用与软件迭代&amp;mdash;&amp;mdash;这是个人机器人从技术探索走向消费市场的关键环节，也是检验商业化能力的重要维度。&lt;/p&gt;
+&lt;p&gt;随着人工智能从数字世界走向物理世界，机器人产业的竞争正从技术展示延伸至工程化、产品化和商业化能力，启元此次量产实践提供了一个观察个人机器人产业化进程的具体样本。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6a/c6/6ac6ee1d2fa459291f1d8ee580151b75.png" /&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;一个月从 0 到 5000 台，&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;量产制造体系成形&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;「自产线启动以来，从 0 台到 5000 台稳定量产下线，仅用时 1 个月。 」启元机器人联席总裁、中央研发部总裁高全中表示，启元机器人的产线目前每 2.5 分钟下线一台机器人，日产能从 10 余台提升至 200 余台。&lt;/p&gt;
+&lt;p&gt;对个人机器人而言，量产并非简单增加产线或提高装配速度。机器人融合机械结构、运动控制、感知交互与智能算法等多个系统，既要实现复杂功能，也要在批量制造中控制装配精度、产品一致性与运行可靠性。衡量量产能力，不能只看下线数量，还要看制造体系能否支撑持续生产、质量标准能否适应规模化复制、供应链能否匹配交付需求。&lt;/p&gt;
+&lt;p&gt;据介绍，围绕这些环节，启元机器人在生产端通过工艺固化、质量收敛、自动化装配与标定测试提升批量一致性；供应链端联合供应商建立原材料立库、采用半自动化装配线体、搭建端到端制造 IT 系统，实现生产流程可追溯。同时建立涵盖百万级线束弯折测试、十万级关节耐久测试及模组抗冲击测试的验证标准，以提高产品在长期使用过程中的稳定性。&lt;/p&gt;
+&lt;p&gt;这些能力共同构成从样机研发走向规模化制造的工程基础。5000 台下线仍是阶段性进展，后续需通过持续交付、产品质量、售后与用户反馈进一步检验制造体系稳定性；但量产体系的价值不仅在于提高当期产出，更为后续产能扩张、供应链协同与产品迭代提供了可复用基础设施。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;发售后真实使用，商业化链路延伸&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;量产解决产品能否稳定供给的问题，而个人机器人能否打开消费市场，取决于产品是否具有明确使用价值、用户是否愿意持续使用。&lt;/p&gt;
+&lt;p&gt;9 月 20 日，启元机器人正式发售启元 Q1、启元 T1 两款个人机器人，聚焦学习、互动娱乐与家庭生活等个人场景；10 月 25 日，启元机器人将编号「NO.5000」的启元 T1 交付给代表用户董璇，使产线成果与真实使用场景进一步连接&amp;mdash;&amp;mdash;个人机器人开始从发布会上的技术展示，进入用户的实际生活。从产品发布到真实使用，是验证产品定位、功能设计和市场需求是否匹配的重要过程。&lt;/p&gt;
+&lt;p&gt;应用层面，启元 Q1、启元 T1 在学习场景支持 AI 启蒙课程、图形化编程、英语口语练习与百科知识问答；互动娱乐方面支持语音游戏、唱歌跳舞与外观 DIY；生活场景可拍摄跟随，并搭配运动相机实现多种运镜效果。这一产品思路区别于传统单一功能设备：通过机器人本体、智能交互与应用能力的结合，让产品参与不同生活活动，并在实际使用中不断拓展价值。&lt;/p&gt;
+&lt;p&gt;家庭场景对安全与交互提出更高要求。启元机器人表示产品支持 360 度全向感知避障，针对摔倒、被拎起、遇阻及低电量等设置安全响应机制；交互层面通过 PrimeVista 交互模型探索更自然的语言交流体验。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https:</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 16:42:40 +0800</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>帮用户抢 iPhone 折叠屏的 Agent，正在塑造 AI 时代电商的形状</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373002</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr"/>
+      <c r="F701" s="2" t="inlineStr"/>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/63/91/6391b5eaf5f268ab1691e932148c6d47.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Shopify AI 交易订单增长了 13 倍。&lt;/p&gt;
+&lt;p&gt;10 月 16 日清晨，苹果第一款折叠屏手机 iPhone Duo 开启预购。1999 美元起售，首批产能紧张，没过多久交付日期就排到了明年 1 月。&lt;/p&gt;
+&lt;p&gt;这一次抢首发的，不只是守在屏幕前的人。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/92/7d/927d8a23c547e81c3aab9d16b837431d.png" /&gt;&lt;/p&gt;
+&lt;p&gt;今年 Agent 成为 iPhone Duo 黄牛最严厉的父亲｜图片来源：Apple&lt;/p&gt;
+&lt;p&gt;在 MacRumors 论坛上，一位没抢到的用户愤愤不平地吐槽，Reddit 上有人在炫耀自己设置的 Muse 机器人一口气拿下了好几台，真人还没来得及点，库存就被 AI 扫走了。&lt;/p&gt;
+&lt;p&gt;Muse 是 Meta 在 9 月 8 日推出的个人 Agent，上线后一度登顶美区 App Store 免费榜，下载量很快超过 250 万。Meta 方面表示，购物已经成为 Muse 最主要的使用场景之一。就在 iPhone Duo 开售前后，Muse 还专门发了新版本适配这台新机，更新说明里紧跟着的一句，是让聊天里的购物变得更方便。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;AI 替人购物，已经从发布会上的演示，走进了真实的抢货现场。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;但并不是每家商店都欢迎这些新顾客。 9 月下旬，亚马逊开始封禁 Muse。 到了 10 月，马斯克旗下 Grok Bot 的用户在亚马逊下单时，也撞上了同一句警告，未经授权的 AI 代理继续访问，违反亚马逊的使用条款。&lt;/p&gt;
+&lt;p&gt;另一家公司，Shopify，则走了完全相反的路。9 月 21 日，Shopify CEO Tobi L&amp;uuml;tke 宣布与 Muse 深度合作，让 Muse 可以用 Shop Pay 在所有 Shopify 店铺完成结账。&lt;/p&gt;
+&lt;p&gt;而 Shopify 的财报，已经给出了这条路的早期回报。&lt;strong&gt;今年一季度，来自 AI 搜索的订单同比增长接近 13 倍，AI 带来的店铺流量增长 8 倍&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;一边关门，一边开门。&lt;strong&gt;当越来越多的购物决定交给 Agent，「让不让 Agent 进门」，会不会成为 AI 时代电商排位的关键变量？&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;13 倍增长背后的空间&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Shopify 是这一轮 AI 购物热潮里最积极的「玩家」。&lt;/p&gt;
+&lt;p&gt;2025 年四季度，它报出 AI 驱动的订单增长 15 倍。2026 年一季度，AI 带来的店铺流量同比增长 8 倍，AI 搜索产生的订单增长接近 13 倍，而且来自 AI 搜索的新买家订单，增速接近传统自然搜索的两倍。同一个季度，Shopify 交出了四年多来最快的营收增速。&lt;/p&gt;
+&lt;p&gt;到了二季度，倍数回落到 3 倍，AI 带来的流量和订单都是去年同期的三倍。但这一季的结构更耐看，&lt;strong&gt;75% 的 AI 归因购买发生在平台前 100 大品类之外&lt;/strong&gt;，通过 Shopify Catalog 完成的 AI 搜索，转化率是普通 AI 搜索的两倍。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这组数据说明的是「增长很快」，而不是「规模很大」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Shopify 自己说得很坦白。二季度电话会上，总裁 Harley Finkelstein 承认，agentic commerce 的交易量相对于平台庞大的 GMV 仍然很小。至今 Shopify 也没有披露过 AI 渠道 GMV 的绝对值或占比，而它二季度的 GMV 是 1160 亿美元。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/13/20/1320cb79</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 15:59:20 +0800</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>左手开源模型，右手创作 Agent，Hi3D 的 AI 3D 下半场</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/372939</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr"/>
+      <c r="F702" s="2" t="inlineStr"/>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;&lt;strong&gt;作者｜Cynthia&lt;/strong&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;编辑｜郑玄&lt;/strong&gt;&lt;/section&gt;
+&lt;p&gt;2026 年的 AI 3D 赛道，正站在一个微妙的分水岭上。&lt;/p&gt;
+&lt;p&gt;一级市场的热度仍在攀升，新模型、新创业公司层出不穷，单图生 3D 的正面渲染效果几乎已经做到了以假乱真。&lt;/p&gt;
+&lt;p&gt;但剥开炫目的 Demo 外壳：绝大多数生成结果依然停留在「转台展示」阶段：一个精致的角色或机械模型，在灯光下缓缓旋转，鳞片、衣褶和金属刻纹栩栩如生；可这些细节一旦进入游戏引擎装配、工业仿真以及 3D 打印的真实生产流程就立刻原形毕现：结构断裂、背面崩坏、细节粘连、网格不可编辑等问题开始集中爆发，大量人工修补成本吞噬了 AI 带来的效率红利。&lt;/p&gt;
+&lt;p&gt;正面视图保真度不等于 3D 质量成为新的行业共识。AI 3D 的竞赛，也从 能不能生成」的上半场，进入了能不能落地的下半场。&lt;/p&gt;
+&lt;p&gt;也正是在这个节点上，头部玩家 Hi3D 接连落下两枚棋子：正式开源经过生产验证的 Hi3D V1.0 底座，同时推出以创作者为核心的 Hi3D Agent，一头连接产业底层，一头深度扎根进入真实的创作全流程。&lt;/p&gt;
+&lt;p&gt;在此之前，这家成立不到三年的公司已经交出了一份扎实的成绩单：半年内连续完成两轮融资、总额近 5000 万美元，红杉中国、IDG 资本、美团龙珠等一线机构扎堆下注；旗下 Hi3D 平台覆盖&lt;strong&gt;120+ 国家与地区、200 万 + 创作者&lt;/strong&gt;，与拓竹科技、xTool 等头部设备商深度集成。&lt;/p&gt;
+&lt;p&gt;从稀疏几何技术的学术突破，到生产级模型的开源开放，再到 Agent 创作系统的全链路打通，Hi3D 已经拿下了通往 3D 生成下半场的门票。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;3D 生成，被高估的 Demo，&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;被低估的生产鸿沟&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;单图生 3D 的底层逻辑，天然带着视角偏见。随着&lt;strong&gt;ULIP、Uni3D 等指标被反复刷新，重正面、轻整体，重外观、轻内部逻辑的一度成为这个行业过去几年的共同写照。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;但 3D 资产的本质，是可旋转、可编辑、可加工的立体对象。一张角色图片里，垂落的发丝可以只占几个像素。进入三维空间后，模型必须决定它的厚度、与肩膀之间的距离，以及它如何连接头部。更进一步，物体的光影与轮廓之外，背面、底部、被遮挡的内部结构，全部需要模型从训练数据中学到的三维先验进行推理。&lt;/p&gt;
+&lt;p&gt;否则，一个正面相似的 3D 模型，很可能转个角度就露出马脚&amp;mdash;&amp;mdash;本该闭合的壳体出现破洞，对称的零件左右扭曲，纤细的结构要么融成一团，要么直接凭空消失。&lt;/p&gt;
+&lt;p&gt;更进一步，解决了多视角下的几何一致性问题后，一个模型能否被下游工具使用，还取决于它的精细结构保留度、网格拓扑合理性，甚至是壁厚、封闭性等工程属性。&lt;/p&gt;
+&lt;p&gt;有实测数据显示：同处 1536&amp;sup3; 分辨率档位，即使一些头部玩家的产品，3D 打印切片成功率仅为 7%-17%。看起来细节拉满的模型，实际走向实体生产就会变得困难重重。&lt;/p&gt;
+&lt;p&gt;这也解释了为什么资本市场热度不减，产业端却始终处于试点多、规模化少的状态。&lt;strong&gt;而当行业走向下半场，谁能先跨过 Demo 好看&amp;rarr;生产好用这道坎，谁才能真正拿到 AI 3D 产业化的入场券&lt;/strong&gt;。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;Hi3D V1.0 开源：&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;把 200 万资产训练的生产级底座，&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;交还给全行业&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Hi3D V1.0 的技术起点，可以追溯到 2025 年的 Sparc3D。&lt;/p&gt;
+&lt;p&gt;这项由 Math Magic、南洋理工大学及帝国理工学院研究者参与的研究，处理的是高分辨率三维建模中的一个基础问题：怎样保存复杂表面，又不让计算和存储成本随着分辨率失控。&lt;/p&gt;
+&lt;p&gt;三维网格背后的体素空间有立方级的规模变化。每个方向从 1024 提高到 1536，线性分辨率增加 50%，完整网格中的单元数量就会变成原来的 3.375 倍。大量空白区域如果也参与计算，成本会迅速上升。&lt;/p&gt;
+&lt;p&gt;Sparc3D 采用稀疏表示，将计算更多集中在与物</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 01:15:28 +0000</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>VCs will make billions on Anthropic’s IPO, but Amazon is set to make much (much) more</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/27/vcs-will-make-billions-on-anthropics-ipo-but-amazon-is-set-to-make-much-much-more/</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr"/>
+      <c r="F703" s="2" t="inlineStr"/>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>Massive note conversions reveal the true extent of Amazon's ownership in Anthropic.</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 21:38:28 +0000</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>Who’s really in charge at Anthropic after the IPO?</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/27/whos-really-in-charge-at-anthropic-after-the-ipo/</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr"/>
+      <c r="F704" s="2" t="inlineStr"/>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>Here's a clear explanation of Anthropic's incredibly complex governance structure.</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 16:30:57 +0000</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>Google’s Genie 4 world model adds audio, more realistic worlds, and real-time steering</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/27/googles-genie-4-world-model-adds-audio-more-realistic-worlds-and-real-time-steering/</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr"/>
+      <c r="F705" s="2" t="inlineStr"/>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>Genie 4 can maintain a consistent scene for up to two minutes, double Genie 3's limit, and offers better physics and more humanlike characters.</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 14:59:09 +0000</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>Meta AI director Rohit Patel leaves to take on Microsoft Office and Google Workspace</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/27/meta-ai-director-rohit-patel-leaves-to-take-on-microsoft-office-and-google-workspace/</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr"/>
+      <c r="F706" s="2" t="inlineStr"/>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Patel is departing Meta after eight years working on AI evaluations and reinforcement learning, TechCrunch has exclusively learned. His startup, Ndoc, aims to take on Microsoft Office Suite.</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>General Compute raises $100 million Series A, countering the neocloud disaster narrative</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/27/general-compute-raises-100-million-series-a-countering-the-neocloud-disaster-narrative/</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr"/>
+      <c r="F707" s="2" t="inlineStr"/>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>General Compute is betting on inference chips from outside the Nvidia ecosystem.</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T13:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>VisionQuest is what happens when AI really goes rogue</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1017064/visionquest-marvel-rogue-ai</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr"/>
+      <c r="F708" s="2" t="inlineStr"/>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>In Marvel's VisionQuest, a superpowered robot tries to better understand humanity by getting lost in elaborate, digital daydreams in which he and other artificial intelligence-powered beings live together in a home. The series is deeply fantastical, yet it plays with some of the ideas that have come to dominate the conversation about real-world generative artificial [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T12:51:22-04:00</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic’s elaborate plan to keep Wall Street at bay</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1019470/anthropic-ipo-resist-investor-pressure-cut-corners-safety</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr"/>
+      <c r="F709" s="2" t="inlineStr"/>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic wants to have it both ways. With its impending IPO, it wants to tap the vast riches of the public markets and insists it doesn't want to compromise its core mission of developing AI safely and for the benefit of humanity. But greater model capabilities bring greater risks, and shareholders eager for returns may [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T12:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>Google’s next Genie AI model generates more realistic experiences</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/1019076/google-genie-4-ai-model</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr"/>
+      <c r="F710" s="2" t="inlineStr"/>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>Google announced today its Genie 4 world model for generating interactive experiences using AI. The company says the model has four main updates: It allows for more realistic worlds, lets users update an experience in real time with a natural language prompt, can generate audio, and uses Gemini 3.8 Flash under the hood to help [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H710"/>
+  <dimension ref="A1:H717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29505,6 +29505,280 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 01:56:36 +0000</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>小米公布仿生灵巧手：21自由度，全掌1500点触觉覆盖</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14151</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr"/>
+      <c r="F711" s="2" t="inlineStr"/>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>从工厂SOP数据采集到21自由度仿生手的落地，小米机器人正试图在具身智能与柔性制造的交叉点上寻找突破口</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 06:50:09 +0000</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>从触觉到直觉：电子皮肤凭什么让机器“有感觉”？</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14128</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr"/>
+      <c r="F712" s="2" t="inlineStr"/>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>从机械臂指尖的细腻触感，到ICU病床上的无线生命体征贴片，再到VR 手套里的真实触感一这些场景的共同载体</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 17:45:17 GMT</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>Claude Code 撑起史上最大 IPO，被封号不退费的中国开发者撑起那 5%“脏收入”</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/lCw5JBglbgZj9BYeZChS?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr"/>
+      <c r="F713" s="2" t="inlineStr"/>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/lCw5JBglbgZj9BYeZChS?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 27 Oct 2026 12:57:51 +0000</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>不藏了！人形机器人全开源动真格，从机械结构一路拆到运动算法</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/505865.html</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr"/>
+      <c r="F714" s="2" t="inlineStr"/>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人全套图纸开源！从关节到算法，下载就能自己造。</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 29 Oct 2026 08:05:58 +0800</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>苹果发触屏笔记本，最高 11 万元；DeepSeek V5 模型代码现身；宇树首发财报，净利增 270%</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373085</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr"/>
+      <c r="F715" s="2" t="inlineStr"/>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/8e/b7/8eb77bdc8a53d7484dd5362b1cc86f84.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;苹果发布首款触屏 MacBook Pro，顶配超 11 万&lt;/span&gt;&lt;span style="font-weight: bold;"&gt;元&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="1307" src="https://imgslim.geekpark.net/uploads/image/file/73/1a/731a1a9028b3aa673cbc8829eae9c994.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;北京时间 10 月 29 日，苹果发布全新 MacBook Pro，首次为 Mac 引入屏幕触控和灵动岛，并采用双层串联 OLED 技术的 PROLED XDR 显示屏。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;新机提供 14 英寸和 16 英寸两种版本，搭载 M5 Pro 或 M5 Max 芯片。根据苹果中国区发布信息，新机将于 10 月 30 日开启预购，11 月 6 日正式发售，起售价 22999 元。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在交互方面，用户可直接触摸屏幕滚动网页、缩放照片、拖放幻灯片，以及操作 3D 模型或演奏虚拟乐器。苹果表示，触控传感器直接内嵌于显示面板，macOS 可将触控输入转换为点按，让许多现有应用直接支持触控。新机还调整了铰链设计，以提升触屏操作时的稳定性。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;新机最高可选 128GB 统一内存和 16TB 存储，苹果标称电池续航最长可达 24 小时，支持约 30 分钟充至最高 50%电量。搭载 M5 Max 处理器、128G 统一内存和 16TB 硬盘的 16.3 寸触屏 MacBook Pro，官网标价来到 11.26 万元。（来源：凤凰网科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/9d/46/9d46c9fee1d10f480e005ac67433fb12.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;宇树科技公布首份财报，前三季净利 3.87 亿元&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;10 月 28 日晚间，宇树科技发布了 2026 年第三季度报告，也是其上市后的首份财报。财报显示：报告期内公司单季度实现营业收入 6.65 亿元，同比增长 69.93%；归母净利润 1.13 亿元，同比下降 17.37%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;报告显示，年初至报告期末，公司累计实现营业收入 18.17 亿元，同比增长 55.71%；利润总额 4.13 亿元，同比增长 143.05%；归母净利润 3.87 亿元，同比增长 270.54%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;此外，宇树科技的研发投入有所提升，其第三季度单季研发投入 1.27 亿元，同比增长 249.58%，占当期营业收入比例 19.1%；前三季度累计研发投入 2.63 亿元，同比增长 191.48%，占营业收入比例 14.47%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;公司称，研发投入增长主要系持续加大具身智能领域研发投入，尤其是具身大模型相关模型研发与算力投入大幅增长，以及扩充研发团队、持续开展新产品研发所致。（来源：新浪科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;DeepSeek V5 大模型已现身官方代码库&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;近日，有</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 15:37:30 +0800</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>斯坦福的研究，红海的珊瑚，与一个中国模型</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373059</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr"/>
+      <c r="F716" s="2" t="inlineStr"/>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;2026 年 9 月 4 日，又一年柏林国际消费电子展 IFA 大会开幕，会展中心的创新舞台座无虚席。&lt;/p&gt;
+&lt;p&gt;IFA 2026 的开幕主题演讲题目是《个人 AI 时代：想象力的未来》，主讲人是 AMD 高级副总裁、计算与图形事业部总经理 Jack Huynh。&lt;/p&gt;
+&lt;p&gt;作为消费电子圈每年最重要的场合之一，台下所有人都在等 AMD 拿出年度最重磅的内容。Huynh 的前半段演讲照例讲硬件：新一代 Ryzen AI Max PRO 处理器，AMD 历经多年打磨、专为个人 AI 设计的笔记本「Sundance」。&lt;/p&gt;
+&lt;p&gt;到演示环节，他话锋一转：「如果说，用一句 prompt 就创造一整个世界呢？」&lt;/p&gt;
+&lt;p&gt;他双手托着笔记本，屏幕上没有播放键，镜头平稳地向前推进，穿过中国小镇的街巷，又走上欧洲乡村的小路，光影随着视角移动自然变化，世界一路向前铺展，仿佛没有尽头。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/59/18/5918da6c00430cf67023d2522b7d98b6.png" /&gt;&lt;/p&gt;
+&lt;p&gt;这不是一段提前渲染好的视频，而是一个正在实时生成、可以交互的三维世界。&lt;/p&gt;
+&lt;p&gt;过去一段时间，这类能力更多出现在实验室和论文演示里，能以这么高的完成度，出现在消费电子展的主舞台上，还是行业第一次。&lt;/p&gt;
+&lt;p&gt;演示结束时，Huynh 对着话筒说了句：「This is the future of Personal AI。」&lt;/p&gt;
+&lt;p&gt;很多人不知道的是，&lt;strong&gt;驱动这个演示的世界模型 LingBot-World 2.0，正来自蚂蚁集团旗下的具身智能团队灵波科技（Robbyant）。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;三个月后回看，那场演示只是一个开始。&lt;strong&gt;从高校实验室到芯片厂商的开发套件，从独立开发者的工具到垂直行业的工作流，LingBot（灵波）系列模型正在进入全球具身智能的技术底层，成为很多团队创新的起点，甚至还进入了红海珊瑚礁的研究现场。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;成为学术研究的参考基准&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;能被 AMD 选上舞台，不是运气。&lt;strong&gt;在此之前，灵波已经在全球具身智能的学术圈成了一把隐形标尺。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;世界模型赛道有个公认的难题：物体恒存。简单说就是镜头离开一个物体，再转回来，生成模型还能不能把它还原出来？&lt;/p&gt;
+&lt;p&gt;南洋理工大学、清华大学和普林斯顿大学的联合团队，把这个难题当成测试世界模型记忆能力的试金石。世界模型需要利用此前的画面，维持物体和场景的连续性；生成时间越长，保存历史信息的缓存也可能越大。研究者想做的，是压缩缓存的同时，保留后续生成真正需要的信息。&lt;/p&gt;
+&lt;p&gt;团队比较了 LingBot-World v2、LongLive、Self-Forcing 和 Causal Forcing。在特定的对象找回与场景重访测试中，LingBot-World v2 利用完整历史信息生成的画面，与目标画面的 DINO 特征相似度约为 0.68，其他三个候选约为 0.26。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f2/75/f2750857fde9171114f8abd6a4e799df.png" /&gt;&lt;/p&gt;
+&lt;p&gt;这个结果直接决定了他们后续的研究方向：放弃其他候选，直接在灵波的底座上做记忆压缩优化。最终提出的 DeCoPrune 方案，把历史缓存 token 砍掉了 85%，生成速度翻了四倍多的情况下，画面相似度还能保住 0.67。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;类似的故事，在具身智能论文里反复出现。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;斯坦福大学视觉与学习实验室 10 月发布的 OpenWAM 项目，初衷是给世界 - 动作模型（World-Action Model）做一套统一的对比框架。过去各家模型各写各的代码，架构不兼容、接口不统一，想比个优劣得先重写半套环境。他们找了一圈现成的实现，最后把 LingBot-VA 的 Transformer 架构、文本编码器和分词器整套拿了过来，作为整个框架的参考实现。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 19:19:58 +0000</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic just launched tools to show companies what their AI spending is buying</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/28/anthropic-just-launched-tools-to-show-companies-what-their-ai-spending-is-buying/</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr"/>
+      <c r="F717" s="2" t="inlineStr"/>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>The frontier lab is lifting the curtain on how users spend money on its models ahead of a planned IPO.</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H717"/>
+  <dimension ref="A1:H726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29779,6 +29779,356 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 29 Oct 2026 03:27:50 +0000</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>文远知行001号员工带队，景烁科技首轮融资数千万美元</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506281.html</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr"/>
+      <c r="F718" s="2" t="inlineStr"/>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>10月29日，文远知行披露旗下子公司景烁科技首次融资进展</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 29 Oct 2026 02:51:45 +0000</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>小雨智造与国家钢结构质检中心共建实验室，乔忠良：具身智能新质生产力已成事实</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506273.html</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr"/>
+      <c r="F719" s="2" t="inlineStr"/>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>2026年10月27日，“工业具身智能焊接与检测技术联合实验室”正式揭牌成立。</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 11:09:10 +0000</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>【图片中转测试，未发布】工程能力一键复用，专心卷新能力！轮子造一次就够了｜详解FluxVLA Engine技术报告</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506194.html</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr"/>
+      <c r="F720" s="2" t="inlineStr"/>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>让基建作为常驻buff</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 09:01:27 +0000</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>威卡：用数据集链接具身智能和工程机械</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506063.html</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr"/>
+      <c r="F721" s="2" t="inlineStr"/>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>威卡：为工程机械的智能化与少人化，提供一条被验证的路径</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 28 Oct 2026 08:55:26 +0000</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>0营收估值200亿美元，具身版OpenAI又融10亿美元</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506042.html</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr"/>
+      <c r="F722" s="2" t="inlineStr"/>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>斯坦福伯克利宗师组团，贝索斯红杉抢着送钱</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 08:15:04 +0800</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>Google 母集团市值蒸发 5000 亿美元创纪录；苹果高管回应新 iPad mini 60Hz 刷新率；因电池问题，理想 MEGA 退一赔一｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373154</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr"/>
+      <c r="F723" s="2" t="inlineStr"/>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/02/64/02644a2f89f2e3c078fd52a66ef1e4fe.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;谷歌市值创纪录蒸发 5000 亿美元 AI 侵蚀营收&lt;/h1&gt;
+&lt;p&gt;Alphabet Inc 股价一度下跌逾 13%，市值蒸发逾 5000 亿美元，单日市值缩水规模创公司纪录。此前公司公布的搜索和广告业务营收令人失望，加剧了投资者对人工智能（AI）威胁其核心业务的担忧。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fa/f7/faf775e9f314b741c0cd9e4603e99f2e.png" /&gt;&lt;/p&gt;
+&lt;p&gt;这家谷歌母公司公布，第三季度不含合作伙伴分成的营收为 1112 亿美元，低于分析师预测。搜索及其他渠道的广告营收也不及预期，增速为五个季度来最慢。这项业务约占公司总营收的一半，也是为巨额 AI 投资提供资金的关键来源。&lt;/p&gt;
+&lt;p&gt;摩根大通分析师 Doug Anmuth 等人在研报中表示，业绩和股价反应显示，对于投入数千亿美元建设 AI 基础设施的超大规模云服务商而言，一旦核心业务业绩令人失望，容错空间有多小。&lt;/p&gt;
+&lt;p&gt;截至纽约时间上午 9：35，Alphabet 股价下跌 13%，至 281.37 美元，市值蒸发 5110 亿美元。这跟竞争对手微软的表现形成鲜明反差。微软云业务增速超出华尔街预期，同时控制支出，推动股价上涨。&lt;/p&gt;
+&lt;p&gt;谷歌首席商务官 Philipp Schindler 周三晚间在财报电话会议上表示，谷歌搜索中新推出的 AI Mode 标签页日益普及，对公司业绩造成了拖累。他表示，AI 查询的「变现能力较低」，不过公司对此仍持乐观态度，并计划在搜索引擎的这一板块投放更多广告。&lt;/p&gt;
+&lt;p&gt;多年来，谷歌高管一直认为，AI 聊天机器人和相关功能不会大幅侵蚀其搜索业务。但随着消费者转向 ChatGPT、Claude 以及谷歌自身的 AI 功能，投资者担心这会冲击公司的核心盈利来源。&lt;/p&gt;
+&lt;p&gt;第三季度谷歌服务业务总营收 963 亿美元，低于预期的 984 亿美元。YouTube 广告营收 112 亿美元，也低于预期。&lt;/p&gt;
+&lt;p&gt;公司自由现金流连续第二个季度为负，为上市以来首次连续两季出现负值。&lt;/p&gt;
+&lt;p&gt;Alphabet 的股权投资也拖累了公司利润。这些投资录得 87 亿美元亏损，很大程度上源于 Alphabet 所持 SpaceX 股份。这与一年前的投资收益以及第二季度的巨额收益形成鲜明反差；第二季度的收益主要来自 SpaceX 和一家非上市公司的投资，后来确认这家公司是 Anthropic PBC。&lt;/p&gt;
+&lt;p&gt;Alphabet 第三季度每股净利润为 2.12 美元，远低于华尔街预期的 2.99 美元。&lt;/p&gt;
+&lt;p&gt;财报中的一个亮点是谷歌云，该业务被视为衡量公司 AI 产品和托管服务需求的重要指标。谷歌云营收 307 亿美元、利润 111 亿美元，均高于分析师预期的 291 亿美元和 98 亿美元。该业务的大客户包括 Anthropic 等在 AI 竞赛中与谷歌竞争的初创公司。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/64/93/6493ace7c0ce32e295513609584b12cd.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;腾讯汤道生：WorkBuddy 已覆盖中国企业 500 强中的 50%&lt;/h1&gt;
+&lt;p&gt;10 月 29 日消息，在今日举行的腾讯全球数字生态大会上，腾讯表示，今年 3 月，WorkBuddy 正式上线。7 个月的时间里，WorkBuddy 累计迭代 100 个大版本，&lt;strong&gt;完成 90 亿次用户任务请求&lt;/strong&gt;，成为中国用户规模最大的 AI 办公效率智能体。&lt;/p&gt;
+&lt;p&gt;腾讯集团高级执行副总裁、云与智慧产业事业群 CEO 汤道生透露，自今年 3 月上线以来，&lt;strong&gt;WorkBuddy 企业版已落地 50 多个行业，覆盖中国企业 500 强中的 50%、企业 100 强中的 60%&lt;/strong&gt;，开放平台伙伴和开发者超过 5 万家，上架 Skills 超 20 万。&lt;/p&gt;
+&lt;p&gt;据悉，&lt;strong&gt;WorkBuddy 将全面开放产品架构&lt;/st</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 29 Oct 2026 15:09:14 +0800</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>大众把三年在中国攒的家底，打包成了一颗「星」</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373086</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr"/>
+      <c r="F724" s="2" t="inlineStr"/>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e6/7d/e67d5676bb4d31cd5f3eec5e269332ac.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;头图来源：极客公园&lt;/p&gt;
+&lt;p&gt;10 月 28 日，合肥，大众汽车集团（中国）办了自己的第一次技术日。&lt;/p&gt;
+&lt;p&gt;这场发布会的主角叫「VEGA」，名字取自织女星，是大众在中国本土自研的一体化技术矩阵。它把整车平台、电子电气架构和高级驾驶辅助系统三大核心技术打包成了一套体系。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;按大众的说法，它由此成为中国市场唯一一家拥有本土开发自研技术矩阵的外资车企。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/76/fe/76fef3ecf439cbfc0005ea654111cbbd.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;大众汽车集团（中国）董事长兼 CEO 贝瑞德在台上说，短短三年，大众在中国打造出了一套一体化的技术矩阵，在国际汽车制造商之中，能做到这一点的应该屈指可数。&lt;/p&gt;
+&lt;p&gt;这句话的背后，是大众这几年在面对激烈的「中式竞争」后，第一次重新找到了方向的自信。&lt;/p&gt;
+&lt;h2&gt;「在中国造」到「在中国研」&lt;/h2&gt;
+&lt;p&gt;把时间往回拨四年。&lt;/p&gt;
+&lt;p&gt;2022 年，大众把在华战略从「在欧洲，为中国」改成了「在中国，为中国」。贝瑞德的解释是，大众要从过去在中国生产制造，走向在中国自主创新。&lt;/p&gt;
+&lt;p&gt;2023 年，大众在德国以外规模最大的研发中心 VCTC 在合肥成立。如今这里有 3000 多名员工，中国团队从执行方变成了主导方，本土工程师拿到了在本地自主决策的权力。&lt;/p&gt;
+&lt;p&gt;这个转向背后有现实的压力。2025 年，大众集团全球营业利润 89 亿欧元，而 2024 年是 191 亿欧元。在华交付约 269 万辆，规模依然靠前，但本土品牌在智能化上的攻势，让「德国研发、中国生产」的老模式越来越跟不上节奏。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/71/61/71610087db1f6ed416e51f92113a49fd.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;VEG A是大众在中国本土自研的一体化方案|图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;VEGA 就是这四年转型的第一份完整答卷。贝瑞德说，VEGA 不只是一套技术矩阵，更是一种能力，&lt;strong&gt;在中国本土自主研发、自主整合并持续迭代核心技术的能力。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;VEGA 的第一根支柱是新一代整车平台，CMP 和 CSP。&lt;/p&gt;
+&lt;p&gt;CMP 面向 A 级到 A+ 级的主流市场，支持纯电和插混；CSP 面向 B 级到全尺寸及未来的旗舰车型，支持纯电和增程。&lt;/p&gt;
+&lt;p&gt;CMP 车型 CLTC 续航超过 600 公里，最高效版本百公里电耗约 11 千瓦时，30% 到 80% 充电 25 分钟。CSP 纯电车型续航目标约 800 公里，增程版综合续航超过 1500 公里，依托峰值电压超过 850 伏的高压架构，10% 到 80% 最快不到 13 分钟。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/58/0f/580fca118d587956b5ebe437288d61bc.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;首席技术官吴博锐称大众是智能网联汽车时代的「平台之王」｜图片来源：极客公园&lt;/p&gt;
+&lt;p&gt;驾控是大众更愿意强调的部分。CMP 用了 54:46 的前后轴荷分配，后悬架是源自 MQB B 级车的多连杆独立悬架，&lt;strong&gt;目标是把 B 级车的驾控带进 A 级车&lt;/strong&gt;。CSP 则反过来，靠后轮转向把全尺寸车的转弯半径压到 5.5 米以内，零百加速 4.1 秒。&lt;/p&gt;
+&lt;p&gt;首席技术官吴博锐在台上直接说，大众是智能网联汽车时代的「平台之王」。从 MQB 到 CMP，平台化本来就是大众几十年的看家本事，只是这一次，平台是围绕软件设计的。&lt;/p&gt;
+&lt;h2&gt;CEA，让软件先行&lt;/h2&gt;
+&lt;p&gt;第二根支柱是 CEA 电子电气架构，也是这次发布会上「最不像大众」的部分。&lt;/p&gt;
+&lt;p&gt;CEA 首席架构师韩三楚是前长安汽车首席软件架构师。他在台上讲了一个顺序问题。过去一百多年，汽车开发都是先设计机械结构，再加电子部件，最后写软件。三年前，大众在中国决定把这个顺序倒过来，&lt;strong&gt;先定义电子电气架构，再以</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 29 Oct 2026 16:21:00 +0000</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Palantir execs launch Dream with $17M from a16z to build AI world models for construction</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/29/ex-palantir-execs-launch-dream-with-17m-from-a16z-to-build-ai-world-models-for-construction/</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr"/>
+      <c r="F725" s="2" t="inlineStr"/>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>Dream is grounded in real physics and construction standards. Just as LLMs learn from text, Dream's world model is trained on more than 100 million square feet of building data gathered from permit archives across the United States.</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic is asking Wall Street to believe in AGI</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/podcast/1021322/anthropic-ipo-filing-s-1-claude-semianalysis-joey-brookhart-interview</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr"/>
+      <c r="F726" s="2" t="inlineStr"/>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>Today on Decoder, I’m joined by Joey Brookhart, an analyst at the chip and AI research firm SemiAnalysis, to help me dig into the story inside the numbers of the Anthropic IPO filing — a document known as an S-1. Anthropic just filed its S-1 to go public on the Nasdaq, and it could start [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H726"/>
+  <dimension ref="A1:H734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30129,6 +30129,298 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 01:31:21 +0000</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤三维力简析</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14176</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr"/>
+      <c r="F727" s="2" t="inlineStr"/>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤三维力就是让机器像人的皮肤一样，不光知道“被按了”，还知道“往哪个方向用力、用了多大、有没有在滑”</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 01:29:08 +0000</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>小米公布仿生灵巧手：21自由度，全掌1500点触觉覆盖</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14175</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr"/>
+      <c r="F728" s="2" t="inlineStr"/>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>从工厂SOP数据采集到21自由度仿生手的落地，小米机器人正试图在具身智能与柔性制造的交叉点上寻找突破口</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 01:27:00 +0000</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>柔性触觉传感器四大制造工艺</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/14167</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr"/>
+      <c r="F729" s="2" t="inlineStr"/>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>光刻与蚀刻、3D打印、喷墨打印、丝网印刷等工艺，已成为柔性传感器研发与制造中值得关注的技术路线。</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:30:03+00:00</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Spot Plays to Show Its Whole-Body Manipulation</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-whole-body-manipulation</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr"/>
+      <c r="F730" s="2" t="inlineStr"/>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 03:48:04 +0000</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>从学习人类到学习机器人同伴，清华大学联合无问芯穹、智元提出具身智能规模化落地新路径</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506662.html</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr"/>
+      <c r="F731" s="2" t="inlineStr"/>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>让机器人成为彼此的“老师”</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 00:19:06 +0000</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>买车送终身AI？智己LS8纯电版25万起！全系线控底盘宁德时代标配</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/10/506569.html</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr"/>
+      <c r="F732" s="2" t="inlineStr"/>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>Momenta世界模型上车</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 31 Oct 2026 08:03:20 +0800</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>苹果官宣 Apple 智能接入阿里千问；DeepSeek 完成第二轮 1055 亿元融资，估值达 6155 亿元；英特尔股价开盘跌超 30%｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/373220</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr"/>
+      <c r="F733" s="2" t="inlineStr"/>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/25/34/2534bb5db2534bf8ea4b0982daa6e132.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;国行 Apple 智能确定上线时间：11 月开放测试，千问接入 Siri&lt;/h2&gt;
+&lt;p&gt;10 月 31 日，苹果宣布，国行 Apple 智能首批功能将于 11 月 4 日随 iOS 开发者 Beta 版开放测试，12 月随 iOS 27.3 正式面向用户推出。首批功能包括实时翻译、写作工具、照片消除、智绘表情和通知摘要等，支持 iPhone 15 Pro 系列、iPhone 16 及后续机型，以及 iPhone Air、iPhone Duo。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b3/72/b372d4c7d34112e68be8ee5678c2f366.png" /&gt;&lt;/p&gt;
+&lt;p&gt;阿里巴巴强调，在任何问题、文档和图片发送给千问之前，都会先征得用户同意。&lt;/p&gt;
+&lt;p&gt;苹果表示，这些功能由其自有模型驱动；用户也可以选择接入阿里巴巴千问，在 Siri、写作工具和视觉智能中处理部分请求。不过，首批更新不包含新版 Siri AI，iPad、Mac 等其他平台还需等待必要审批。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fd/9a/fd9a8a1c38b2dfa1b62830f2db3a7747.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 撤回 Pro 200 降额计划，同时提高 Work 和 Codex 用量&lt;/h2&gt;
+&lt;p&gt;当地时间 10 月 29 日，OpenAI 宣布调整 Pro 和 Business Premium 订阅中的 Work、Codex 使用额度。Pro 100 和 Pro 500 的原有额度翻倍；此前额度较低的 Pro 200 用户也获得翻倍提升，与原本享有较高额度的 Pro 200 用户持平。新额度立即生效，现有订阅用户无需等到续费。&lt;/p&gt;
+&lt;p&gt;这也意味着，OpenAI 撤回了 9 月底通知中的 Pro 200 降额计划，原本享有较高额度的用户可以继续保留。需要注意的是，额度翻倍不保证可完成的任务数也翻倍：实际消耗取决于模型、任务和速度模式，Fast 模式消耗额度的速度约为标准模式的 2.5 倍，Ultrafast 则为 8 倍。（来源：ITBears）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;英特尔股价开盘跌超 30%，或将创下有记录以来最大单日跌幅&lt;/h2&gt;
+&lt;p&gt;10 月 30 日开盘后，英特尔股价大幅下挫，盘中跌幅一度超过 30%，公司市值蒸发超过 1,370 亿美元（现汇率约合 9,147.3 亿元人民币），超过 2024 年最大单日跌幅（约 26%），如果能达到 31% 将超越 1974 年 7 月 5 日创下的终极历史纪录。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/74/1a/741a63b26907d91599f9f37054d8f6a3.png" /&gt;&lt;/p&gt;
+&lt;p&gt;路透社报道称，此次暴跌主要源于英特尔发布低于市场预期的第四季度业绩指引，同时警告个人电脑市场疲软、内存价格上涨等问题可能持续至 2027 年上半年。&lt;/p&gt;
+&lt;p&gt;英特尔 2026 年第三季度财报显示，尽管公司当季营收同比增长 21%，达到 165.1 亿美元（现汇率约合 1,102.35 亿元人民币），但第四季度业绩指引低于市场预期，令投资者对其业务复苏前景产生担忧。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;header&gt;
+&lt;h2&gt;Google 关闭 AI 编程智能体 Jules 推出不到两年&lt;/h2&gt;
+&lt;p&gt;10 月 30 日，Google 将关闭其 AI 编程智能体 Jules，把从该工具中获得的经验引入其 AI 编程平台 Antigravity。2024 年 12 月，Google 推出 Jules，将其定位为一款能够完成</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 21:52:03 +0000</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic expected to receive high ‘junk’ rating from credit agencies following IPO, FT report says</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/10/30/anthropic-expected-to-receive-high-junk-rating-from-credit-agencies-following-ipo-report-says/</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr"/>
+      <c r="F734" s="2" t="inlineStr"/>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>Blackstone's forecast is just a prediction, but naturally, a high junk rating would make it more difficult and costlier for Anthropic to raise the money to keep funding its massive spending that has undergirded its business.</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
